--- a/temp/searchByMACTable.xlsx
+++ b/temp/searchByMACTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="51">
   <si>
     <t>2.1</t>
   </si>
@@ -131,6 +131,42 @@
   </si>
   <si>
     <t>21</t>
+  </si>
+  <si>
+    <t>ЭСПЦ-2</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>нет</t>
+  </si>
+  <si>
+    <t>11.2</t>
+  </si>
+  <si>
+    <t>9.1</t>
+  </si>
+  <si>
+    <t>8.1</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
 </sst>
 </file>
@@ -521,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:BC211"/>
+  <dimension ref="A3:BC321"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -6370,7 +6406,7 @@
       <c r="J208" s="5"/>
       <c r="K208" s="5"/>
     </row>
-    <row r="209" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C209" s="5">
         <v>5</v>
       </c>
@@ -6388,7 +6424,7 @@
       <c r="J209" s="5"/>
       <c r="K209" s="5"/>
     </row>
-    <row r="210" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C210" s="5">
         <v>13</v>
       </c>
@@ -6406,7 +6442,7 @@
       <c r="J210" s="5"/>
       <c r="K210" s="5"/>
     </row>
-    <row r="211" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C211" s="5">
         <v>21</v>
       </c>
@@ -6423,6 +6459,802 @@
       <c r="H211" s="5"/>
       <c r="J211" s="5"/>
       <c r="K211" s="5"/>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B222" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C223" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G223" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C224" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="225" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C225" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="226" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C226" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="227" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C227" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="228" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C228" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="229" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C229" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="230" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C230" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="231" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C231" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="232" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C232" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="233" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C233" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="234" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C234" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="236" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B236" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F236" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="237" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C237" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="238" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C238" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="239" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C239" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="240" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C240" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="241" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C241" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="242" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C242" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="243" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C243" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="244" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C244" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="245" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C245" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="246" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C246" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="247" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C247" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="248" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C248" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="249" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C249" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="251" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B251" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="252" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C252" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G252" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="253" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C253" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="254" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C254" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="255" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C255" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="256" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C256" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="257" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C257" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="258" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C258" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="259" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C259" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="260" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C260" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="261" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C261" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="262" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C262" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="263" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C263" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="265" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B265" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F265" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="266" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C266" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G266" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="267" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C267" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G267" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="268" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C268" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G268" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="269" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C269" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G269" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="270" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C270" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G270" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="271" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G271" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="272" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G272" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="273" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G273" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="275" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B275" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="276" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C276" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F276" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="277" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C277" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G277" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="278" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C278" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G278" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="279" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C279" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G279" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="280" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C280" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="281" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C281" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="282" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C282" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="283" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C283" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="284" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C284" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="285" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C285" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="287" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B287" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F287" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="288" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C288" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G288" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="289" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C289" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G289" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="290" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C290" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="291" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C291" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="292" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C292" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="293" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C293" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="294" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C294" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="295" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C295" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="296" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C296" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="297" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C297" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="298" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C298" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="300" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B300" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F300" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="301" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C301" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G301" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="302" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C302" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G302" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="303" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C303" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G303" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="304" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C304" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G304" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="305" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C305" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G305" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="306" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C306" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G306" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="307" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G307" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="308" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B308" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="309" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C309" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="310" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C310" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="311" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C311" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="312" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C312" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="313" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C313" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="314" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C314" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="315" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C315" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="316" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C316" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="317" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C317" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="318" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C318" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="319" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C319" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="320" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C320" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="321" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C321" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/temp/searchByMACTable.xlsx
+++ b/temp/searchByMACTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="55">
   <si>
     <t>2.1</t>
   </si>
@@ -167,6 +167,18 @@
   </si>
   <si>
     <t>22</t>
+  </si>
+  <si>
+    <t>24.1</t>
+  </si>
+  <si>
+    <t>13.2</t>
+  </si>
+  <si>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>17.48</t>
   </si>
 </sst>
 </file>
@@ -557,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BC321"/>
+  <dimension ref="A3:BC402"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -6472,6 +6484,9 @@
       <c r="F222" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="I222" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C223" s="1" t="s">
@@ -6492,7 +6507,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="225" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C225" s="1" t="s">
         <v>33</v>
       </c>
@@ -6500,7 +6515,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="226" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C226" s="1" t="s">
         <v>36</v>
       </c>
@@ -6508,7 +6523,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="227" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C227" s="1" t="s">
         <v>35</v>
       </c>
@@ -6516,7 +6531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="228" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C228" s="1" t="s">
         <v>31</v>
       </c>
@@ -6524,91 +6539,128 @@
         <v>18</v>
       </c>
     </row>
-    <row r="229" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C229" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="230" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="J229" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K229" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="230" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C230" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="231" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="J230" s="3"/>
+      <c r="K230" s="3"/>
+    </row>
+    <row r="231" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C231" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="232" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="J231" s="3"/>
+      <c r="K231" s="3"/>
+    </row>
+    <row r="232" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C232" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="233" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="J232" s="3"/>
+      <c r="K232" s="3"/>
+    </row>
+    <row r="233" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C233" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="234" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="J233" s="3"/>
+      <c r="K233" s="3"/>
+    </row>
+    <row r="234" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C234" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="236" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="J234" s="3"/>
+      <c r="K234" s="3"/>
+    </row>
+    <row r="235" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="J235" s="3"/>
+      <c r="K235" s="3"/>
+    </row>
+    <row r="236" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B236" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="237" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I236" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J236" s="3"/>
+      <c r="K236" s="3"/>
+    </row>
+    <row r="237" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C237" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="238" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="J237" s="3"/>
+      <c r="K237" s="3"/>
+    </row>
+    <row r="238" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C238" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="239" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="J238" s="3"/>
+      <c r="K238" s="3"/>
+    </row>
+    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C239" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="240" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="J239" s="3"/>
+      <c r="K239" s="3"/>
+    </row>
+    <row r="240" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C240" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D240" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J240" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K240" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -7248,12 +7300,633 @@
         <v>48</v>
       </c>
     </row>
-    <row r="321" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C321" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D321" s="1" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="323" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B323" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F323" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="324" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C324" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G324" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="325" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C325" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C326" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C327" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C328" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C329" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C330" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C331" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C332" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C333" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C334" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C335" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B337" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F337" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="338" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C338" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G338" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="339" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C339" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G339" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="340" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C340" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="341" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C341" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="342" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C342" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="343" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C343" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="344" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C344" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="345" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C345" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="346" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C346" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="347" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C347" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="348" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C348" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="350" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B350" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F350" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="351" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C351" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G351" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="352" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C352" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G352" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="353" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C353" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G353" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="354" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C354" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G354" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="355" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C355" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="356" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C356" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="357" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C357" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="358" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C358" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="359" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C359" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="361" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B361" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="362" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C362" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="363" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C363" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="364" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C364" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="365" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C365" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D365" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="366" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C366" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="367" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C367" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="368" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C368" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="369" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C369" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="370" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C370" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="371" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C371" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="372" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C372" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D372" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="373" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C373" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D373" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="374" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C374" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D374" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="376" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B376" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="377" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C377" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D377" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="378" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C378" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="379" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C379" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D379" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="380" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C380" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D380" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="381" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C381" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D381" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="382" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C382" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D382" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="383" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C383" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D383" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="384" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C384" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D384" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="385" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C385" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D385" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="386" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C386" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D386" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="387" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C387" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D387" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="388" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C388" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D388" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="389" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C389" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D389" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="391" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B391" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F391" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="392" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C392" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D392" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G392" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="393" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C393" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D393" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G393" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="394" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C394" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D394" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="395" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C395" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="396" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C396" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D396" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="397" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C397" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D397" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="398" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C398" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D398" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="399" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C399" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D399" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="400" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C400" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D400" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="401" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C401" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D401" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="402" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C402" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D402" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/temp/searchByMACTable.xlsx
+++ b/temp/searchByMACTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="56">
   <si>
     <t>2.1</t>
   </si>
@@ -148,9 +148,6 @@
     <t>7</t>
   </si>
   <si>
-    <t>нет</t>
-  </si>
-  <si>
     <t>11.2</t>
   </si>
   <si>
@@ -180,12 +177,18 @@
   <si>
     <t>17.48</t>
   </si>
+  <si>
+    <t>12.24</t>
+  </si>
+  <si>
+    <t>9.2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,8 +231,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -239,6 +249,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -255,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -265,6 +281,9 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -569,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BC402"/>
+  <dimension ref="A3:BW430"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -578,14 +597,14 @@
     <col min="4" max="4" width="5" style="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="1" customWidth="1"/>
     <col min="6" max="8" width="5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="1"/>
+    <col min="9" max="9" width="4.85546875" style="1" customWidth="1"/>
     <col min="10" max="10" width="5.140625" style="1" customWidth="1"/>
     <col min="11" max="11" width="6.140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="1"/>
+    <col min="12" max="12" width="4.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="4.42578125" style="1" customWidth="1"/>
     <col min="14" max="14" width="5.28515625" style="1" customWidth="1"/>
     <col min="15" max="15" width="4.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="10" style="1" customWidth="1"/>
+    <col min="16" max="16" width="5.140625" style="1" customWidth="1"/>
     <col min="17" max="17" width="5.28515625" style="1" customWidth="1"/>
     <col min="18" max="18" width="4.5703125" style="1" customWidth="1"/>
     <col min="19" max="21" width="4.85546875" style="1" customWidth="1"/>
@@ -614,13 +633,16 @@
     <col min="48" max="48" width="4.28515625" style="1" customWidth="1"/>
     <col min="49" max="49" width="4.42578125" style="1" customWidth="1"/>
     <col min="50" max="50" width="4" style="1" customWidth="1"/>
-    <col min="51" max="51" width="4.28515625" style="1" customWidth="1"/>
-    <col min="52" max="52" width="4.5703125" style="1" customWidth="1"/>
-    <col min="53" max="53" width="4.28515625" style="1" customWidth="1"/>
-    <col min="54" max="54" width="4.5703125" style="1" customWidth="1"/>
-    <col min="55" max="55" width="4.42578125" style="1" customWidth="1"/>
-    <col min="56" max="56" width="5" style="1" customWidth="1"/>
-    <col min="57" max="16384" width="9.140625" style="1"/>
+    <col min="51" max="71" width="4.28515625" style="1" customWidth="1"/>
+    <col min="72" max="72" width="4.5703125" style="1" customWidth="1"/>
+    <col min="73" max="73" width="4.28515625" style="1" customWidth="1"/>
+    <col min="74" max="74" width="4.5703125" style="1" customWidth="1"/>
+    <col min="75" max="75" width="4.42578125" style="1" customWidth="1"/>
+    <col min="76" max="76" width="5" style="1" customWidth="1"/>
+    <col min="77" max="77" width="5.42578125" style="1" customWidth="1"/>
+    <col min="78" max="79" width="5" style="1" customWidth="1"/>
+    <col min="80" max="80" width="5.28515625" style="1" customWidth="1"/>
+    <col min="81" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:39" x14ac:dyDescent="0.25">
@@ -3332,7 +3354,7 @@
       <c r="AP80" s="5"/>
       <c r="AQ80" s="5"/>
     </row>
-    <row r="81" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C81" s="5">
         <v>3</v>
       </c>
@@ -3379,7 +3401,7 @@
       <c r="AP81" s="5"/>
       <c r="AQ81" s="5"/>
     </row>
-    <row r="82" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C82" s="5">
         <v>19</v>
       </c>
@@ -3396,7 +3418,7 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C83" s="5">
         <v>10</v>
       </c>
@@ -3432,7 +3454,7 @@
       <c r="AT83" s="3"/>
       <c r="AU83" s="3"/>
     </row>
-    <row r="84" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C84" s="5">
         <v>12</v>
       </c>
@@ -3471,10 +3493,30 @@
       <c r="AU84" s="3"/>
       <c r="AX84" s="5"/>
       <c r="AY84" s="5"/>
+      <c r="AZ84" s="5"/>
+      <c r="BA84" s="5"/>
       <c r="BB84" s="5"/>
       <c r="BC84" s="5"/>
-    </row>
-    <row r="85" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD84" s="5"/>
+      <c r="BE84" s="5"/>
+      <c r="BF84" s="5"/>
+      <c r="BG84" s="5"/>
+      <c r="BH84" s="5"/>
+      <c r="BI84" s="5"/>
+      <c r="BJ84" s="5"/>
+      <c r="BK84" s="5"/>
+      <c r="BL84" s="5"/>
+      <c r="BM84" s="5"/>
+      <c r="BN84" s="5"/>
+      <c r="BO84" s="5"/>
+      <c r="BP84" s="5"/>
+      <c r="BQ84" s="5"/>
+      <c r="BR84" s="5"/>
+      <c r="BS84" s="5"/>
+      <c r="BV84" s="5"/>
+      <c r="BW84" s="5"/>
+    </row>
+    <row r="85" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C85" s="5">
         <v>11</v>
       </c>
@@ -3517,10 +3559,30 @@
       <c r="AU85" s="3"/>
       <c r="AX85" s="5"/>
       <c r="AY85" s="5"/>
+      <c r="AZ85" s="5"/>
+      <c r="BA85" s="5"/>
       <c r="BB85" s="5"/>
       <c r="BC85" s="5"/>
-    </row>
-    <row r="86" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD85" s="5"/>
+      <c r="BE85" s="5"/>
+      <c r="BF85" s="5"/>
+      <c r="BG85" s="5"/>
+      <c r="BH85" s="5"/>
+      <c r="BI85" s="5"/>
+      <c r="BJ85" s="5"/>
+      <c r="BK85" s="5"/>
+      <c r="BL85" s="5"/>
+      <c r="BM85" s="5"/>
+      <c r="BN85" s="5"/>
+      <c r="BO85" s="5"/>
+      <c r="BP85" s="5"/>
+      <c r="BQ85" s="5"/>
+      <c r="BR85" s="5"/>
+      <c r="BS85" s="5"/>
+      <c r="BV85" s="5"/>
+      <c r="BW85" s="5"/>
+    </row>
+    <row r="86" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C86" s="5">
         <v>8</v>
       </c>
@@ -3559,10 +3621,30 @@
       <c r="AU86" s="3"/>
       <c r="AX86" s="5"/>
       <c r="AY86" s="5"/>
+      <c r="AZ86" s="5"/>
+      <c r="BA86" s="5"/>
       <c r="BB86" s="5"/>
       <c r="BC86" s="5"/>
-    </row>
-    <row r="87" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD86" s="5"/>
+      <c r="BE86" s="5"/>
+      <c r="BF86" s="5"/>
+      <c r="BG86" s="5"/>
+      <c r="BH86" s="5"/>
+      <c r="BI86" s="5"/>
+      <c r="BJ86" s="5"/>
+      <c r="BK86" s="5"/>
+      <c r="BL86" s="5"/>
+      <c r="BM86" s="5"/>
+      <c r="BN86" s="5"/>
+      <c r="BO86" s="5"/>
+      <c r="BP86" s="5"/>
+      <c r="BQ86" s="5"/>
+      <c r="BR86" s="5"/>
+      <c r="BS86" s="5"/>
+      <c r="BV86" s="5"/>
+      <c r="BW86" s="5"/>
+    </row>
+    <row r="87" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C87" s="5">
         <v>4</v>
       </c>
@@ -3617,10 +3699,30 @@
       <c r="AU87" s="3"/>
       <c r="AX87" s="5"/>
       <c r="AY87" s="5"/>
+      <c r="AZ87" s="5"/>
+      <c r="BA87" s="5"/>
       <c r="BB87" s="5"/>
       <c r="BC87" s="5"/>
-    </row>
-    <row r="88" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD87" s="5"/>
+      <c r="BE87" s="5"/>
+      <c r="BF87" s="5"/>
+      <c r="BG87" s="5"/>
+      <c r="BH87" s="5"/>
+      <c r="BI87" s="5"/>
+      <c r="BJ87" s="5"/>
+      <c r="BK87" s="5"/>
+      <c r="BL87" s="5"/>
+      <c r="BM87" s="5"/>
+      <c r="BN87" s="5"/>
+      <c r="BO87" s="5"/>
+      <c r="BP87" s="5"/>
+      <c r="BQ87" s="5"/>
+      <c r="BR87" s="5"/>
+      <c r="BS87" s="5"/>
+      <c r="BV87" s="5"/>
+      <c r="BW87" s="5"/>
+    </row>
+    <row r="88" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C88" s="5">
         <v>5</v>
       </c>
@@ -3674,10 +3776,30 @@
       <c r="AU88" s="3"/>
       <c r="AX88" s="5"/>
       <c r="AY88" s="5"/>
+      <c r="AZ88" s="5"/>
+      <c r="BA88" s="5"/>
       <c r="BB88" s="5"/>
       <c r="BC88" s="5"/>
-    </row>
-    <row r="89" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD88" s="5"/>
+      <c r="BE88" s="5"/>
+      <c r="BF88" s="5"/>
+      <c r="BG88" s="5"/>
+      <c r="BH88" s="5"/>
+      <c r="BI88" s="5"/>
+      <c r="BJ88" s="5"/>
+      <c r="BK88" s="5"/>
+      <c r="BL88" s="5"/>
+      <c r="BM88" s="5"/>
+      <c r="BN88" s="5"/>
+      <c r="BO88" s="5"/>
+      <c r="BP88" s="5"/>
+      <c r="BQ88" s="5"/>
+      <c r="BR88" s="5"/>
+      <c r="BS88" s="5"/>
+      <c r="BV88" s="5"/>
+      <c r="BW88" s="5"/>
+    </row>
+    <row r="89" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C89" s="5">
         <v>13</v>
       </c>
@@ -3731,10 +3853,30 @@
       <c r="AU89" s="3"/>
       <c r="AX89" s="5"/>
       <c r="AY89" s="5"/>
+      <c r="AZ89" s="5"/>
+      <c r="BA89" s="5"/>
       <c r="BB89" s="5"/>
       <c r="BC89" s="5"/>
-    </row>
-    <row r="90" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD89" s="5"/>
+      <c r="BE89" s="5"/>
+      <c r="BF89" s="5"/>
+      <c r="BG89" s="5"/>
+      <c r="BH89" s="5"/>
+      <c r="BI89" s="5"/>
+      <c r="BJ89" s="5"/>
+      <c r="BK89" s="5"/>
+      <c r="BL89" s="5"/>
+      <c r="BM89" s="5"/>
+      <c r="BN89" s="5"/>
+      <c r="BO89" s="5"/>
+      <c r="BP89" s="5"/>
+      <c r="BQ89" s="5"/>
+      <c r="BR89" s="5"/>
+      <c r="BS89" s="5"/>
+      <c r="BV89" s="5"/>
+      <c r="BW89" s="5"/>
+    </row>
+    <row r="90" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C90" s="5">
         <v>21</v>
       </c>
@@ -3792,10 +3934,30 @@
       </c>
       <c r="AX90" s="5"/>
       <c r="AY90" s="5"/>
+      <c r="AZ90" s="5"/>
+      <c r="BA90" s="5"/>
       <c r="BB90" s="5"/>
       <c r="BC90" s="5"/>
-    </row>
-    <row r="91" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD90" s="5"/>
+      <c r="BE90" s="5"/>
+      <c r="BF90" s="5"/>
+      <c r="BG90" s="5"/>
+      <c r="BH90" s="5"/>
+      <c r="BI90" s="5"/>
+      <c r="BJ90" s="5"/>
+      <c r="BK90" s="5"/>
+      <c r="BL90" s="5"/>
+      <c r="BM90" s="5"/>
+      <c r="BN90" s="5"/>
+      <c r="BO90" s="5"/>
+      <c r="BP90" s="5"/>
+      <c r="BQ90" s="5"/>
+      <c r="BR90" s="5"/>
+      <c r="BS90" s="5"/>
+      <c r="BV90" s="5"/>
+      <c r="BW90" s="5"/>
+    </row>
+    <row r="91" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C91" s="5">
         <v>6</v>
       </c>
@@ -3816,7 +3978,7 @@
       <c r="AT91" s="3"/>
       <c r="AU91" s="3"/>
     </row>
-    <row r="92" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
@@ -3843,8 +4005,28 @@
       </c>
       <c r="AX92" s="3"/>
       <c r="AY92" s="3"/>
-    </row>
-    <row r="93" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="AZ92" s="3"/>
+      <c r="BA92" s="3"/>
+      <c r="BB92" s="3"/>
+      <c r="BC92" s="3"/>
+      <c r="BD92" s="3"/>
+      <c r="BE92" s="3"/>
+      <c r="BF92" s="3"/>
+      <c r="BG92" s="3"/>
+      <c r="BH92" s="3"/>
+      <c r="BI92" s="3"/>
+      <c r="BJ92" s="3"/>
+      <c r="BK92" s="3"/>
+      <c r="BL92" s="3"/>
+      <c r="BM92" s="3"/>
+      <c r="BN92" s="3"/>
+      <c r="BO92" s="3"/>
+      <c r="BP92" s="3"/>
+      <c r="BQ92" s="3"/>
+      <c r="BR92" s="3"/>
+      <c r="BS92" s="3"/>
+    </row>
+    <row r="93" spans="2:75" x14ac:dyDescent="0.25">
       <c r="B93" s="1">
         <v>12</v>
       </c>
@@ -3880,10 +4062,30 @@
       <c r="AW93" s="3"/>
       <c r="AX93" s="3"/>
       <c r="AY93" s="3"/>
-      <c r="BB93" s="5"/>
-      <c r="BC93" s="5"/>
-    </row>
-    <row r="94" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="AZ93" s="3"/>
+      <c r="BA93" s="3"/>
+      <c r="BB93" s="3"/>
+      <c r="BC93" s="3"/>
+      <c r="BD93" s="3"/>
+      <c r="BE93" s="3"/>
+      <c r="BF93" s="3"/>
+      <c r="BG93" s="3"/>
+      <c r="BH93" s="3"/>
+      <c r="BI93" s="3"/>
+      <c r="BJ93" s="3"/>
+      <c r="BK93" s="3"/>
+      <c r="BL93" s="3"/>
+      <c r="BM93" s="3"/>
+      <c r="BN93" s="3"/>
+      <c r="BO93" s="3"/>
+      <c r="BP93" s="3"/>
+      <c r="BQ93" s="3"/>
+      <c r="BR93" s="3"/>
+      <c r="BS93" s="3"/>
+      <c r="BV93" s="5"/>
+      <c r="BW93" s="5"/>
+    </row>
+    <row r="94" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C94" s="5">
         <v>2</v>
       </c>
@@ -3930,10 +4132,30 @@
       <c r="AW94" s="3"/>
       <c r="AX94" s="3"/>
       <c r="AY94" s="3"/>
-      <c r="BB94" s="5"/>
-      <c r="BC94" s="5"/>
-    </row>
-    <row r="95" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="AZ94" s="3"/>
+      <c r="BA94" s="3"/>
+      <c r="BB94" s="3"/>
+      <c r="BC94" s="3"/>
+      <c r="BD94" s="3"/>
+      <c r="BE94" s="3"/>
+      <c r="BF94" s="3"/>
+      <c r="BG94" s="3"/>
+      <c r="BH94" s="3"/>
+      <c r="BI94" s="3"/>
+      <c r="BJ94" s="3"/>
+      <c r="BK94" s="3"/>
+      <c r="BL94" s="3"/>
+      <c r="BM94" s="3"/>
+      <c r="BN94" s="3"/>
+      <c r="BO94" s="3"/>
+      <c r="BP94" s="3"/>
+      <c r="BQ94" s="3"/>
+      <c r="BR94" s="3"/>
+      <c r="BS94" s="3"/>
+      <c r="BV94" s="5"/>
+      <c r="BW94" s="5"/>
+    </row>
+    <row r="95" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C95" s="5">
         <v>1</v>
       </c>
@@ -3972,10 +4194,30 @@
       <c r="AW95" s="3"/>
       <c r="AX95" s="3"/>
       <c r="AY95" s="3"/>
-      <c r="BB95" s="5"/>
-      <c r="BC95" s="5"/>
-    </row>
-    <row r="96" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="AZ95" s="3"/>
+      <c r="BA95" s="3"/>
+      <c r="BB95" s="3"/>
+      <c r="BC95" s="3"/>
+      <c r="BD95" s="3"/>
+      <c r="BE95" s="3"/>
+      <c r="BF95" s="3"/>
+      <c r="BG95" s="3"/>
+      <c r="BH95" s="3"/>
+      <c r="BI95" s="3"/>
+      <c r="BJ95" s="3"/>
+      <c r="BK95" s="3"/>
+      <c r="BL95" s="3"/>
+      <c r="BM95" s="3"/>
+      <c r="BN95" s="3"/>
+      <c r="BO95" s="3"/>
+      <c r="BP95" s="3"/>
+      <c r="BQ95" s="3"/>
+      <c r="BR95" s="3"/>
+      <c r="BS95" s="3"/>
+      <c r="BV95" s="5"/>
+      <c r="BW95" s="5"/>
+    </row>
+    <row r="96" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C96" s="5">
         <v>3</v>
       </c>
@@ -4022,10 +4264,30 @@
       <c r="AW96" s="3"/>
       <c r="AX96" s="3"/>
       <c r="AY96" s="3"/>
-      <c r="BB96" s="5"/>
-      <c r="BC96" s="5"/>
-    </row>
-    <row r="97" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="AZ96" s="3"/>
+      <c r="BA96" s="3"/>
+      <c r="BB96" s="3"/>
+      <c r="BC96" s="3"/>
+      <c r="BD96" s="3"/>
+      <c r="BE96" s="3"/>
+      <c r="BF96" s="3"/>
+      <c r="BG96" s="3"/>
+      <c r="BH96" s="3"/>
+      <c r="BI96" s="3"/>
+      <c r="BJ96" s="3"/>
+      <c r="BK96" s="3"/>
+      <c r="BL96" s="3"/>
+      <c r="BM96" s="3"/>
+      <c r="BN96" s="3"/>
+      <c r="BO96" s="3"/>
+      <c r="BP96" s="3"/>
+      <c r="BQ96" s="3"/>
+      <c r="BR96" s="3"/>
+      <c r="BS96" s="3"/>
+      <c r="BV96" s="5"/>
+      <c r="BW96" s="5"/>
+    </row>
+    <row r="97" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C97" s="5">
         <v>19</v>
       </c>
@@ -4080,10 +4342,30 @@
       <c r="AW97" s="3"/>
       <c r="AX97" s="3"/>
       <c r="AY97" s="3"/>
-      <c r="BB97" s="5"/>
-      <c r="BC97" s="5"/>
-    </row>
-    <row r="98" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="AZ97" s="3"/>
+      <c r="BA97" s="3"/>
+      <c r="BB97" s="3"/>
+      <c r="BC97" s="3"/>
+      <c r="BD97" s="3"/>
+      <c r="BE97" s="3"/>
+      <c r="BF97" s="3"/>
+      <c r="BG97" s="3"/>
+      <c r="BH97" s="3"/>
+      <c r="BI97" s="3"/>
+      <c r="BJ97" s="3"/>
+      <c r="BK97" s="3"/>
+      <c r="BL97" s="3"/>
+      <c r="BM97" s="3"/>
+      <c r="BN97" s="3"/>
+      <c r="BO97" s="3"/>
+      <c r="BP97" s="3"/>
+      <c r="BQ97" s="3"/>
+      <c r="BR97" s="3"/>
+      <c r="BS97" s="3"/>
+      <c r="BV97" s="5"/>
+      <c r="BW97" s="5"/>
+    </row>
+    <row r="98" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C98" s="5">
         <v>10</v>
       </c>
@@ -4138,10 +4420,30 @@
       <c r="AW98" s="3"/>
       <c r="AX98" s="3"/>
       <c r="AY98" s="3"/>
-      <c r="BB98" s="5"/>
-      <c r="BC98" s="5"/>
-    </row>
-    <row r="99" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="AZ98" s="3"/>
+      <c r="BA98" s="3"/>
+      <c r="BB98" s="3"/>
+      <c r="BC98" s="3"/>
+      <c r="BD98" s="3"/>
+      <c r="BE98" s="3"/>
+      <c r="BF98" s="3"/>
+      <c r="BG98" s="3"/>
+      <c r="BH98" s="3"/>
+      <c r="BI98" s="3"/>
+      <c r="BJ98" s="3"/>
+      <c r="BK98" s="3"/>
+      <c r="BL98" s="3"/>
+      <c r="BM98" s="3"/>
+      <c r="BN98" s="3"/>
+      <c r="BO98" s="3"/>
+      <c r="BP98" s="3"/>
+      <c r="BQ98" s="3"/>
+      <c r="BR98" s="3"/>
+      <c r="BS98" s="3"/>
+      <c r="BV98" s="5"/>
+      <c r="BW98" s="5"/>
+    </row>
+    <row r="99" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C99" s="5">
         <v>17</v>
       </c>
@@ -4196,10 +4498,30 @@
       <c r="AY99" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="BB99" s="5"/>
-      <c r="BC99" s="5"/>
-    </row>
-    <row r="100" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="AZ99" s="3"/>
+      <c r="BA99" s="3"/>
+      <c r="BB99" s="3"/>
+      <c r="BC99" s="3"/>
+      <c r="BD99" s="3"/>
+      <c r="BE99" s="3"/>
+      <c r="BF99" s="3"/>
+      <c r="BG99" s="3"/>
+      <c r="BH99" s="3"/>
+      <c r="BI99" s="3"/>
+      <c r="BJ99" s="3"/>
+      <c r="BK99" s="3"/>
+      <c r="BL99" s="3"/>
+      <c r="BM99" s="3"/>
+      <c r="BN99" s="3"/>
+      <c r="BO99" s="3"/>
+      <c r="BP99" s="3"/>
+      <c r="BQ99" s="3"/>
+      <c r="BR99" s="3"/>
+      <c r="BS99" s="3"/>
+      <c r="BV99" s="5"/>
+      <c r="BW99" s="5"/>
+    </row>
+    <row r="100" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C100" s="5">
         <v>11</v>
       </c>
@@ -4222,8 +4544,28 @@
       <c r="AW100" s="3"/>
       <c r="AX100" s="3"/>
       <c r="AY100" s="3"/>
-    </row>
-    <row r="101" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="AZ100" s="3"/>
+      <c r="BA100" s="3"/>
+      <c r="BB100" s="3"/>
+      <c r="BC100" s="3"/>
+      <c r="BD100" s="3"/>
+      <c r="BE100" s="3"/>
+      <c r="BF100" s="3"/>
+      <c r="BG100" s="3"/>
+      <c r="BH100" s="3"/>
+      <c r="BI100" s="3"/>
+      <c r="BJ100" s="3"/>
+      <c r="BK100" s="3"/>
+      <c r="BL100" s="3"/>
+      <c r="BM100" s="3"/>
+      <c r="BN100" s="3"/>
+      <c r="BO100" s="3"/>
+      <c r="BP100" s="3"/>
+      <c r="BQ100" s="3"/>
+      <c r="BR100" s="3"/>
+      <c r="BS100" s="3"/>
+    </row>
+    <row r="101" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C101" s="5">
         <v>8</v>
       </c>
@@ -4258,13 +4600,33 @@
       <c r="AW101" s="3"/>
       <c r="AX101" s="3"/>
       <c r="AY101" s="3"/>
-      <c r="BA101" s="3" t="s">
-        <v>38</v>
-      </c>
+      <c r="AZ101" s="3"/>
+      <c r="BA101" s="3"/>
       <c r="BB101" s="3"/>
       <c r="BC101" s="3"/>
-    </row>
-    <row r="102" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD101" s="3"/>
+      <c r="BE101" s="3"/>
+      <c r="BF101" s="3"/>
+      <c r="BG101" s="3"/>
+      <c r="BH101" s="3"/>
+      <c r="BI101" s="3"/>
+      <c r="BJ101" s="3"/>
+      <c r="BK101" s="3"/>
+      <c r="BL101" s="3"/>
+      <c r="BM101" s="3"/>
+      <c r="BN101" s="3"/>
+      <c r="BO101" s="3"/>
+      <c r="BP101" s="3"/>
+      <c r="BQ101" s="3"/>
+      <c r="BR101" s="3"/>
+      <c r="BS101" s="3"/>
+      <c r="BU101" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="BV101" s="3"/>
+      <c r="BW101" s="3"/>
+    </row>
+    <row r="102" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C102" s="5">
         <v>4</v>
       </c>
@@ -4303,11 +4665,31 @@
       <c r="AW102" s="3"/>
       <c r="AX102" s="3"/>
       <c r="AY102" s="3"/>
+      <c r="AZ102" s="3"/>
       <c r="BA102" s="3"/>
       <c r="BB102" s="3"/>
       <c r="BC102" s="3"/>
-    </row>
-    <row r="103" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD102" s="3"/>
+      <c r="BE102" s="3"/>
+      <c r="BF102" s="3"/>
+      <c r="BG102" s="3"/>
+      <c r="BH102" s="3"/>
+      <c r="BI102" s="3"/>
+      <c r="BJ102" s="3"/>
+      <c r="BK102" s="3"/>
+      <c r="BL102" s="3"/>
+      <c r="BM102" s="3"/>
+      <c r="BN102" s="3"/>
+      <c r="BO102" s="3"/>
+      <c r="BP102" s="3"/>
+      <c r="BQ102" s="3"/>
+      <c r="BR102" s="3"/>
+      <c r="BS102" s="3"/>
+      <c r="BU102" s="3"/>
+      <c r="BV102" s="3"/>
+      <c r="BW102" s="3"/>
+    </row>
+    <row r="103" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C103" s="5">
         <v>5</v>
       </c>
@@ -4350,11 +4732,31 @@
       <c r="AW103" s="3"/>
       <c r="AX103" s="3"/>
       <c r="AY103" s="3"/>
+      <c r="AZ103" s="3"/>
       <c r="BA103" s="3"/>
       <c r="BB103" s="3"/>
       <c r="BC103" s="3"/>
-    </row>
-    <row r="104" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD103" s="3"/>
+      <c r="BE103" s="3"/>
+      <c r="BF103" s="3"/>
+      <c r="BG103" s="3"/>
+      <c r="BH103" s="3"/>
+      <c r="BI103" s="3"/>
+      <c r="BJ103" s="3"/>
+      <c r="BK103" s="3"/>
+      <c r="BL103" s="3"/>
+      <c r="BM103" s="3"/>
+      <c r="BN103" s="3"/>
+      <c r="BO103" s="3"/>
+      <c r="BP103" s="3"/>
+      <c r="BQ103" s="3"/>
+      <c r="BR103" s="3"/>
+      <c r="BS103" s="3"/>
+      <c r="BU103" s="3"/>
+      <c r="BV103" s="3"/>
+      <c r="BW103" s="3"/>
+    </row>
+    <row r="104" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C104" s="5">
         <v>13</v>
       </c>
@@ -4393,11 +4795,31 @@
       <c r="AW104" s="3"/>
       <c r="AX104" s="3"/>
       <c r="AY104" s="3"/>
+      <c r="AZ104" s="3"/>
       <c r="BA104" s="3"/>
       <c r="BB104" s="3"/>
       <c r="BC104" s="3"/>
-    </row>
-    <row r="105" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD104" s="3"/>
+      <c r="BE104" s="3"/>
+      <c r="BF104" s="3"/>
+      <c r="BG104" s="3"/>
+      <c r="BH104" s="3"/>
+      <c r="BI104" s="3"/>
+      <c r="BJ104" s="3"/>
+      <c r="BK104" s="3"/>
+      <c r="BL104" s="3"/>
+      <c r="BM104" s="3"/>
+      <c r="BN104" s="3"/>
+      <c r="BO104" s="3"/>
+      <c r="BP104" s="3"/>
+      <c r="BQ104" s="3"/>
+      <c r="BR104" s="3"/>
+      <c r="BS104" s="3"/>
+      <c r="BU104" s="3"/>
+      <c r="BV104" s="3"/>
+      <c r="BW104" s="3"/>
+    </row>
+    <row r="105" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C105" s="5">
         <v>21</v>
       </c>
@@ -4444,11 +4866,31 @@
       <c r="AW105" s="3"/>
       <c r="AX105" s="3"/>
       <c r="AY105" s="3"/>
+      <c r="AZ105" s="3"/>
       <c r="BA105" s="3"/>
       <c r="BB105" s="3"/>
       <c r="BC105" s="3"/>
-    </row>
-    <row r="106" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD105" s="3"/>
+      <c r="BE105" s="3"/>
+      <c r="BF105" s="3"/>
+      <c r="BG105" s="3"/>
+      <c r="BH105" s="3"/>
+      <c r="BI105" s="3"/>
+      <c r="BJ105" s="3"/>
+      <c r="BK105" s="3"/>
+      <c r="BL105" s="3"/>
+      <c r="BM105" s="3"/>
+      <c r="BN105" s="3"/>
+      <c r="BO105" s="3"/>
+      <c r="BP105" s="3"/>
+      <c r="BQ105" s="3"/>
+      <c r="BR105" s="3"/>
+      <c r="BS105" s="3"/>
+      <c r="BU105" s="3"/>
+      <c r="BV105" s="3"/>
+      <c r="BW105" s="3"/>
+    </row>
+    <row r="106" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C106" s="5">
         <v>6</v>
       </c>
@@ -4499,11 +4941,31 @@
       <c r="AW106" s="3"/>
       <c r="AX106" s="3"/>
       <c r="AY106" s="3"/>
+      <c r="AZ106" s="3"/>
       <c r="BA106" s="3"/>
       <c r="BB106" s="3"/>
       <c r="BC106" s="3"/>
-    </row>
-    <row r="107" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD106" s="3"/>
+      <c r="BE106" s="3"/>
+      <c r="BF106" s="3"/>
+      <c r="BG106" s="3"/>
+      <c r="BH106" s="3"/>
+      <c r="BI106" s="3"/>
+      <c r="BJ106" s="3"/>
+      <c r="BK106" s="3"/>
+      <c r="BL106" s="3"/>
+      <c r="BM106" s="3"/>
+      <c r="BN106" s="3"/>
+      <c r="BO106" s="3"/>
+      <c r="BP106" s="3"/>
+      <c r="BQ106" s="3"/>
+      <c r="BR106" s="3"/>
+      <c r="BS106" s="3"/>
+      <c r="BU106" s="3"/>
+      <c r="BV106" s="3"/>
+      <c r="BW106" s="3"/>
+    </row>
+    <row r="107" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C107" s="5"/>
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
@@ -4548,11 +5010,31 @@
       <c r="AW107" s="3"/>
       <c r="AX107" s="3"/>
       <c r="AY107" s="3"/>
+      <c r="AZ107" s="3"/>
       <c r="BA107" s="3"/>
       <c r="BB107" s="3"/>
       <c r="BC107" s="3"/>
-    </row>
-    <row r="108" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD107" s="3"/>
+      <c r="BE107" s="3"/>
+      <c r="BF107" s="3"/>
+      <c r="BG107" s="3"/>
+      <c r="BH107" s="3"/>
+      <c r="BI107" s="3"/>
+      <c r="BJ107" s="3"/>
+      <c r="BK107" s="3"/>
+      <c r="BL107" s="3"/>
+      <c r="BM107" s="3"/>
+      <c r="BN107" s="3"/>
+      <c r="BO107" s="3"/>
+      <c r="BP107" s="3"/>
+      <c r="BQ107" s="3"/>
+      <c r="BR107" s="3"/>
+      <c r="BS107" s="3"/>
+      <c r="BU107" s="3"/>
+      <c r="BV107" s="3"/>
+      <c r="BW107" s="3"/>
+    </row>
+    <row r="108" spans="2:75" x14ac:dyDescent="0.25">
       <c r="B108" s="1">
         <v>11</v>
       </c>
@@ -4600,15 +5082,35 @@
       <c r="AW108" s="3"/>
       <c r="AX108" s="3"/>
       <c r="AY108" s="3"/>
+      <c r="AZ108" s="3"/>
       <c r="BA108" s="3"/>
-      <c r="BB108" s="3">
+      <c r="BB108" s="3"/>
+      <c r="BC108" s="3"/>
+      <c r="BD108" s="3"/>
+      <c r="BE108" s="3"/>
+      <c r="BF108" s="3"/>
+      <c r="BG108" s="3"/>
+      <c r="BH108" s="3"/>
+      <c r="BI108" s="3"/>
+      <c r="BJ108" s="3"/>
+      <c r="BK108" s="3"/>
+      <c r="BL108" s="3"/>
+      <c r="BM108" s="3"/>
+      <c r="BN108" s="3"/>
+      <c r="BO108" s="3"/>
+      <c r="BP108" s="3"/>
+      <c r="BQ108" s="3"/>
+      <c r="BR108" s="3"/>
+      <c r="BS108" s="3"/>
+      <c r="BU108" s="3"/>
+      <c r="BV108" s="3">
         <v>6</v>
       </c>
-      <c r="BC108" s="3" t="s">
+      <c r="BW108" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C109" s="5">
         <v>2</v>
       </c>
@@ -4631,11 +5133,31 @@
       <c r="AW109" s="3"/>
       <c r="AX109" s="3"/>
       <c r="AY109" s="3"/>
+      <c r="AZ109" s="3"/>
       <c r="BA109" s="3"/>
       <c r="BB109" s="3"/>
       <c r="BC109" s="3"/>
-    </row>
-    <row r="110" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD109" s="3"/>
+      <c r="BE109" s="3"/>
+      <c r="BF109" s="3"/>
+      <c r="BG109" s="3"/>
+      <c r="BH109" s="3"/>
+      <c r="BI109" s="3"/>
+      <c r="BJ109" s="3"/>
+      <c r="BK109" s="3"/>
+      <c r="BL109" s="3"/>
+      <c r="BM109" s="3"/>
+      <c r="BN109" s="3"/>
+      <c r="BO109" s="3"/>
+      <c r="BP109" s="3"/>
+      <c r="BQ109" s="3"/>
+      <c r="BR109" s="3"/>
+      <c r="BS109" s="3"/>
+      <c r="BU109" s="3"/>
+      <c r="BV109" s="3"/>
+      <c r="BW109" s="3"/>
+    </row>
+    <row r="110" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C110" s="5">
         <v>1</v>
       </c>
@@ -4670,13 +5192,33 @@
       </c>
       <c r="AX110" s="3"/>
       <c r="AY110" s="3"/>
-      <c r="BA110" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="AZ110" s="3"/>
+      <c r="BA110" s="3"/>
       <c r="BB110" s="3"/>
       <c r="BC110" s="3"/>
-    </row>
-    <row r="111" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD110" s="3"/>
+      <c r="BE110" s="3"/>
+      <c r="BF110" s="3"/>
+      <c r="BG110" s="3"/>
+      <c r="BH110" s="3"/>
+      <c r="BI110" s="3"/>
+      <c r="BJ110" s="3"/>
+      <c r="BK110" s="3"/>
+      <c r="BL110" s="3"/>
+      <c r="BM110" s="3"/>
+      <c r="BN110" s="3"/>
+      <c r="BO110" s="3"/>
+      <c r="BP110" s="3"/>
+      <c r="BQ110" s="3"/>
+      <c r="BR110" s="3"/>
+      <c r="BS110" s="3"/>
+      <c r="BU110" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="BV110" s="3"/>
+      <c r="BW110" s="3"/>
+    </row>
+    <row r="111" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C111" s="5">
         <v>3</v>
       </c>
@@ -4715,11 +5257,31 @@
       <c r="AW111" s="3"/>
       <c r="AX111" s="3"/>
       <c r="AY111" s="3"/>
+      <c r="AZ111" s="3"/>
       <c r="BA111" s="3"/>
       <c r="BB111" s="3"/>
       <c r="BC111" s="3"/>
-    </row>
-    <row r="112" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD111" s="3"/>
+      <c r="BE111" s="3"/>
+      <c r="BF111" s="3"/>
+      <c r="BG111" s="3"/>
+      <c r="BH111" s="3"/>
+      <c r="BI111" s="3"/>
+      <c r="BJ111" s="3"/>
+      <c r="BK111" s="3"/>
+      <c r="BL111" s="3"/>
+      <c r="BM111" s="3"/>
+      <c r="BN111" s="3"/>
+      <c r="BO111" s="3"/>
+      <c r="BP111" s="3"/>
+      <c r="BQ111" s="3"/>
+      <c r="BR111" s="3"/>
+      <c r="BS111" s="3"/>
+      <c r="BU111" s="3"/>
+      <c r="BV111" s="3"/>
+      <c r="BW111" s="3"/>
+    </row>
+    <row r="112" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C112" s="5">
         <v>19</v>
       </c>
@@ -4766,11 +5328,31 @@
       <c r="AW112" s="3"/>
       <c r="AX112" s="3"/>
       <c r="AY112" s="3"/>
+      <c r="AZ112" s="3"/>
       <c r="BA112" s="3"/>
       <c r="BB112" s="3"/>
       <c r="BC112" s="3"/>
-    </row>
-    <row r="113" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD112" s="3"/>
+      <c r="BE112" s="3"/>
+      <c r="BF112" s="3"/>
+      <c r="BG112" s="3"/>
+      <c r="BH112" s="3"/>
+      <c r="BI112" s="3"/>
+      <c r="BJ112" s="3"/>
+      <c r="BK112" s="3"/>
+      <c r="BL112" s="3"/>
+      <c r="BM112" s="3"/>
+      <c r="BN112" s="3"/>
+      <c r="BO112" s="3"/>
+      <c r="BP112" s="3"/>
+      <c r="BQ112" s="3"/>
+      <c r="BR112" s="3"/>
+      <c r="BS112" s="3"/>
+      <c r="BU112" s="3"/>
+      <c r="BV112" s="3"/>
+      <c r="BW112" s="3"/>
+    </row>
+    <row r="113" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C113" s="5">
         <v>10</v>
       </c>
@@ -4813,11 +5395,31 @@
       <c r="AW113" s="3"/>
       <c r="AX113" s="3"/>
       <c r="AY113" s="3"/>
+      <c r="AZ113" s="3"/>
       <c r="BA113" s="3"/>
       <c r="BB113" s="3"/>
       <c r="BC113" s="3"/>
-    </row>
-    <row r="114" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD113" s="3"/>
+      <c r="BE113" s="3"/>
+      <c r="BF113" s="3"/>
+      <c r="BG113" s="3"/>
+      <c r="BH113" s="3"/>
+      <c r="BI113" s="3"/>
+      <c r="BJ113" s="3"/>
+      <c r="BK113" s="3"/>
+      <c r="BL113" s="3"/>
+      <c r="BM113" s="3"/>
+      <c r="BN113" s="3"/>
+      <c r="BO113" s="3"/>
+      <c r="BP113" s="3"/>
+      <c r="BQ113" s="3"/>
+      <c r="BR113" s="3"/>
+      <c r="BS113" s="3"/>
+      <c r="BU113" s="3"/>
+      <c r="BV113" s="3"/>
+      <c r="BW113" s="3"/>
+    </row>
+    <row r="114" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C114" s="5">
         <v>17</v>
       </c>
@@ -4864,11 +5466,31 @@
       <c r="AW114" s="3"/>
       <c r="AX114" s="3"/>
       <c r="AY114" s="3"/>
+      <c r="AZ114" s="3"/>
       <c r="BA114" s="3"/>
       <c r="BB114" s="3"/>
       <c r="BC114" s="3"/>
-    </row>
-    <row r="115" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD114" s="3"/>
+      <c r="BE114" s="3"/>
+      <c r="BF114" s="3"/>
+      <c r="BG114" s="3"/>
+      <c r="BH114" s="3"/>
+      <c r="BI114" s="3"/>
+      <c r="BJ114" s="3"/>
+      <c r="BK114" s="3"/>
+      <c r="BL114" s="3"/>
+      <c r="BM114" s="3"/>
+      <c r="BN114" s="3"/>
+      <c r="BO114" s="3"/>
+      <c r="BP114" s="3"/>
+      <c r="BQ114" s="3"/>
+      <c r="BR114" s="3"/>
+      <c r="BS114" s="3"/>
+      <c r="BU114" s="3"/>
+      <c r="BV114" s="3"/>
+      <c r="BW114" s="3"/>
+    </row>
+    <row r="115" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C115" s="5">
         <v>12</v>
       </c>
@@ -4927,11 +5549,31 @@
       <c r="AW115" s="3"/>
       <c r="AX115" s="3"/>
       <c r="AY115" s="3"/>
+      <c r="AZ115" s="3"/>
       <c r="BA115" s="3"/>
       <c r="BB115" s="3"/>
       <c r="BC115" s="3"/>
-    </row>
-    <row r="116" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD115" s="3"/>
+      <c r="BE115" s="3"/>
+      <c r="BF115" s="3"/>
+      <c r="BG115" s="3"/>
+      <c r="BH115" s="3"/>
+      <c r="BI115" s="3"/>
+      <c r="BJ115" s="3"/>
+      <c r="BK115" s="3"/>
+      <c r="BL115" s="3"/>
+      <c r="BM115" s="3"/>
+      <c r="BN115" s="3"/>
+      <c r="BO115" s="3"/>
+      <c r="BP115" s="3"/>
+      <c r="BQ115" s="3"/>
+      <c r="BR115" s="3"/>
+      <c r="BS115" s="3"/>
+      <c r="BU115" s="3"/>
+      <c r="BV115" s="3"/>
+      <c r="BW115" s="3"/>
+    </row>
+    <row r="116" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C116" s="5">
         <v>8</v>
       </c>
@@ -4989,11 +5631,31 @@
       <c r="AY116" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="AZ116" s="3"/>
       <c r="BA116" s="3"/>
       <c r="BB116" s="3"/>
       <c r="BC116" s="3"/>
-    </row>
-    <row r="117" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BD116" s="3"/>
+      <c r="BE116" s="3"/>
+      <c r="BF116" s="3"/>
+      <c r="BG116" s="3"/>
+      <c r="BH116" s="3"/>
+      <c r="BI116" s="3"/>
+      <c r="BJ116" s="3"/>
+      <c r="BK116" s="3"/>
+      <c r="BL116" s="3"/>
+      <c r="BM116" s="3"/>
+      <c r="BN116" s="3"/>
+      <c r="BO116" s="3"/>
+      <c r="BP116" s="3"/>
+      <c r="BQ116" s="3"/>
+      <c r="BR116" s="3"/>
+      <c r="BS116" s="3"/>
+      <c r="BU116" s="3"/>
+      <c r="BV116" s="3"/>
+      <c r="BW116" s="3"/>
+    </row>
+    <row r="117" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C117" s="5">
         <v>4</v>
       </c>
@@ -5042,15 +5704,35 @@
       <c r="AU117" s="5"/>
       <c r="AX117" s="5"/>
       <c r="AY117" s="5"/>
-      <c r="BA117" s="3"/>
-      <c r="BB117" s="3">
+      <c r="AZ117" s="5"/>
+      <c r="BA117" s="5"/>
+      <c r="BB117" s="5"/>
+      <c r="BC117" s="5"/>
+      <c r="BD117" s="5"/>
+      <c r="BE117" s="5"/>
+      <c r="BF117" s="5"/>
+      <c r="BG117" s="5"/>
+      <c r="BH117" s="5"/>
+      <c r="BI117" s="5"/>
+      <c r="BJ117" s="5"/>
+      <c r="BK117" s="5"/>
+      <c r="BL117" s="5"/>
+      <c r="BM117" s="5"/>
+      <c r="BN117" s="5"/>
+      <c r="BO117" s="5"/>
+      <c r="BP117" s="5"/>
+      <c r="BQ117" s="5"/>
+      <c r="BR117" s="5"/>
+      <c r="BS117" s="5"/>
+      <c r="BU117" s="3"/>
+      <c r="BV117" s="3">
         <v>21</v>
       </c>
-      <c r="BC117" s="3" t="s">
+      <c r="BW117" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="118" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C118" s="5">
         <v>5</v>
       </c>
@@ -5064,7 +5746,7 @@
       <c r="J118" s="5"/>
       <c r="K118" s="5"/>
     </row>
-    <row r="119" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C119" s="5">
         <v>13</v>
       </c>
@@ -5078,7 +5760,7 @@
       <c r="J119" s="5"/>
       <c r="K119" s="5"/>
     </row>
-    <row r="120" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C120" s="5">
         <v>21</v>
       </c>
@@ -5092,7 +5774,7 @@
       <c r="J120" s="5"/>
       <c r="K120" s="5"/>
     </row>
-    <row r="121" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C121" s="5">
         <v>6</v>
       </c>
@@ -5106,7 +5788,7 @@
       <c r="J121" s="5"/>
       <c r="K121" s="5"/>
     </row>
-    <row r="122" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C122" s="5"/>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
@@ -5114,7 +5796,7 @@
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
     </row>
-    <row r="123" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:75" x14ac:dyDescent="0.25">
       <c r="B123" s="1">
         <v>8</v>
       </c>
@@ -5125,7 +5807,7 @@
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
     </row>
-    <row r="124" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C124" s="5">
         <v>2</v>
       </c>
@@ -5143,7 +5825,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="125" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C125" s="5">
         <v>1</v>
       </c>
@@ -5157,7 +5839,7 @@
       <c r="J125" s="5"/>
       <c r="K125" s="5"/>
     </row>
-    <row r="126" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C126" s="5">
         <v>3</v>
       </c>
@@ -5171,7 +5853,7 @@
       <c r="J126" s="5"/>
       <c r="K126" s="5"/>
     </row>
-    <row r="127" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C127" s="5">
         <v>19</v>
       </c>
@@ -5189,7 +5871,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="128" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C128" s="5">
         <v>10</v>
       </c>
@@ -6418,7 +7100,7 @@
       <c r="J208" s="5"/>
       <c r="K208" s="5"/>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:71" x14ac:dyDescent="0.25">
       <c r="C209" s="5">
         <v>5</v>
       </c>
@@ -6436,7 +7118,7 @@
       <c r="J209" s="5"/>
       <c r="K209" s="5"/>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:71" x14ac:dyDescent="0.25">
       <c r="C210" s="5">
         <v>13</v>
       </c>
@@ -6454,7 +7136,7 @@
       <c r="J210" s="5"/>
       <c r="K210" s="5"/>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:71" x14ac:dyDescent="0.25">
       <c r="C211" s="5">
         <v>21</v>
       </c>
@@ -6472,1461 +7154,7321 @@
       <c r="J211" s="5"/>
       <c r="K211" s="5"/>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:71" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:71" x14ac:dyDescent="0.25">
       <c r="B222" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F222" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I222" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="AW222" s="5"/>
+      <c r="AX222" s="5"/>
+      <c r="AY222" s="5"/>
+      <c r="AZ222" s="5"/>
+      <c r="BA222" s="5"/>
+      <c r="BB222" s="5"/>
+      <c r="BC222" s="5"/>
+      <c r="BD222" s="5"/>
+      <c r="BE222" s="5"/>
+      <c r="BF222" s="2"/>
+      <c r="BG222" s="2"/>
+      <c r="BH222" s="2"/>
+      <c r="BI222" s="5"/>
+      <c r="BJ222" s="5"/>
+      <c r="BK222" s="5"/>
+      <c r="BL222" s="2"/>
+      <c r="BM222" s="5"/>
+      <c r="BN222" s="5"/>
+      <c r="BO222" s="5"/>
+      <c r="BP222" s="5"/>
+      <c r="BQ222" s="5"/>
+      <c r="BR222" s="5"/>
+      <c r="BS222" s="5"/>
+    </row>
+    <row r="223" spans="1:71" x14ac:dyDescent="0.25">
       <c r="C223" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G223" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="AW223" s="5"/>
+      <c r="AX223" s="5"/>
+      <c r="AY223" s="5"/>
+      <c r="AZ223" s="5"/>
+      <c r="BA223" s="5"/>
+      <c r="BB223" s="5"/>
+      <c r="BC223" s="5"/>
+      <c r="BD223" s="5"/>
+      <c r="BE223" s="5"/>
+      <c r="BF223" s="2"/>
+      <c r="BG223" s="2"/>
+      <c r="BH223" s="2"/>
+      <c r="BI223" s="5"/>
+      <c r="BJ223" s="5"/>
+      <c r="BK223" s="5"/>
+      <c r="BL223" s="2"/>
+      <c r="BM223" s="5"/>
+      <c r="BN223" s="5"/>
+      <c r="BO223" s="5"/>
+      <c r="BP223" s="5"/>
+      <c r="BQ223" s="5"/>
+      <c r="BR223" s="5"/>
+      <c r="BS223" s="5"/>
+    </row>
+    <row r="224" spans="1:71" x14ac:dyDescent="0.25">
       <c r="C224" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="225" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="AW224" s="5"/>
+      <c r="AX224" s="5"/>
+      <c r="AY224" s="5"/>
+      <c r="AZ224" s="5"/>
+      <c r="BA224" s="5"/>
+      <c r="BB224" s="5"/>
+      <c r="BC224" s="5"/>
+      <c r="BD224" s="5"/>
+      <c r="BE224" s="5"/>
+      <c r="BF224" s="3"/>
+      <c r="BG224" s="3"/>
+      <c r="BH224" s="3"/>
+      <c r="BI224" s="5"/>
+      <c r="BJ224" s="5"/>
+      <c r="BK224" s="5"/>
+      <c r="BL224" s="3"/>
+      <c r="BM224" s="5"/>
+      <c r="BN224" s="5"/>
+      <c r="BO224" s="5"/>
+      <c r="BP224" s="5"/>
+      <c r="BQ224" s="5"/>
+      <c r="BR224" s="5"/>
+      <c r="BS224" s="5"/>
+    </row>
+    <row r="225" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C225" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="226" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="AW225" s="5"/>
+      <c r="AX225" s="5"/>
+      <c r="AY225" s="5"/>
+      <c r="AZ225" s="5"/>
+      <c r="BA225" s="5"/>
+      <c r="BB225" s="5"/>
+      <c r="BC225" s="5"/>
+      <c r="BD225" s="5"/>
+      <c r="BE225" s="5"/>
+      <c r="BF225" s="2"/>
+      <c r="BG225" s="2"/>
+      <c r="BH225" s="2"/>
+      <c r="BI225" s="5"/>
+      <c r="BJ225" s="5"/>
+      <c r="BK225" s="5"/>
+      <c r="BL225" s="2"/>
+      <c r="BM225" s="5"/>
+      <c r="BN225" s="9"/>
+      <c r="BO225" s="9"/>
+      <c r="BP225" s="9"/>
+      <c r="BQ225" s="9"/>
+      <c r="BR225" s="9"/>
+      <c r="BS225" s="9"/>
+    </row>
+    <row r="226" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C226" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="227" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="AW226" s="5"/>
+      <c r="AX226" s="5"/>
+      <c r="AY226" s="5"/>
+      <c r="AZ226" s="5"/>
+      <c r="BA226" s="5"/>
+      <c r="BB226" s="5"/>
+      <c r="BC226" s="5"/>
+      <c r="BD226" s="5"/>
+      <c r="BE226" s="5"/>
+      <c r="BF226" s="2"/>
+      <c r="BG226" s="2"/>
+      <c r="BH226" s="2"/>
+      <c r="BI226" s="5"/>
+      <c r="BJ226" s="5"/>
+      <c r="BK226" s="5"/>
+      <c r="BL226" s="2"/>
+      <c r="BM226" s="2"/>
+      <c r="BN226" s="2"/>
+      <c r="BO226" s="2"/>
+      <c r="BP226" s="2"/>
+      <c r="BQ226" s="2"/>
+      <c r="BR226" s="2"/>
+      <c r="BS226" s="2"/>
+    </row>
+    <row r="227" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C227" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="228" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="AW227" s="2"/>
+      <c r="AX227" s="2"/>
+      <c r="AY227" s="2"/>
+      <c r="AZ227" s="2"/>
+      <c r="BA227" s="2"/>
+      <c r="BB227" s="2"/>
+      <c r="BC227" s="2"/>
+      <c r="BD227" s="2"/>
+      <c r="BE227" s="2"/>
+      <c r="BF227" s="2"/>
+      <c r="BG227" s="2"/>
+      <c r="BH227" s="2"/>
+      <c r="BI227" s="2"/>
+      <c r="BJ227" s="2"/>
+      <c r="BK227" s="2"/>
+      <c r="BL227" s="2"/>
+      <c r="BM227" s="2"/>
+      <c r="BN227" s="2"/>
+      <c r="BO227" s="2"/>
+      <c r="BP227" s="2"/>
+      <c r="BQ227" s="2"/>
+      <c r="BR227" s="2"/>
+      <c r="BS227" s="2"/>
+    </row>
+    <row r="228" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C228" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D228" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J228" s="3"/>
+      <c r="K228" s="3"/>
+      <c r="AW228" s="2"/>
+      <c r="AX228" s="2"/>
+      <c r="AY228" s="2"/>
+      <c r="AZ228" s="2"/>
+      <c r="BA228" s="2"/>
+      <c r="BB228" s="2"/>
+      <c r="BC228" s="2"/>
+      <c r="BD228" s="2"/>
+      <c r="BE228" s="2"/>
+      <c r="BF228" s="2"/>
+      <c r="BG228" s="2"/>
+      <c r="BH228" s="2"/>
+      <c r="BI228" s="2"/>
+      <c r="BJ228" s="2"/>
+      <c r="BK228" s="2"/>
+      <c r="BL228" s="2"/>
+      <c r="BM228" s="2"/>
+      <c r="BN228" s="2"/>
+      <c r="BO228" s="2"/>
+      <c r="BP228" s="2"/>
+      <c r="BQ228" s="2"/>
+      <c r="BR228" s="2"/>
+      <c r="BS228" s="2"/>
+      <c r="BV228" s="3"/>
+      <c r="BW228" s="3"/>
+    </row>
+    <row r="229" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="C229" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J229" s="3"/>
+      <c r="K229" s="3"/>
+      <c r="AW229" s="2"/>
+      <c r="AX229" s="2"/>
+      <c r="AY229" s="2"/>
+      <c r="AZ229" s="2"/>
+      <c r="BA229" s="2"/>
+      <c r="BB229" s="2"/>
+      <c r="BC229" s="2"/>
+      <c r="BD229" s="2"/>
+      <c r="BE229" s="2"/>
+      <c r="BF229" s="2"/>
+      <c r="BG229" s="2"/>
+      <c r="BH229" s="2"/>
+      <c r="BI229" s="2"/>
+      <c r="BJ229" s="2"/>
+      <c r="BK229" s="2"/>
+      <c r="BL229" s="2"/>
+      <c r="BM229" s="2"/>
+      <c r="BN229" s="2"/>
+      <c r="BO229" s="2"/>
+      <c r="BP229" s="2"/>
+      <c r="BQ229" s="2"/>
+      <c r="BR229" s="2"/>
+      <c r="BS229" s="2"/>
+      <c r="BV229" s="3"/>
+      <c r="BW229" s="3"/>
+    </row>
+    <row r="230" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="C230" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D230" s="1" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="229" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C229" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J229" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K229" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="230" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C230" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
-    </row>
-    <row r="231" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="AW230" s="2"/>
+      <c r="AX230" s="2"/>
+      <c r="AY230" s="2"/>
+      <c r="AZ230" s="2"/>
+      <c r="BA230" s="2"/>
+      <c r="BB230" s="2"/>
+      <c r="BC230" s="2"/>
+      <c r="BD230" s="2"/>
+      <c r="BE230" s="2"/>
+      <c r="BF230" s="2"/>
+      <c r="BG230" s="2"/>
+      <c r="BH230" s="2"/>
+      <c r="BI230" s="2"/>
+      <c r="BJ230" s="2"/>
+      <c r="BK230" s="2"/>
+      <c r="BL230" s="2"/>
+      <c r="BM230" s="2"/>
+      <c r="BN230" s="2"/>
+      <c r="BO230" s="2"/>
+      <c r="BP230" s="2"/>
+      <c r="BQ230" s="2"/>
+      <c r="BR230" s="2"/>
+      <c r="BS230" s="2"/>
+      <c r="BV230" s="3"/>
+      <c r="BW230" s="3"/>
+    </row>
+    <row r="231" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C231" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
-    </row>
-    <row r="232" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="AW231" s="2"/>
+      <c r="AX231" s="2"/>
+      <c r="AY231" s="2"/>
+      <c r="AZ231" s="2"/>
+      <c r="BA231" s="2"/>
+      <c r="BB231" s="2"/>
+      <c r="BC231" s="2"/>
+      <c r="BD231" s="2"/>
+      <c r="BE231" s="2"/>
+      <c r="BF231" s="2"/>
+      <c r="BG231" s="2"/>
+      <c r="BH231" s="2"/>
+      <c r="BI231" s="2"/>
+      <c r="BJ231" s="2"/>
+      <c r="BK231" s="2"/>
+      <c r="BL231" s="2"/>
+      <c r="BM231" s="2"/>
+      <c r="BN231" s="2"/>
+      <c r="BO231" s="2"/>
+      <c r="BP231" s="2"/>
+      <c r="BQ231" s="2"/>
+      <c r="BR231" s="2"/>
+      <c r="BS231" s="2"/>
+      <c r="BV231" s="3"/>
+      <c r="BW231" s="3"/>
+    </row>
+    <row r="232" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C232" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
-    </row>
-    <row r="233" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="AW232" s="2"/>
+      <c r="AX232" s="2"/>
+      <c r="AY232" s="2"/>
+      <c r="AZ232" s="2"/>
+      <c r="BA232" s="2"/>
+      <c r="BB232" s="2"/>
+      <c r="BC232" s="2"/>
+      <c r="BD232" s="2"/>
+      <c r="BE232" s="2"/>
+      <c r="BF232" s="2"/>
+      <c r="BG232" s="2"/>
+      <c r="BH232" s="2"/>
+      <c r="BI232" s="2"/>
+      <c r="BJ232" s="2"/>
+      <c r="BK232" s="2"/>
+      <c r="BL232" s="2"/>
+      <c r="BM232" s="2"/>
+      <c r="BN232" s="2"/>
+      <c r="BO232" s="2"/>
+      <c r="BP232" s="2"/>
+      <c r="BQ232" s="2"/>
+      <c r="BR232" s="2"/>
+      <c r="BS232" s="2"/>
+      <c r="BV232" s="3"/>
+      <c r="BW232" s="3"/>
+    </row>
+    <row r="233" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C233" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
-    </row>
-    <row r="234" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="AW233" s="2"/>
+      <c r="AX233" s="2"/>
+      <c r="AY233" s="2"/>
+      <c r="AZ233" s="2"/>
+      <c r="BA233" s="2"/>
+      <c r="BB233" s="2"/>
+      <c r="BC233" s="2"/>
+      <c r="BD233" s="2"/>
+      <c r="BE233" s="2"/>
+      <c r="BF233" s="2"/>
+      <c r="BG233" s="2"/>
+      <c r="BH233" s="2"/>
+      <c r="BI233" s="2"/>
+      <c r="BJ233" s="2"/>
+      <c r="BK233" s="2"/>
+      <c r="BL233" s="2"/>
+      <c r="BM233" s="2"/>
+      <c r="BN233" s="2"/>
+      <c r="BO233" s="2"/>
+      <c r="BP233" s="2"/>
+      <c r="BQ233" s="2"/>
+      <c r="BR233" s="2"/>
+      <c r="BS233" s="2"/>
+      <c r="BV233" s="3"/>
+      <c r="BW233" s="3"/>
+    </row>
+    <row r="234" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C234" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>18</v>
       </c>
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
-    </row>
-    <row r="235" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="AW234" s="2"/>
+      <c r="AX234" s="2"/>
+      <c r="AY234" s="2"/>
+      <c r="AZ234" s="2"/>
+      <c r="BA234" s="2"/>
+      <c r="BB234" s="2"/>
+      <c r="BC234" s="2"/>
+      <c r="BD234" s="2"/>
+      <c r="BE234" s="2"/>
+      <c r="BF234" s="2"/>
+      <c r="BG234" s="2"/>
+      <c r="BH234" s="2"/>
+      <c r="BI234" s="2"/>
+      <c r="BJ234" s="2"/>
+      <c r="BK234" s="2"/>
+      <c r="BL234" s="2"/>
+      <c r="BM234" s="2"/>
+      <c r="BN234" s="2"/>
+      <c r="BO234" s="2"/>
+      <c r="BP234" s="2"/>
+      <c r="BQ234" s="2"/>
+      <c r="BR234" s="2"/>
+      <c r="BS234" s="2"/>
+      <c r="BV234" s="3"/>
+      <c r="BW234" s="3"/>
+    </row>
+    <row r="235" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="C235" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
-    </row>
-    <row r="236" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B236" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F236" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I236" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="AW235" s="2"/>
+      <c r="AX235" s="2"/>
+      <c r="AY235" s="2"/>
+      <c r="AZ235" s="2"/>
+      <c r="BA235" s="2"/>
+      <c r="BB235" s="2"/>
+      <c r="BC235" s="2"/>
+      <c r="BD235" s="2"/>
+      <c r="BE235" s="2"/>
+      <c r="BF235" s="2"/>
+      <c r="BG235" s="2"/>
+      <c r="BH235" s="2"/>
+      <c r="BI235" s="2"/>
+      <c r="BJ235" s="2"/>
+      <c r="BK235" s="2"/>
+      <c r="BL235" s="2"/>
+      <c r="BM235" s="2"/>
+      <c r="BN235" s="2"/>
+      <c r="BO235" s="2"/>
+      <c r="BP235" s="2"/>
+      <c r="BQ235" s="2"/>
+      <c r="BR235" s="2"/>
+      <c r="BS235" s="2"/>
+      <c r="BV235" s="3"/>
+      <c r="BW235" s="3"/>
+    </row>
+    <row r="236" spans="2:75" x14ac:dyDescent="0.25">
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
-    </row>
-    <row r="237" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C237" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>20</v>
+      <c r="AW236" s="2"/>
+      <c r="AX236" s="2"/>
+      <c r="AY236" s="2"/>
+      <c r="AZ236" s="2"/>
+      <c r="BA236" s="2"/>
+      <c r="BB236" s="2"/>
+      <c r="BC236" s="2"/>
+      <c r="BD236" s="2"/>
+      <c r="BE236" s="2"/>
+      <c r="BF236" s="2"/>
+      <c r="BG236" s="2"/>
+      <c r="BH236" s="2"/>
+      <c r="BI236" s="2"/>
+      <c r="BJ236" s="2"/>
+      <c r="BK236" s="2"/>
+      <c r="BL236" s="2"/>
+      <c r="BM236" s="2"/>
+      <c r="BN236" s="2"/>
+      <c r="BO236" s="2"/>
+      <c r="BP236" s="2"/>
+      <c r="BQ236" s="2"/>
+      <c r="BR236" s="2"/>
+      <c r="BS236" s="2"/>
+      <c r="BV236" s="3"/>
+      <c r="BW236" s="3"/>
+    </row>
+    <row r="237" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B237" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
-    </row>
-    <row r="238" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="AW237" s="2"/>
+      <c r="AX237" s="2"/>
+      <c r="AY237" s="2"/>
+      <c r="AZ237" s="2"/>
+      <c r="BA237" s="2"/>
+      <c r="BB237" s="2"/>
+      <c r="BC237" s="2"/>
+      <c r="BD237" s="2"/>
+      <c r="BE237" s="2"/>
+      <c r="BF237" s="2"/>
+      <c r="BG237" s="2"/>
+      <c r="BH237" s="2"/>
+      <c r="BI237" s="2"/>
+      <c r="BJ237" s="2"/>
+      <c r="BK237" s="2"/>
+      <c r="BL237" s="2"/>
+      <c r="BM237" s="2"/>
+      <c r="BN237" s="2"/>
+      <c r="BO237" s="2"/>
+      <c r="BP237" s="2"/>
+      <c r="BQ237" s="2"/>
+      <c r="BR237" s="2"/>
+      <c r="BS237" s="2"/>
+      <c r="BV237" s="3"/>
+      <c r="BW237" s="3"/>
+    </row>
+    <row r="238" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C238" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
-    </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="AW238" s="2"/>
+      <c r="AX238" s="2"/>
+      <c r="AY238" s="2"/>
+      <c r="AZ238" s="2"/>
+      <c r="BA238" s="2"/>
+      <c r="BB238" s="2"/>
+      <c r="BC238" s="2"/>
+      <c r="BD238" s="2"/>
+      <c r="BE238" s="2"/>
+      <c r="BF238" s="2"/>
+      <c r="BG238" s="2"/>
+      <c r="BH238" s="2"/>
+      <c r="BI238" s="2"/>
+      <c r="BJ238" s="2"/>
+      <c r="BK238" s="2"/>
+      <c r="BL238" s="2"/>
+      <c r="BM238" s="2"/>
+      <c r="BN238" s="2"/>
+      <c r="BO238" s="2"/>
+      <c r="BP238" s="2"/>
+      <c r="BQ238" s="2"/>
+      <c r="BR238" s="2"/>
+      <c r="BS238" s="2"/>
+      <c r="BV238" s="3"/>
+      <c r="BW238" s="3"/>
+    </row>
+    <row r="239" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C239" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
-    </row>
-    <row r="240" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="AW239" s="2"/>
+      <c r="AX239" s="2"/>
+      <c r="AY239" s="2"/>
+      <c r="AZ239" s="2"/>
+      <c r="BA239" s="2"/>
+      <c r="BB239" s="2"/>
+      <c r="BC239" s="2"/>
+      <c r="BD239" s="2"/>
+      <c r="BE239" s="2"/>
+      <c r="BF239" s="2"/>
+      <c r="BG239" s="2"/>
+      <c r="BH239" s="2"/>
+      <c r="BI239" s="2"/>
+      <c r="BJ239" s="2"/>
+      <c r="BK239" s="2"/>
+      <c r="BL239" s="2"/>
+      <c r="BM239" s="2"/>
+      <c r="BN239" s="2"/>
+      <c r="BO239" s="2"/>
+      <c r="BP239" s="2"/>
+      <c r="BQ239" s="2"/>
+      <c r="BR239" s="2"/>
+      <c r="BS239" s="2"/>
+      <c r="BV239" s="3"/>
+      <c r="BW239" s="3"/>
+    </row>
+    <row r="240" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C240" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J240" s="3" t="s">
+      <c r="J240" s="3"/>
+      <c r="K240" s="3"/>
+      <c r="AW240" s="2"/>
+      <c r="AX240" s="2"/>
+      <c r="AY240" s="2"/>
+      <c r="AZ240" s="2"/>
+      <c r="BA240" s="2"/>
+      <c r="BB240" s="2"/>
+      <c r="BC240" s="2"/>
+      <c r="BD240" s="2"/>
+      <c r="BE240" s="2"/>
+      <c r="BF240" s="2"/>
+      <c r="BG240" s="2"/>
+      <c r="BH240" s="2"/>
+      <c r="BI240" s="2"/>
+      <c r="BJ240" s="2"/>
+      <c r="BK240" s="2"/>
+      <c r="BL240" s="2"/>
+      <c r="BM240" s="2"/>
+      <c r="BN240" s="2"/>
+      <c r="BO240" s="2"/>
+      <c r="BP240" s="2"/>
+      <c r="BQ240" s="2"/>
+      <c r="BR240" s="2"/>
+      <c r="BS240" s="2"/>
+      <c r="BV240" s="3"/>
+      <c r="BW240" s="3"/>
+    </row>
+    <row r="241" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="C241" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="K240" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="241" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C241" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="242" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J241" s="3"/>
+      <c r="K241" s="3"/>
+      <c r="AW241" s="2"/>
+      <c r="AX241" s="2"/>
+      <c r="AY241" s="2"/>
+      <c r="AZ241" s="2"/>
+      <c r="BA241" s="2"/>
+      <c r="BB241" s="2"/>
+      <c r="BC241" s="2"/>
+      <c r="BD241" s="2"/>
+      <c r="BE241" s="2"/>
+      <c r="BF241" s="2"/>
+      <c r="BG241" s="2"/>
+      <c r="BH241" s="2"/>
+      <c r="BI241" s="2"/>
+      <c r="BJ241" s="2"/>
+      <c r="BK241" s="2"/>
+      <c r="BL241" s="2"/>
+      <c r="BM241" s="2"/>
+      <c r="BN241" s="2"/>
+      <c r="BO241" s="2"/>
+      <c r="BP241" s="2"/>
+      <c r="BQ241" s="2"/>
+      <c r="BR241" s="2"/>
+      <c r="BS241" s="2"/>
+      <c r="BV241" s="3"/>
+      <c r="BW241" s="3"/>
+    </row>
+    <row r="242" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C242" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="243" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="AW242" s="2"/>
+      <c r="AX242" s="2"/>
+      <c r="AY242" s="2"/>
+      <c r="AZ242" s="2"/>
+      <c r="BA242" s="2"/>
+      <c r="BB242" s="2"/>
+      <c r="BC242" s="2"/>
+      <c r="BD242" s="2"/>
+      <c r="BE242" s="2"/>
+      <c r="BF242" s="2"/>
+      <c r="BG242" s="2"/>
+      <c r="BH242" s="2"/>
+      <c r="BI242" s="2"/>
+      <c r="BJ242" s="2"/>
+      <c r="BK242" s="2"/>
+      <c r="BL242" s="2"/>
+      <c r="BM242" s="2"/>
+      <c r="BN242" s="2"/>
+      <c r="BO242" s="2"/>
+      <c r="BP242" s="2"/>
+      <c r="BQ242" s="2"/>
+      <c r="BR242" s="2"/>
+      <c r="BS242" s="2"/>
+    </row>
+    <row r="243" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C243" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="244" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="AW243" s="2"/>
+      <c r="AX243" s="2"/>
+      <c r="AY243" s="2"/>
+      <c r="AZ243" s="2"/>
+      <c r="BA243" s="2"/>
+      <c r="BB243" s="2"/>
+      <c r="BC243" s="2"/>
+      <c r="BD243" s="2"/>
+      <c r="BE243" s="2"/>
+      <c r="BF243" s="2"/>
+      <c r="BG243" s="2"/>
+      <c r="BH243" s="2"/>
+      <c r="BI243" s="2"/>
+      <c r="BJ243" s="2"/>
+      <c r="BK243" s="2"/>
+      <c r="BL243" s="2"/>
+      <c r="BM243" s="2"/>
+      <c r="BN243" s="2"/>
+      <c r="BO243" s="2"/>
+      <c r="BP243" s="2"/>
+      <c r="BQ243" s="2"/>
+      <c r="BR243" s="2"/>
+      <c r="BS243" s="2"/>
+    </row>
+    <row r="244" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C244" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="245" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="AW244" s="2"/>
+      <c r="AX244" s="2"/>
+      <c r="AY244" s="2"/>
+      <c r="AZ244" s="2"/>
+      <c r="BA244" s="2"/>
+      <c r="BB244" s="2"/>
+      <c r="BC244" s="2"/>
+      <c r="BD244" s="2"/>
+      <c r="BE244" s="2"/>
+      <c r="BF244" s="2"/>
+      <c r="BG244" s="2"/>
+      <c r="BH244" s="2"/>
+      <c r="BI244" s="2"/>
+      <c r="BJ244" s="2"/>
+      <c r="BK244" s="2"/>
+      <c r="BL244" s="2"/>
+      <c r="BM244" s="2"/>
+      <c r="BN244" s="2"/>
+      <c r="BO244" s="2"/>
+      <c r="BP244" s="2"/>
+      <c r="BQ244" s="2"/>
+      <c r="BR244" s="2"/>
+      <c r="BS244" s="2"/>
+    </row>
+    <row r="245" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C245" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="246" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="AW245" s="2"/>
+      <c r="AX245" s="2"/>
+      <c r="AY245" s="2"/>
+      <c r="AZ245" s="2"/>
+      <c r="BA245" s="2"/>
+      <c r="BB245" s="2"/>
+      <c r="BC245" s="2"/>
+      <c r="BD245" s="2"/>
+      <c r="BE245" s="2"/>
+      <c r="BF245" s="2"/>
+      <c r="BG245" s="2"/>
+      <c r="BH245" s="2"/>
+      <c r="BI245" s="2"/>
+      <c r="BJ245" s="2"/>
+      <c r="BK245" s="2"/>
+      <c r="BL245" s="2"/>
+      <c r="BM245" s="2"/>
+      <c r="BN245" s="2"/>
+      <c r="BO245" s="2"/>
+      <c r="BP245" s="2"/>
+      <c r="BQ245" s="2"/>
+      <c r="BR245" s="2"/>
+      <c r="BS245" s="2"/>
+    </row>
+    <row r="246" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C246" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="247" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="AW246" s="2"/>
+      <c r="AX246" s="2"/>
+      <c r="AY246" s="2"/>
+      <c r="AZ246" s="2"/>
+      <c r="BA246" s="2"/>
+      <c r="BB246" s="2"/>
+      <c r="BC246" s="2"/>
+      <c r="BD246" s="2"/>
+      <c r="BE246" s="2"/>
+      <c r="BF246" s="2"/>
+      <c r="BG246" s="2"/>
+      <c r="BH246" s="2"/>
+      <c r="BI246" s="2"/>
+      <c r="BJ246" s="2"/>
+      <c r="BK246" s="2"/>
+      <c r="BL246" s="2"/>
+      <c r="BM246" s="2"/>
+      <c r="BN246" s="2"/>
+      <c r="BO246" s="2"/>
+      <c r="BP246" s="2"/>
+      <c r="BQ246" s="2"/>
+      <c r="BR246" s="2"/>
+      <c r="BS246" s="2"/>
+    </row>
+    <row r="247" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C247" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="248" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="AW247" s="2"/>
+      <c r="AX247" s="2"/>
+      <c r="AY247" s="2"/>
+      <c r="AZ247" s="2"/>
+      <c r="BA247" s="2"/>
+      <c r="BB247" s="2"/>
+      <c r="BC247" s="2"/>
+      <c r="BD247" s="2"/>
+      <c r="BE247" s="2"/>
+      <c r="BF247" s="2"/>
+      <c r="BG247" s="2"/>
+      <c r="BH247" s="2"/>
+      <c r="BI247" s="2"/>
+      <c r="BJ247" s="2"/>
+      <c r="BK247" s="2"/>
+      <c r="BL247" s="2"/>
+      <c r="BM247" s="2"/>
+      <c r="BN247" s="2"/>
+      <c r="BO247" s="2"/>
+      <c r="BP247" s="2"/>
+      <c r="BQ247" s="2"/>
+      <c r="BR247" s="2"/>
+      <c r="BS247" s="2"/>
+    </row>
+    <row r="248" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C248" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="249" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="AW248" s="2"/>
+      <c r="AX248" s="2"/>
+      <c r="AY248" s="2"/>
+      <c r="AZ248" s="2"/>
+      <c r="BA248" s="2"/>
+      <c r="BB248" s="2"/>
+      <c r="BC248" s="2"/>
+      <c r="BD248" s="2"/>
+      <c r="BE248" s="2"/>
+      <c r="BF248" s="2"/>
+      <c r="BG248" s="2"/>
+      <c r="BH248" s="2"/>
+      <c r="BI248" s="2"/>
+      <c r="BJ248" s="2"/>
+      <c r="BK248" s="2"/>
+      <c r="BL248" s="2"/>
+      <c r="BM248" s="2"/>
+      <c r="BN248" s="2"/>
+      <c r="BO248" s="2"/>
+      <c r="BP248" s="2"/>
+      <c r="BQ248" s="2"/>
+      <c r="BR248" s="2"/>
+      <c r="BS248" s="2"/>
+    </row>
+    <row r="249" spans="2:75" x14ac:dyDescent="0.25">
       <c r="C249" s="1" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="251" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B251" s="1" t="s">
+      <c r="AW249" s="2"/>
+      <c r="AX249" s="2"/>
+      <c r="AY249" s="2"/>
+      <c r="AZ249" s="2"/>
+      <c r="BA249" s="2"/>
+      <c r="BB249" s="2"/>
+      <c r="BC249" s="2"/>
+      <c r="BD249" s="2"/>
+      <c r="BE249" s="2"/>
+      <c r="BF249" s="2"/>
+      <c r="BG249" s="2"/>
+      <c r="BH249" s="2"/>
+      <c r="BI249" s="2"/>
+      <c r="BJ249" s="2"/>
+      <c r="BK249" s="2"/>
+      <c r="BL249" s="2"/>
+      <c r="BM249" s="2"/>
+      <c r="BN249" s="2"/>
+      <c r="BO249" s="2"/>
+      <c r="BP249" s="2"/>
+      <c r="BQ249" s="2"/>
+      <c r="BR249" s="2"/>
+      <c r="BS249" s="2"/>
+    </row>
+    <row r="250" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="C250" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW250" s="2"/>
+      <c r="AX250" s="2"/>
+      <c r="AY250" s="2"/>
+      <c r="AZ250" s="2"/>
+      <c r="BA250" s="2"/>
+      <c r="BB250" s="2"/>
+      <c r="BC250" s="2"/>
+      <c r="BD250" s="2"/>
+      <c r="BE250" s="2"/>
+      <c r="BF250" s="2"/>
+      <c r="BG250" s="2"/>
+      <c r="BH250" s="2"/>
+      <c r="BI250" s="2"/>
+      <c r="BJ250" s="2"/>
+      <c r="BK250" s="2"/>
+      <c r="BL250" s="2"/>
+      <c r="BM250" s="2"/>
+      <c r="BN250" s="2"/>
+      <c r="BO250" s="2"/>
+      <c r="BP250" s="2"/>
+      <c r="BQ250" s="2"/>
+      <c r="BR250" s="2"/>
+      <c r="BS250" s="2"/>
+    </row>
+    <row r="251" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="AW251" s="2"/>
+      <c r="AX251" s="2"/>
+      <c r="AY251" s="2"/>
+      <c r="AZ251" s="2"/>
+      <c r="BA251" s="2"/>
+      <c r="BB251" s="2"/>
+      <c r="BC251" s="2"/>
+      <c r="BD251" s="2"/>
+      <c r="BE251" s="2"/>
+      <c r="BF251" s="2"/>
+      <c r="BG251" s="2"/>
+      <c r="BH251" s="2"/>
+      <c r="BI251" s="2"/>
+      <c r="BJ251" s="2"/>
+      <c r="BK251" s="2"/>
+      <c r="BL251" s="2"/>
+      <c r="BM251" s="2"/>
+      <c r="BN251" s="2"/>
+      <c r="BO251" s="2"/>
+      <c r="BP251" s="2"/>
+      <c r="BQ251" s="2"/>
+      <c r="BR251" s="2"/>
+      <c r="BS251" s="2"/>
+    </row>
+    <row r="252" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B252" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F251" s="1" t="s">
+      <c r="F252" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J252" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N252" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="V252" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z252" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AW252" s="5"/>
+      <c r="AX252" s="5"/>
+      <c r="AY252" s="5"/>
+      <c r="AZ252" s="5"/>
+      <c r="BA252" s="5"/>
+      <c r="BB252" s="5"/>
+      <c r="BC252" s="5"/>
+      <c r="BD252" s="2"/>
+      <c r="BE252" s="2"/>
+      <c r="BF252" s="2"/>
+      <c r="BG252" s="2"/>
+      <c r="BH252" s="2"/>
+      <c r="BI252" s="5"/>
+      <c r="BJ252" s="5"/>
+      <c r="BK252" s="5"/>
+      <c r="BL252" s="2"/>
+      <c r="BM252" s="5"/>
+      <c r="BN252" s="5"/>
+      <c r="BO252" s="5"/>
+      <c r="BP252" s="5"/>
+      <c r="BQ252" s="5"/>
+      <c r="BR252" s="5"/>
+      <c r="BS252" s="5"/>
+    </row>
+    <row r="253" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="C253" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D253" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="252" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C252" s="1" t="s">
+      <c r="G253" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D252" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G252" s="1" t="s">
+      <c r="H253" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W253" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X253" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW253" s="5"/>
+      <c r="AX253" s="5"/>
+      <c r="AY253" s="5"/>
+      <c r="AZ253" s="5"/>
+      <c r="BA253" s="5"/>
+      <c r="BB253" s="5"/>
+      <c r="BC253" s="5"/>
+      <c r="BD253" s="2"/>
+      <c r="BE253" s="2"/>
+      <c r="BF253" s="2"/>
+      <c r="BG253" s="2"/>
+      <c r="BH253" s="2"/>
+      <c r="BI253" s="5"/>
+      <c r="BJ253" s="5"/>
+      <c r="BK253" s="5"/>
+      <c r="BL253" s="2"/>
+      <c r="BM253" s="5"/>
+      <c r="BN253" s="5"/>
+      <c r="BO253" s="5"/>
+      <c r="BP253" s="5"/>
+      <c r="BQ253" s="5"/>
+      <c r="BR253" s="5"/>
+      <c r="BS253" s="5"/>
+    </row>
+    <row r="254" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="C254" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G254" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H254" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W254" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X254" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW254" s="5"/>
+      <c r="AX254" s="5"/>
+      <c r="AY254" s="5"/>
+      <c r="AZ254" s="5"/>
+      <c r="BA254" s="5"/>
+      <c r="BB254" s="5"/>
+      <c r="BC254" s="5"/>
+      <c r="BD254" s="2"/>
+      <c r="BE254" s="2"/>
+      <c r="BF254" s="2"/>
+      <c r="BG254" s="2"/>
+      <c r="BH254" s="2"/>
+      <c r="BI254" s="5"/>
+      <c r="BJ254" s="5"/>
+      <c r="BK254" s="5"/>
+      <c r="BL254" s="2"/>
+      <c r="BM254" s="5"/>
+      <c r="BN254" s="5"/>
+      <c r="BO254" s="5"/>
+      <c r="BP254" s="5"/>
+      <c r="BQ254" s="5"/>
+      <c r="BR254" s="5"/>
+      <c r="BS254" s="5"/>
+    </row>
+    <row r="255" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="C255" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G255" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H255" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W255" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X255" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW255" s="5"/>
+      <c r="AX255" s="5"/>
+      <c r="AY255" s="5"/>
+      <c r="AZ255" s="5"/>
+      <c r="BA255" s="5"/>
+      <c r="BB255" s="5"/>
+      <c r="BC255" s="5"/>
+      <c r="BD255" s="2"/>
+      <c r="BE255" s="2"/>
+      <c r="BF255" s="2"/>
+      <c r="BG255" s="2"/>
+      <c r="BH255" s="2"/>
+      <c r="BI255" s="5"/>
+      <c r="BJ255" s="5"/>
+      <c r="BK255" s="5"/>
+      <c r="BL255" s="2"/>
+      <c r="BM255" s="5"/>
+      <c r="BN255" s="5"/>
+      <c r="BO255" s="5"/>
+      <c r="BP255" s="5"/>
+      <c r="BQ255" s="5"/>
+      <c r="BR255" s="5"/>
+      <c r="BS255" s="5"/>
+    </row>
+    <row r="256" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="C256" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W256" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X256" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA256" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB256" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW256" s="5"/>
+      <c r="AX256" s="5"/>
+      <c r="AY256" s="5"/>
+      <c r="AZ256" s="5"/>
+      <c r="BA256" s="5"/>
+      <c r="BB256" s="5"/>
+      <c r="BC256" s="5"/>
+      <c r="BD256" s="2"/>
+      <c r="BE256" s="2"/>
+      <c r="BF256" s="2"/>
+      <c r="BG256" s="2"/>
+      <c r="BH256" s="2"/>
+      <c r="BI256" s="5"/>
+      <c r="BJ256" s="5"/>
+      <c r="BK256" s="5"/>
+      <c r="BL256" s="2"/>
+      <c r="BM256" s="5"/>
+      <c r="BN256" s="9"/>
+      <c r="BO256" s="9"/>
+      <c r="BP256" s="9"/>
+      <c r="BQ256" s="5"/>
+      <c r="BR256" s="5"/>
+      <c r="BS256" s="5"/>
+    </row>
+    <row r="257" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C257" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G257" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H257" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K257" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L257" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O257" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P257" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AW257" s="5"/>
+      <c r="AX257" s="5"/>
+      <c r="AY257" s="5"/>
+      <c r="AZ257" s="5"/>
+      <c r="BA257" s="5"/>
+      <c r="BB257" s="5"/>
+      <c r="BC257" s="5"/>
+      <c r="BD257" s="2"/>
+      <c r="BE257" s="2"/>
+      <c r="BF257" s="2"/>
+      <c r="BG257" s="2"/>
+      <c r="BH257" s="2"/>
+      <c r="BI257" s="5"/>
+      <c r="BJ257" s="5"/>
+      <c r="BK257" s="5"/>
+      <c r="BL257" s="2"/>
+      <c r="BM257" s="5"/>
+      <c r="BN257" s="5"/>
+      <c r="BO257" s="5"/>
+      <c r="BP257" s="5"/>
+      <c r="BQ257" s="5"/>
+      <c r="BR257" s="5"/>
+      <c r="BS257" s="5"/>
+    </row>
+    <row r="258" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C258" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="253" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C253" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D253" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="254" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C254" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="255" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C255" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D255" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="256" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C256" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D256" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="257" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C257" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="258" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C258" s="1" t="s">
+      <c r="D258" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G258" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H258" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W258" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X258" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW258" s="5"/>
+      <c r="AX258" s="5"/>
+      <c r="AY258" s="5"/>
+      <c r="AZ258" s="5"/>
+      <c r="BA258" s="5"/>
+      <c r="BB258" s="5"/>
+      <c r="BC258" s="5"/>
+      <c r="BD258" s="2"/>
+      <c r="BE258" s="2"/>
+      <c r="BF258" s="2"/>
+      <c r="BG258" s="2"/>
+      <c r="BH258" s="2"/>
+      <c r="BI258" s="5"/>
+      <c r="BJ258" s="5"/>
+      <c r="BK258" s="5"/>
+      <c r="BL258" s="2"/>
+      <c r="BM258" s="5"/>
+      <c r="BN258" s="5"/>
+      <c r="BO258" s="5"/>
+      <c r="BP258" s="5"/>
+      <c r="BQ258" s="5"/>
+      <c r="BR258" s="5"/>
+      <c r="BS258" s="5"/>
+    </row>
+    <row r="259" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C259" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D258" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="259" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C259" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="D259" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="260" spans="2:7" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="W259" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X259" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA259" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB259" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW259" s="5"/>
+      <c r="AX259" s="5"/>
+      <c r="AY259" s="5"/>
+      <c r="AZ259" s="5"/>
+      <c r="BA259" s="5"/>
+      <c r="BB259" s="5"/>
+      <c r="BC259" s="5"/>
+      <c r="BD259" s="2"/>
+      <c r="BE259" s="2"/>
+      <c r="BF259" s="2"/>
+      <c r="BG259" s="2"/>
+      <c r="BH259" s="2"/>
+      <c r="BI259" s="2"/>
+      <c r="BJ259" s="2"/>
+      <c r="BK259" s="2"/>
+      <c r="BL259" s="2"/>
+      <c r="BM259" s="2"/>
+      <c r="BN259" s="2"/>
+      <c r="BO259" s="2"/>
+      <c r="BP259" s="2"/>
+      <c r="BQ259" s="2"/>
+      <c r="BR259" s="2"/>
+      <c r="BS259" s="2"/>
+    </row>
+    <row r="260" spans="2:71" x14ac:dyDescent="0.25">
       <c r="C260" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="261" spans="2:7" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="W260" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="X260" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA260" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB260" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW260" s="5"/>
+      <c r="AX260" s="5"/>
+      <c r="AY260" s="5"/>
+      <c r="AZ260" s="5"/>
+      <c r="BA260" s="5"/>
+      <c r="BB260" s="5"/>
+      <c r="BC260" s="5"/>
+      <c r="BD260" s="2"/>
+      <c r="BE260" s="2"/>
+      <c r="BF260" s="2"/>
+      <c r="BG260" s="2"/>
+      <c r="BH260" s="2"/>
+      <c r="BI260" s="2"/>
+      <c r="BJ260" s="2"/>
+      <c r="BK260" s="2"/>
+      <c r="BL260" s="2"/>
+      <c r="BM260" s="2"/>
+      <c r="BN260" s="2"/>
+      <c r="BO260" s="2"/>
+      <c r="BP260" s="2"/>
+      <c r="BQ260" s="2"/>
+      <c r="BR260" s="2"/>
+      <c r="BS260" s="2"/>
+    </row>
+    <row r="261" spans="2:71" x14ac:dyDescent="0.25">
       <c r="C261" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="262" spans="2:7" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="G261" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H261" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W261" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="X261" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW261" s="5"/>
+      <c r="AX261" s="5"/>
+      <c r="AY261" s="5"/>
+      <c r="AZ261" s="5"/>
+      <c r="BA261" s="5"/>
+      <c r="BB261" s="5"/>
+      <c r="BC261" s="5"/>
+      <c r="BD261" s="2"/>
+      <c r="BE261" s="2"/>
+      <c r="BF261" s="2"/>
+      <c r="BG261" s="2"/>
+      <c r="BH261" s="2"/>
+      <c r="BI261" s="2"/>
+      <c r="BJ261" s="2"/>
+      <c r="BK261" s="2"/>
+      <c r="BL261" s="2"/>
+      <c r="BM261" s="2"/>
+      <c r="BN261" s="2"/>
+      <c r="BO261" s="2"/>
+      <c r="BP261" s="2"/>
+      <c r="BQ261" s="2"/>
+      <c r="BR261" s="2"/>
+      <c r="BS261" s="2"/>
+    </row>
+    <row r="262" spans="2:71" x14ac:dyDescent="0.25">
       <c r="C262" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="263" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G262" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H262" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K262" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L262" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AW262" s="5"/>
+      <c r="AX262" s="5"/>
+      <c r="AY262" s="5"/>
+      <c r="AZ262" s="5"/>
+      <c r="BA262" s="5"/>
+      <c r="BB262" s="5"/>
+      <c r="BC262" s="5"/>
+      <c r="BD262" s="2"/>
+      <c r="BE262" s="2"/>
+      <c r="BF262" s="2"/>
+      <c r="BG262" s="2"/>
+      <c r="BH262" s="2"/>
+      <c r="BI262" s="2"/>
+      <c r="BJ262" s="2"/>
+      <c r="BK262" s="2"/>
+      <c r="BL262" s="2"/>
+      <c r="BM262" s="2"/>
+      <c r="BN262" s="2"/>
+      <c r="BO262" s="2"/>
+      <c r="BP262" s="2"/>
+      <c r="BQ262" s="2"/>
+      <c r="BR262" s="2"/>
+      <c r="BS262" s="2"/>
+    </row>
+    <row r="263" spans="2:71" x14ac:dyDescent="0.25">
       <c r="C263" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D263" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W263" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X263" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA263" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB263" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW263" s="5"/>
+      <c r="AX263" s="5"/>
+      <c r="AY263" s="5"/>
+      <c r="AZ263" s="5"/>
+      <c r="BA263" s="5"/>
+      <c r="BB263" s="5"/>
+      <c r="BC263" s="5"/>
+      <c r="BD263" s="2"/>
+      <c r="BE263" s="2"/>
+      <c r="BF263" s="2"/>
+      <c r="BG263" s="2"/>
+      <c r="BH263" s="2"/>
+      <c r="BI263" s="2"/>
+      <c r="BJ263" s="2"/>
+      <c r="BK263" s="2"/>
+      <c r="BL263" s="2"/>
+      <c r="BM263" s="2"/>
+      <c r="BN263" s="2"/>
+      <c r="BO263" s="2"/>
+      <c r="BP263" s="2"/>
+      <c r="BQ263" s="2"/>
+      <c r="BR263" s="2"/>
+      <c r="BS263" s="2"/>
+    </row>
+    <row r="264" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C264" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W264" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X264" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA264" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB264" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW264" s="5"/>
+      <c r="AX264" s="5"/>
+      <c r="AY264" s="5"/>
+      <c r="AZ264" s="5"/>
+      <c r="BA264" s="5"/>
+      <c r="BB264" s="5"/>
+      <c r="BC264" s="5"/>
+      <c r="BD264" s="2"/>
+      <c r="BE264" s="2"/>
+      <c r="BF264" s="2"/>
+      <c r="BG264" s="2"/>
+      <c r="BH264" s="2"/>
+      <c r="BI264" s="2"/>
+      <c r="BJ264" s="2"/>
+      <c r="BK264" s="2"/>
+      <c r="BL264" s="2"/>
+      <c r="BM264" s="2"/>
+      <c r="BN264" s="2"/>
+      <c r="BO264" s="2"/>
+      <c r="BP264" s="2"/>
+      <c r="BQ264" s="2"/>
+      <c r="BR264" s="2"/>
+      <c r="BS264" s="2"/>
+    </row>
+    <row r="265" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C265" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G265" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H265" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W265" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="X265" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA265" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB265" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW265" s="5"/>
+      <c r="AX265" s="5"/>
+      <c r="AY265" s="5"/>
+      <c r="AZ265" s="5"/>
+      <c r="BA265" s="5"/>
+      <c r="BB265" s="5"/>
+      <c r="BC265" s="5"/>
+      <c r="BD265" s="2"/>
+      <c r="BE265" s="2"/>
+      <c r="BF265" s="2"/>
+      <c r="BG265" s="2"/>
+      <c r="BH265" s="2"/>
+      <c r="BI265" s="2"/>
+      <c r="BJ265" s="2"/>
+      <c r="BK265" s="2"/>
+      <c r="BL265" s="2"/>
+      <c r="BM265" s="2"/>
+      <c r="BN265" s="2"/>
+      <c r="BO265" s="2"/>
+      <c r="BP265" s="2"/>
+      <c r="BQ265" s="2"/>
+      <c r="BR265" s="2"/>
+      <c r="BS265" s="2"/>
+    </row>
+    <row r="266" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="AW266" s="5"/>
+      <c r="AX266" s="5"/>
+      <c r="AY266" s="5"/>
+      <c r="AZ266" s="5"/>
+      <c r="BA266" s="5"/>
+      <c r="BB266" s="5"/>
+      <c r="BC266" s="5"/>
+      <c r="BD266" s="2"/>
+      <c r="BE266" s="2"/>
+      <c r="BF266" s="2"/>
+      <c r="BG266" s="2"/>
+      <c r="BH266" s="2"/>
+      <c r="BI266" s="2"/>
+      <c r="BJ266" s="2"/>
+      <c r="BK266" s="2"/>
+      <c r="BL266" s="2"/>
+      <c r="BM266" s="2"/>
+      <c r="BN266" s="2"/>
+      <c r="BO266" s="2"/>
+      <c r="BP266" s="2"/>
+      <c r="BQ266" s="2"/>
+      <c r="BR266" s="2"/>
+      <c r="BS266" s="2"/>
+    </row>
+    <row r="267" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="B267" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F267" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V267" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z267" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AW267" s="5"/>
+      <c r="BA267" s="5"/>
+      <c r="BB267" s="5"/>
+      <c r="BC267" s="5"/>
+      <c r="BD267" s="2"/>
+      <c r="BE267" s="2"/>
+      <c r="BF267" s="2"/>
+      <c r="BG267" s="2"/>
+      <c r="BH267" s="2"/>
+      <c r="BI267" s="5"/>
+      <c r="BJ267" s="5"/>
+      <c r="BK267" s="5"/>
+      <c r="BL267" s="2"/>
+      <c r="BM267" s="2"/>
+      <c r="BN267" s="2"/>
+      <c r="BO267" s="2"/>
+      <c r="BP267" s="2"/>
+      <c r="BQ267" s="5"/>
+      <c r="BR267" s="5"/>
+      <c r="BS267" s="5"/>
+    </row>
+    <row r="268" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C268" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G268" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H268" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="W268" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X268" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW268" s="5"/>
+      <c r="AY268" s="3"/>
+      <c r="AZ268" s="3"/>
+      <c r="BA268" s="5"/>
+      <c r="BB268" s="5"/>
+      <c r="BC268" s="5"/>
+      <c r="BD268" s="2"/>
+      <c r="BE268" s="2"/>
+      <c r="BF268" s="2"/>
+      <c r="BG268" s="2"/>
+      <c r="BH268" s="2"/>
+      <c r="BI268" s="5"/>
+      <c r="BJ268" s="5"/>
+      <c r="BK268" s="5"/>
+      <c r="BL268" s="2"/>
+      <c r="BM268" s="2"/>
+      <c r="BN268" s="2"/>
+      <c r="BO268" s="2"/>
+      <c r="BP268" s="2"/>
+      <c r="BQ268" s="5"/>
+      <c r="BR268" s="5"/>
+      <c r="BS268" s="5"/>
+    </row>
+    <row r="269" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C269" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G269" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H269" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="W269" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X269" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW269" s="5"/>
+      <c r="BA269" s="5"/>
+      <c r="BB269" s="5"/>
+      <c r="BC269" s="5"/>
+      <c r="BD269" s="2"/>
+      <c r="BE269" s="2"/>
+      <c r="BF269" s="2"/>
+      <c r="BG269" s="2"/>
+      <c r="BH269" s="2"/>
+      <c r="BI269" s="5"/>
+      <c r="BJ269" s="5"/>
+      <c r="BK269" s="5"/>
+      <c r="BL269" s="2"/>
+      <c r="BM269" s="2"/>
+      <c r="BN269" s="2"/>
+      <c r="BO269" s="2"/>
+      <c r="BP269" s="2"/>
+      <c r="BQ269" s="5"/>
+      <c r="BR269" s="5"/>
+      <c r="BS269" s="5"/>
+    </row>
+    <row r="270" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C270" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G270" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H270" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W270" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X270" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AW270" s="5"/>
+      <c r="BA270" s="5"/>
+      <c r="BB270" s="5"/>
+      <c r="BC270" s="5"/>
+      <c r="BD270" s="2"/>
+      <c r="BE270" s="2"/>
+      <c r="BF270" s="2"/>
+      <c r="BG270" s="2"/>
+      <c r="BH270" s="2"/>
+      <c r="BI270" s="5"/>
+      <c r="BJ270" s="5"/>
+      <c r="BK270" s="5"/>
+      <c r="BL270" s="2"/>
+      <c r="BM270" s="2"/>
+      <c r="BN270" s="2"/>
+      <c r="BO270" s="2"/>
+      <c r="BP270" s="2"/>
+      <c r="BQ270" s="5"/>
+      <c r="BR270" s="5"/>
+      <c r="BS270" s="5"/>
+    </row>
+    <row r="271" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C271" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW271" s="5"/>
+      <c r="BA271" s="5"/>
+      <c r="BB271" s="5"/>
+      <c r="BC271" s="5"/>
+      <c r="BD271" s="2"/>
+      <c r="BE271" s="2"/>
+      <c r="BF271" s="2"/>
+      <c r="BG271" s="2"/>
+      <c r="BH271" s="2"/>
+      <c r="BI271" s="5"/>
+      <c r="BJ271" s="5"/>
+      <c r="BK271" s="5"/>
+      <c r="BL271" s="2"/>
+      <c r="BM271" s="2"/>
+      <c r="BN271" s="2"/>
+      <c r="BO271" s="2"/>
+      <c r="BP271" s="2"/>
+      <c r="BQ271" s="5"/>
+      <c r="BR271" s="5"/>
+      <c r="BS271" s="5"/>
+    </row>
+    <row r="272" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C272" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D272" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G272" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H272" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="W272" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X272" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA272" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB272" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AW272" s="5"/>
+      <c r="BA272" s="5"/>
+      <c r="BB272" s="5"/>
+      <c r="BC272" s="5"/>
+      <c r="BD272" s="2"/>
+      <c r="BE272" s="2"/>
+      <c r="BF272" s="2"/>
+      <c r="BG272" s="2"/>
+      <c r="BH272" s="2"/>
+      <c r="BI272" s="5"/>
+      <c r="BJ272" s="5"/>
+      <c r="BK272" s="5"/>
+      <c r="BL272" s="2"/>
+      <c r="BM272" s="2"/>
+      <c r="BN272" s="2"/>
+      <c r="BO272" s="2"/>
+      <c r="BP272" s="2"/>
+      <c r="BQ272" s="5"/>
+      <c r="BR272" s="3"/>
+      <c r="BS272" s="3"/>
+    </row>
+    <row r="273" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C273" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G273" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H273" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AW273" s="2"/>
+      <c r="BA273" s="2"/>
+      <c r="BB273" s="2"/>
+      <c r="BC273" s="2"/>
+      <c r="BD273" s="2"/>
+      <c r="BE273" s="2"/>
+      <c r="BF273" s="2"/>
+      <c r="BG273" s="2"/>
+      <c r="BH273" s="2"/>
+      <c r="BI273" s="2"/>
+      <c r="BJ273" s="2"/>
+      <c r="BK273" s="2"/>
+      <c r="BL273" s="2"/>
+      <c r="BM273" s="2"/>
+      <c r="BN273" s="2"/>
+      <c r="BO273" s="2"/>
+      <c r="BP273" s="2"/>
+      <c r="BQ273" s="2"/>
+      <c r="BR273" s="2"/>
+      <c r="BS273" s="2"/>
+    </row>
+    <row r="274" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C274" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G274" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H274" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="W274" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X274" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW274" s="2"/>
+      <c r="BA274" s="2"/>
+      <c r="BB274" s="2"/>
+      <c r="BC274" s="2"/>
+      <c r="BD274" s="2"/>
+      <c r="BE274" s="2"/>
+      <c r="BF274" s="2"/>
+      <c r="BG274" s="2"/>
+      <c r="BH274" s="2"/>
+      <c r="BI274" s="2"/>
+      <c r="BJ274" s="2"/>
+      <c r="BK274" s="2"/>
+      <c r="BL274" s="2"/>
+      <c r="BM274" s="2"/>
+      <c r="BN274" s="2"/>
+      <c r="BO274" s="2"/>
+      <c r="BP274" s="2"/>
+      <c r="BQ274" s="2"/>
+      <c r="BR274" s="2"/>
+      <c r="BS274" s="2"/>
+    </row>
+    <row r="275" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C275" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW275" s="2"/>
+      <c r="BA275" s="2"/>
+      <c r="BB275" s="2"/>
+      <c r="BC275" s="2"/>
+      <c r="BD275" s="2"/>
+      <c r="BE275" s="2"/>
+      <c r="BF275" s="2"/>
+      <c r="BG275" s="2"/>
+      <c r="BH275" s="2"/>
+      <c r="BI275" s="2"/>
+      <c r="BJ275" s="2"/>
+      <c r="BK275" s="2"/>
+      <c r="BL275" s="2"/>
+      <c r="BM275" s="2"/>
+      <c r="BN275" s="2"/>
+      <c r="BO275" s="2"/>
+      <c r="BP275" s="2"/>
+      <c r="BQ275" s="2"/>
+      <c r="BR275" s="2"/>
+      <c r="BS275" s="2"/>
+    </row>
+    <row r="276" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C276" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW276" s="2"/>
+      <c r="BA276" s="2"/>
+      <c r="BB276" s="2"/>
+      <c r="BC276" s="2"/>
+      <c r="BD276" s="2"/>
+      <c r="BE276" s="2"/>
+      <c r="BF276" s="2"/>
+      <c r="BG276" s="2"/>
+      <c r="BH276" s="2"/>
+      <c r="BI276" s="2"/>
+      <c r="BJ276" s="2"/>
+      <c r="BK276" s="2"/>
+      <c r="BL276" s="2"/>
+      <c r="BM276" s="2"/>
+      <c r="BN276" s="2"/>
+      <c r="BO276" s="2"/>
+      <c r="BP276" s="2"/>
+      <c r="BQ276" s="2"/>
+      <c r="BR276" s="2"/>
+      <c r="BS276" s="2"/>
+    </row>
+    <row r="277" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C277" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G277" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H277" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="W277" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="X277" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW277" s="2"/>
+      <c r="BA277" s="2"/>
+      <c r="BB277" s="2"/>
+      <c r="BC277" s="2"/>
+      <c r="BD277" s="2"/>
+      <c r="BE277" s="2"/>
+      <c r="BF277" s="2"/>
+      <c r="BG277" s="2"/>
+      <c r="BH277" s="2"/>
+      <c r="BI277" s="2"/>
+      <c r="BJ277" s="2"/>
+      <c r="BK277" s="2"/>
+      <c r="BL277" s="2"/>
+      <c r="BM277" s="2"/>
+      <c r="BN277" s="2"/>
+      <c r="BO277" s="2"/>
+      <c r="BP277" s="2"/>
+      <c r="BQ277" s="2"/>
+      <c r="BR277" s="2"/>
+      <c r="BS277" s="2"/>
+    </row>
+    <row r="278" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C278" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G278" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H278" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AW278" s="2"/>
+      <c r="AX278" s="2"/>
+      <c r="AY278" s="2"/>
+      <c r="AZ278" s="2"/>
+      <c r="BA278" s="2"/>
+      <c r="BB278" s="2"/>
+      <c r="BC278" s="2"/>
+      <c r="BD278" s="2"/>
+      <c r="BE278" s="2"/>
+      <c r="BF278" s="2"/>
+      <c r="BG278" s="2"/>
+      <c r="BH278" s="2"/>
+      <c r="BI278" s="2"/>
+      <c r="BJ278" s="2"/>
+      <c r="BK278" s="2"/>
+      <c r="BL278" s="2"/>
+      <c r="BM278" s="2"/>
+      <c r="BN278" s="2"/>
+      <c r="BO278" s="2"/>
+      <c r="BP278" s="2"/>
+      <c r="BQ278" s="2"/>
+      <c r="BR278" s="2"/>
+      <c r="BS278" s="2"/>
+    </row>
+    <row r="279" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C279" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW279" s="2"/>
+      <c r="AX279" s="2"/>
+      <c r="AY279" s="2"/>
+      <c r="AZ279" s="2"/>
+      <c r="BA279" s="2"/>
+      <c r="BB279" s="2"/>
+      <c r="BC279" s="2"/>
+      <c r="BD279" s="2"/>
+      <c r="BE279" s="2"/>
+      <c r="BF279" s="2"/>
+      <c r="BG279" s="2"/>
+      <c r="BH279" s="2"/>
+      <c r="BI279" s="2"/>
+      <c r="BJ279" s="2"/>
+      <c r="BK279" s="2"/>
+      <c r="BL279" s="2"/>
+      <c r="BM279" s="2"/>
+      <c r="BN279" s="2"/>
+      <c r="BO279" s="2"/>
+      <c r="BP279" s="2"/>
+      <c r="BQ279" s="2"/>
+      <c r="BR279" s="2"/>
+      <c r="BS279" s="2"/>
+    </row>
+    <row r="280" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C280" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW280" s="2"/>
+      <c r="AX280" s="2"/>
+      <c r="AY280" s="2"/>
+      <c r="AZ280" s="2"/>
+      <c r="BA280" s="2"/>
+      <c r="BB280" s="2"/>
+      <c r="BC280" s="2"/>
+      <c r="BD280" s="2"/>
+      <c r="BE280" s="2"/>
+      <c r="BF280" s="2"/>
+      <c r="BG280" s="2"/>
+      <c r="BH280" s="2"/>
+      <c r="BI280" s="2"/>
+      <c r="BJ280" s="2"/>
+      <c r="BK280" s="2"/>
+      <c r="BL280" s="2"/>
+      <c r="BM280" s="2"/>
+      <c r="BN280" s="2"/>
+      <c r="BO280" s="2"/>
+      <c r="BP280" s="2"/>
+      <c r="BQ280" s="2"/>
+      <c r="BR280" s="2"/>
+      <c r="BS280" s="2"/>
+    </row>
+    <row r="281" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="AW281" s="2"/>
+      <c r="AX281" s="2"/>
+      <c r="AY281" s="2"/>
+      <c r="AZ281" s="2"/>
+      <c r="BA281" s="2"/>
+      <c r="BB281" s="2"/>
+      <c r="BC281" s="2"/>
+      <c r="BD281" s="2"/>
+      <c r="BE281" s="2"/>
+      <c r="BF281" s="2"/>
+      <c r="BG281" s="2"/>
+      <c r="BH281" s="2"/>
+      <c r="BI281" s="2"/>
+      <c r="BJ281" s="2"/>
+      <c r="BK281" s="2"/>
+      <c r="BL281" s="2"/>
+      <c r="BM281" s="2"/>
+      <c r="BN281" s="2"/>
+      <c r="BO281" s="2"/>
+      <c r="BP281" s="2"/>
+      <c r="BQ281" s="2"/>
+      <c r="BR281" s="2"/>
+      <c r="BS281" s="2"/>
+    </row>
+    <row r="282" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="B282" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F282" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="V282" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AW282" s="2"/>
+      <c r="BA282" s="2"/>
+      <c r="BB282" s="2"/>
+      <c r="BC282" s="2"/>
+      <c r="BD282" s="2"/>
+      <c r="BE282" s="2"/>
+      <c r="BF282" s="2"/>
+      <c r="BG282" s="2"/>
+      <c r="BH282" s="2"/>
+      <c r="BI282" s="2"/>
+      <c r="BJ282" s="2"/>
+      <c r="BK282" s="2"/>
+      <c r="BL282" s="2"/>
+      <c r="BM282" s="2"/>
+      <c r="BN282" s="2"/>
+      <c r="BO282" s="2"/>
+      <c r="BP282" s="2"/>
+      <c r="BQ282" s="2"/>
+      <c r="BR282" s="2"/>
+      <c r="BS282" s="2"/>
+    </row>
+    <row r="283" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C283" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D283" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="265" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B265" s="1" t="s">
+      <c r="G283" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H283" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="W283" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X283" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW283" s="2"/>
+      <c r="BA283" s="2"/>
+      <c r="BB283" s="2"/>
+      <c r="BC283" s="2"/>
+      <c r="BD283" s="2"/>
+      <c r="BE283" s="2"/>
+      <c r="BF283" s="2"/>
+      <c r="BG283" s="2"/>
+      <c r="BH283" s="2"/>
+      <c r="BI283" s="2"/>
+      <c r="BJ283" s="2"/>
+      <c r="BK283" s="2"/>
+      <c r="BL283" s="2"/>
+      <c r="BM283" s="2"/>
+      <c r="BN283" s="2"/>
+      <c r="BO283" s="2"/>
+      <c r="BP283" s="2"/>
+      <c r="BQ283" s="2"/>
+      <c r="BR283" s="2"/>
+      <c r="BS283" s="2"/>
+    </row>
+    <row r="284" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C284" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G284" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H284" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="W284" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X284" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AW284" s="2"/>
+      <c r="BA284" s="2"/>
+      <c r="BB284" s="2"/>
+      <c r="BC284" s="2"/>
+      <c r="BD284" s="2"/>
+      <c r="BE284" s="2"/>
+      <c r="BF284" s="2"/>
+      <c r="BG284" s="2"/>
+      <c r="BH284" s="2"/>
+      <c r="BI284" s="2"/>
+      <c r="BJ284" s="2"/>
+      <c r="BK284" s="2"/>
+      <c r="BL284" s="2"/>
+      <c r="BM284" s="2"/>
+      <c r="BN284" s="2"/>
+      <c r="BO284" s="2"/>
+      <c r="BP284" s="2"/>
+      <c r="BQ284" s="2"/>
+      <c r="BR284" s="2"/>
+      <c r="BS284" s="2"/>
+    </row>
+    <row r="285" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C285" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="R285" s="10"/>
+      <c r="S285" s="10"/>
+      <c r="AW285" s="2"/>
+      <c r="BA285" s="2"/>
+      <c r="BB285" s="2"/>
+      <c r="BC285" s="2"/>
+      <c r="BD285" s="2"/>
+      <c r="BE285" s="2"/>
+      <c r="BF285" s="2"/>
+      <c r="BG285" s="2"/>
+      <c r="BH285" s="2"/>
+      <c r="BI285" s="2"/>
+      <c r="BJ285" s="2"/>
+      <c r="BK285" s="2"/>
+      <c r="BL285" s="2"/>
+      <c r="BM285" s="2"/>
+      <c r="BN285" s="2"/>
+      <c r="BO285" s="2"/>
+      <c r="BP285" s="2"/>
+      <c r="BQ285" s="2"/>
+      <c r="BR285" s="2"/>
+      <c r="BS285" s="2"/>
+    </row>
+    <row r="286" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C286" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G286" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H286" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R286" s="10"/>
+      <c r="S286" s="10"/>
+      <c r="W286" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X286" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AW286" s="2"/>
+      <c r="BA286" s="2"/>
+      <c r="BB286" s="2"/>
+      <c r="BC286" s="2"/>
+      <c r="BD286" s="2"/>
+      <c r="BE286" s="2"/>
+      <c r="BF286" s="2"/>
+      <c r="BG286" s="2"/>
+      <c r="BH286" s="2"/>
+      <c r="BI286" s="2"/>
+      <c r="BJ286" s="2"/>
+      <c r="BK286" s="2"/>
+      <c r="BL286" s="2"/>
+      <c r="BM286" s="2"/>
+      <c r="BN286" s="2"/>
+      <c r="BO286" s="2"/>
+      <c r="BP286" s="2"/>
+      <c r="BQ286" s="2"/>
+      <c r="BR286" s="2"/>
+      <c r="BS286" s="2"/>
+    </row>
+    <row r="287" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C287" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G287" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H287" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R287" s="10"/>
+      <c r="S287" s="10"/>
+      <c r="AW287" s="2"/>
+      <c r="BA287" s="2"/>
+      <c r="BB287" s="2"/>
+      <c r="BC287" s="2"/>
+      <c r="BD287" s="2"/>
+      <c r="BE287" s="2"/>
+      <c r="BF287" s="2"/>
+      <c r="BG287" s="2"/>
+      <c r="BH287" s="2"/>
+      <c r="BI287" s="2"/>
+      <c r="BJ287" s="2"/>
+      <c r="BK287" s="2"/>
+      <c r="BL287" s="2"/>
+      <c r="BM287" s="2"/>
+      <c r="BN287" s="2"/>
+      <c r="BO287" s="2"/>
+      <c r="BP287" s="2"/>
+      <c r="BQ287" s="2"/>
+      <c r="BR287" s="2"/>
+      <c r="BS287" s="2"/>
+    </row>
+    <row r="288" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C288" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G288" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H288" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="W288" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X288" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW288" s="2"/>
+      <c r="BA288" s="2"/>
+      <c r="BB288" s="2"/>
+      <c r="BC288" s="2"/>
+      <c r="BD288" s="2"/>
+      <c r="BE288" s="2"/>
+      <c r="BF288" s="2"/>
+      <c r="BG288" s="2"/>
+      <c r="BH288" s="2"/>
+      <c r="BI288" s="2"/>
+      <c r="BJ288" s="2"/>
+      <c r="BK288" s="2"/>
+      <c r="BL288" s="2"/>
+      <c r="BM288" s="2"/>
+      <c r="BN288" s="2"/>
+      <c r="BO288" s="2"/>
+      <c r="BP288" s="2"/>
+      <c r="BQ288" s="2"/>
+      <c r="BR288" s="2"/>
+      <c r="BS288" s="2"/>
+    </row>
+    <row r="289" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C289" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F265" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="266" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C266" s="1" t="s">
+      <c r="D289" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G289" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H289" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="W289" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="X289" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AW289" s="2"/>
+      <c r="AY289" s="3"/>
+      <c r="AZ289" s="3"/>
+      <c r="BA289" s="2"/>
+      <c r="BB289" s="2"/>
+      <c r="BC289" s="2"/>
+      <c r="BD289" s="2"/>
+      <c r="BE289" s="2"/>
+      <c r="BF289" s="2"/>
+      <c r="BG289" s="2"/>
+      <c r="BH289" s="2"/>
+      <c r="BI289" s="2"/>
+      <c r="BJ289" s="2"/>
+      <c r="BK289" s="2"/>
+      <c r="BL289" s="2"/>
+      <c r="BM289" s="2"/>
+      <c r="BN289" s="2"/>
+      <c r="BO289" s="2"/>
+      <c r="BP289" s="2"/>
+      <c r="BQ289" s="2"/>
+      <c r="BR289" s="2"/>
+      <c r="BS289" s="2"/>
+    </row>
+    <row r="290" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C290" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW290" s="2"/>
+      <c r="BA290" s="2"/>
+      <c r="BB290" s="2"/>
+      <c r="BC290" s="2"/>
+      <c r="BD290" s="2"/>
+      <c r="BE290" s="2"/>
+      <c r="BF290" s="2"/>
+      <c r="BG290" s="2"/>
+      <c r="BH290" s="2"/>
+      <c r="BI290" s="2"/>
+      <c r="BJ290" s="2"/>
+      <c r="BK290" s="2"/>
+      <c r="BL290" s="2"/>
+      <c r="BM290" s="2"/>
+      <c r="BN290" s="2"/>
+      <c r="BO290" s="2"/>
+      <c r="BP290" s="2"/>
+      <c r="BQ290" s="2"/>
+      <c r="BR290" s="2"/>
+      <c r="BS290" s="2"/>
+    </row>
+    <row r="291" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C291" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW291" s="2"/>
+      <c r="BA291" s="2"/>
+      <c r="BB291" s="2"/>
+      <c r="BC291" s="2"/>
+      <c r="BD291" s="2"/>
+      <c r="BE291" s="2"/>
+      <c r="BF291" s="2"/>
+      <c r="BG291" s="2"/>
+      <c r="BH291" s="2"/>
+      <c r="BI291" s="2"/>
+      <c r="BJ291" s="2"/>
+      <c r="BK291" s="2"/>
+      <c r="BL291" s="2"/>
+      <c r="BM291" s="2"/>
+      <c r="BN291" s="2"/>
+      <c r="BO291" s="2"/>
+      <c r="BP291" s="2"/>
+      <c r="BQ291" s="2"/>
+      <c r="BR291" s="2"/>
+      <c r="BS291" s="2"/>
+    </row>
+    <row r="292" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C292" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G292" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H292" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N292" s="3"/>
+      <c r="O292" s="3"/>
+      <c r="W292" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="X292" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU292" s="3"/>
+      <c r="AV292" s="3"/>
+      <c r="AW292" s="2"/>
+      <c r="BA292" s="2"/>
+      <c r="BB292" s="2"/>
+      <c r="BC292" s="2"/>
+      <c r="BD292" s="2"/>
+      <c r="BE292" s="2"/>
+      <c r="BF292" s="2"/>
+      <c r="BG292" s="2"/>
+      <c r="BH292" s="2"/>
+      <c r="BI292" s="2"/>
+      <c r="BJ292" s="2"/>
+      <c r="BK292" s="2"/>
+      <c r="BL292" s="2"/>
+      <c r="BM292" s="2"/>
+      <c r="BN292" s="2"/>
+      <c r="BO292" s="2"/>
+      <c r="BP292" s="2"/>
+      <c r="BQ292" s="2"/>
+      <c r="BR292" s="2"/>
+      <c r="BS292" s="2"/>
+    </row>
+    <row r="293" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C293" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G293" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H293" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N293" s="3"/>
+      <c r="O293" s="3"/>
+      <c r="AW293" s="2"/>
+      <c r="AX293" s="2"/>
+      <c r="AY293" s="2"/>
+      <c r="AZ293" s="2"/>
+      <c r="BA293" s="2"/>
+      <c r="BB293" s="2"/>
+      <c r="BC293" s="2"/>
+      <c r="BD293" s="2"/>
+      <c r="BE293" s="2"/>
+      <c r="BF293" s="2"/>
+      <c r="BG293" s="2"/>
+      <c r="BH293" s="2"/>
+      <c r="BI293" s="2"/>
+      <c r="BJ293" s="2"/>
+      <c r="BK293" s="2"/>
+      <c r="BL293" s="2"/>
+      <c r="BM293" s="2"/>
+      <c r="BN293" s="2"/>
+      <c r="BO293" s="2"/>
+      <c r="BP293" s="2"/>
+      <c r="BQ293" s="2"/>
+      <c r="BR293" s="2"/>
+      <c r="BS293" s="2"/>
+    </row>
+    <row r="294" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C294" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N294" s="3"/>
+      <c r="O294" s="3"/>
+      <c r="AW294" s="2"/>
+      <c r="AX294" s="2"/>
+      <c r="AY294" s="2"/>
+      <c r="AZ294" s="2"/>
+      <c r="BA294" s="2"/>
+      <c r="BB294" s="2"/>
+      <c r="BC294" s="2"/>
+      <c r="BD294" s="2"/>
+      <c r="BE294" s="2"/>
+      <c r="BF294" s="2"/>
+      <c r="BG294" s="2"/>
+      <c r="BH294" s="2"/>
+      <c r="BI294" s="2"/>
+      <c r="BJ294" s="2"/>
+      <c r="BK294" s="2"/>
+      <c r="BL294" s="2"/>
+      <c r="BM294" s="2"/>
+      <c r="BN294" s="2"/>
+      <c r="BO294" s="2"/>
+      <c r="BP294" s="2"/>
+      <c r="BQ294" s="2"/>
+      <c r="BR294" s="2"/>
+      <c r="BS294" s="2"/>
+    </row>
+    <row r="295" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C295" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N295" s="3"/>
+      <c r="O295" s="3"/>
+      <c r="AW295" s="2"/>
+      <c r="AX295" s="2"/>
+      <c r="AY295" s="2"/>
+      <c r="AZ295" s="2"/>
+      <c r="BA295" s="2"/>
+      <c r="BB295" s="2"/>
+      <c r="BC295" s="2"/>
+      <c r="BD295" s="2"/>
+      <c r="BE295" s="2"/>
+      <c r="BF295" s="2"/>
+      <c r="BG295" s="2"/>
+      <c r="BH295" s="2"/>
+      <c r="BI295" s="2"/>
+      <c r="BJ295" s="2"/>
+      <c r="BK295" s="2"/>
+      <c r="BL295" s="2"/>
+      <c r="BM295" s="2"/>
+      <c r="BN295" s="2"/>
+      <c r="BO295" s="2"/>
+      <c r="BP295" s="2"/>
+      <c r="BQ295" s="2"/>
+      <c r="BR295" s="2"/>
+      <c r="BS295" s="2"/>
+    </row>
+    <row r="296" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="N296" s="3"/>
+      <c r="O296" s="3"/>
+      <c r="AW296" s="2"/>
+      <c r="AX296" s="2"/>
+      <c r="AY296" s="2"/>
+      <c r="AZ296" s="2"/>
+      <c r="BA296" s="2"/>
+      <c r="BB296" s="2"/>
+      <c r="BC296" s="2"/>
+      <c r="BD296" s="2"/>
+      <c r="BE296" s="2"/>
+      <c r="BF296" s="2"/>
+      <c r="BG296" s="2"/>
+      <c r="BH296" s="2"/>
+      <c r="BI296" s="2"/>
+      <c r="BJ296" s="2"/>
+      <c r="BK296" s="2"/>
+      <c r="BL296" s="2"/>
+      <c r="BM296" s="2"/>
+      <c r="BN296" s="2"/>
+      <c r="BO296" s="2"/>
+      <c r="BP296" s="2"/>
+      <c r="BQ296" s="2"/>
+      <c r="BR296" s="2"/>
+      <c r="BS296" s="2"/>
+    </row>
+    <row r="297" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="B297" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F297" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N297" s="3"/>
+      <c r="O297" s="3"/>
+      <c r="V297" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW297" s="2"/>
+      <c r="AX297" s="2"/>
+      <c r="AY297" s="2"/>
+      <c r="AZ297" s="2"/>
+      <c r="BA297" s="2"/>
+      <c r="BB297" s="2"/>
+      <c r="BC297" s="2"/>
+      <c r="BD297" s="2"/>
+      <c r="BE297" s="2"/>
+      <c r="BF297" s="2"/>
+      <c r="BG297" s="2"/>
+      <c r="BH297" s="2"/>
+      <c r="BI297" s="2"/>
+      <c r="BJ297" s="2"/>
+      <c r="BK297" s="2"/>
+      <c r="BL297" s="2"/>
+      <c r="BM297" s="2"/>
+      <c r="BN297" s="2"/>
+      <c r="BO297" s="2"/>
+      <c r="BP297" s="2"/>
+      <c r="BQ297" s="2"/>
+      <c r="BR297" s="2"/>
+      <c r="BS297" s="2"/>
+    </row>
+    <row r="298" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C298" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G298" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H298" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N298" s="3"/>
+      <c r="O298" s="3"/>
+      <c r="W298" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X298" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU298" s="3"/>
+      <c r="AV298" s="3"/>
+      <c r="AW298" s="2"/>
+      <c r="AX298" s="2"/>
+      <c r="AY298" s="2"/>
+      <c r="AZ298" s="2"/>
+      <c r="BA298" s="2"/>
+      <c r="BB298" s="2"/>
+      <c r="BC298" s="2"/>
+      <c r="BD298" s="2"/>
+      <c r="BE298" s="2"/>
+      <c r="BF298" s="2"/>
+      <c r="BG298" s="2"/>
+      <c r="BH298" s="2"/>
+      <c r="BI298" s="2"/>
+      <c r="BJ298" s="2"/>
+      <c r="BK298" s="2"/>
+      <c r="BL298" s="2"/>
+      <c r="BM298" s="2"/>
+      <c r="BN298" s="2"/>
+      <c r="BO298" s="2"/>
+      <c r="BP298" s="2"/>
+      <c r="BQ298" s="2"/>
+      <c r="BR298" s="2"/>
+      <c r="BS298" s="2"/>
+    </row>
+    <row r="299" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C299" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D266" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G266" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="267" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C267" s="1" t="s">
+      <c r="D299" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G299" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H299" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W299" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X299" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AW299" s="2"/>
+      <c r="AX299" s="2"/>
+      <c r="AY299" s="2"/>
+      <c r="AZ299" s="2"/>
+      <c r="BA299" s="2"/>
+      <c r="BB299" s="2"/>
+      <c r="BC299" s="2"/>
+      <c r="BD299" s="2"/>
+      <c r="BE299" s="2"/>
+      <c r="BF299" s="2"/>
+      <c r="BG299" s="2"/>
+      <c r="BH299" s="2"/>
+      <c r="BI299" s="2"/>
+      <c r="BJ299" s="2"/>
+      <c r="BK299" s="2"/>
+      <c r="BL299" s="2"/>
+      <c r="BM299" s="2"/>
+      <c r="BN299" s="2"/>
+      <c r="BO299" s="2"/>
+      <c r="BP299" s="2"/>
+      <c r="BQ299" s="2"/>
+      <c r="BR299" s="2"/>
+      <c r="BS299" s="2"/>
+    </row>
+    <row r="300" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C300" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G300" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H300" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="W300" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X300" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW300" s="2"/>
+      <c r="AX300" s="2"/>
+      <c r="AY300" s="2"/>
+      <c r="AZ300" s="2"/>
+      <c r="BA300" s="2"/>
+      <c r="BB300" s="2"/>
+      <c r="BC300" s="2"/>
+      <c r="BD300" s="2"/>
+      <c r="BE300" s="2"/>
+      <c r="BF300" s="2"/>
+      <c r="BG300" s="2"/>
+      <c r="BH300" s="2"/>
+      <c r="BI300" s="2"/>
+      <c r="BJ300" s="2"/>
+      <c r="BK300" s="2"/>
+      <c r="BL300" s="2"/>
+      <c r="BM300" s="2"/>
+      <c r="BN300" s="2"/>
+      <c r="BO300" s="2"/>
+      <c r="BP300" s="2"/>
+      <c r="BQ300" s="2"/>
+      <c r="BR300" s="2"/>
+      <c r="BS300" s="2"/>
+    </row>
+    <row r="301" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C301" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AW301" s="2"/>
+      <c r="AX301" s="2"/>
+      <c r="AY301" s="2"/>
+      <c r="AZ301" s="2"/>
+      <c r="BA301" s="2"/>
+      <c r="BB301" s="2"/>
+      <c r="BC301" s="2"/>
+      <c r="BD301" s="2"/>
+      <c r="BE301" s="2"/>
+      <c r="BF301" s="2"/>
+      <c r="BG301" s="2"/>
+      <c r="BH301" s="2"/>
+      <c r="BI301" s="2"/>
+      <c r="BJ301" s="2"/>
+      <c r="BK301" s="2"/>
+      <c r="BL301" s="2"/>
+      <c r="BM301" s="2"/>
+      <c r="BN301" s="2"/>
+      <c r="BO301" s="2"/>
+      <c r="BP301" s="2"/>
+      <c r="BQ301" s="2"/>
+      <c r="BR301" s="2"/>
+      <c r="BS301" s="2"/>
+    </row>
+    <row r="302" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C302" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D267" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G267" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="268" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C268" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G268" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="269" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C269" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G269" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="270" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C270" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D270" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G270" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="271" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="G271" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="272" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="G272" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="273" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="G273" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="275" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B275" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="276" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C276" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D276" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F276" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="277" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C277" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G277" s="1" t="s">
+      <c r="D302" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G302" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="278" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C278" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G278" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="279" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C279" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D279" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G279" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="280" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C280" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="281" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C281" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="282" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C282" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="283" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C283" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="284" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C284" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D284" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="285" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C285" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="287" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B287" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F287" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="288" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C288" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D288" s="1" t="s">
+      <c r="H302" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G288" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="289" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C289" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G289" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="290" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C290" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D290" s="1" t="s">
+      <c r="W302" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X302" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="291" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C291" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D291" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="292" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C292" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="293" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C293" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="294" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C294" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="295" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C295" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="296" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C296" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D296" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="297" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C297" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D297" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="298" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C298" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="300" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B300" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F300" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="301" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C301" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G301" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="302" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C302" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G302" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="303" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="AW302" s="2"/>
+      <c r="AX302" s="2"/>
+      <c r="AY302" s="2"/>
+      <c r="AZ302" s="2"/>
+      <c r="BA302" s="2"/>
+      <c r="BB302" s="2"/>
+      <c r="BC302" s="2"/>
+      <c r="BD302" s="2"/>
+      <c r="BE302" s="2"/>
+      <c r="BF302" s="2"/>
+      <c r="BG302" s="2"/>
+      <c r="BH302" s="2"/>
+      <c r="BI302" s="2"/>
+      <c r="BJ302" s="2"/>
+      <c r="BK302" s="2"/>
+      <c r="BL302" s="2"/>
+      <c r="BM302" s="2"/>
+      <c r="BN302" s="2"/>
+      <c r="BO302" s="2"/>
+      <c r="BP302" s="2"/>
+      <c r="BQ302" s="2"/>
+      <c r="BR302" s="2"/>
+      <c r="BS302" s="2"/>
+    </row>
+    <row r="303" spans="2:71" x14ac:dyDescent="0.25">
       <c r="C303" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D303" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G303" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H303" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW303" s="2"/>
+      <c r="AX303" s="2"/>
+      <c r="AY303" s="2"/>
+      <c r="AZ303" s="2"/>
+      <c r="BA303" s="2"/>
+      <c r="BB303" s="2"/>
+      <c r="BC303" s="2"/>
+      <c r="BD303" s="2"/>
+      <c r="BE303" s="2"/>
+      <c r="BF303" s="2"/>
+      <c r="BG303" s="2"/>
+      <c r="BH303" s="2"/>
+      <c r="BI303" s="2"/>
+      <c r="BJ303" s="2"/>
+      <c r="BK303" s="2"/>
+      <c r="BL303" s="2"/>
+      <c r="BM303" s="2"/>
+      <c r="BN303" s="2"/>
+      <c r="BO303" s="2"/>
+      <c r="BP303" s="2"/>
+      <c r="BQ303" s="2"/>
+      <c r="BR303" s="2"/>
+      <c r="BS303" s="2"/>
+    </row>
+    <row r="304" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C304" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G304" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H304" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W304" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X304" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ304" s="3"/>
+      <c r="AR304" s="3"/>
+      <c r="AW304" s="2"/>
+      <c r="AX304" s="2"/>
+      <c r="AY304" s="2"/>
+      <c r="AZ304" s="2"/>
+      <c r="BA304" s="2"/>
+      <c r="BB304" s="2"/>
+      <c r="BC304" s="2"/>
+      <c r="BD304" s="2"/>
+      <c r="BE304" s="2"/>
+      <c r="BF304" s="2"/>
+      <c r="BG304" s="2"/>
+      <c r="BH304" s="2"/>
+      <c r="BI304" s="2"/>
+      <c r="BJ304" s="2"/>
+      <c r="BK304" s="2"/>
+      <c r="BL304" s="2"/>
+      <c r="BM304" s="2"/>
+      <c r="BN304" s="2"/>
+      <c r="BO304" s="2"/>
+      <c r="BP304" s="2"/>
+      <c r="BQ304" s="2"/>
+      <c r="BR304" s="2"/>
+      <c r="BS304" s="2"/>
+    </row>
+    <row r="305" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C305" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G305" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H305" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="W305" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="X305" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH305" s="3"/>
+      <c r="AI305" s="3"/>
+      <c r="AW305" s="2"/>
+      <c r="AX305" s="2"/>
+      <c r="AY305" s="2"/>
+      <c r="AZ305" s="2"/>
+      <c r="BA305" s="2"/>
+      <c r="BB305" s="2"/>
+      <c r="BC305" s="2"/>
+      <c r="BD305" s="2"/>
+      <c r="BE305" s="2"/>
+      <c r="BF305" s="2"/>
+      <c r="BG305" s="2"/>
+      <c r="BH305" s="2"/>
+      <c r="BI305" s="2"/>
+      <c r="BJ305" s="2"/>
+      <c r="BK305" s="2"/>
+      <c r="BL305" s="2"/>
+      <c r="BM305" s="2"/>
+      <c r="BN305" s="2"/>
+      <c r="BO305" s="2"/>
+      <c r="BP305" s="2"/>
+      <c r="BQ305" s="2"/>
+      <c r="BR305" s="2"/>
+      <c r="BS305" s="2"/>
+    </row>
+    <row r="306" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C306" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH306" s="3"/>
+      <c r="AI306" s="3"/>
+      <c r="AW306" s="2"/>
+      <c r="AX306" s="2"/>
+      <c r="AY306" s="2"/>
+      <c r="AZ306" s="2"/>
+      <c r="BA306" s="2"/>
+      <c r="BB306" s="2"/>
+      <c r="BC306" s="2"/>
+      <c r="BD306" s="2"/>
+      <c r="BE306" s="2"/>
+      <c r="BF306" s="2"/>
+      <c r="BG306" s="2"/>
+      <c r="BH306" s="2"/>
+      <c r="BI306" s="2"/>
+      <c r="BJ306" s="2"/>
+      <c r="BK306" s="2"/>
+      <c r="BL306" s="2"/>
+      <c r="BM306" s="2"/>
+      <c r="BN306" s="2"/>
+      <c r="BO306" s="2"/>
+      <c r="BP306" s="2"/>
+      <c r="BQ306" s="2"/>
+      <c r="BR306" s="2"/>
+      <c r="BS306" s="2"/>
+    </row>
+    <row r="307" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C307" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH307" s="3"/>
+      <c r="AI307" s="3"/>
+      <c r="AW307" s="2"/>
+      <c r="AX307" s="2"/>
+      <c r="AY307" s="2"/>
+      <c r="AZ307" s="2"/>
+      <c r="BA307" s="2"/>
+      <c r="BB307" s="2"/>
+      <c r="BC307" s="2"/>
+      <c r="BD307" s="2"/>
+      <c r="BE307" s="2"/>
+      <c r="BF307" s="2"/>
+      <c r="BG307" s="2"/>
+      <c r="BH307" s="2"/>
+      <c r="BI307" s="2"/>
+      <c r="BJ307" s="2"/>
+      <c r="BK307" s="2"/>
+      <c r="BL307" s="2"/>
+      <c r="BM307" s="2"/>
+      <c r="BN307" s="2"/>
+      <c r="BO307" s="2"/>
+      <c r="BP307" s="2"/>
+      <c r="BQ307" s="2"/>
+      <c r="BR307" s="2"/>
+      <c r="BS307" s="2"/>
+    </row>
+    <row r="308" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C308" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH308" s="3"/>
+      <c r="AI308" s="3"/>
+      <c r="AW308" s="2"/>
+      <c r="AX308" s="2"/>
+      <c r="AY308" s="2"/>
+      <c r="AZ308" s="2"/>
+      <c r="BA308" s="2"/>
+      <c r="BB308" s="2"/>
+      <c r="BC308" s="2"/>
+      <c r="BD308" s="2"/>
+      <c r="BE308" s="2"/>
+      <c r="BF308" s="2"/>
+      <c r="BG308" s="2"/>
+      <c r="BH308" s="2"/>
+      <c r="BI308" s="2"/>
+      <c r="BJ308" s="2"/>
+      <c r="BK308" s="2"/>
+      <c r="BL308" s="2"/>
+      <c r="BM308" s="2"/>
+      <c r="BN308" s="2"/>
+      <c r="BO308" s="2"/>
+      <c r="BP308" s="2"/>
+      <c r="BQ308" s="2"/>
+      <c r="BR308" s="2"/>
+      <c r="BS308" s="2"/>
+    </row>
+    <row r="309" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C309" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G309" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H309" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH309" s="3"/>
+      <c r="AI309" s="3"/>
+      <c r="AW309" s="2"/>
+      <c r="AX309" s="2"/>
+      <c r="AY309" s="2"/>
+      <c r="AZ309" s="2"/>
+      <c r="BA309" s="2"/>
+      <c r="BB309" s="2"/>
+      <c r="BC309" s="2"/>
+      <c r="BD309" s="2"/>
+      <c r="BE309" s="2"/>
+      <c r="BF309" s="2"/>
+      <c r="BG309" s="2"/>
+      <c r="BH309" s="2"/>
+      <c r="BI309" s="2"/>
+      <c r="BJ309" s="2"/>
+      <c r="BK309" s="2"/>
+      <c r="BL309" s="2"/>
+      <c r="BM309" s="2"/>
+      <c r="BN309" s="2"/>
+      <c r="BO309" s="2"/>
+      <c r="BP309" s="2"/>
+      <c r="BQ309" s="2"/>
+      <c r="BR309" s="2"/>
+      <c r="BS309" s="2"/>
+    </row>
+    <row r="310" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C310" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="V310" s="3"/>
+      <c r="W310" s="3"/>
+      <c r="AH310" s="3"/>
+      <c r="AI310" s="3"/>
+      <c r="AW310" s="2"/>
+      <c r="AX310" s="2"/>
+      <c r="AY310" s="2"/>
+      <c r="AZ310" s="2"/>
+      <c r="BA310" s="2"/>
+      <c r="BB310" s="2"/>
+      <c r="BC310" s="2"/>
+      <c r="BD310" s="2"/>
+      <c r="BE310" s="2"/>
+      <c r="BF310" s="2"/>
+      <c r="BG310" s="2"/>
+      <c r="BH310" s="2"/>
+      <c r="BI310" s="2"/>
+      <c r="BJ310" s="2"/>
+      <c r="BK310" s="2"/>
+      <c r="BL310" s="2"/>
+      <c r="BM310" s="2"/>
+      <c r="BN310" s="2"/>
+      <c r="BO310" s="2"/>
+      <c r="BP310" s="2"/>
+      <c r="BQ310" s="2"/>
+      <c r="BR310" s="2"/>
+      <c r="BS310" s="2"/>
+    </row>
+    <row r="311" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="V311" s="3"/>
+      <c r="W311" s="3"/>
+      <c r="AH311" s="3"/>
+      <c r="AI311" s="3"/>
+      <c r="AW311" s="2"/>
+      <c r="AX311" s="2"/>
+      <c r="AY311" s="2"/>
+      <c r="AZ311" s="2"/>
+      <c r="BA311" s="2"/>
+      <c r="BB311" s="2"/>
+      <c r="BC311" s="2"/>
+      <c r="BD311" s="2"/>
+      <c r="BE311" s="2"/>
+      <c r="BF311" s="2"/>
+      <c r="BG311" s="2"/>
+      <c r="BH311" s="2"/>
+      <c r="BI311" s="2"/>
+      <c r="BJ311" s="2"/>
+      <c r="BK311" s="2"/>
+      <c r="BL311" s="2"/>
+      <c r="BM311" s="2"/>
+      <c r="BN311" s="2"/>
+      <c r="BO311" s="2"/>
+      <c r="BP311" s="2"/>
+      <c r="BQ311" s="2"/>
+      <c r="BR311" s="2"/>
+      <c r="BS311" s="2"/>
+    </row>
+    <row r="312" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="B312" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F312" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V312" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW312" s="2"/>
+      <c r="AX312" s="2"/>
+      <c r="AY312" s="2"/>
+      <c r="AZ312" s="2"/>
+      <c r="BA312" s="2"/>
+      <c r="BB312" s="2"/>
+      <c r="BC312" s="2"/>
+      <c r="BD312" s="2"/>
+      <c r="BE312" s="2"/>
+      <c r="BF312" s="2"/>
+      <c r="BG312" s="2"/>
+      <c r="BH312" s="2"/>
+      <c r="BI312" s="2"/>
+      <c r="BJ312" s="2"/>
+      <c r="BK312" s="2"/>
+      <c r="BL312" s="2"/>
+      <c r="BM312" s="2"/>
+      <c r="BN312" s="2"/>
+      <c r="BO312" s="2"/>
+      <c r="BP312" s="2"/>
+      <c r="BQ312" s="2"/>
+      <c r="BR312" s="2"/>
+      <c r="BS312" s="2"/>
+    </row>
+    <row r="313" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C313" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D313" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G303" s="1" t="s">
+      <c r="G313" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H313" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="W313" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X313" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW313" s="2"/>
+      <c r="AX313" s="2"/>
+      <c r="AY313" s="2"/>
+      <c r="AZ313" s="2"/>
+      <c r="BA313" s="2"/>
+      <c r="BB313" s="2"/>
+      <c r="BC313" s="2"/>
+      <c r="BD313" s="2"/>
+      <c r="BE313" s="2"/>
+      <c r="BF313" s="2"/>
+      <c r="BG313" s="2"/>
+      <c r="BH313" s="2"/>
+      <c r="BI313" s="2"/>
+      <c r="BJ313" s="2"/>
+      <c r="BK313" s="2"/>
+      <c r="BL313" s="2"/>
+      <c r="BM313" s="2"/>
+      <c r="BN313" s="2"/>
+      <c r="BO313" s="2"/>
+      <c r="BP313" s="2"/>
+      <c r="BQ313" s="2"/>
+      <c r="BR313" s="2"/>
+      <c r="BS313" s="2"/>
+    </row>
+    <row r="314" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C314" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G314" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H314" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="W314" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X314" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM314" s="3"/>
+      <c r="AN314" s="3"/>
+      <c r="AW314" s="2"/>
+      <c r="AX314" s="2"/>
+      <c r="AY314" s="2"/>
+      <c r="AZ314" s="2"/>
+      <c r="BA314" s="2"/>
+      <c r="BB314" s="2"/>
+      <c r="BC314" s="2"/>
+      <c r="BD314" s="2"/>
+      <c r="BE314" s="2"/>
+      <c r="BF314" s="2"/>
+      <c r="BG314" s="2"/>
+      <c r="BH314" s="2"/>
+      <c r="BI314" s="2"/>
+      <c r="BJ314" s="2"/>
+      <c r="BK314" s="2"/>
+      <c r="BL314" s="2"/>
+      <c r="BM314" s="2"/>
+      <c r="BN314" s="2"/>
+      <c r="BO314" s="2"/>
+      <c r="BP314" s="2"/>
+      <c r="BQ314" s="2"/>
+      <c r="BR314" s="2"/>
+      <c r="BS314" s="2"/>
+    </row>
+    <row r="315" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C315" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G315" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H315" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="W315" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X315" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH315" s="3"/>
+      <c r="AI315" s="3"/>
+      <c r="AL315" s="3"/>
+      <c r="AM315" s="3"/>
+      <c r="AP315" s="3"/>
+      <c r="AQ315" s="3"/>
+      <c r="AW315" s="2"/>
+      <c r="AX315" s="2"/>
+      <c r="AY315" s="2"/>
+      <c r="AZ315" s="2"/>
+      <c r="BA315" s="2"/>
+      <c r="BB315" s="2"/>
+      <c r="BC315" s="2"/>
+      <c r="BD315" s="2"/>
+      <c r="BE315" s="2"/>
+      <c r="BF315" s="2"/>
+      <c r="BG315" s="2"/>
+      <c r="BH315" s="2"/>
+      <c r="BI315" s="2"/>
+      <c r="BJ315" s="2"/>
+      <c r="BK315" s="2"/>
+      <c r="BL315" s="2"/>
+      <c r="BM315" s="2"/>
+      <c r="BN315" s="2"/>
+      <c r="BO315" s="2"/>
+      <c r="BP315" s="2"/>
+      <c r="BQ315" s="2"/>
+      <c r="BR315" s="2"/>
+      <c r="BS315" s="2"/>
+    </row>
+    <row r="316" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C316" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH316" s="3"/>
+      <c r="AI316" s="3"/>
+      <c r="AL316" s="3"/>
+      <c r="AM316" s="3"/>
+      <c r="AP316" s="3"/>
+      <c r="AQ316" s="3"/>
+      <c r="AW316" s="2"/>
+      <c r="AX316" s="2"/>
+      <c r="AY316" s="2"/>
+      <c r="AZ316" s="2"/>
+      <c r="BA316" s="2"/>
+      <c r="BB316" s="2"/>
+      <c r="BC316" s="2"/>
+      <c r="BD316" s="2"/>
+      <c r="BE316" s="2"/>
+      <c r="BF316" s="2"/>
+      <c r="BG316" s="2"/>
+      <c r="BH316" s="2"/>
+      <c r="BI316" s="2"/>
+      <c r="BJ316" s="2"/>
+      <c r="BK316" s="2"/>
+      <c r="BL316" s="2"/>
+      <c r="BM316" s="2"/>
+      <c r="BN316" s="2"/>
+      <c r="BO316" s="2"/>
+      <c r="BP316" s="2"/>
+      <c r="BQ316" s="2"/>
+      <c r="BR316" s="2"/>
+      <c r="BS316" s="2"/>
+    </row>
+    <row r="317" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C317" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="304" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C304" s="1" t="s">
+      <c r="D317" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G317" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H317" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="W317" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X317" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH317" s="3"/>
+      <c r="AI317" s="3"/>
+      <c r="AL317" s="3"/>
+      <c r="AM317" s="3"/>
+      <c r="AP317" s="3"/>
+      <c r="AQ317" s="3"/>
+      <c r="AW317" s="2"/>
+      <c r="AX317" s="2"/>
+      <c r="AY317" s="2"/>
+      <c r="AZ317" s="2"/>
+      <c r="BA317" s="2"/>
+      <c r="BB317" s="2"/>
+      <c r="BC317" s="2"/>
+      <c r="BD317" s="2"/>
+      <c r="BE317" s="2"/>
+      <c r="BF317" s="2"/>
+      <c r="BG317" s="2"/>
+      <c r="BH317" s="2"/>
+      <c r="BI317" s="2"/>
+      <c r="BJ317" s="2"/>
+      <c r="BK317" s="2"/>
+      <c r="BL317" s="2"/>
+      <c r="BM317" s="2"/>
+      <c r="BN317" s="2"/>
+      <c r="BO317" s="2"/>
+      <c r="BP317" s="2"/>
+      <c r="BQ317" s="2"/>
+      <c r="BR317" s="2"/>
+      <c r="BS317" s="2"/>
+    </row>
+    <row r="318" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C318" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G318" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H318" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH318" s="3"/>
+      <c r="AI318" s="3"/>
+      <c r="AL318" s="3"/>
+      <c r="AM318" s="3"/>
+      <c r="AP318" s="3"/>
+      <c r="AQ318" s="3"/>
+      <c r="AW318" s="2"/>
+      <c r="AX318" s="2"/>
+      <c r="AY318" s="2"/>
+      <c r="AZ318" s="2"/>
+      <c r="BA318" s="2"/>
+      <c r="BB318" s="2"/>
+      <c r="BC318" s="2"/>
+      <c r="BD318" s="2"/>
+      <c r="BE318" s="2"/>
+      <c r="BF318" s="2"/>
+      <c r="BG318" s="2"/>
+      <c r="BH318" s="2"/>
+      <c r="BI318" s="2"/>
+      <c r="BJ318" s="2"/>
+      <c r="BK318" s="2"/>
+      <c r="BL318" s="2"/>
+      <c r="BM318" s="2"/>
+      <c r="BN318" s="2"/>
+      <c r="BO318" s="2"/>
+      <c r="BP318" s="2"/>
+      <c r="BQ318" s="2"/>
+      <c r="BR318" s="2"/>
+      <c r="BS318" s="2"/>
+    </row>
+    <row r="319" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C319" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D304" s="1" t="s">
+      <c r="D319" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G304" s="1" t="s">
+      <c r="G319" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H319" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="W319" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="X319" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH319" s="3"/>
+      <c r="AI319" s="3"/>
+      <c r="AL319" s="3"/>
+      <c r="AM319" s="3"/>
+      <c r="AP319" s="3"/>
+      <c r="AQ319" s="3"/>
+      <c r="AW319" s="2"/>
+      <c r="AX319" s="2"/>
+      <c r="AY319" s="2"/>
+      <c r="AZ319" s="2"/>
+      <c r="BA319" s="2"/>
+      <c r="BB319" s="2"/>
+      <c r="BC319" s="2"/>
+      <c r="BD319" s="2"/>
+      <c r="BE319" s="2"/>
+      <c r="BF319" s="2"/>
+      <c r="BG319" s="2"/>
+      <c r="BH319" s="2"/>
+      <c r="BI319" s="2"/>
+      <c r="BJ319" s="2"/>
+      <c r="BK319" s="2"/>
+      <c r="BL319" s="2"/>
+      <c r="BM319" s="2"/>
+      <c r="BN319" s="2"/>
+      <c r="BO319" s="2"/>
+      <c r="BP319" s="2"/>
+      <c r="BQ319" s="2"/>
+      <c r="BR319" s="2"/>
+      <c r="BS319" s="2"/>
+    </row>
+    <row r="320" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C320" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="305" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C305" s="1" t="s">
+      <c r="D320" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH320" s="3"/>
+      <c r="AI320" s="3"/>
+      <c r="AL320" s="3"/>
+      <c r="AM320" s="3"/>
+      <c r="AP320" s="3"/>
+      <c r="AQ320" s="3"/>
+      <c r="AW320" s="2"/>
+      <c r="AX320" s="2"/>
+      <c r="AY320" s="2"/>
+      <c r="AZ320" s="2"/>
+      <c r="BA320" s="2"/>
+      <c r="BB320" s="2"/>
+      <c r="BC320" s="2"/>
+      <c r="BD320" s="2"/>
+      <c r="BE320" s="2"/>
+      <c r="BF320" s="2"/>
+      <c r="BG320" s="2"/>
+      <c r="BH320" s="2"/>
+      <c r="BI320" s="2"/>
+      <c r="BJ320" s="2"/>
+      <c r="BK320" s="2"/>
+      <c r="BL320" s="2"/>
+      <c r="BM320" s="2"/>
+      <c r="BN320" s="2"/>
+      <c r="BO320" s="2"/>
+      <c r="BP320" s="2"/>
+      <c r="BQ320" s="2"/>
+      <c r="BR320" s="2"/>
+      <c r="BS320" s="2"/>
+    </row>
+    <row r="321" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C321" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH321" s="3"/>
+      <c r="AI321" s="3"/>
+      <c r="AL321" s="3"/>
+      <c r="AM321" s="3"/>
+      <c r="AP321" s="3"/>
+      <c r="AQ321" s="3"/>
+      <c r="AW321" s="2"/>
+      <c r="AX321" s="2"/>
+      <c r="AY321" s="2"/>
+      <c r="AZ321" s="2"/>
+      <c r="BA321" s="2"/>
+      <c r="BB321" s="2"/>
+      <c r="BC321" s="2"/>
+      <c r="BD321" s="2"/>
+      <c r="BE321" s="2"/>
+      <c r="BF321" s="2"/>
+      <c r="BG321" s="2"/>
+      <c r="BH321" s="2"/>
+      <c r="BI321" s="2"/>
+      <c r="BJ321" s="2"/>
+      <c r="BK321" s="2"/>
+      <c r="BL321" s="2"/>
+      <c r="BM321" s="2"/>
+      <c r="BN321" s="2"/>
+      <c r="BO321" s="2"/>
+      <c r="BP321" s="2"/>
+      <c r="BQ321" s="2"/>
+      <c r="BR321" s="2"/>
+      <c r="BS321" s="2"/>
+    </row>
+    <row r="322" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C322" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH322" s="3"/>
+      <c r="AI322" s="3"/>
+      <c r="AL322" s="3"/>
+      <c r="AM322" s="3"/>
+      <c r="AP322" s="3"/>
+      <c r="AQ322" s="3"/>
+      <c r="AW322" s="2"/>
+      <c r="AX322" s="2"/>
+      <c r="AY322" s="2"/>
+      <c r="AZ322" s="2"/>
+      <c r="BA322" s="2"/>
+      <c r="BB322" s="2"/>
+      <c r="BC322" s="2"/>
+      <c r="BD322" s="2"/>
+      <c r="BE322" s="2"/>
+      <c r="BF322" s="2"/>
+      <c r="BG322" s="2"/>
+      <c r="BH322" s="2"/>
+      <c r="BI322" s="2"/>
+      <c r="BJ322" s="2"/>
+      <c r="BK322" s="2"/>
+      <c r="BL322" s="2"/>
+      <c r="BM322" s="2"/>
+      <c r="BN322" s="2"/>
+      <c r="BO322" s="2"/>
+      <c r="BP322" s="2"/>
+      <c r="BQ322" s="2"/>
+      <c r="BR322" s="2"/>
+      <c r="BS322" s="2"/>
+    </row>
+    <row r="323" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C323" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D305" s="1" t="s">
+      <c r="D323" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G305" s="1" t="s">
+      <c r="G323" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H323" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="W323" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="X323" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH323" s="3"/>
+      <c r="AL323" s="3"/>
+      <c r="AP323" s="3"/>
+      <c r="AQ323" s="3"/>
+      <c r="AR323" s="3"/>
+      <c r="AW323" s="2"/>
+      <c r="AX323" s="2"/>
+      <c r="AY323" s="2"/>
+      <c r="AZ323" s="2"/>
+      <c r="BA323" s="2"/>
+      <c r="BB323" s="2"/>
+      <c r="BC323" s="2"/>
+      <c r="BD323" s="2"/>
+      <c r="BE323" s="2"/>
+      <c r="BF323" s="2"/>
+      <c r="BG323" s="2"/>
+      <c r="BH323" s="2"/>
+      <c r="BI323" s="2"/>
+      <c r="BJ323" s="2"/>
+      <c r="BK323" s="2"/>
+      <c r="BL323" s="2"/>
+      <c r="BM323" s="2"/>
+      <c r="BN323" s="2"/>
+      <c r="BO323" s="2"/>
+      <c r="BP323" s="2"/>
+      <c r="BQ323" s="2"/>
+      <c r="BR323" s="2"/>
+      <c r="BS323" s="2"/>
+    </row>
+    <row r="324" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C324" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G324" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H324" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z324" s="3"/>
+      <c r="AA324" s="3"/>
+      <c r="AL324" s="3"/>
+      <c r="AM324" s="3"/>
+      <c r="AW324" s="2"/>
+      <c r="AX324" s="2"/>
+      <c r="AY324" s="2"/>
+      <c r="AZ324" s="2"/>
+      <c r="BA324" s="2"/>
+      <c r="BB324" s="2"/>
+      <c r="BC324" s="2"/>
+      <c r="BD324" s="2"/>
+      <c r="BE324" s="2"/>
+      <c r="BF324" s="2"/>
+      <c r="BG324" s="2"/>
+      <c r="BH324" s="2"/>
+      <c r="BI324" s="2"/>
+      <c r="BJ324" s="2"/>
+      <c r="BK324" s="2"/>
+      <c r="BL324" s="2"/>
+      <c r="BM324" s="2"/>
+      <c r="BN324" s="2"/>
+      <c r="BO324" s="2"/>
+      <c r="BP324" s="2"/>
+      <c r="BQ324" s="2"/>
+      <c r="BR324" s="2"/>
+      <c r="BS324" s="2"/>
+    </row>
+    <row r="325" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C325" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z325" s="3"/>
+      <c r="AA325" s="3"/>
+      <c r="AL325" s="3"/>
+      <c r="AM325" s="3"/>
+      <c r="AW325" s="2"/>
+      <c r="AX325" s="2"/>
+      <c r="AY325" s="2"/>
+      <c r="AZ325" s="2"/>
+      <c r="BA325" s="2"/>
+      <c r="BB325" s="2"/>
+      <c r="BC325" s="2"/>
+      <c r="BD325" s="2"/>
+      <c r="BE325" s="2"/>
+      <c r="BF325" s="2"/>
+      <c r="BG325" s="2"/>
+      <c r="BH325" s="2"/>
+      <c r="BI325" s="2"/>
+      <c r="BJ325" s="2"/>
+      <c r="BK325" s="2"/>
+      <c r="BL325" s="2"/>
+      <c r="BM325" s="2"/>
+      <c r="BN325" s="2"/>
+      <c r="BO325" s="2"/>
+      <c r="BP325" s="2"/>
+      <c r="BQ325" s="2"/>
+      <c r="BR325" s="2"/>
+      <c r="BS325" s="2"/>
+    </row>
+    <row r="326" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="Z326" s="3"/>
+      <c r="AA326" s="3"/>
+      <c r="AL326" s="3"/>
+      <c r="AM326" s="3"/>
+      <c r="AW326" s="2"/>
+      <c r="AX326" s="2"/>
+      <c r="AY326" s="2"/>
+      <c r="AZ326" s="2"/>
+      <c r="BA326" s="2"/>
+      <c r="BB326" s="2"/>
+      <c r="BC326" s="2"/>
+      <c r="BD326" s="2"/>
+      <c r="BE326" s="2"/>
+      <c r="BF326" s="2"/>
+      <c r="BG326" s="2"/>
+      <c r="BH326" s="2"/>
+      <c r="BI326" s="2"/>
+      <c r="BJ326" s="2"/>
+      <c r="BK326" s="2"/>
+      <c r="BL326" s="2"/>
+      <c r="BM326" s="2"/>
+      <c r="BN326" s="2"/>
+      <c r="BO326" s="2"/>
+      <c r="BP326" s="2"/>
+      <c r="BQ326" s="2"/>
+      <c r="BR326" s="2"/>
+      <c r="BS326" s="2"/>
+    </row>
+    <row r="327" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="B327" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F327" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V327" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW327" s="5"/>
+      <c r="AX327" s="5"/>
+      <c r="AY327" s="5"/>
+      <c r="AZ327" s="5"/>
+      <c r="BA327" s="5"/>
+      <c r="BB327" s="5"/>
+      <c r="BC327" s="5"/>
+      <c r="BD327" s="5"/>
+      <c r="BE327" s="5"/>
+      <c r="BF327" s="2"/>
+      <c r="BG327" s="2"/>
+      <c r="BH327" s="2"/>
+      <c r="BI327" s="2"/>
+      <c r="BJ327" s="2"/>
+      <c r="BK327" s="2"/>
+      <c r="BL327" s="2"/>
+      <c r="BM327" s="2"/>
+      <c r="BN327" s="2"/>
+      <c r="BO327" s="2"/>
+      <c r="BP327" s="2"/>
+      <c r="BQ327" s="2"/>
+      <c r="BR327" s="2"/>
+      <c r="BS327" s="2"/>
+    </row>
+    <row r="328" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C328" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G328" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H328" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W328" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X328" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW328" s="5"/>
+      <c r="AX328" s="5"/>
+      <c r="AY328" s="5"/>
+      <c r="AZ328" s="5"/>
+      <c r="BA328" s="5"/>
+      <c r="BB328" s="5"/>
+      <c r="BC328" s="5"/>
+      <c r="BD328" s="5"/>
+      <c r="BE328" s="5"/>
+      <c r="BF328" s="2"/>
+      <c r="BG328" s="2"/>
+      <c r="BH328" s="2"/>
+      <c r="BI328" s="2"/>
+      <c r="BJ328" s="2"/>
+      <c r="BK328" s="2"/>
+      <c r="BL328" s="2"/>
+      <c r="BM328" s="2"/>
+      <c r="BN328" s="2"/>
+      <c r="BO328" s="2"/>
+      <c r="BP328" s="2"/>
+      <c r="BQ328" s="2"/>
+      <c r="BR328" s="2"/>
+      <c r="BS328" s="2"/>
+    </row>
+    <row r="329" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C329" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G329" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H329" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W329" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X329" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW329" s="5"/>
+      <c r="AX329" s="5"/>
+      <c r="AY329" s="5"/>
+      <c r="AZ329" s="5"/>
+      <c r="BA329" s="5"/>
+      <c r="BB329" s="5"/>
+      <c r="BC329" s="5"/>
+      <c r="BD329" s="5"/>
+      <c r="BE329" s="5"/>
+      <c r="BF329" s="2"/>
+      <c r="BG329" s="2"/>
+      <c r="BH329" s="2"/>
+      <c r="BI329" s="2"/>
+      <c r="BJ329" s="2"/>
+      <c r="BK329" s="2"/>
+      <c r="BL329" s="2"/>
+      <c r="BM329" s="2"/>
+      <c r="BN329" s="2"/>
+      <c r="BO329" s="2"/>
+      <c r="BP329" s="2"/>
+      <c r="BQ329" s="2"/>
+      <c r="BR329" s="2"/>
+      <c r="BS329" s="2"/>
+    </row>
+    <row r="330" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C330" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW330" s="5"/>
+      <c r="AX330" s="5"/>
+      <c r="AY330" s="5"/>
+      <c r="AZ330" s="5"/>
+      <c r="BA330" s="5"/>
+      <c r="BB330" s="5"/>
+      <c r="BC330" s="5"/>
+      <c r="BD330" s="5"/>
+      <c r="BE330" s="5"/>
+      <c r="BF330" s="3"/>
+      <c r="BG330" s="3"/>
+      <c r="BH330" s="3"/>
+      <c r="BI330" s="3"/>
+      <c r="BJ330" s="3"/>
+      <c r="BK330" s="3"/>
+      <c r="BL330" s="3"/>
+      <c r="BM330" s="3"/>
+      <c r="BN330" s="3"/>
+      <c r="BO330" s="3"/>
+      <c r="BP330" s="3"/>
+      <c r="BQ330" s="3"/>
+      <c r="BR330" s="3"/>
+      <c r="BS330" s="3"/>
+    </row>
+    <row r="331" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C331" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G331" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H331" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W331" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X331" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW331" s="5"/>
+      <c r="AX331" s="5"/>
+      <c r="AY331" s="5"/>
+      <c r="AZ331" s="5"/>
+      <c r="BA331" s="5"/>
+      <c r="BB331" s="5"/>
+      <c r="BC331" s="5"/>
+      <c r="BD331" s="5"/>
+      <c r="BE331" s="5"/>
+      <c r="BF331" s="2"/>
+      <c r="BG331" s="2"/>
+      <c r="BH331" s="2"/>
+      <c r="BI331" s="2"/>
+      <c r="BJ331" s="2"/>
+      <c r="BK331" s="2"/>
+      <c r="BL331" s="2"/>
+      <c r="BM331" s="2"/>
+      <c r="BN331" s="2"/>
+      <c r="BO331" s="2"/>
+      <c r="BP331" s="2"/>
+      <c r="BQ331" s="2"/>
+      <c r="BR331" s="2"/>
+      <c r="BS331" s="2"/>
+    </row>
+    <row r="332" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C332" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G332" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H332" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW332" s="5"/>
+      <c r="AX332" s="5"/>
+      <c r="AY332" s="5"/>
+      <c r="AZ332" s="5"/>
+      <c r="BA332" s="5"/>
+      <c r="BB332" s="5"/>
+      <c r="BC332" s="5"/>
+      <c r="BD332" s="5"/>
+      <c r="BE332" s="5"/>
+      <c r="BF332" s="2"/>
+      <c r="BG332" s="2"/>
+      <c r="BH332" s="2"/>
+      <c r="BI332" s="2"/>
+      <c r="BJ332" s="2"/>
+      <c r="BK332" s="2"/>
+      <c r="BL332" s="2"/>
+      <c r="BM332" s="2"/>
+      <c r="BN332" s="2"/>
+      <c r="BO332" s="2"/>
+      <c r="BP332" s="2"/>
+      <c r="BQ332" s="2"/>
+      <c r="BR332" s="2"/>
+      <c r="BS332" s="2"/>
+    </row>
+    <row r="333" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C333" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G333" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H333" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W333" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X333" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM333" s="3"/>
+      <c r="AN333" s="3"/>
+      <c r="AW333" s="5"/>
+      <c r="AX333" s="5"/>
+      <c r="AY333" s="5"/>
+      <c r="AZ333" s="5"/>
+      <c r="BA333" s="5"/>
+      <c r="BB333" s="5"/>
+      <c r="BC333" s="5"/>
+      <c r="BD333" s="5"/>
+      <c r="BE333" s="5"/>
+      <c r="BF333" s="2"/>
+      <c r="BG333" s="2"/>
+      <c r="BH333" s="2"/>
+      <c r="BI333" s="2"/>
+      <c r="BJ333" s="2"/>
+      <c r="BK333" s="2"/>
+      <c r="BL333" s="2"/>
+      <c r="BM333" s="2"/>
+      <c r="BN333" s="2"/>
+      <c r="BO333" s="2"/>
+      <c r="BP333" s="2"/>
+      <c r="BQ333" s="2"/>
+      <c r="BR333" s="2"/>
+      <c r="BS333" s="2"/>
+    </row>
+    <row r="334" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C334" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G334" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H334" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W334" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="X334" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW334" s="5"/>
+      <c r="AX334" s="5"/>
+      <c r="AY334" s="5"/>
+      <c r="AZ334" s="5"/>
+      <c r="BA334" s="5"/>
+      <c r="BB334" s="5"/>
+      <c r="BC334" s="5"/>
+      <c r="BD334" s="5"/>
+      <c r="BE334" s="5"/>
+      <c r="BF334" s="2"/>
+      <c r="BG334" s="2"/>
+      <c r="BH334" s="2"/>
+      <c r="BI334" s="2"/>
+      <c r="BJ334" s="2"/>
+      <c r="BK334" s="2"/>
+      <c r="BL334" s="2"/>
+      <c r="BM334" s="2"/>
+      <c r="BN334" s="2"/>
+      <c r="BO334" s="2"/>
+      <c r="BP334" s="2"/>
+      <c r="BQ334" s="2"/>
+      <c r="BR334" s="2"/>
+      <c r="BS334" s="2"/>
+    </row>
+    <row r="335" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C335" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW335" s="2"/>
+      <c r="AX335" s="2"/>
+      <c r="AY335" s="2"/>
+      <c r="AZ335" s="2"/>
+      <c r="BA335" s="2"/>
+      <c r="BB335" s="2"/>
+      <c r="BC335" s="2"/>
+      <c r="BD335" s="2"/>
+      <c r="BE335" s="2"/>
+      <c r="BF335" s="2"/>
+      <c r="BG335" s="2"/>
+      <c r="BH335" s="2"/>
+      <c r="BI335" s="2"/>
+      <c r="BJ335" s="2"/>
+      <c r="BK335" s="2"/>
+      <c r="BL335" s="2"/>
+      <c r="BM335" s="2"/>
+      <c r="BN335" s="2"/>
+      <c r="BO335" s="2"/>
+      <c r="BP335" s="2"/>
+      <c r="BQ335" s="2"/>
+      <c r="BR335" s="2"/>
+      <c r="BS335" s="2"/>
+    </row>
+    <row r="336" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C336" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW336" s="2"/>
+      <c r="AX336" s="2"/>
+      <c r="AY336" s="2"/>
+      <c r="AZ336" s="2"/>
+      <c r="BA336" s="2"/>
+      <c r="BB336" s="2"/>
+      <c r="BC336" s="2"/>
+      <c r="BD336" s="2"/>
+      <c r="BE336" s="2"/>
+      <c r="BF336" s="2"/>
+      <c r="BG336" s="2"/>
+      <c r="BH336" s="2"/>
+      <c r="BI336" s="2"/>
+      <c r="BJ336" s="2"/>
+      <c r="BK336" s="2"/>
+      <c r="BL336" s="2"/>
+      <c r="BM336" s="2"/>
+      <c r="BN336" s="2"/>
+      <c r="BO336" s="2"/>
+      <c r="BP336" s="2"/>
+      <c r="BQ336" s="2"/>
+      <c r="BR336" s="2"/>
+      <c r="BS336" s="2"/>
+    </row>
+    <row r="337" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C337" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="306" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C306" s="1" t="s">
+      <c r="D337" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AW337" s="2"/>
+      <c r="AX337" s="2"/>
+      <c r="AY337" s="2"/>
+      <c r="AZ337" s="2"/>
+      <c r="BA337" s="2"/>
+      <c r="BB337" s="2"/>
+      <c r="BC337" s="2"/>
+      <c r="BD337" s="2"/>
+      <c r="BE337" s="2"/>
+      <c r="BF337" s="2"/>
+      <c r="BG337" s="2"/>
+      <c r="BH337" s="2"/>
+      <c r="BI337" s="2"/>
+      <c r="BJ337" s="2"/>
+      <c r="BK337" s="2"/>
+      <c r="BL337" s="2"/>
+      <c r="BM337" s="2"/>
+      <c r="BN337" s="2"/>
+      <c r="BO337" s="2"/>
+      <c r="BP337" s="2"/>
+      <c r="BQ337" s="2"/>
+      <c r="BR337" s="2"/>
+      <c r="BS337" s="2"/>
+    </row>
+    <row r="338" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C338" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G338" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H338" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W338" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="X338" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW338" s="2"/>
+      <c r="AX338" s="2"/>
+      <c r="AY338" s="2"/>
+      <c r="AZ338" s="2"/>
+      <c r="BA338" s="2"/>
+      <c r="BB338" s="2"/>
+      <c r="BC338" s="2"/>
+      <c r="BD338" s="2"/>
+      <c r="BE338" s="2"/>
+      <c r="BF338" s="2"/>
+      <c r="BG338" s="2"/>
+      <c r="BH338" s="2"/>
+      <c r="BI338" s="2"/>
+      <c r="BJ338" s="2"/>
+      <c r="BK338" s="2"/>
+      <c r="BL338" s="2"/>
+      <c r="BM338" s="2"/>
+      <c r="BN338" s="2"/>
+      <c r="BO338" s="2"/>
+      <c r="BP338" s="2"/>
+      <c r="BQ338" s="2"/>
+      <c r="BR338" s="2"/>
+      <c r="BS338" s="2"/>
+    </row>
+    <row r="339" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C339" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D306" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G306" s="1" t="s">
+      <c r="D339" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G339" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H339" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW339" s="2"/>
+      <c r="AX339" s="2"/>
+      <c r="AY339" s="2"/>
+      <c r="AZ339" s="2"/>
+      <c r="BA339" s="2"/>
+      <c r="BB339" s="2"/>
+      <c r="BC339" s="2"/>
+      <c r="BD339" s="2"/>
+      <c r="BE339" s="2"/>
+      <c r="BF339" s="2"/>
+      <c r="BG339" s="2"/>
+      <c r="BH339" s="2"/>
+      <c r="BI339" s="2"/>
+      <c r="BJ339" s="2"/>
+      <c r="BK339" s="2"/>
+      <c r="BL339" s="2"/>
+      <c r="BM339" s="2"/>
+      <c r="BN339" s="2"/>
+      <c r="BO339" s="2"/>
+      <c r="BP339" s="2"/>
+      <c r="BQ339" s="2"/>
+      <c r="BR339" s="2"/>
+      <c r="BS339" s="2"/>
+    </row>
+    <row r="340" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C340" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AW340" s="2"/>
+      <c r="AX340" s="2"/>
+      <c r="AY340" s="2"/>
+      <c r="AZ340" s="2"/>
+      <c r="BA340" s="2"/>
+      <c r="BB340" s="2"/>
+      <c r="BC340" s="2"/>
+      <c r="BD340" s="2"/>
+      <c r="BE340" s="2"/>
+      <c r="BF340" s="2"/>
+      <c r="BG340" s="2"/>
+      <c r="BH340" s="2"/>
+      <c r="BI340" s="2"/>
+      <c r="BJ340" s="2"/>
+      <c r="BK340" s="2"/>
+      <c r="BL340" s="2"/>
+      <c r="BM340" s="2"/>
+      <c r="BN340" s="2"/>
+      <c r="BO340" s="2"/>
+      <c r="BP340" s="2"/>
+      <c r="BQ340" s="2"/>
+      <c r="BR340" s="2"/>
+      <c r="BS340" s="2"/>
+    </row>
+    <row r="341" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="AW341" s="2"/>
+      <c r="AX341" s="2"/>
+      <c r="AY341" s="2"/>
+      <c r="AZ341" s="2"/>
+      <c r="BA341" s="2"/>
+      <c r="BB341" s="2"/>
+      <c r="BC341" s="2"/>
+      <c r="BD341" s="2"/>
+      <c r="BE341" s="2"/>
+      <c r="BF341" s="2"/>
+      <c r="BG341" s="2"/>
+      <c r="BH341" s="2"/>
+      <c r="BI341" s="2"/>
+      <c r="BJ341" s="2"/>
+      <c r="BK341" s="2"/>
+      <c r="BL341" s="2"/>
+      <c r="BM341" s="2"/>
+      <c r="BN341" s="2"/>
+      <c r="BO341" s="2"/>
+      <c r="BP341" s="2"/>
+      <c r="BQ341" s="2"/>
+      <c r="BR341" s="2"/>
+      <c r="BS341" s="2"/>
+    </row>
+    <row r="342" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="B342" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AW342" s="2"/>
+      <c r="AX342" s="2"/>
+      <c r="AY342" s="2"/>
+      <c r="AZ342" s="2"/>
+      <c r="BA342" s="2"/>
+      <c r="BB342" s="2"/>
+      <c r="BC342" s="2"/>
+      <c r="BD342" s="2"/>
+      <c r="BE342" s="2"/>
+      <c r="BF342" s="2"/>
+      <c r="BG342" s="2"/>
+      <c r="BH342" s="2"/>
+      <c r="BI342" s="2"/>
+      <c r="BJ342" s="2"/>
+      <c r="BK342" s="2"/>
+      <c r="BL342" s="2"/>
+      <c r="BM342" s="2"/>
+      <c r="BN342" s="2"/>
+      <c r="BO342" s="2"/>
+      <c r="BP342" s="2"/>
+      <c r="BQ342" s="2"/>
+      <c r="BR342" s="2"/>
+      <c r="BS342" s="2"/>
+    </row>
+    <row r="343" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C343" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW343" s="2"/>
+      <c r="AX343" s="2"/>
+      <c r="AY343" s="2"/>
+      <c r="AZ343" s="2"/>
+      <c r="BA343" s="2"/>
+      <c r="BB343" s="2"/>
+      <c r="BC343" s="2"/>
+      <c r="BD343" s="2"/>
+      <c r="BE343" s="2"/>
+      <c r="BF343" s="2"/>
+      <c r="BG343" s="2"/>
+      <c r="BH343" s="2"/>
+      <c r="BI343" s="2"/>
+      <c r="BJ343" s="2"/>
+      <c r="BK343" s="2"/>
+      <c r="BL343" s="2"/>
+      <c r="BM343" s="2"/>
+      <c r="BN343" s="2"/>
+      <c r="BO343" s="2"/>
+      <c r="BP343" s="2"/>
+      <c r="BQ343" s="2"/>
+      <c r="BR343" s="2"/>
+      <c r="BS343" s="2"/>
+    </row>
+    <row r="344" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C344" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW344" s="2"/>
+      <c r="AX344" s="2"/>
+      <c r="AY344" s="2"/>
+      <c r="AZ344" s="2"/>
+      <c r="BA344" s="2"/>
+      <c r="BB344" s="2"/>
+      <c r="BC344" s="2"/>
+      <c r="BD344" s="2"/>
+      <c r="BE344" s="2"/>
+      <c r="BF344" s="2"/>
+      <c r="BG344" s="2"/>
+      <c r="BH344" s="2"/>
+      <c r="BI344" s="2"/>
+      <c r="BJ344" s="2"/>
+      <c r="BK344" s="2"/>
+      <c r="BL344" s="2"/>
+      <c r="BM344" s="2"/>
+      <c r="BN344" s="2"/>
+      <c r="BO344" s="2"/>
+      <c r="BP344" s="2"/>
+      <c r="BQ344" s="2"/>
+      <c r="BR344" s="2"/>
+      <c r="BS344" s="2"/>
+    </row>
+    <row r="345" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C345" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW345" s="2"/>
+      <c r="AX345" s="2"/>
+      <c r="AY345" s="2"/>
+      <c r="AZ345" s="2"/>
+      <c r="BA345" s="2"/>
+      <c r="BB345" s="2"/>
+      <c r="BC345" s="2"/>
+      <c r="BD345" s="2"/>
+      <c r="BE345" s="2"/>
+      <c r="BF345" s="2"/>
+      <c r="BG345" s="2"/>
+      <c r="BH345" s="2"/>
+      <c r="BI345" s="2"/>
+      <c r="BJ345" s="2"/>
+      <c r="BK345" s="2"/>
+      <c r="BL345" s="2"/>
+      <c r="BM345" s="2"/>
+      <c r="BN345" s="2"/>
+      <c r="BO345" s="2"/>
+      <c r="BP345" s="2"/>
+      <c r="BQ345" s="2"/>
+      <c r="BR345" s="2"/>
+      <c r="BS345" s="2"/>
+    </row>
+    <row r="346" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C346" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW346" s="2"/>
+      <c r="AX346" s="2"/>
+      <c r="AY346" s="2"/>
+      <c r="AZ346" s="2"/>
+      <c r="BA346" s="2"/>
+      <c r="BB346" s="2"/>
+      <c r="BC346" s="2"/>
+      <c r="BD346" s="2"/>
+      <c r="BE346" s="2"/>
+      <c r="BF346" s="2"/>
+      <c r="BG346" s="2"/>
+      <c r="BH346" s="2"/>
+      <c r="BI346" s="2"/>
+      <c r="BJ346" s="2"/>
+      <c r="BK346" s="2"/>
+      <c r="BL346" s="2"/>
+      <c r="BM346" s="2"/>
+      <c r="BN346" s="2"/>
+      <c r="BO346" s="2"/>
+      <c r="BP346" s="2"/>
+      <c r="BQ346" s="2"/>
+      <c r="BR346" s="2"/>
+      <c r="BS346" s="2"/>
+    </row>
+    <row r="347" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C347" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW347" s="2"/>
+      <c r="AX347" s="2"/>
+      <c r="AY347" s="2"/>
+      <c r="AZ347" s="2"/>
+      <c r="BA347" s="2"/>
+      <c r="BB347" s="2"/>
+      <c r="BC347" s="2"/>
+      <c r="BD347" s="2"/>
+      <c r="BE347" s="2"/>
+      <c r="BF347" s="2"/>
+      <c r="BG347" s="2"/>
+      <c r="BH347" s="2"/>
+      <c r="BI347" s="2"/>
+      <c r="BJ347" s="2"/>
+      <c r="BK347" s="2"/>
+      <c r="BL347" s="2"/>
+      <c r="BM347" s="2"/>
+      <c r="BN347" s="2"/>
+      <c r="BO347" s="2"/>
+      <c r="BP347" s="2"/>
+      <c r="BQ347" s="2"/>
+      <c r="BR347" s="2"/>
+      <c r="BS347" s="2"/>
+    </row>
+    <row r="348" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C348" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW348" s="2"/>
+      <c r="AX348" s="2"/>
+      <c r="AY348" s="2"/>
+      <c r="AZ348" s="2"/>
+      <c r="BA348" s="2"/>
+      <c r="BB348" s="2"/>
+      <c r="BC348" s="2"/>
+      <c r="BD348" s="2"/>
+      <c r="BE348" s="2"/>
+      <c r="BF348" s="2"/>
+      <c r="BG348" s="2"/>
+      <c r="BH348" s="2"/>
+      <c r="BI348" s="2"/>
+      <c r="BJ348" s="2"/>
+      <c r="BK348" s="2"/>
+      <c r="BL348" s="2"/>
+      <c r="BM348" s="2"/>
+      <c r="BN348" s="2"/>
+      <c r="BO348" s="2"/>
+      <c r="BP348" s="2"/>
+      <c r="BQ348" s="2"/>
+      <c r="BR348" s="2"/>
+      <c r="BS348" s="2"/>
+    </row>
+    <row r="349" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C349" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D349" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW349" s="2"/>
+      <c r="AX349" s="2"/>
+      <c r="AY349" s="2"/>
+      <c r="AZ349" s="2"/>
+      <c r="BA349" s="2"/>
+      <c r="BB349" s="2"/>
+      <c r="BC349" s="2"/>
+      <c r="BD349" s="2"/>
+      <c r="BE349" s="2"/>
+      <c r="BF349" s="2"/>
+      <c r="BG349" s="2"/>
+      <c r="BH349" s="2"/>
+      <c r="BI349" s="2"/>
+      <c r="BJ349" s="2"/>
+      <c r="BK349" s="2"/>
+      <c r="BL349" s="2"/>
+      <c r="BM349" s="2"/>
+      <c r="BN349" s="2"/>
+      <c r="BO349" s="2"/>
+      <c r="BP349" s="2"/>
+      <c r="BQ349" s="2"/>
+      <c r="BR349" s="2"/>
+      <c r="BS349" s="2"/>
+    </row>
+    <row r="350" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C350" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D350" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW350" s="2"/>
+      <c r="AX350" s="2"/>
+      <c r="AY350" s="2"/>
+      <c r="AZ350" s="2"/>
+      <c r="BA350" s="2"/>
+      <c r="BB350" s="2"/>
+      <c r="BC350" s="2"/>
+      <c r="BD350" s="2"/>
+      <c r="BE350" s="2"/>
+      <c r="BF350" s="2"/>
+      <c r="BG350" s="2"/>
+      <c r="BH350" s="2"/>
+      <c r="BI350" s="2"/>
+      <c r="BJ350" s="2"/>
+      <c r="BK350" s="2"/>
+      <c r="BL350" s="2"/>
+      <c r="BM350" s="2"/>
+      <c r="BN350" s="2"/>
+      <c r="BO350" s="2"/>
+      <c r="BP350" s="2"/>
+      <c r="BQ350" s="2"/>
+      <c r="BR350" s="2"/>
+      <c r="BS350" s="2"/>
+    </row>
+    <row r="351" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C351" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW351" s="2"/>
+      <c r="AX351" s="2"/>
+      <c r="AY351" s="2"/>
+      <c r="AZ351" s="2"/>
+      <c r="BA351" s="2"/>
+      <c r="BB351" s="2"/>
+      <c r="BC351" s="2"/>
+      <c r="BD351" s="2"/>
+      <c r="BE351" s="2"/>
+      <c r="BF351" s="2"/>
+      <c r="BG351" s="2"/>
+      <c r="BH351" s="2"/>
+      <c r="BI351" s="2"/>
+      <c r="BJ351" s="2"/>
+      <c r="BK351" s="2"/>
+      <c r="BL351" s="2"/>
+      <c r="BM351" s="2"/>
+      <c r="BN351" s="2"/>
+      <c r="BO351" s="2"/>
+      <c r="BP351" s="2"/>
+      <c r="BQ351" s="2"/>
+      <c r="BR351" s="2"/>
+      <c r="BS351" s="2"/>
+    </row>
+    <row r="352" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C352" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="307" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="G307" s="1" t="s">
+      <c r="D352" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW352" s="2"/>
+      <c r="AX352" s="2"/>
+      <c r="AY352" s="2"/>
+      <c r="AZ352" s="2"/>
+      <c r="BA352" s="2"/>
+      <c r="BB352" s="2"/>
+      <c r="BC352" s="2"/>
+      <c r="BD352" s="2"/>
+      <c r="BE352" s="2"/>
+      <c r="BF352" s="2"/>
+      <c r="BG352" s="2"/>
+      <c r="BH352" s="2"/>
+      <c r="BI352" s="2"/>
+      <c r="BJ352" s="2"/>
+      <c r="BK352" s="2"/>
+      <c r="BL352" s="2"/>
+      <c r="BM352" s="2"/>
+      <c r="BN352" s="2"/>
+      <c r="BO352" s="2"/>
+      <c r="BP352" s="2"/>
+      <c r="BQ352" s="2"/>
+      <c r="BR352" s="2"/>
+      <c r="BS352" s="2"/>
+    </row>
+    <row r="353" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C353" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW353" s="2"/>
+      <c r="AX353" s="2"/>
+      <c r="AY353" s="2"/>
+      <c r="AZ353" s="2"/>
+      <c r="BA353" s="2"/>
+      <c r="BB353" s="2"/>
+      <c r="BC353" s="2"/>
+      <c r="BD353" s="2"/>
+      <c r="BE353" s="2"/>
+      <c r="BF353" s="2"/>
+      <c r="BG353" s="2"/>
+      <c r="BH353" s="2"/>
+      <c r="BI353" s="2"/>
+      <c r="BJ353" s="2"/>
+      <c r="BK353" s="2"/>
+      <c r="BL353" s="2"/>
+      <c r="BM353" s="2"/>
+      <c r="BN353" s="2"/>
+      <c r="BO353" s="2"/>
+      <c r="BP353" s="2"/>
+      <c r="BQ353" s="2"/>
+      <c r="BR353" s="2"/>
+      <c r="BS353" s="2"/>
+    </row>
+    <row r="354" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C354" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW354" s="2"/>
+      <c r="AX354" s="2"/>
+      <c r="AY354" s="2"/>
+      <c r="AZ354" s="2"/>
+      <c r="BA354" s="2"/>
+      <c r="BB354" s="2"/>
+      <c r="BC354" s="2"/>
+      <c r="BD354" s="2"/>
+      <c r="BE354" s="2"/>
+      <c r="BF354" s="2"/>
+      <c r="BG354" s="2"/>
+      <c r="BH354" s="2"/>
+      <c r="BI354" s="2"/>
+      <c r="BJ354" s="2"/>
+      <c r="BK354" s="2"/>
+      <c r="BL354" s="2"/>
+      <c r="BM354" s="2"/>
+      <c r="BN354" s="2"/>
+      <c r="BO354" s="2"/>
+      <c r="BP354" s="2"/>
+      <c r="BQ354" s="2"/>
+      <c r="BR354" s="2"/>
+      <c r="BS354" s="2"/>
+    </row>
+    <row r="355" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C355" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW355" s="2"/>
+      <c r="AX355" s="2"/>
+      <c r="AY355" s="2"/>
+      <c r="AZ355" s="2"/>
+      <c r="BA355" s="2"/>
+      <c r="BB355" s="2"/>
+      <c r="BC355" s="2"/>
+      <c r="BD355" s="2"/>
+      <c r="BE355" s="2"/>
+      <c r="BF355" s="2"/>
+      <c r="BG355" s="2"/>
+      <c r="BH355" s="2"/>
+      <c r="BI355" s="2"/>
+      <c r="BJ355" s="2"/>
+      <c r="BK355" s="2"/>
+      <c r="BL355" s="2"/>
+      <c r="BM355" s="2"/>
+      <c r="BN355" s="2"/>
+      <c r="BO355" s="2"/>
+      <c r="BP355" s="2"/>
+      <c r="BQ355" s="2"/>
+      <c r="BR355" s="2"/>
+      <c r="BS355" s="2"/>
+    </row>
+    <row r="356" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="AW356" s="2"/>
+      <c r="AX356" s="2"/>
+      <c r="AY356" s="2"/>
+      <c r="AZ356" s="2"/>
+      <c r="BA356" s="2"/>
+      <c r="BB356" s="2"/>
+      <c r="BC356" s="2"/>
+      <c r="BD356" s="2"/>
+      <c r="BE356" s="2"/>
+      <c r="BF356" s="2"/>
+      <c r="BG356" s="2"/>
+      <c r="BH356" s="2"/>
+      <c r="BI356" s="2"/>
+      <c r="BJ356" s="2"/>
+      <c r="BK356" s="2"/>
+      <c r="BL356" s="2"/>
+      <c r="BM356" s="2"/>
+      <c r="BN356" s="2"/>
+      <c r="BO356" s="2"/>
+      <c r="BP356" s="2"/>
+      <c r="BQ356" s="2"/>
+      <c r="BR356" s="2"/>
+      <c r="BS356" s="2"/>
+    </row>
+    <row r="357" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="B357" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AW357" s="2"/>
+      <c r="AX357" s="2"/>
+      <c r="AY357" s="2"/>
+      <c r="AZ357" s="2"/>
+      <c r="BA357" s="2"/>
+      <c r="BB357" s="2"/>
+      <c r="BC357" s="2"/>
+      <c r="BD357" s="2"/>
+      <c r="BE357" s="2"/>
+      <c r="BF357" s="2"/>
+      <c r="BG357" s="2"/>
+      <c r="BH357" s="2"/>
+      <c r="BI357" s="2"/>
+      <c r="BJ357" s="2"/>
+      <c r="BK357" s="2"/>
+      <c r="BL357" s="2"/>
+      <c r="BM357" s="2"/>
+      <c r="BN357" s="2"/>
+      <c r="BO357" s="2"/>
+      <c r="BP357" s="2"/>
+      <c r="BQ357" s="2"/>
+      <c r="BR357" s="2"/>
+      <c r="BS357" s="2"/>
+    </row>
+    <row r="358" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C358" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW358" s="2"/>
+      <c r="AX358" s="2"/>
+      <c r="AY358" s="2"/>
+      <c r="AZ358" s="2"/>
+      <c r="BA358" s="2"/>
+      <c r="BB358" s="2"/>
+      <c r="BC358" s="2"/>
+      <c r="BD358" s="2"/>
+      <c r="BE358" s="2"/>
+      <c r="BF358" s="2"/>
+      <c r="BG358" s="2"/>
+      <c r="BH358" s="2"/>
+      <c r="BI358" s="2"/>
+      <c r="BJ358" s="2"/>
+      <c r="BK358" s="2"/>
+      <c r="BL358" s="2"/>
+      <c r="BM358" s="2"/>
+      <c r="BN358" s="2"/>
+      <c r="BO358" s="2"/>
+      <c r="BP358" s="2"/>
+      <c r="BQ358" s="2"/>
+      <c r="BR358" s="2"/>
+      <c r="BS358" s="2"/>
+    </row>
+    <row r="359" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C359" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW359" s="2"/>
+      <c r="AX359" s="2"/>
+      <c r="AY359" s="2"/>
+      <c r="AZ359" s="2"/>
+      <c r="BA359" s="2"/>
+      <c r="BB359" s="2"/>
+      <c r="BC359" s="2"/>
+      <c r="BD359" s="2"/>
+      <c r="BE359" s="2"/>
+      <c r="BF359" s="2"/>
+      <c r="BG359" s="2"/>
+      <c r="BH359" s="2"/>
+      <c r="BI359" s="2"/>
+      <c r="BJ359" s="2"/>
+      <c r="BK359" s="2"/>
+      <c r="BL359" s="2"/>
+      <c r="BM359" s="2"/>
+      <c r="BN359" s="2"/>
+      <c r="BO359" s="2"/>
+      <c r="BP359" s="2"/>
+      <c r="BQ359" s="2"/>
+      <c r="BR359" s="2"/>
+      <c r="BS359" s="2"/>
+    </row>
+    <row r="360" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C360" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D360" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW360" s="2"/>
+      <c r="AX360" s="2"/>
+      <c r="AY360" s="2"/>
+      <c r="AZ360" s="2"/>
+      <c r="BA360" s="2"/>
+      <c r="BB360" s="2"/>
+      <c r="BC360" s="2"/>
+      <c r="BD360" s="2"/>
+      <c r="BE360" s="2"/>
+      <c r="BF360" s="2"/>
+      <c r="BG360" s="2"/>
+      <c r="BH360" s="2"/>
+      <c r="BI360" s="2"/>
+      <c r="BJ360" s="2"/>
+      <c r="BK360" s="2"/>
+      <c r="BL360" s="2"/>
+      <c r="BM360" s="2"/>
+      <c r="BN360" s="2"/>
+      <c r="BO360" s="2"/>
+      <c r="BP360" s="2"/>
+      <c r="BQ360" s="2"/>
+      <c r="BR360" s="2"/>
+      <c r="BS360" s="2"/>
+    </row>
+    <row r="361" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C361" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW361" s="2"/>
+      <c r="AX361" s="2"/>
+      <c r="AY361" s="2"/>
+      <c r="AZ361" s="2"/>
+      <c r="BA361" s="2"/>
+      <c r="BB361" s="2"/>
+      <c r="BC361" s="2"/>
+      <c r="BD361" s="2"/>
+      <c r="BE361" s="2"/>
+      <c r="BF361" s="2"/>
+      <c r="BG361" s="2"/>
+      <c r="BH361" s="2"/>
+      <c r="BI361" s="2"/>
+      <c r="BJ361" s="2"/>
+      <c r="BK361" s="2"/>
+      <c r="BL361" s="2"/>
+      <c r="BM361" s="2"/>
+      <c r="BN361" s="2"/>
+      <c r="BO361" s="2"/>
+      <c r="BP361" s="2"/>
+      <c r="BQ361" s="2"/>
+      <c r="BR361" s="2"/>
+      <c r="BS361" s="2"/>
+    </row>
+    <row r="362" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C362" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW362" s="2"/>
+      <c r="AX362" s="2"/>
+      <c r="AY362" s="2"/>
+      <c r="AZ362" s="2"/>
+      <c r="BA362" s="2"/>
+      <c r="BB362" s="2"/>
+      <c r="BC362" s="2"/>
+      <c r="BD362" s="2"/>
+      <c r="BE362" s="2"/>
+      <c r="BF362" s="2"/>
+      <c r="BG362" s="2"/>
+      <c r="BH362" s="2"/>
+      <c r="BI362" s="2"/>
+      <c r="BJ362" s="2"/>
+      <c r="BK362" s="2"/>
+      <c r="BL362" s="2"/>
+      <c r="BM362" s="2"/>
+      <c r="BN362" s="2"/>
+      <c r="BO362" s="2"/>
+      <c r="BP362" s="2"/>
+      <c r="BQ362" s="2"/>
+      <c r="BR362" s="2"/>
+      <c r="BS362" s="2"/>
+    </row>
+    <row r="363" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C363" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW363" s="2"/>
+      <c r="AX363" s="2"/>
+      <c r="AY363" s="2"/>
+      <c r="AZ363" s="2"/>
+      <c r="BA363" s="2"/>
+      <c r="BB363" s="2"/>
+      <c r="BC363" s="2"/>
+      <c r="BD363" s="2"/>
+      <c r="BE363" s="2"/>
+      <c r="BF363" s="2"/>
+      <c r="BG363" s="2"/>
+      <c r="BH363" s="2"/>
+      <c r="BI363" s="2"/>
+      <c r="BJ363" s="2"/>
+      <c r="BK363" s="2"/>
+      <c r="BL363" s="2"/>
+      <c r="BM363" s="2"/>
+      <c r="BN363" s="2"/>
+      <c r="BO363" s="2"/>
+      <c r="BP363" s="2"/>
+      <c r="BQ363" s="2"/>
+      <c r="BR363" s="2"/>
+      <c r="BS363" s="2"/>
+    </row>
+    <row r="364" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C364" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW364" s="2"/>
+      <c r="AX364" s="2"/>
+      <c r="AY364" s="2"/>
+      <c r="AZ364" s="2"/>
+      <c r="BA364" s="2"/>
+      <c r="BB364" s="2"/>
+      <c r="BC364" s="2"/>
+      <c r="BD364" s="2"/>
+      <c r="BE364" s="2"/>
+      <c r="BF364" s="2"/>
+      <c r="BG364" s="2"/>
+      <c r="BH364" s="2"/>
+      <c r="BI364" s="2"/>
+      <c r="BJ364" s="2"/>
+      <c r="BK364" s="2"/>
+      <c r="BL364" s="2"/>
+      <c r="BM364" s="2"/>
+      <c r="BN364" s="2"/>
+      <c r="BO364" s="2"/>
+      <c r="BP364" s="2"/>
+      <c r="BQ364" s="2"/>
+      <c r="BR364" s="2"/>
+      <c r="BS364" s="2"/>
+    </row>
+    <row r="365" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C365" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D365" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW365" s="2"/>
+      <c r="AX365" s="2"/>
+      <c r="AY365" s="2"/>
+      <c r="AZ365" s="2"/>
+      <c r="BA365" s="2"/>
+      <c r="BB365" s="2"/>
+      <c r="BC365" s="2"/>
+      <c r="BD365" s="2"/>
+      <c r="BE365" s="2"/>
+      <c r="BF365" s="2"/>
+      <c r="BG365" s="2"/>
+      <c r="BH365" s="2"/>
+      <c r="BI365" s="2"/>
+      <c r="BJ365" s="2"/>
+      <c r="BK365" s="2"/>
+      <c r="BL365" s="2"/>
+      <c r="BM365" s="2"/>
+      <c r="BN365" s="2"/>
+      <c r="BO365" s="2"/>
+      <c r="BP365" s="2"/>
+      <c r="BQ365" s="2"/>
+      <c r="BR365" s="2"/>
+      <c r="BS365" s="2"/>
+    </row>
+    <row r="366" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C366" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW366" s="2"/>
+      <c r="AX366" s="2"/>
+      <c r="AY366" s="2"/>
+      <c r="AZ366" s="2"/>
+      <c r="BA366" s="2"/>
+      <c r="BB366" s="2"/>
+      <c r="BC366" s="2"/>
+      <c r="BD366" s="2"/>
+      <c r="BE366" s="2"/>
+      <c r="BF366" s="2"/>
+      <c r="BG366" s="2"/>
+      <c r="BH366" s="2"/>
+      <c r="BI366" s="2"/>
+      <c r="BJ366" s="2"/>
+      <c r="BK366" s="2"/>
+      <c r="BL366" s="2"/>
+      <c r="BM366" s="2"/>
+      <c r="BN366" s="2"/>
+      <c r="BO366" s="2"/>
+      <c r="BP366" s="2"/>
+      <c r="BQ366" s="2"/>
+      <c r="BR366" s="2"/>
+      <c r="BS366" s="2"/>
+    </row>
+    <row r="367" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C367" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW367" s="2"/>
+      <c r="AX367" s="2"/>
+      <c r="AY367" s="2"/>
+      <c r="AZ367" s="2"/>
+      <c r="BA367" s="2"/>
+      <c r="BB367" s="2"/>
+      <c r="BC367" s="2"/>
+      <c r="BD367" s="2"/>
+      <c r="BE367" s="2"/>
+      <c r="BF367" s="2"/>
+      <c r="BG367" s="2"/>
+      <c r="BH367" s="2"/>
+      <c r="BI367" s="2"/>
+      <c r="BJ367" s="2"/>
+      <c r="BK367" s="2"/>
+      <c r="BL367" s="2"/>
+      <c r="BM367" s="2"/>
+      <c r="BN367" s="2"/>
+      <c r="BO367" s="2"/>
+      <c r="BP367" s="2"/>
+      <c r="BQ367" s="2"/>
+      <c r="BR367" s="2"/>
+      <c r="BS367" s="2"/>
+    </row>
+    <row r="368" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C368" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW368" s="2"/>
+      <c r="AX368" s="2"/>
+      <c r="AY368" s="2"/>
+      <c r="AZ368" s="2"/>
+      <c r="BA368" s="2"/>
+      <c r="BB368" s="2"/>
+      <c r="BC368" s="2"/>
+      <c r="BD368" s="2"/>
+      <c r="BE368" s="2"/>
+      <c r="BF368" s="2"/>
+      <c r="BG368" s="2"/>
+      <c r="BH368" s="2"/>
+      <c r="BI368" s="2"/>
+      <c r="BJ368" s="2"/>
+      <c r="BK368" s="2"/>
+      <c r="BL368" s="2"/>
+      <c r="BM368" s="2"/>
+      <c r="BN368" s="2"/>
+      <c r="BO368" s="2"/>
+      <c r="BP368" s="2"/>
+      <c r="BQ368" s="2"/>
+      <c r="BR368" s="2"/>
+      <c r="BS368" s="2"/>
+    </row>
+    <row r="369" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C369" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="308" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B308" s="1" t="s">
+      <c r="D369" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW369" s="2"/>
+      <c r="AX369" s="2"/>
+      <c r="AY369" s="2"/>
+      <c r="AZ369" s="2"/>
+      <c r="BA369" s="2"/>
+      <c r="BB369" s="2"/>
+      <c r="BC369" s="2"/>
+      <c r="BD369" s="2"/>
+      <c r="BE369" s="2"/>
+      <c r="BF369" s="2"/>
+      <c r="BG369" s="2"/>
+      <c r="BH369" s="2"/>
+      <c r="BI369" s="2"/>
+      <c r="BJ369" s="2"/>
+      <c r="BK369" s="2"/>
+      <c r="BL369" s="2"/>
+      <c r="BM369" s="2"/>
+      <c r="BN369" s="2"/>
+      <c r="BO369" s="2"/>
+      <c r="BP369" s="2"/>
+      <c r="BQ369" s="2"/>
+      <c r="BR369" s="2"/>
+      <c r="BS369" s="2"/>
+    </row>
+    <row r="370" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C370" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW370" s="2"/>
+      <c r="AX370" s="2"/>
+      <c r="AY370" s="2"/>
+      <c r="AZ370" s="2"/>
+      <c r="BA370" s="2"/>
+      <c r="BB370" s="2"/>
+      <c r="BC370" s="2"/>
+      <c r="BD370" s="2"/>
+      <c r="BE370" s="2"/>
+      <c r="BF370" s="2"/>
+      <c r="BG370" s="2"/>
+      <c r="BH370" s="2"/>
+      <c r="BI370" s="2"/>
+      <c r="BJ370" s="2"/>
+      <c r="BK370" s="2"/>
+      <c r="BL370" s="2"/>
+      <c r="BM370" s="2"/>
+      <c r="BN370" s="2"/>
+      <c r="BO370" s="2"/>
+      <c r="BP370" s="2"/>
+      <c r="BQ370" s="2"/>
+      <c r="BR370" s="2"/>
+      <c r="BS370" s="2"/>
+    </row>
+    <row r="371" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="AW371" s="2"/>
+      <c r="AX371" s="2"/>
+      <c r="AY371" s="2"/>
+      <c r="AZ371" s="2"/>
+      <c r="BA371" s="2"/>
+      <c r="BB371" s="2"/>
+      <c r="BC371" s="2"/>
+      <c r="BD371" s="2"/>
+      <c r="BE371" s="2"/>
+      <c r="BF371" s="2"/>
+      <c r="BG371" s="2"/>
+      <c r="BH371" s="2"/>
+      <c r="BI371" s="2"/>
+      <c r="BJ371" s="2"/>
+      <c r="BK371" s="2"/>
+      <c r="BL371" s="2"/>
+      <c r="BM371" s="2"/>
+      <c r="BN371" s="2"/>
+      <c r="BO371" s="2"/>
+      <c r="BP371" s="2"/>
+      <c r="BQ371" s="2"/>
+      <c r="BR371" s="2"/>
+      <c r="BS371" s="2"/>
+    </row>
+    <row r="372" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="B372" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AW372" s="2"/>
+      <c r="AX372" s="2"/>
+      <c r="AY372" s="2"/>
+      <c r="AZ372" s="2"/>
+      <c r="BA372" s="2"/>
+      <c r="BB372" s="2"/>
+      <c r="BC372" s="2"/>
+      <c r="BD372" s="2"/>
+      <c r="BE372" s="2"/>
+      <c r="BF372" s="2"/>
+      <c r="BG372" s="2"/>
+      <c r="BH372" s="2"/>
+      <c r="BI372" s="2"/>
+      <c r="BJ372" s="2"/>
+      <c r="BK372" s="2"/>
+      <c r="BL372" s="2"/>
+      <c r="BM372" s="2"/>
+      <c r="BN372" s="2"/>
+      <c r="BO372" s="2"/>
+      <c r="BP372" s="2"/>
+      <c r="BQ372" s="2"/>
+      <c r="BR372" s="2"/>
+      <c r="BS372" s="2"/>
+    </row>
+    <row r="373" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C373" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D373" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW373" s="2"/>
+      <c r="AX373" s="2"/>
+      <c r="AY373" s="2"/>
+      <c r="AZ373" s="2"/>
+      <c r="BA373" s="2"/>
+      <c r="BB373" s="2"/>
+      <c r="BC373" s="2"/>
+      <c r="BD373" s="2"/>
+      <c r="BE373" s="2"/>
+      <c r="BF373" s="2"/>
+      <c r="BG373" s="2"/>
+      <c r="BH373" s="2"/>
+      <c r="BI373" s="2"/>
+      <c r="BJ373" s="2"/>
+      <c r="BK373" s="2"/>
+      <c r="BL373" s="2"/>
+      <c r="BM373" s="2"/>
+      <c r="BN373" s="2"/>
+      <c r="BO373" s="2"/>
+      <c r="BP373" s="2"/>
+      <c r="BQ373" s="2"/>
+      <c r="BR373" s="2"/>
+      <c r="BS373" s="2"/>
+    </row>
+    <row r="374" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C374" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="309" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C309" s="1" t="s">
+      <c r="D374" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW374" s="2"/>
+      <c r="AX374" s="2"/>
+      <c r="AY374" s="2"/>
+      <c r="AZ374" s="2"/>
+      <c r="BA374" s="2"/>
+      <c r="BB374" s="2"/>
+      <c r="BC374" s="2"/>
+      <c r="BD374" s="2"/>
+      <c r="BE374" s="2"/>
+      <c r="BF374" s="2"/>
+      <c r="BG374" s="2"/>
+      <c r="BH374" s="2"/>
+      <c r="BI374" s="2"/>
+      <c r="BJ374" s="2"/>
+      <c r="BK374" s="2"/>
+      <c r="BL374" s="2"/>
+      <c r="BM374" s="2"/>
+      <c r="BN374" s="2"/>
+      <c r="BO374" s="2"/>
+      <c r="BP374" s="2"/>
+      <c r="BQ374" s="2"/>
+      <c r="BR374" s="2"/>
+      <c r="BS374" s="2"/>
+    </row>
+    <row r="375" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C375" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D375" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW375" s="2"/>
+      <c r="AX375" s="2"/>
+      <c r="AY375" s="2"/>
+      <c r="AZ375" s="2"/>
+      <c r="BA375" s="2"/>
+      <c r="BB375" s="2"/>
+      <c r="BC375" s="2"/>
+      <c r="BD375" s="2"/>
+      <c r="BE375" s="2"/>
+      <c r="BF375" s="2"/>
+      <c r="BG375" s="2"/>
+      <c r="BH375" s="2"/>
+      <c r="BI375" s="2"/>
+      <c r="BJ375" s="2"/>
+      <c r="BK375" s="2"/>
+      <c r="BL375" s="2"/>
+      <c r="BM375" s="2"/>
+      <c r="BN375" s="2"/>
+      <c r="BO375" s="2"/>
+      <c r="BP375" s="2"/>
+      <c r="BQ375" s="2"/>
+      <c r="BR375" s="2"/>
+      <c r="BS375" s="2"/>
+    </row>
+    <row r="376" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C376" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D376" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW376" s="2"/>
+      <c r="AX376" s="2"/>
+      <c r="AY376" s="2"/>
+      <c r="AZ376" s="2"/>
+      <c r="BA376" s="2"/>
+      <c r="BB376" s="2"/>
+      <c r="BC376" s="2"/>
+      <c r="BD376" s="2"/>
+      <c r="BE376" s="2"/>
+      <c r="BF376" s="2"/>
+      <c r="BG376" s="2"/>
+      <c r="BH376" s="2"/>
+      <c r="BI376" s="2"/>
+      <c r="BJ376" s="2"/>
+      <c r="BK376" s="2"/>
+      <c r="BL376" s="2"/>
+      <c r="BM376" s="2"/>
+      <c r="BN376" s="2"/>
+      <c r="BO376" s="2"/>
+      <c r="BP376" s="2"/>
+      <c r="BQ376" s="2"/>
+      <c r="BR376" s="2"/>
+      <c r="BS376" s="2"/>
+    </row>
+    <row r="377" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C377" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D377" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW377" s="2"/>
+      <c r="AX377" s="2"/>
+      <c r="AY377" s="2"/>
+      <c r="AZ377" s="2"/>
+      <c r="BA377" s="2"/>
+      <c r="BB377" s="2"/>
+      <c r="BC377" s="2"/>
+      <c r="BD377" s="2"/>
+      <c r="BE377" s="2"/>
+      <c r="BF377" s="2"/>
+      <c r="BG377" s="2"/>
+      <c r="BH377" s="2"/>
+      <c r="BI377" s="2"/>
+      <c r="BJ377" s="2"/>
+      <c r="BK377" s="2"/>
+      <c r="BL377" s="2"/>
+      <c r="BM377" s="2"/>
+      <c r="BN377" s="2"/>
+      <c r="BO377" s="2"/>
+      <c r="BP377" s="2"/>
+      <c r="BQ377" s="2"/>
+      <c r="BR377" s="2"/>
+      <c r="BS377" s="2"/>
+    </row>
+    <row r="378" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C378" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW378" s="2"/>
+      <c r="AX378" s="2"/>
+      <c r="AY378" s="2"/>
+      <c r="AZ378" s="2"/>
+      <c r="BA378" s="2"/>
+      <c r="BB378" s="2"/>
+      <c r="BC378" s="2"/>
+      <c r="BD378" s="2"/>
+      <c r="BE378" s="2"/>
+      <c r="BF378" s="2"/>
+      <c r="BG378" s="2"/>
+      <c r="BH378" s="2"/>
+      <c r="BI378" s="2"/>
+      <c r="BJ378" s="2"/>
+      <c r="BK378" s="2"/>
+      <c r="BL378" s="2"/>
+      <c r="BM378" s="2"/>
+      <c r="BN378" s="2"/>
+      <c r="BO378" s="2"/>
+      <c r="BP378" s="2"/>
+      <c r="BQ378" s="2"/>
+      <c r="BR378" s="2"/>
+      <c r="BS378" s="2"/>
+    </row>
+    <row r="379" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C379" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D379" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW379" s="2"/>
+      <c r="AX379" s="2"/>
+      <c r="AY379" s="2"/>
+      <c r="AZ379" s="2"/>
+      <c r="BA379" s="2"/>
+      <c r="BB379" s="2"/>
+      <c r="BC379" s="2"/>
+      <c r="BD379" s="2"/>
+      <c r="BE379" s="2"/>
+      <c r="BF379" s="2"/>
+      <c r="BG379" s="2"/>
+      <c r="BH379" s="2"/>
+      <c r="BI379" s="2"/>
+      <c r="BJ379" s="2"/>
+      <c r="BK379" s="2"/>
+      <c r="BL379" s="2"/>
+      <c r="BM379" s="2"/>
+      <c r="BN379" s="2"/>
+      <c r="BO379" s="2"/>
+      <c r="BP379" s="2"/>
+      <c r="BQ379" s="2"/>
+      <c r="BR379" s="2"/>
+      <c r="BS379" s="2"/>
+    </row>
+    <row r="380" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C380" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D380" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW380" s="2"/>
+      <c r="AX380" s="2"/>
+      <c r="AY380" s="2"/>
+      <c r="AZ380" s="2"/>
+      <c r="BA380" s="2"/>
+      <c r="BB380" s="2"/>
+      <c r="BC380" s="2"/>
+      <c r="BD380" s="2"/>
+      <c r="BE380" s="2"/>
+      <c r="BF380" s="2"/>
+      <c r="BG380" s="2"/>
+      <c r="BH380" s="2"/>
+      <c r="BI380" s="2"/>
+      <c r="BJ380" s="2"/>
+      <c r="BK380" s="2"/>
+      <c r="BL380" s="2"/>
+      <c r="BM380" s="2"/>
+      <c r="BN380" s="2"/>
+      <c r="BO380" s="2"/>
+      <c r="BP380" s="2"/>
+      <c r="BQ380" s="2"/>
+      <c r="BR380" s="2"/>
+      <c r="BS380" s="2"/>
+    </row>
+    <row r="381" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C381" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D381" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW381" s="2"/>
+      <c r="AX381" s="2"/>
+      <c r="AY381" s="2"/>
+      <c r="AZ381" s="2"/>
+      <c r="BA381" s="2"/>
+      <c r="BB381" s="2"/>
+      <c r="BC381" s="2"/>
+      <c r="BD381" s="2"/>
+      <c r="BE381" s="2"/>
+      <c r="BF381" s="2"/>
+      <c r="BG381" s="2"/>
+      <c r="BH381" s="2"/>
+      <c r="BI381" s="2"/>
+      <c r="BJ381" s="2"/>
+      <c r="BK381" s="2"/>
+      <c r="BL381" s="2"/>
+      <c r="BM381" s="2"/>
+      <c r="BN381" s="2"/>
+      <c r="BO381" s="2"/>
+      <c r="BP381" s="2"/>
+      <c r="BQ381" s="2"/>
+      <c r="BR381" s="2"/>
+      <c r="BS381" s="2"/>
+    </row>
+    <row r="382" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C382" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D382" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW382" s="2"/>
+      <c r="AX382" s="2"/>
+      <c r="AY382" s="2"/>
+      <c r="AZ382" s="2"/>
+      <c r="BA382" s="2"/>
+      <c r="BB382" s="2"/>
+      <c r="BC382" s="2"/>
+      <c r="BD382" s="2"/>
+      <c r="BE382" s="2"/>
+      <c r="BF382" s="2"/>
+      <c r="BG382" s="2"/>
+      <c r="BH382" s="2"/>
+      <c r="BI382" s="2"/>
+      <c r="BJ382" s="2"/>
+      <c r="BK382" s="2"/>
+      <c r="BL382" s="2"/>
+      <c r="BM382" s="2"/>
+      <c r="BN382" s="2"/>
+      <c r="BO382" s="2"/>
+      <c r="BP382" s="2"/>
+      <c r="BQ382" s="2"/>
+      <c r="BR382" s="2"/>
+      <c r="BS382" s="2"/>
+    </row>
+    <row r="383" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C383" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D383" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW383" s="2"/>
+      <c r="AX383" s="2"/>
+      <c r="AY383" s="2"/>
+      <c r="AZ383" s="2"/>
+      <c r="BA383" s="2"/>
+      <c r="BB383" s="2"/>
+      <c r="BC383" s="2"/>
+      <c r="BD383" s="2"/>
+      <c r="BE383" s="2"/>
+      <c r="BF383" s="2"/>
+      <c r="BG383" s="2"/>
+      <c r="BH383" s="2"/>
+      <c r="BI383" s="2"/>
+      <c r="BJ383" s="2"/>
+      <c r="BK383" s="2"/>
+      <c r="BL383" s="2"/>
+      <c r="BM383" s="2"/>
+      <c r="BN383" s="2"/>
+      <c r="BO383" s="2"/>
+      <c r="BP383" s="2"/>
+      <c r="BQ383" s="2"/>
+      <c r="BR383" s="2"/>
+      <c r="BS383" s="2"/>
+    </row>
+    <row r="384" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C384" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D384" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW384" s="2"/>
+      <c r="AX384" s="2"/>
+      <c r="AY384" s="2"/>
+      <c r="AZ384" s="2"/>
+      <c r="BA384" s="2"/>
+      <c r="BB384" s="2"/>
+      <c r="BC384" s="2"/>
+      <c r="BD384" s="2"/>
+      <c r="BE384" s="2"/>
+      <c r="BF384" s="2"/>
+      <c r="BG384" s="2"/>
+      <c r="BH384" s="2"/>
+      <c r="BI384" s="2"/>
+      <c r="BJ384" s="2"/>
+      <c r="BK384" s="2"/>
+      <c r="BL384" s="2"/>
+      <c r="BM384" s="2"/>
+      <c r="BN384" s="2"/>
+      <c r="BO384" s="2"/>
+      <c r="BP384" s="2"/>
+      <c r="BQ384" s="2"/>
+      <c r="BR384" s="2"/>
+      <c r="BS384" s="2"/>
+    </row>
+    <row r="385" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C385" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D385" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW385" s="2"/>
+      <c r="AX385" s="2"/>
+      <c r="AY385" s="2"/>
+      <c r="AZ385" s="2"/>
+      <c r="BA385" s="2"/>
+      <c r="BB385" s="2"/>
+      <c r="BC385" s="2"/>
+      <c r="BD385" s="2"/>
+      <c r="BE385" s="2"/>
+      <c r="BF385" s="2"/>
+      <c r="BG385" s="2"/>
+      <c r="BH385" s="2"/>
+      <c r="BI385" s="2"/>
+      <c r="BJ385" s="2"/>
+      <c r="BK385" s="2"/>
+      <c r="BL385" s="2"/>
+      <c r="BM385" s="2"/>
+      <c r="BN385" s="2"/>
+      <c r="BO385" s="2"/>
+      <c r="BP385" s="2"/>
+      <c r="BQ385" s="2"/>
+      <c r="BR385" s="2"/>
+      <c r="BS385" s="2"/>
+    </row>
+    <row r="386" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="AW386" s="2"/>
+      <c r="AX386" s="2"/>
+      <c r="AY386" s="2"/>
+      <c r="AZ386" s="2"/>
+      <c r="BA386" s="2"/>
+      <c r="BB386" s="2"/>
+      <c r="BC386" s="2"/>
+      <c r="BD386" s="2"/>
+      <c r="BE386" s="2"/>
+      <c r="BF386" s="2"/>
+      <c r="BG386" s="2"/>
+      <c r="BH386" s="2"/>
+      <c r="BI386" s="2"/>
+      <c r="BJ386" s="2"/>
+      <c r="BK386" s="2"/>
+      <c r="BL386" s="2"/>
+      <c r="BM386" s="2"/>
+      <c r="BN386" s="2"/>
+      <c r="BO386" s="2"/>
+      <c r="BP386" s="2"/>
+      <c r="BQ386" s="2"/>
+      <c r="BR386" s="2"/>
+      <c r="BS386" s="2"/>
+    </row>
+    <row r="387" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="B387" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F387" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J387" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N387" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="R387" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AW387" s="2"/>
+      <c r="AX387" s="2"/>
+      <c r="AY387" s="2"/>
+      <c r="AZ387" s="2"/>
+      <c r="BA387" s="2"/>
+      <c r="BB387" s="2"/>
+      <c r="BC387" s="2"/>
+      <c r="BD387" s="2"/>
+      <c r="BE387" s="2"/>
+      <c r="BF387" s="2"/>
+      <c r="BG387" s="2"/>
+      <c r="BH387" s="2"/>
+      <c r="BI387" s="2"/>
+      <c r="BJ387" s="2"/>
+      <c r="BK387" s="2"/>
+      <c r="BL387" s="2"/>
+      <c r="BM387" s="2"/>
+      <c r="BN387" s="2"/>
+      <c r="BO387" s="2"/>
+      <c r="BP387" s="2"/>
+      <c r="BQ387" s="2"/>
+      <c r="BR387" s="2"/>
+      <c r="BS387" s="2"/>
+    </row>
+    <row r="388" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C388" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D309" s="1" t="s">
+      <c r="D388" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G388" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H388" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW388" s="2"/>
+      <c r="AX388" s="2"/>
+      <c r="AY388" s="2"/>
+      <c r="AZ388" s="2"/>
+      <c r="BA388" s="2"/>
+      <c r="BB388" s="2"/>
+      <c r="BC388" s="2"/>
+      <c r="BD388" s="2"/>
+      <c r="BE388" s="2"/>
+      <c r="BF388" s="2"/>
+      <c r="BG388" s="2"/>
+      <c r="BH388" s="2"/>
+      <c r="BI388" s="2"/>
+      <c r="BJ388" s="2"/>
+      <c r="BK388" s="2"/>
+      <c r="BL388" s="2"/>
+      <c r="BM388" s="2"/>
+      <c r="BN388" s="2"/>
+      <c r="BO388" s="2"/>
+      <c r="BP388" s="2"/>
+      <c r="BQ388" s="2"/>
+      <c r="BR388" s="2"/>
+      <c r="BS388" s="2"/>
+    </row>
+    <row r="389" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C389" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D389" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G389" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H389" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW389" s="2"/>
+      <c r="AX389" s="2"/>
+      <c r="AY389" s="2"/>
+      <c r="AZ389" s="2"/>
+      <c r="BA389" s="2"/>
+      <c r="BB389" s="2"/>
+      <c r="BC389" s="2"/>
+      <c r="BD389" s="2"/>
+      <c r="BE389" s="2"/>
+      <c r="BF389" s="2"/>
+      <c r="BG389" s="2"/>
+      <c r="BH389" s="2"/>
+      <c r="BI389" s="2"/>
+      <c r="BJ389" s="2"/>
+      <c r="BK389" s="2"/>
+      <c r="BL389" s="2"/>
+      <c r="BM389" s="2"/>
+      <c r="BN389" s="2"/>
+      <c r="BO389" s="2"/>
+      <c r="BP389" s="2"/>
+      <c r="BQ389" s="2"/>
+      <c r="BR389" s="2"/>
+      <c r="BS389" s="2"/>
+    </row>
+    <row r="390" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C390" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="310" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C310" s="1" t="s">
+      <c r="D390" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G390" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D310" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="311" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C311" s="1" t="s">
+      <c r="H390" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW390" s="2"/>
+      <c r="AX390" s="2"/>
+      <c r="AY390" s="2"/>
+      <c r="AZ390" s="2"/>
+      <c r="BA390" s="2"/>
+      <c r="BB390" s="2"/>
+      <c r="BC390" s="2"/>
+      <c r="BD390" s="2"/>
+      <c r="BE390" s="2"/>
+      <c r="BF390" s="2"/>
+      <c r="BG390" s="2"/>
+      <c r="BH390" s="2"/>
+      <c r="BI390" s="2"/>
+      <c r="BJ390" s="2"/>
+      <c r="BK390" s="2"/>
+      <c r="BL390" s="2"/>
+      <c r="BM390" s="2"/>
+      <c r="BN390" s="2"/>
+      <c r="BO390" s="2"/>
+      <c r="BP390" s="2"/>
+      <c r="BQ390" s="2"/>
+      <c r="BR390" s="2"/>
+      <c r="BS390" s="2"/>
+    </row>
+    <row r="391" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C391" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D311" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="312" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C312" s="1" t="s">
+      <c r="D391" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW391" s="2"/>
+      <c r="AX391" s="2"/>
+      <c r="AY391" s="2"/>
+      <c r="AZ391" s="2"/>
+      <c r="BA391" s="2"/>
+      <c r="BB391" s="2"/>
+      <c r="BC391" s="2"/>
+      <c r="BD391" s="2"/>
+      <c r="BE391" s="2"/>
+      <c r="BF391" s="2"/>
+      <c r="BG391" s="2"/>
+      <c r="BH391" s="2"/>
+      <c r="BI391" s="2"/>
+      <c r="BJ391" s="2"/>
+      <c r="BK391" s="2"/>
+      <c r="BL391" s="2"/>
+      <c r="BM391" s="2"/>
+      <c r="BN391" s="2"/>
+      <c r="BO391" s="2"/>
+      <c r="BP391" s="2"/>
+      <c r="BQ391" s="2"/>
+      <c r="BR391" s="2"/>
+      <c r="BS391" s="2"/>
+    </row>
+    <row r="392" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C392" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D392" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G392" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H392" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW392" s="2"/>
+      <c r="AX392" s="2"/>
+      <c r="AY392" s="2"/>
+      <c r="AZ392" s="2"/>
+      <c r="BA392" s="2"/>
+      <c r="BB392" s="2"/>
+      <c r="BC392" s="2"/>
+      <c r="BD392" s="2"/>
+      <c r="BE392" s="2"/>
+      <c r="BF392" s="2"/>
+      <c r="BG392" s="2"/>
+      <c r="BH392" s="2"/>
+      <c r="BI392" s="2"/>
+      <c r="BJ392" s="2"/>
+      <c r="BK392" s="2"/>
+      <c r="BL392" s="2"/>
+      <c r="BM392" s="2"/>
+      <c r="BN392" s="2"/>
+      <c r="BO392" s="2"/>
+      <c r="BP392" s="2"/>
+      <c r="BQ392" s="2"/>
+      <c r="BR392" s="2"/>
+      <c r="BS392" s="2"/>
+    </row>
+    <row r="393" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C393" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D393" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G393" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H393" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW393" s="2"/>
+      <c r="AX393" s="2"/>
+      <c r="AY393" s="2"/>
+      <c r="AZ393" s="2"/>
+      <c r="BA393" s="2"/>
+      <c r="BB393" s="2"/>
+      <c r="BC393" s="2"/>
+      <c r="BD393" s="2"/>
+      <c r="BE393" s="2"/>
+      <c r="BF393" s="2"/>
+      <c r="BG393" s="2"/>
+      <c r="BH393" s="2"/>
+      <c r="BI393" s="2"/>
+      <c r="BJ393" s="2"/>
+      <c r="BK393" s="2"/>
+      <c r="BL393" s="2"/>
+      <c r="BM393" s="2"/>
+      <c r="BN393" s="2"/>
+      <c r="BO393" s="2"/>
+      <c r="BP393" s="2"/>
+      <c r="BQ393" s="2"/>
+      <c r="BR393" s="2"/>
+      <c r="BS393" s="2"/>
+    </row>
+    <row r="394" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C394" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D394" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW394" s="2"/>
+      <c r="AX394" s="2"/>
+      <c r="AY394" s="2"/>
+      <c r="AZ394" s="2"/>
+      <c r="BA394" s="2"/>
+      <c r="BB394" s="2"/>
+      <c r="BC394" s="2"/>
+      <c r="BD394" s="2"/>
+      <c r="BE394" s="2"/>
+      <c r="BF394" s="2"/>
+      <c r="BG394" s="2"/>
+      <c r="BH394" s="2"/>
+      <c r="BI394" s="2"/>
+      <c r="BJ394" s="2"/>
+      <c r="BK394" s="2"/>
+      <c r="BL394" s="2"/>
+      <c r="BM394" s="2"/>
+      <c r="BN394" s="2"/>
+      <c r="BO394" s="2"/>
+      <c r="BP394" s="2"/>
+      <c r="BQ394" s="2"/>
+      <c r="BR394" s="2"/>
+      <c r="BS394" s="2"/>
+    </row>
+    <row r="395" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C395" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW395" s="2"/>
+      <c r="AX395" s="2"/>
+      <c r="AY395" s="2"/>
+      <c r="AZ395" s="2"/>
+      <c r="BA395" s="2"/>
+      <c r="BB395" s="2"/>
+      <c r="BC395" s="2"/>
+      <c r="BD395" s="2"/>
+      <c r="BE395" s="2"/>
+      <c r="BF395" s="2"/>
+      <c r="BG395" s="2"/>
+      <c r="BH395" s="2"/>
+      <c r="BI395" s="2"/>
+      <c r="BJ395" s="2"/>
+      <c r="BK395" s="2"/>
+      <c r="BL395" s="2"/>
+      <c r="BM395" s="2"/>
+      <c r="BN395" s="2"/>
+      <c r="BO395" s="2"/>
+      <c r="BP395" s="2"/>
+      <c r="BQ395" s="2"/>
+      <c r="BR395" s="2"/>
+      <c r="BS395" s="2"/>
+    </row>
+    <row r="396" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C396" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D396" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW396" s="2"/>
+      <c r="AX396" s="2"/>
+      <c r="AY396" s="2"/>
+      <c r="AZ396" s="2"/>
+      <c r="BA396" s="2"/>
+      <c r="BB396" s="2"/>
+      <c r="BC396" s="2"/>
+      <c r="BD396" s="2"/>
+      <c r="BE396" s="2"/>
+      <c r="BF396" s="2"/>
+      <c r="BG396" s="2"/>
+      <c r="BH396" s="2"/>
+      <c r="BI396" s="2"/>
+      <c r="BJ396" s="2"/>
+      <c r="BK396" s="2"/>
+      <c r="BL396" s="2"/>
+      <c r="BM396" s="2"/>
+      <c r="BN396" s="2"/>
+      <c r="BO396" s="2"/>
+      <c r="BP396" s="2"/>
+      <c r="BQ396" s="2"/>
+      <c r="BR396" s="2"/>
+      <c r="BS396" s="2"/>
+    </row>
+    <row r="397" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C397" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D397" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G397" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H397" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW397" s="2"/>
+      <c r="AX397" s="2"/>
+      <c r="AY397" s="2"/>
+      <c r="AZ397" s="2"/>
+      <c r="BA397" s="2"/>
+      <c r="BB397" s="2"/>
+      <c r="BC397" s="2"/>
+      <c r="BD397" s="2"/>
+      <c r="BE397" s="2"/>
+      <c r="BF397" s="2"/>
+      <c r="BG397" s="2"/>
+      <c r="BH397" s="2"/>
+      <c r="BI397" s="2"/>
+      <c r="BJ397" s="2"/>
+      <c r="BK397" s="2"/>
+      <c r="BL397" s="2"/>
+      <c r="BM397" s="2"/>
+      <c r="BN397" s="2"/>
+      <c r="BO397" s="2"/>
+      <c r="BP397" s="2"/>
+      <c r="BQ397" s="2"/>
+      <c r="BR397" s="2"/>
+      <c r="BS397" s="2"/>
+    </row>
+    <row r="398" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C398" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D398" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G398" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H398" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K398" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L398" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S398" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="T398" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AW398" s="2"/>
+      <c r="AX398" s="2"/>
+      <c r="AY398" s="2"/>
+      <c r="AZ398" s="2"/>
+      <c r="BA398" s="2"/>
+      <c r="BB398" s="2"/>
+      <c r="BC398" s="2"/>
+      <c r="BD398" s="2"/>
+      <c r="BE398" s="2"/>
+      <c r="BF398" s="2"/>
+      <c r="BG398" s="2"/>
+      <c r="BH398" s="2"/>
+      <c r="BI398" s="2"/>
+      <c r="BJ398" s="2"/>
+      <c r="BK398" s="2"/>
+      <c r="BL398" s="2"/>
+      <c r="BM398" s="2"/>
+      <c r="BN398" s="2"/>
+      <c r="BO398" s="2"/>
+      <c r="BP398" s="2"/>
+      <c r="BQ398" s="2"/>
+      <c r="BR398" s="2"/>
+      <c r="BS398" s="2"/>
+    </row>
+    <row r="399" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C399" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D399" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW399" s="2"/>
+      <c r="AX399" s="2"/>
+      <c r="AY399" s="2"/>
+      <c r="AZ399" s="2"/>
+      <c r="BA399" s="2"/>
+      <c r="BB399" s="2"/>
+      <c r="BC399" s="2"/>
+      <c r="BD399" s="2"/>
+      <c r="BE399" s="2"/>
+      <c r="BF399" s="2"/>
+      <c r="BG399" s="2"/>
+      <c r="BH399" s="2"/>
+      <c r="BI399" s="2"/>
+      <c r="BJ399" s="2"/>
+      <c r="BK399" s="2"/>
+      <c r="BL399" s="2"/>
+      <c r="BM399" s="2"/>
+      <c r="BN399" s="2"/>
+      <c r="BO399" s="2"/>
+      <c r="BP399" s="2"/>
+      <c r="BQ399" s="2"/>
+      <c r="BR399" s="2"/>
+      <c r="BS399" s="2"/>
+    </row>
+    <row r="400" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C400" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D312" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="313" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C313" s="1" t="s">
+      <c r="D400" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G400" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H400" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K400" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L400" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O400" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P400" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW400" s="2"/>
+      <c r="AX400" s="2"/>
+      <c r="AY400" s="2"/>
+      <c r="AZ400" s="2"/>
+      <c r="BA400" s="2"/>
+      <c r="BB400" s="2"/>
+      <c r="BC400" s="2"/>
+      <c r="BD400" s="2"/>
+      <c r="BE400" s="2"/>
+      <c r="BF400" s="2"/>
+      <c r="BG400" s="2"/>
+      <c r="BH400" s="2"/>
+      <c r="BI400" s="2"/>
+      <c r="BJ400" s="2"/>
+      <c r="BK400" s="2"/>
+      <c r="BL400" s="2"/>
+      <c r="BM400" s="2"/>
+      <c r="BN400" s="2"/>
+      <c r="BO400" s="2"/>
+      <c r="BP400" s="2"/>
+      <c r="BQ400" s="2"/>
+      <c r="BR400" s="2"/>
+      <c r="BS400" s="2"/>
+    </row>
+    <row r="401" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="AW401" s="2"/>
+      <c r="AX401" s="2"/>
+      <c r="AY401" s="2"/>
+      <c r="AZ401" s="2"/>
+      <c r="BA401" s="2"/>
+      <c r="BB401" s="2"/>
+      <c r="BC401" s="2"/>
+      <c r="BD401" s="2"/>
+      <c r="BE401" s="2"/>
+      <c r="BF401" s="2"/>
+      <c r="BG401" s="2"/>
+      <c r="BH401" s="2"/>
+      <c r="BI401" s="2"/>
+      <c r="BJ401" s="2"/>
+      <c r="BK401" s="2"/>
+      <c r="BL401" s="2"/>
+      <c r="BM401" s="2"/>
+      <c r="BN401" s="2"/>
+      <c r="BO401" s="2"/>
+      <c r="BP401" s="2"/>
+      <c r="BQ401" s="2"/>
+      <c r="BR401" s="2"/>
+      <c r="BS401" s="2"/>
+    </row>
+    <row r="402" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="B402" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F402" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J402" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="R402" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AW402" s="2"/>
+      <c r="AX402" s="2"/>
+      <c r="AY402" s="2"/>
+      <c r="AZ402" s="2"/>
+      <c r="BA402" s="2"/>
+      <c r="BB402" s="2"/>
+      <c r="BC402" s="2"/>
+      <c r="BD402" s="2"/>
+      <c r="BE402" s="2"/>
+      <c r="BF402" s="2"/>
+      <c r="BG402" s="2"/>
+      <c r="BH402" s="2"/>
+      <c r="BI402" s="2"/>
+      <c r="BJ402" s="2"/>
+      <c r="BK402" s="2"/>
+      <c r="BL402" s="2"/>
+      <c r="BM402" s="2"/>
+      <c r="BN402" s="2"/>
+      <c r="BO402" s="2"/>
+      <c r="BP402" s="2"/>
+      <c r="BQ402" s="2"/>
+      <c r="BR402" s="2"/>
+      <c r="BS402" s="2"/>
+    </row>
+    <row r="403" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C403" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D403" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G403" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H403" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AW403" s="2"/>
+      <c r="AX403" s="2"/>
+      <c r="AY403" s="2"/>
+      <c r="AZ403" s="2"/>
+      <c r="BA403" s="2"/>
+      <c r="BB403" s="2"/>
+      <c r="BC403" s="2"/>
+      <c r="BD403" s="2"/>
+      <c r="BE403" s="2"/>
+      <c r="BF403" s="2"/>
+      <c r="BG403" s="2"/>
+      <c r="BH403" s="2"/>
+      <c r="BI403" s="2"/>
+      <c r="BJ403" s="2"/>
+      <c r="BK403" s="2"/>
+      <c r="BL403" s="2"/>
+      <c r="BM403" s="2"/>
+      <c r="BN403" s="2"/>
+      <c r="BO403" s="2"/>
+      <c r="BP403" s="2"/>
+      <c r="BQ403" s="2"/>
+      <c r="BR403" s="2"/>
+      <c r="BS403" s="2"/>
+    </row>
+    <row r="404" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C404" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D404" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G404" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H404" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AW404" s="2"/>
+      <c r="AX404" s="2"/>
+      <c r="AY404" s="2"/>
+      <c r="AZ404" s="2"/>
+      <c r="BA404" s="2"/>
+      <c r="BB404" s="2"/>
+      <c r="BC404" s="2"/>
+      <c r="BD404" s="2"/>
+      <c r="BE404" s="2"/>
+      <c r="BF404" s="2"/>
+      <c r="BG404" s="2"/>
+      <c r="BH404" s="2"/>
+      <c r="BI404" s="2"/>
+      <c r="BJ404" s="2"/>
+      <c r="BK404" s="2"/>
+      <c r="BL404" s="2"/>
+      <c r="BM404" s="2"/>
+      <c r="BN404" s="2"/>
+      <c r="BO404" s="2"/>
+      <c r="BP404" s="2"/>
+      <c r="BQ404" s="2"/>
+      <c r="BR404" s="2"/>
+      <c r="BS404" s="2"/>
+    </row>
+    <row r="405" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C405" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D405" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G405" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H405" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AW405" s="2"/>
+      <c r="AX405" s="2"/>
+      <c r="AY405" s="2"/>
+      <c r="AZ405" s="2"/>
+      <c r="BA405" s="2"/>
+      <c r="BB405" s="2"/>
+      <c r="BC405" s="2"/>
+      <c r="BD405" s="2"/>
+      <c r="BE405" s="2"/>
+      <c r="BF405" s="2"/>
+      <c r="BG405" s="2"/>
+      <c r="BH405" s="2"/>
+      <c r="BI405" s="2"/>
+      <c r="BJ405" s="2"/>
+      <c r="BK405" s="2"/>
+      <c r="BL405" s="2"/>
+      <c r="BM405" s="2"/>
+      <c r="BN405" s="2"/>
+      <c r="BO405" s="2"/>
+      <c r="BP405" s="2"/>
+      <c r="BQ405" s="2"/>
+      <c r="BR405" s="2"/>
+      <c r="BS405" s="2"/>
+    </row>
+    <row r="406" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C406" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D406" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AW406" s="2"/>
+      <c r="AX406" s="2"/>
+      <c r="AY406" s="2"/>
+      <c r="AZ406" s="2"/>
+      <c r="BA406" s="2"/>
+      <c r="BB406" s="2"/>
+      <c r="BC406" s="2"/>
+      <c r="BD406" s="2"/>
+      <c r="BE406" s="2"/>
+      <c r="BF406" s="2"/>
+      <c r="BG406" s="2"/>
+      <c r="BH406" s="2"/>
+      <c r="BI406" s="2"/>
+      <c r="BJ406" s="2"/>
+      <c r="BK406" s="2"/>
+      <c r="BL406" s="2"/>
+      <c r="BM406" s="2"/>
+      <c r="BN406" s="2"/>
+      <c r="BO406" s="2"/>
+      <c r="BP406" s="2"/>
+      <c r="BQ406" s="2"/>
+      <c r="BR406" s="2"/>
+      <c r="BS406" s="2"/>
+    </row>
+    <row r="407" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C407" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D313" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="314" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C314" s="1" t="s">
+      <c r="D407" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G407" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H407" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K407" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L407" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S407" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="T407" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AW407" s="2"/>
+      <c r="AX407" s="2"/>
+      <c r="AY407" s="2"/>
+      <c r="AZ407" s="2"/>
+      <c r="BA407" s="2"/>
+      <c r="BB407" s="2"/>
+      <c r="BC407" s="2"/>
+      <c r="BD407" s="2"/>
+      <c r="BE407" s="2"/>
+      <c r="BF407" s="2"/>
+      <c r="BG407" s="2"/>
+      <c r="BH407" s="2"/>
+      <c r="BI407" s="2"/>
+      <c r="BJ407" s="2"/>
+      <c r="BK407" s="2"/>
+      <c r="BL407" s="2"/>
+      <c r="BM407" s="2"/>
+      <c r="BN407" s="2"/>
+      <c r="BO407" s="2"/>
+      <c r="BP407" s="2"/>
+      <c r="BQ407" s="2"/>
+      <c r="BR407" s="2"/>
+      <c r="BS407" s="2"/>
+    </row>
+    <row r="408" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C408" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D408" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G408" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H408" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AW408" s="2"/>
+      <c r="AX408" s="2"/>
+      <c r="AY408" s="2"/>
+      <c r="AZ408" s="2"/>
+      <c r="BA408" s="2"/>
+      <c r="BB408" s="2"/>
+      <c r="BC408" s="2"/>
+      <c r="BD408" s="2"/>
+      <c r="BE408" s="2"/>
+      <c r="BF408" s="2"/>
+      <c r="BG408" s="2"/>
+      <c r="BH408" s="2"/>
+      <c r="BI408" s="2"/>
+      <c r="BJ408" s="2"/>
+      <c r="BK408" s="2"/>
+      <c r="BL408" s="2"/>
+      <c r="BM408" s="2"/>
+      <c r="BN408" s="2"/>
+      <c r="BO408" s="2"/>
+      <c r="BP408" s="2"/>
+      <c r="BQ408" s="2"/>
+      <c r="BR408" s="2"/>
+      <c r="BS408" s="2"/>
+    </row>
+    <row r="409" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C409" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D409" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AW409" s="2"/>
+      <c r="AX409" s="2"/>
+      <c r="AY409" s="2"/>
+      <c r="AZ409" s="2"/>
+      <c r="BA409" s="2"/>
+      <c r="BB409" s="2"/>
+      <c r="BC409" s="2"/>
+      <c r="BD409" s="2"/>
+      <c r="BE409" s="2"/>
+      <c r="BF409" s="2"/>
+      <c r="BG409" s="2"/>
+      <c r="BH409" s="2"/>
+      <c r="BI409" s="2"/>
+      <c r="BJ409" s="2"/>
+      <c r="BK409" s="2"/>
+      <c r="BL409" s="2"/>
+      <c r="BM409" s="2"/>
+      <c r="BN409" s="2"/>
+      <c r="BO409" s="2"/>
+      <c r="BP409" s="2"/>
+      <c r="BQ409" s="2"/>
+      <c r="BR409" s="2"/>
+      <c r="BS409" s="2"/>
+    </row>
+    <row r="410" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C410" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D410" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AW410" s="2"/>
+      <c r="AX410" s="2"/>
+      <c r="AY410" s="2"/>
+      <c r="AZ410" s="2"/>
+      <c r="BA410" s="2"/>
+      <c r="BB410" s="2"/>
+      <c r="BC410" s="2"/>
+      <c r="BD410" s="2"/>
+      <c r="BE410" s="2"/>
+      <c r="BF410" s="2"/>
+      <c r="BG410" s="2"/>
+      <c r="BH410" s="2"/>
+      <c r="BI410" s="2"/>
+      <c r="BJ410" s="2"/>
+      <c r="BK410" s="2"/>
+      <c r="BL410" s="2"/>
+      <c r="BM410" s="2"/>
+      <c r="BN410" s="2"/>
+      <c r="BO410" s="2"/>
+      <c r="BP410" s="2"/>
+      <c r="BQ410" s="2"/>
+      <c r="BR410" s="2"/>
+      <c r="BS410" s="2"/>
+    </row>
+    <row r="411" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C411" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D411" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AW411" s="2"/>
+      <c r="AX411" s="2"/>
+      <c r="AY411" s="2"/>
+      <c r="AZ411" s="2"/>
+      <c r="BA411" s="2"/>
+      <c r="BB411" s="2"/>
+      <c r="BC411" s="2"/>
+      <c r="BD411" s="2"/>
+      <c r="BE411" s="2"/>
+      <c r="BF411" s="2"/>
+      <c r="BG411" s="2"/>
+      <c r="BH411" s="2"/>
+      <c r="BI411" s="2"/>
+      <c r="BJ411" s="2"/>
+      <c r="BK411" s="2"/>
+      <c r="BL411" s="2"/>
+      <c r="BM411" s="2"/>
+      <c r="BN411" s="2"/>
+      <c r="BO411" s="2"/>
+      <c r="BP411" s="2"/>
+      <c r="BQ411" s="2"/>
+      <c r="BR411" s="2"/>
+      <c r="BS411" s="2"/>
+    </row>
+    <row r="412" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C412" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D412" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G412" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H412" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AW412" s="2"/>
+      <c r="AX412" s="2"/>
+      <c r="AY412" s="2"/>
+      <c r="AZ412" s="2"/>
+      <c r="BA412" s="2"/>
+      <c r="BB412" s="2"/>
+      <c r="BC412" s="2"/>
+      <c r="BD412" s="2"/>
+      <c r="BE412" s="2"/>
+      <c r="BF412" s="2"/>
+      <c r="BG412" s="2"/>
+      <c r="BH412" s="2"/>
+      <c r="BI412" s="2"/>
+      <c r="BJ412" s="2"/>
+      <c r="BK412" s="2"/>
+      <c r="BL412" s="2"/>
+      <c r="BM412" s="2"/>
+      <c r="BN412" s="2"/>
+      <c r="BO412" s="2"/>
+      <c r="BP412" s="2"/>
+      <c r="BQ412" s="2"/>
+      <c r="BR412" s="2"/>
+      <c r="BS412" s="2"/>
+    </row>
+    <row r="413" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C413" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D413" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AW413" s="2"/>
+      <c r="AX413" s="2"/>
+      <c r="AY413" s="2"/>
+      <c r="AZ413" s="2"/>
+      <c r="BA413" s="2"/>
+      <c r="BB413" s="2"/>
+      <c r="BC413" s="2"/>
+      <c r="BD413" s="2"/>
+      <c r="BE413" s="2"/>
+      <c r="BF413" s="2"/>
+      <c r="BG413" s="2"/>
+      <c r="BH413" s="2"/>
+      <c r="BI413" s="2"/>
+      <c r="BJ413" s="2"/>
+      <c r="BK413" s="2"/>
+      <c r="BL413" s="2"/>
+      <c r="BM413" s="2"/>
+      <c r="BN413" s="2"/>
+      <c r="BO413" s="2"/>
+      <c r="BP413" s="2"/>
+      <c r="BQ413" s="2"/>
+      <c r="BR413" s="2"/>
+      <c r="BS413" s="2"/>
+    </row>
+    <row r="414" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C414" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D414" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G414" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H414" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K414" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L414" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AW414" s="2"/>
+      <c r="AX414" s="2"/>
+      <c r="AY414" s="2"/>
+      <c r="AZ414" s="2"/>
+      <c r="BA414" s="2"/>
+      <c r="BB414" s="2"/>
+      <c r="BC414" s="2"/>
+      <c r="BD414" s="2"/>
+      <c r="BE414" s="2"/>
+      <c r="BF414" s="2"/>
+      <c r="BG414" s="2"/>
+      <c r="BH414" s="2"/>
+      <c r="BI414" s="2"/>
+      <c r="BJ414" s="2"/>
+      <c r="BK414" s="2"/>
+      <c r="BL414" s="2"/>
+      <c r="BM414" s="2"/>
+      <c r="BN414" s="2"/>
+      <c r="BO414" s="2"/>
+      <c r="BP414" s="2"/>
+      <c r="BQ414" s="2"/>
+      <c r="BR414" s="2"/>
+      <c r="BS414" s="2"/>
+    </row>
+    <row r="415" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C415" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D314" s="1" t="s">
+      <c r="D415" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G415" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H415" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AW415" s="2"/>
+      <c r="AX415" s="2"/>
+      <c r="AY415" s="2"/>
+      <c r="AZ415" s="2"/>
+      <c r="BA415" s="2"/>
+      <c r="BB415" s="2"/>
+      <c r="BC415" s="2"/>
+      <c r="BD415" s="2"/>
+      <c r="BE415" s="2"/>
+      <c r="BF415" s="2"/>
+      <c r="BG415" s="2"/>
+      <c r="BH415" s="2"/>
+      <c r="BI415" s="2"/>
+      <c r="BJ415" s="2"/>
+      <c r="BK415" s="2"/>
+      <c r="BL415" s="2"/>
+      <c r="BM415" s="2"/>
+      <c r="BN415" s="2"/>
+      <c r="BO415" s="2"/>
+      <c r="BP415" s="2"/>
+      <c r="BQ415" s="2"/>
+      <c r="BR415" s="2"/>
+      <c r="BS415" s="2"/>
+    </row>
+    <row r="416" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="AW416" s="2"/>
+      <c r="AX416" s="2"/>
+      <c r="AY416" s="2"/>
+      <c r="AZ416" s="2"/>
+      <c r="BA416" s="2"/>
+      <c r="BB416" s="2"/>
+      <c r="BC416" s="2"/>
+      <c r="BD416" s="2"/>
+      <c r="BE416" s="2"/>
+      <c r="BF416" s="2"/>
+      <c r="BG416" s="2"/>
+      <c r="BH416" s="2"/>
+      <c r="BI416" s="2"/>
+      <c r="BJ416" s="2"/>
+      <c r="BK416" s="2"/>
+      <c r="BL416" s="2"/>
+      <c r="BM416" s="2"/>
+      <c r="BN416" s="2"/>
+      <c r="BO416" s="2"/>
+      <c r="BP416" s="2"/>
+      <c r="BQ416" s="2"/>
+      <c r="BR416" s="2"/>
+      <c r="BS416" s="2"/>
+    </row>
+    <row r="417" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="B417" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="315" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C315" s="1" t="s">
+      <c r="F417" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V417" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW417" s="5"/>
+      <c r="AX417" s="5"/>
+      <c r="AY417" s="5"/>
+      <c r="AZ417" s="5"/>
+      <c r="BA417" s="2"/>
+      <c r="BB417" s="2"/>
+      <c r="BC417" s="2"/>
+      <c r="BD417" s="2"/>
+      <c r="BE417" s="2"/>
+      <c r="BF417" s="2"/>
+      <c r="BG417" s="2"/>
+      <c r="BH417" s="2"/>
+      <c r="BI417" s="2"/>
+      <c r="BJ417" s="2"/>
+      <c r="BK417" s="2"/>
+      <c r="BL417" s="2"/>
+      <c r="BM417" s="2"/>
+      <c r="BN417" s="2"/>
+      <c r="BO417" s="2"/>
+      <c r="BP417" s="2"/>
+      <c r="BQ417" s="2"/>
+      <c r="BR417" s="2"/>
+      <c r="BS417" s="2"/>
+    </row>
+    <row r="418" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C418" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G418" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H418" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W418" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X418" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW418" s="5"/>
+      <c r="AX418" s="5"/>
+      <c r="AY418" s="5"/>
+      <c r="AZ418" s="5"/>
+      <c r="BA418" s="2"/>
+      <c r="BB418" s="2"/>
+      <c r="BC418" s="2"/>
+      <c r="BD418" s="2"/>
+      <c r="BE418" s="2"/>
+      <c r="BF418" s="2"/>
+      <c r="BG418" s="2"/>
+      <c r="BH418" s="2"/>
+      <c r="BI418" s="2"/>
+      <c r="BJ418" s="2"/>
+      <c r="BK418" s="2"/>
+      <c r="BL418" s="2"/>
+      <c r="BM418" s="2"/>
+      <c r="BN418" s="2"/>
+      <c r="BO418" s="2"/>
+      <c r="BP418" s="2"/>
+      <c r="BQ418" s="2"/>
+      <c r="BR418" s="2"/>
+      <c r="BS418" s="2"/>
+    </row>
+    <row r="419" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C419" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D419" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G419" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H419" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W419" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X419" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW419" s="5"/>
+      <c r="AX419" s="5"/>
+      <c r="AY419" s="5"/>
+      <c r="AZ419" s="5"/>
+      <c r="BA419" s="2"/>
+      <c r="BB419" s="2"/>
+      <c r="BC419" s="2"/>
+      <c r="BD419" s="2"/>
+      <c r="BE419" s="2"/>
+      <c r="BF419" s="2"/>
+      <c r="BG419" s="2"/>
+      <c r="BH419" s="2"/>
+      <c r="BI419" s="2"/>
+      <c r="BJ419" s="2"/>
+      <c r="BK419" s="2"/>
+      <c r="BL419" s="2"/>
+      <c r="BM419" s="2"/>
+      <c r="BN419" s="2"/>
+      <c r="BO419" s="2"/>
+      <c r="BP419" s="2"/>
+      <c r="BQ419" s="2"/>
+      <c r="BR419" s="2"/>
+      <c r="BS419" s="2"/>
+    </row>
+    <row r="420" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C420" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D420" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW420" s="5"/>
+      <c r="AX420" s="5"/>
+      <c r="AY420" s="5"/>
+      <c r="AZ420" s="5"/>
+      <c r="BA420" s="2"/>
+      <c r="BB420" s="2"/>
+      <c r="BC420" s="2"/>
+      <c r="BD420" s="2"/>
+      <c r="BE420" s="2"/>
+      <c r="BF420" s="2"/>
+      <c r="BG420" s="2"/>
+      <c r="BH420" s="2"/>
+      <c r="BI420" s="2"/>
+      <c r="BJ420" s="2"/>
+      <c r="BK420" s="2"/>
+      <c r="BL420" s="2"/>
+      <c r="BM420" s="2"/>
+      <c r="BN420" s="2"/>
+      <c r="BO420" s="2"/>
+      <c r="BP420" s="2"/>
+      <c r="BQ420" s="2"/>
+      <c r="BR420" s="2"/>
+      <c r="BS420" s="2"/>
+    </row>
+    <row r="421" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C421" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D421" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G421" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H421" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W421" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X421" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW421" s="5"/>
+      <c r="AX421" s="5"/>
+      <c r="AY421" s="5"/>
+      <c r="AZ421" s="5"/>
+      <c r="BA421" s="2"/>
+      <c r="BB421" s="2"/>
+      <c r="BC421" s="2"/>
+      <c r="BD421" s="2"/>
+      <c r="BE421" s="2"/>
+      <c r="BF421" s="2"/>
+      <c r="BG421" s="2"/>
+      <c r="BH421" s="2"/>
+      <c r="BI421" s="2"/>
+      <c r="BJ421" s="2"/>
+      <c r="BK421" s="2"/>
+      <c r="BL421" s="2"/>
+      <c r="BM421" s="2"/>
+      <c r="BN421" s="2"/>
+      <c r="BO421" s="2"/>
+      <c r="BP421" s="2"/>
+      <c r="BQ421" s="2"/>
+      <c r="BR421" s="2"/>
+      <c r="BS421" s="2"/>
+    </row>
+    <row r="422" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C422" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D422" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G422" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H422" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW422" s="5"/>
+      <c r="AX422" s="5"/>
+      <c r="AY422" s="5"/>
+      <c r="AZ422" s="5"/>
+      <c r="BA422" s="2"/>
+      <c r="BB422" s="2"/>
+      <c r="BC422" s="2"/>
+      <c r="BD422" s="2"/>
+      <c r="BE422" s="2"/>
+      <c r="BF422" s="2"/>
+      <c r="BG422" s="2"/>
+      <c r="BH422" s="2"/>
+      <c r="BI422" s="2"/>
+      <c r="BJ422" s="2"/>
+      <c r="BK422" s="2"/>
+      <c r="BL422" s="2"/>
+      <c r="BM422" s="2"/>
+      <c r="BN422" s="2"/>
+      <c r="BO422" s="2"/>
+      <c r="BP422" s="2"/>
+      <c r="BQ422" s="2"/>
+      <c r="BR422" s="2"/>
+      <c r="BS422" s="2"/>
+    </row>
+    <row r="423" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C423" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D423" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G423" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H423" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W423" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X423" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW423" s="5"/>
+      <c r="AX423" s="5"/>
+      <c r="AY423" s="5"/>
+      <c r="AZ423" s="5"/>
+      <c r="BA423" s="2"/>
+      <c r="BB423" s="2"/>
+      <c r="BC423" s="2"/>
+      <c r="BD423" s="2"/>
+      <c r="BE423" s="2"/>
+      <c r="BF423" s="2"/>
+      <c r="BG423" s="2"/>
+      <c r="BH423" s="2"/>
+      <c r="BI423" s="2"/>
+      <c r="BJ423" s="2"/>
+      <c r="BK423" s="2"/>
+      <c r="BL423" s="2"/>
+      <c r="BM423" s="2"/>
+      <c r="BN423" s="2"/>
+      <c r="BO423" s="2"/>
+      <c r="BP423" s="2"/>
+      <c r="BQ423" s="2"/>
+      <c r="BR423" s="2"/>
+      <c r="BS423" s="2"/>
+    </row>
+    <row r="424" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C424" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D315" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="316" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C316" s="1" t="s">
+      <c r="D424" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G424" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H424" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W424" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="X424" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW424" s="5"/>
+      <c r="AX424" s="5"/>
+      <c r="AY424" s="5"/>
+      <c r="AZ424" s="5"/>
+      <c r="BA424" s="2"/>
+      <c r="BB424" s="2"/>
+      <c r="BC424" s="2"/>
+      <c r="BD424" s="2"/>
+      <c r="BE424" s="2"/>
+      <c r="BF424" s="2"/>
+      <c r="BG424" s="2"/>
+      <c r="BH424" s="2"/>
+      <c r="BI424" s="2"/>
+      <c r="BJ424" s="2"/>
+      <c r="BK424" s="2"/>
+      <c r="BL424" s="2"/>
+      <c r="BM424" s="2"/>
+      <c r="BN424" s="2"/>
+      <c r="BO424" s="2"/>
+      <c r="BP424" s="2"/>
+      <c r="BQ424" s="2"/>
+      <c r="BR424" s="2"/>
+      <c r="BS424" s="2"/>
+    </row>
+    <row r="425" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C425" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW425" s="2"/>
+      <c r="AX425" s="2"/>
+      <c r="AY425" s="2"/>
+      <c r="AZ425" s="2"/>
+      <c r="BA425" s="2"/>
+      <c r="BB425" s="2"/>
+      <c r="BC425" s="2"/>
+      <c r="BD425" s="2"/>
+      <c r="BE425" s="2"/>
+      <c r="BF425" s="2"/>
+      <c r="BG425" s="2"/>
+      <c r="BH425" s="2"/>
+      <c r="BI425" s="2"/>
+      <c r="BJ425" s="2"/>
+      <c r="BK425" s="2"/>
+      <c r="BL425" s="2"/>
+      <c r="BM425" s="2"/>
+      <c r="BN425" s="2"/>
+      <c r="BO425" s="2"/>
+      <c r="BP425" s="2"/>
+      <c r="BQ425" s="2"/>
+      <c r="BR425" s="2"/>
+      <c r="BS425" s="2"/>
+    </row>
+    <row r="426" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C426" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D426" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW426" s="2"/>
+      <c r="AX426" s="2"/>
+      <c r="AY426" s="2"/>
+      <c r="AZ426" s="2"/>
+      <c r="BA426" s="2"/>
+      <c r="BB426" s="2"/>
+      <c r="BC426" s="2"/>
+      <c r="BD426" s="2"/>
+      <c r="BE426" s="2"/>
+      <c r="BF426" s="2"/>
+      <c r="BG426" s="2"/>
+      <c r="BH426" s="2"/>
+      <c r="BI426" s="2"/>
+      <c r="BJ426" s="2"/>
+      <c r="BK426" s="2"/>
+      <c r="BL426" s="2"/>
+      <c r="BM426" s="2"/>
+      <c r="BN426" s="2"/>
+      <c r="BO426" s="2"/>
+      <c r="BP426" s="2"/>
+      <c r="BQ426" s="2"/>
+      <c r="BR426" s="2"/>
+      <c r="BS426" s="2"/>
+    </row>
+    <row r="427" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C427" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D427" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G427" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H427" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W427" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="X427" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW427" s="2"/>
+      <c r="AX427" s="2"/>
+      <c r="AY427" s="2"/>
+      <c r="AZ427" s="2"/>
+      <c r="BA427" s="2"/>
+      <c r="BB427" s="2"/>
+      <c r="BC427" s="2"/>
+      <c r="BD427" s="2"/>
+      <c r="BE427" s="2"/>
+      <c r="BF427" s="2"/>
+      <c r="BG427" s="2"/>
+      <c r="BH427" s="2"/>
+      <c r="BI427" s="2"/>
+      <c r="BJ427" s="2"/>
+      <c r="BK427" s="2"/>
+      <c r="BL427" s="2"/>
+      <c r="BM427" s="2"/>
+      <c r="BN427" s="2"/>
+      <c r="BO427" s="2"/>
+      <c r="BP427" s="2"/>
+      <c r="BQ427" s="2"/>
+      <c r="BR427" s="2"/>
+      <c r="BS427" s="2"/>
+    </row>
+    <row r="428" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C428" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D428" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G428" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H428" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW428" s="2"/>
+      <c r="AX428" s="2"/>
+      <c r="AY428" s="2"/>
+      <c r="AZ428" s="2"/>
+      <c r="BA428" s="2"/>
+      <c r="BB428" s="2"/>
+      <c r="BC428" s="2"/>
+      <c r="BD428" s="2"/>
+      <c r="BE428" s="2"/>
+      <c r="BF428" s="2"/>
+      <c r="BG428" s="2"/>
+      <c r="BH428" s="2"/>
+      <c r="BI428" s="2"/>
+      <c r="BJ428" s="2"/>
+      <c r="BK428" s="2"/>
+      <c r="BL428" s="2"/>
+      <c r="BM428" s="2"/>
+      <c r="BN428" s="2"/>
+      <c r="BO428" s="2"/>
+      <c r="BP428" s="2"/>
+      <c r="BQ428" s="2"/>
+      <c r="BR428" s="2"/>
+      <c r="BS428" s="2"/>
+    </row>
+    <row r="429" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C429" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D429" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="430" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="C430" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D316" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="317" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C317" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D317" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="318" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C318" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D318" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="319" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C319" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="320" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C320" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="321" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C321" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D321" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="323" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B323" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F323" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="324" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C324" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D324" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G324" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="325" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C325" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D325" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C326" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D326" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C327" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D327" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C328" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C329" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C330" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C331" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D331" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C332" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C333" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C334" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D334" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="335" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C335" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D335" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B337" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F337" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="338" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C338" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G338" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="339" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C339" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D339" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G339" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="340" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C340" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D340" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="341" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C341" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D341" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="342" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C342" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D342" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="343" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C343" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D343" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="344" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C344" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D344" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="345" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C345" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D345" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="346" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C346" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D346" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="347" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C347" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="348" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C348" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D348" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="350" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B350" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F350" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="351" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C351" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D351" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G351" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="352" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C352" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G352" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="353" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C353" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D353" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G353" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="354" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C354" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G354" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="355" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C355" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="356" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C356" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D356" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="357" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C357" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D357" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="358" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C358" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D358" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="359" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C359" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D359" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="361" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B361" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="362" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C362" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D362" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="363" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C363" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D363" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="364" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C364" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D364" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="365" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C365" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D365" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="366" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C366" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D366" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="367" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C367" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D367" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="368" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C368" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D368" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="369" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C369" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D369" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="370" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C370" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D370" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="371" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C371" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D371" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="372" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C372" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D372" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="373" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C373" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D373" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="374" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C374" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D374" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="376" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B376" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="377" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C377" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D377" s="1" t="s">
+      <c r="D430" s="1" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="378" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C378" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D378" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="379" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C379" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D379" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="380" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C380" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D380" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="381" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C381" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D381" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="382" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C382" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D382" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="383" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C383" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D383" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="384" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C384" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D384" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="385" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C385" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D385" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="386" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C386" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D386" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="387" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C387" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D387" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="388" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C388" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D388" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="389" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C389" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D389" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="391" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B391" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F391" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="392" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C392" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D392" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G392" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="393" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C393" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D393" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G393" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="394" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C394" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D394" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="395" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C395" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D395" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="396" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C396" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D396" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="397" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C397" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D397" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="398" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C398" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D398" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="399" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C399" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D399" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="400" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C400" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D400" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="401" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C401" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D401" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="402" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C402" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D402" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/temp/searchByMACTable.xlsx
+++ b/temp/searchByMACTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="102">
   <si>
     <t>2.1</t>
   </si>
@@ -133,16 +133,10 @@
     <t>21</t>
   </si>
   <si>
-    <t>ЭСПЦ-2</t>
-  </si>
-  <si>
     <t>9</t>
   </si>
   <si>
     <t>24</t>
-  </si>
-  <si>
-    <t>4.3</t>
   </si>
   <si>
     <t>7</t>
@@ -157,31 +151,175 @@
     <t>8.1</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>24.1</t>
-  </si>
-  <si>
     <t>13.2</t>
-  </si>
-  <si>
-    <t>7.1</t>
-  </si>
-  <si>
-    <t>17.48</t>
   </si>
   <si>
     <t>12.24</t>
   </si>
   <si>
     <t>9.2</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>11_1</t>
+  </si>
+  <si>
+    <t>12_1</t>
+  </si>
+  <si>
+    <t>10_1</t>
+  </si>
+  <si>
+    <t>8_8</t>
+  </si>
+  <si>
+    <t>6.2_6</t>
+  </si>
+  <si>
+    <t>13_1</t>
+  </si>
+  <si>
+    <t>17_1</t>
+  </si>
+  <si>
+    <t>9_1</t>
+  </si>
+  <si>
+    <t>8_1</t>
+  </si>
+  <si>
+    <t>6.2_1</t>
+  </si>
+  <si>
+    <t>7_1</t>
+  </si>
+  <si>
+    <t>11_2</t>
+  </si>
+  <si>
+    <t>13_2</t>
+  </si>
+  <si>
+    <t>7_2</t>
+  </si>
+  <si>
+    <t>11_3</t>
+  </si>
+  <si>
+    <t>13_3</t>
+  </si>
+  <si>
+    <t>13_4</t>
+  </si>
+  <si>
+    <t>7_4</t>
+  </si>
+  <si>
+    <t>11_5</t>
+  </si>
+  <si>
+    <t>12_5</t>
+  </si>
+  <si>
+    <t>9_5</t>
+  </si>
+  <si>
+    <t>10_5</t>
+  </si>
+  <si>
+    <t>8_5</t>
+  </si>
+  <si>
+    <t>6.2_5</t>
+  </si>
+  <si>
+    <t>17_5</t>
+  </si>
+  <si>
+    <t>12_6</t>
+  </si>
+  <si>
+    <t>9_6</t>
+  </si>
+  <si>
+    <t>10_6</t>
+  </si>
+  <si>
+    <t>8_6</t>
+  </si>
+  <si>
+    <t>9_7</t>
+  </si>
+  <si>
+    <t>10_7</t>
+  </si>
+  <si>
+    <t>8_7</t>
+  </si>
+  <si>
+    <t>6.2_7</t>
+  </si>
+  <si>
+    <t>10_8</t>
+  </si>
+  <si>
+    <t>6.2_8</t>
+  </si>
+  <si>
+    <t>8_9</t>
+  </si>
+  <si>
+    <t>6.2_9</t>
+  </si>
+  <si>
+    <t>10_10</t>
+  </si>
+  <si>
+    <t>8_10</t>
+  </si>
+  <si>
+    <t>9_11</t>
+  </si>
+  <si>
+    <t>10_11</t>
+  </si>
+  <si>
+    <t>12_12</t>
+  </si>
+  <si>
+    <t>9_12</t>
+  </si>
+  <si>
+    <t>11_13</t>
+  </si>
+  <si>
+    <t>12_13</t>
+  </si>
+  <si>
+    <t>12_14</t>
+  </si>
+  <si>
+    <t>17_14</t>
+  </si>
+  <si>
+    <t>6.2.17</t>
+  </si>
+  <si>
+    <t>6.2.16</t>
+  </si>
+  <si>
+    <t>6.2.23</t>
+  </si>
+  <si>
+    <t>6.2.22</t>
   </si>
 </sst>
 </file>
@@ -588,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BW430"/>
+  <dimension ref="B3:BW428"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -599,17 +737,18 @@
     <col min="6" max="8" width="5" style="1" customWidth="1"/>
     <col min="9" max="9" width="4.85546875" style="1" customWidth="1"/>
     <col min="10" max="10" width="5.140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="6.140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="4.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="4.42578125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.28515625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="4.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="5.140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="5.28515625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="4.5703125" style="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" customWidth="1"/>
-    <col min="22" max="22" width="4.42578125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="4.28515625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="6.140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.140625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.85546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="7.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="7.85546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="6.28515625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="6.42578125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="7" style="1" customWidth="1"/>
+    <col min="22" max="22" width="6" style="1" customWidth="1"/>
+    <col min="23" max="23" width="6.28515625" style="1" customWidth="1"/>
     <col min="24" max="24" width="4.85546875" style="1" customWidth="1"/>
     <col min="25" max="25" width="4.28515625" style="1" customWidth="1"/>
     <col min="26" max="26" width="4.42578125" style="1" customWidth="1"/>
@@ -7100,7 +7239,7 @@
       <c r="J208" s="5"/>
       <c r="K208" s="5"/>
     </row>
-    <row r="209" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="209" spans="3:71" x14ac:dyDescent="0.25">
       <c r="C209" s="5">
         <v>5</v>
       </c>
@@ -7118,7 +7257,7 @@
       <c r="J209" s="5"/>
       <c r="K209" s="5"/>
     </row>
-    <row r="210" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="210" spans="3:71" x14ac:dyDescent="0.25">
       <c r="C210" s="5">
         <v>13</v>
       </c>
@@ -7136,7 +7275,7 @@
       <c r="J210" s="5"/>
       <c r="K210" s="5"/>
     </row>
-    <row r="211" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="211" spans="3:71" x14ac:dyDescent="0.25">
       <c r="C211" s="5">
         <v>21</v>
       </c>
@@ -7154,17 +7293,115 @@
       <c r="J211" s="5"/>
       <c r="K211" s="5"/>
     </row>
-    <row r="218" spans="1:71" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A220" s="1" t="s">
+    <row r="218" spans="3:71" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="3:71" x14ac:dyDescent="0.25">
+      <c r="I221" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J221" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K221" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L221" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M221" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N221" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O221" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P221" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q221" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R221" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="222" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="B222" s="1" t="s">
+      <c r="S221" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T221" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U221" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V221" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W221" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z221" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA221" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB221" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC221" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AW222" s="5"/>
+      <c r="AD221" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE221" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF221" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG221" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH221" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI221" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ221" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AK221" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL221" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM221" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ221" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AR221" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="222" spans="3:71" x14ac:dyDescent="0.25">
+      <c r="I222" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y222" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z222" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR222" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="AX222" s="5"/>
       <c r="AY222" s="5"/>
       <c r="AZ222" s="5"/>
@@ -7188,14 +7425,19 @@
       <c r="BR222" s="5"/>
       <c r="BS222" s="5"/>
     </row>
-    <row r="223" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="C223" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AW223" s="5"/>
+    <row r="223" spans="3:71" x14ac:dyDescent="0.25">
+      <c r="I223" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y223" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA223" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR223" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="AX223" s="5"/>
       <c r="AY223" s="5"/>
       <c r="AZ223" s="5"/>
@@ -7219,14 +7461,34 @@
       <c r="BR223" s="5"/>
       <c r="BS223" s="5"/>
     </row>
-    <row r="224" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="C224" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D224" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AW224" s="5"/>
+    <row r="224" spans="3:71" x14ac:dyDescent="0.25">
+      <c r="I224" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J224" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K224" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L224" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="N224" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="V224" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y224" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB224" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR224" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="AX224" s="5"/>
       <c r="AY224" s="5"/>
       <c r="AZ224" s="5"/>
@@ -7250,14 +7512,43 @@
       <c r="BR224" s="5"/>
       <c r="BS224" s="5"/>
     </row>
-    <row r="225" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C225" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D225" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AW225" s="5"/>
+    <row r="225" spans="9:75" x14ac:dyDescent="0.25">
+      <c r="I225" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J225" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N225" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O225" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="U225" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="V225" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="W225" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y225" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC225" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AQ225" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AR225" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS225" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="AX225" s="5"/>
       <c r="AY225" s="5"/>
       <c r="AZ225" s="5"/>
@@ -7281,14 +7572,43 @@
       <c r="BR225" s="9"/>
       <c r="BS225" s="9"/>
     </row>
-    <row r="226" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C226" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D226" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AW226" s="5"/>
+    <row r="226" spans="9:75" x14ac:dyDescent="0.25">
+      <c r="I226" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J226" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N226" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O226" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P226" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="T226" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="U226" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y226" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD226" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AQ226" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AR226" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS226" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="AX226" s="5"/>
       <c r="AY226" s="5"/>
       <c r="AZ226" s="5"/>
@@ -7312,14 +7632,49 @@
       <c r="BR226" s="2"/>
       <c r="BS226" s="2"/>
     </row>
-    <row r="227" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C227" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D227" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AW227" s="2"/>
+    <row r="227" spans="9:75" x14ac:dyDescent="0.25">
+      <c r="I227" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J227" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N227" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O227" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P227" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q227" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="S227" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T227" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y227" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE227" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AQ227" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR227" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS227" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT227" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="AX227" s="2"/>
       <c r="AY227" s="2"/>
       <c r="AZ227" s="2"/>
@@ -7343,16 +7698,49 @@
       <c r="BR227" s="2"/>
       <c r="BS227" s="2"/>
     </row>
-    <row r="228" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C228" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D228" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J228" s="3"/>
-      <c r="K228" s="3"/>
-      <c r="AW228" s="2"/>
+    <row r="228" spans="9:75" x14ac:dyDescent="0.25">
+      <c r="I228" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J228" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N228" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O228" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P228" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q228" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="R228" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="S228" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y228" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF228" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AQ228" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AR228" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS228" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT228" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="AX228" s="2"/>
       <c r="AY228" s="2"/>
       <c r="AZ228" s="2"/>
@@ -7378,16 +7766,46 @@
       <c r="BV228" s="3"/>
       <c r="BW228" s="3"/>
     </row>
-    <row r="229" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C229" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D229" s="1" t="s">
+    <row r="229" spans="9:75" x14ac:dyDescent="0.25">
+      <c r="I229" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J229" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="N229" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O229" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P229" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q229" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="R229" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y229" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG229" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ229" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR229" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS229" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J229" s="3"/>
-      <c r="K229" s="3"/>
-      <c r="AW229" s="2"/>
+      <c r="AT229" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AX229" s="2"/>
       <c r="AY229" s="2"/>
       <c r="AZ229" s="2"/>
@@ -7413,16 +7831,28 @@
       <c r="BV229" s="3"/>
       <c r="BW229" s="3"/>
     </row>
-    <row r="230" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C230" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J230" s="3"/>
-      <c r="K230" s="3"/>
-      <c r="AW230" s="2"/>
+    <row r="230" spans="9:75" x14ac:dyDescent="0.25">
+      <c r="I230" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y230" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH230" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ230" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR230" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS230" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AT230" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="AX230" s="2"/>
       <c r="AY230" s="2"/>
       <c r="AZ230" s="2"/>
@@ -7448,16 +7878,28 @@
       <c r="BV230" s="3"/>
       <c r="BW230" s="3"/>
     </row>
-    <row r="231" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C231" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D231" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J231" s="3"/>
-      <c r="K231" s="3"/>
-      <c r="AW231" s="2"/>
+    <row r="231" spans="9:75" x14ac:dyDescent="0.25">
+      <c r="I231" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y231" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI231" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ231" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AR231" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS231" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AT231" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="AX231" s="2"/>
       <c r="AY231" s="2"/>
       <c r="AZ231" s="2"/>
@@ -7483,16 +7925,31 @@
       <c r="BV231" s="3"/>
       <c r="BW231" s="3"/>
     </row>
-    <row r="232" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C232" s="1" t="s">
+    <row r="232" spans="9:75" x14ac:dyDescent="0.25">
+      <c r="I232" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y232" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AJ232" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ232" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR232" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS232" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AT232" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU232" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D232" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J232" s="3"/>
-      <c r="K232" s="3"/>
-      <c r="AW232" s="2"/>
       <c r="AX232" s="2"/>
       <c r="AY232" s="2"/>
       <c r="AZ232" s="2"/>
@@ -7518,16 +7975,43 @@
       <c r="BV232" s="3"/>
       <c r="BW232" s="3"/>
     </row>
-    <row r="233" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C233" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D233" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J233" s="3"/>
-      <c r="K233" s="3"/>
-      <c r="AW233" s="2"/>
+    <row r="233" spans="9:75" x14ac:dyDescent="0.25">
+      <c r="I233" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J233" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K233" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L233" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M233" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y233" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK233" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AQ233" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR233" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS233" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AT233" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU233" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="AX233" s="2"/>
       <c r="AY233" s="2"/>
       <c r="AZ233" s="2"/>
@@ -7553,16 +8037,43 @@
       <c r="BV233" s="3"/>
       <c r="BW233" s="3"/>
     </row>
-    <row r="234" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C234" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J234" s="3"/>
-      <c r="K234" s="3"/>
-      <c r="AW234" s="2"/>
+    <row r="234" spans="9:75" x14ac:dyDescent="0.25">
+      <c r="I234" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J234" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K234" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M234" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y234" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AL234" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AQ234" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AR234" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS234" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AT234" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU234" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AV234" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="AX234" s="2"/>
       <c r="AY234" s="2"/>
       <c r="AZ234" s="2"/>
@@ -7588,16 +8099,43 @@
       <c r="BV234" s="3"/>
       <c r="BW234" s="3"/>
     </row>
-    <row r="235" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C235" s="1" t="s">
+    <row r="235" spans="9:75" x14ac:dyDescent="0.25">
+      <c r="I235" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J235" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N235" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="W235" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y235" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM235" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AQ235" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D235" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J235" s="3"/>
-      <c r="K235" s="3"/>
-      <c r="AW235" s="2"/>
+      <c r="AR235" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS235" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AT235" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU235" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AV235" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="AX235" s="2"/>
       <c r="AY235" s="2"/>
       <c r="AZ235" s="2"/>
@@ -7623,10 +8161,30 @@
       <c r="BV235" s="3"/>
       <c r="BW235" s="3"/>
     </row>
-    <row r="236" spans="2:75" x14ac:dyDescent="0.25">
+    <row r="236" spans="9:75" x14ac:dyDescent="0.25">
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
-      <c r="AW236" s="2"/>
+      <c r="AQ236" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AR236" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS236" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AT236" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU236" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AV236" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AW236" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="AX236" s="2"/>
       <c r="AY236" s="2"/>
       <c r="AZ236" s="2"/>
@@ -7652,13 +8210,30 @@
       <c r="BV236" s="3"/>
       <c r="BW236" s="3"/>
     </row>
-    <row r="237" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="B237" s="1" t="s">
-        <v>29</v>
-      </c>
+    <row r="237" spans="9:75" x14ac:dyDescent="0.25">
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
-      <c r="AW237" s="2"/>
+      <c r="AQ237" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR237" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS237" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AT237" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU237" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AV237" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AW237" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="AX237" s="2"/>
       <c r="AY237" s="2"/>
       <c r="AZ237" s="2"/>
@@ -7684,13 +8259,7 @@
       <c r="BV237" s="3"/>
       <c r="BW237" s="3"/>
     </row>
-    <row r="238" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C238" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D238" s="1" t="s">
-        <v>20</v>
-      </c>
+    <row r="238" spans="9:75" x14ac:dyDescent="0.25">
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
       <c r="AW238" s="2"/>
@@ -7719,15 +8288,31 @@
       <c r="BV238" s="3"/>
       <c r="BW238" s="3"/>
     </row>
-    <row r="239" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C239" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D239" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J239" s="3"/>
-      <c r="K239" s="3"/>
+    <row r="239" spans="9:75" x14ac:dyDescent="0.25">
+      <c r="J239" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K239" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L239" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M239" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N239" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O239" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P239" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q239" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="AW239" s="2"/>
       <c r="AX239" s="2"/>
       <c r="AY239" s="2"/>
@@ -7754,15 +8339,31 @@
       <c r="BV239" s="3"/>
       <c r="BW239" s="3"/>
     </row>
-    <row r="240" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C240" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D240" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J240" s="3"/>
-      <c r="K240" s="3"/>
+    <row r="240" spans="9:75" x14ac:dyDescent="0.25">
+      <c r="J240" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K240" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L240" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M240" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N240" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="O240" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="P240" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q240" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="AW240" s="2"/>
       <c r="AX240" s="2"/>
       <c r="AY240" s="2"/>
@@ -7789,15 +8390,31 @@
       <c r="BV240" s="3"/>
       <c r="BW240" s="3"/>
     </row>
-    <row r="241" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C241" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D241" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J241" s="3"/>
-      <c r="K241" s="3"/>
+    <row r="241" spans="10:75" x14ac:dyDescent="0.25">
+      <c r="J241" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K241" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L241" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M241" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="N241" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O241" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P241" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q241" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="AW241" s="2"/>
       <c r="AX241" s="2"/>
       <c r="AY241" s="2"/>
@@ -7824,13 +8441,7 @@
       <c r="BV241" s="3"/>
       <c r="BW241" s="3"/>
     </row>
-    <row r="242" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C242" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>20</v>
-      </c>
+    <row r="242" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW242" s="2"/>
       <c r="AX242" s="2"/>
       <c r="AY242" s="2"/>
@@ -7855,13 +8466,7 @@
       <c r="BR242" s="2"/>
       <c r="BS242" s="2"/>
     </row>
-    <row r="243" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C243" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>20</v>
-      </c>
+    <row r="243" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW243" s="2"/>
       <c r="AX243" s="2"/>
       <c r="AY243" s="2"/>
@@ -7886,13 +8491,7 @@
       <c r="BR243" s="2"/>
       <c r="BS243" s="2"/>
     </row>
-    <row r="244" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C244" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D244" s="1" t="s">
-        <v>20</v>
-      </c>
+    <row r="244" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW244" s="2"/>
       <c r="AX244" s="2"/>
       <c r="AY244" s="2"/>
@@ -7917,13 +8516,7 @@
       <c r="BR244" s="2"/>
       <c r="BS244" s="2"/>
     </row>
-    <row r="245" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C245" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D245" s="1" t="s">
-        <v>20</v>
-      </c>
+    <row r="245" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW245" s="2"/>
       <c r="AX245" s="2"/>
       <c r="AY245" s="2"/>
@@ -7948,13 +8541,7 @@
       <c r="BR245" s="2"/>
       <c r="BS245" s="2"/>
     </row>
-    <row r="246" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C246" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>20</v>
-      </c>
+    <row r="246" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW246" s="2"/>
       <c r="AX246" s="2"/>
       <c r="AY246" s="2"/>
@@ -7979,13 +8566,7 @@
       <c r="BR246" s="2"/>
       <c r="BS246" s="2"/>
     </row>
-    <row r="247" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C247" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D247" s="1" t="s">
-        <v>20</v>
-      </c>
+    <row r="247" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW247" s="2"/>
       <c r="AX247" s="2"/>
       <c r="AY247" s="2"/>
@@ -8010,13 +8591,7 @@
       <c r="BR247" s="2"/>
       <c r="BS247" s="2"/>
     </row>
-    <row r="248" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C248" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>20</v>
-      </c>
+    <row r="248" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW248" s="2"/>
       <c r="AX248" s="2"/>
       <c r="AY248" s="2"/>
@@ -8041,13 +8616,7 @@
       <c r="BR248" s="2"/>
       <c r="BS248" s="2"/>
     </row>
-    <row r="249" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C249" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D249" s="1" t="s">
-        <v>20</v>
-      </c>
+    <row r="249" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW249" s="2"/>
       <c r="AX249" s="2"/>
       <c r="AY249" s="2"/>
@@ -8072,13 +8641,7 @@
       <c r="BR249" s="2"/>
       <c r="BS249" s="2"/>
     </row>
-    <row r="250" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C250" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D250" s="1" t="s">
-        <v>20</v>
-      </c>
+    <row r="250" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW250" s="2"/>
       <c r="AX250" s="2"/>
       <c r="AY250" s="2"/>
@@ -8103,7 +8666,7 @@
       <c r="BR250" s="2"/>
       <c r="BS250" s="2"/>
     </row>
-    <row r="251" spans="2:75" x14ac:dyDescent="0.25">
+    <row r="251" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW251" s="2"/>
       <c r="AX251" s="2"/>
       <c r="AY251" s="2"/>
@@ -8128,25 +8691,7 @@
       <c r="BR251" s="2"/>
       <c r="BS251" s="2"/>
     </row>
-    <row r="252" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="B252" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F252" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J252" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N252" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="V252" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z252" s="1" t="s">
-        <v>33</v>
-      </c>
+    <row r="252" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW252" s="5"/>
       <c r="AX252" s="5"/>
       <c r="AY252" s="5"/>
@@ -8171,25 +8716,7 @@
       <c r="BR252" s="5"/>
       <c r="BS252" s="5"/>
     </row>
-    <row r="253" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C253" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D253" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G253" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H253" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W253" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X253" s="1" t="s">
-        <v>44</v>
-      </c>
+    <row r="253" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW253" s="5"/>
       <c r="AX253" s="5"/>
       <c r="AY253" s="5"/>
@@ -8214,25 +8741,7 @@
       <c r="BR253" s="5"/>
       <c r="BS253" s="5"/>
     </row>
-    <row r="254" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C254" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G254" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H254" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W254" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="X254" s="1" t="s">
-        <v>44</v>
-      </c>
+    <row r="254" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW254" s="5"/>
       <c r="AX254" s="5"/>
       <c r="AY254" s="5"/>
@@ -8257,25 +8766,7 @@
       <c r="BR254" s="5"/>
       <c r="BS254" s="5"/>
     </row>
-    <row r="255" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C255" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D255" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G255" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H255" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W255" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X255" s="1" t="s">
-        <v>44</v>
-      </c>
+    <row r="255" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW255" s="5"/>
       <c r="AX255" s="5"/>
       <c r="AY255" s="5"/>
@@ -8300,25 +8791,7 @@
       <c r="BR255" s="5"/>
       <c r="BS255" s="5"/>
     </row>
-    <row r="256" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="C256" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D256" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W256" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="X256" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA256" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB256" s="1" t="s">
-        <v>44</v>
-      </c>
+    <row r="256" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW256" s="5"/>
       <c r="AX256" s="5"/>
       <c r="AY256" s="5"/>
@@ -8343,31 +8816,9 @@
       <c r="BR256" s="5"/>
       <c r="BS256" s="5"/>
     </row>
-    <row r="257" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C257" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G257" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H257" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K257" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L257" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O257" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="P257" s="3" t="s">
-        <v>15</v>
-      </c>
+    <row r="257" spans="15:71" x14ac:dyDescent="0.25">
+      <c r="O257" s="3"/>
+      <c r="P257" s="3"/>
       <c r="AW257" s="5"/>
       <c r="AX257" s="5"/>
       <c r="AY257" s="5"/>
@@ -8392,25 +8843,7 @@
       <c r="BR257" s="5"/>
       <c r="BS257" s="5"/>
     </row>
-    <row r="258" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C258" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D258" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G258" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H258" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W258" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="X258" s="1" t="s">
-        <v>44</v>
-      </c>
+    <row r="258" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW258" s="5"/>
       <c r="AX258" s="5"/>
       <c r="AY258" s="5"/>
@@ -8435,25 +8868,7 @@
       <c r="BR258" s="5"/>
       <c r="BS258" s="5"/>
     </row>
-    <row r="259" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C259" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D259" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W259" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X259" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA259" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB259" s="1" t="s">
-        <v>44</v>
-      </c>
+    <row r="259" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW259" s="5"/>
       <c r="AX259" s="5"/>
       <c r="AY259" s="5"/>
@@ -8478,25 +8893,7 @@
       <c r="BR259" s="2"/>
       <c r="BS259" s="2"/>
     </row>
-    <row r="260" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C260" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D260" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W260" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="X260" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA260" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB260" s="1" t="s">
-        <v>44</v>
-      </c>
+    <row r="260" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW260" s="5"/>
       <c r="AX260" s="5"/>
       <c r="AY260" s="5"/>
@@ -8521,25 +8918,7 @@
       <c r="BR260" s="2"/>
       <c r="BS260" s="2"/>
     </row>
-    <row r="261" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C261" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D261" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G261" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H261" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W261" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="X261" s="1" t="s">
-        <v>44</v>
-      </c>
+    <row r="261" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW261" s="5"/>
       <c r="AX261" s="5"/>
       <c r="AY261" s="5"/>
@@ -8564,25 +8943,7 @@
       <c r="BR261" s="2"/>
       <c r="BS261" s="2"/>
     </row>
-    <row r="262" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C262" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D262" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G262" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H262" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K262" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L262" s="1" t="s">
-        <v>15</v>
-      </c>
+    <row r="262" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW262" s="5"/>
       <c r="AX262" s="5"/>
       <c r="AY262" s="5"/>
@@ -8607,25 +8968,7 @@
       <c r="BR262" s="2"/>
       <c r="BS262" s="2"/>
     </row>
-    <row r="263" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C263" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W263" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X263" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA263" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB263" s="1" t="s">
-        <v>44</v>
-      </c>
+    <row r="263" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW263" s="5"/>
       <c r="AX263" s="5"/>
       <c r="AY263" s="5"/>
@@ -8650,25 +8993,7 @@
       <c r="BR263" s="2"/>
       <c r="BS263" s="2"/>
     </row>
-    <row r="264" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C264" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W264" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X264" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA264" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB264" s="1" t="s">
-        <v>44</v>
-      </c>
+    <row r="264" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW264" s="5"/>
       <c r="AX264" s="5"/>
       <c r="AY264" s="5"/>
@@ -8693,31 +9018,9 @@
       <c r="BR264" s="2"/>
       <c r="BS264" s="2"/>
     </row>
-    <row r="265" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C265" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D265" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G265" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H265" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W265" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X265" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA265" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB265" s="3" t="s">
-        <v>44</v>
-      </c>
+    <row r="265" spans="15:71" x14ac:dyDescent="0.25">
+      <c r="AA265" s="3"/>
+      <c r="AB265" s="3"/>
       <c r="AW265" s="5"/>
       <c r="AX265" s="5"/>
       <c r="AY265" s="5"/>
@@ -8742,7 +9045,7 @@
       <c r="BR265" s="2"/>
       <c r="BS265" s="2"/>
     </row>
-    <row r="266" spans="2:71" x14ac:dyDescent="0.25">
+    <row r="266" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW266" s="5"/>
       <c r="AX266" s="5"/>
       <c r="AY266" s="5"/>
@@ -8767,19 +9070,7 @@
       <c r="BR266" s="2"/>
       <c r="BS266" s="2"/>
     </row>
-    <row r="267" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="B267" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F267" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V267" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z267" s="1" t="s">
-        <v>34</v>
-      </c>
+    <row r="267" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW267" s="5"/>
       <c r="BA267" s="5"/>
       <c r="BB267" s="5"/>
@@ -8801,25 +9092,7 @@
       <c r="BR267" s="5"/>
       <c r="BS267" s="5"/>
     </row>
-    <row r="268" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C268" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G268" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H268" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="W268" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X268" s="1" t="s">
-        <v>13</v>
-      </c>
+    <row r="268" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW268" s="5"/>
       <c r="AY268" s="3"/>
       <c r="AZ268" s="3"/>
@@ -8843,25 +9116,7 @@
       <c r="BR268" s="5"/>
       <c r="BS268" s="5"/>
     </row>
-    <row r="269" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C269" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G269" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H269" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="W269" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="X269" s="1" t="s">
-        <v>13</v>
-      </c>
+    <row r="269" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW269" s="5"/>
       <c r="BA269" s="5"/>
       <c r="BB269" s="5"/>
@@ -8883,25 +9138,7 @@
       <c r="BR269" s="5"/>
       <c r="BS269" s="5"/>
     </row>
-    <row r="270" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C270" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D270" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G270" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H270" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="W270" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X270" s="1" t="s">
-        <v>54</v>
-      </c>
+    <row r="270" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW270" s="5"/>
       <c r="BA270" s="5"/>
       <c r="BB270" s="5"/>
@@ -8923,13 +9160,7 @@
       <c r="BR270" s="5"/>
       <c r="BS270" s="5"/>
     </row>
-    <row r="271" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C271" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>13</v>
-      </c>
+    <row r="271" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW271" s="5"/>
       <c r="BA271" s="5"/>
       <c r="BB271" s="5"/>
@@ -8951,31 +9182,9 @@
       <c r="BR271" s="5"/>
       <c r="BS271" s="5"/>
     </row>
-    <row r="272" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C272" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D272" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G272" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H272" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="W272" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="X272" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA272" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB272" s="3" t="s">
-        <v>12</v>
-      </c>
+    <row r="272" spans="15:71" x14ac:dyDescent="0.25">
+      <c r="AA272" s="3"/>
+      <c r="AB272" s="3"/>
       <c r="AW272" s="5"/>
       <c r="BA272" s="5"/>
       <c r="BB272" s="5"/>
@@ -8997,19 +9206,7 @@
       <c r="BR272" s="3"/>
       <c r="BS272" s="3"/>
     </row>
-    <row r="273" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C273" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G273" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H273" s="1" t="s">
-        <v>12</v>
-      </c>
+    <row r="273" spans="18:71" x14ac:dyDescent="0.25">
       <c r="AW273" s="2"/>
       <c r="BA273" s="2"/>
       <c r="BB273" s="2"/>
@@ -9031,25 +9228,7 @@
       <c r="BR273" s="2"/>
       <c r="BS273" s="2"/>
     </row>
-    <row r="274" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C274" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D274" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G274" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H274" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="W274" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="X274" s="1" t="s">
-        <v>13</v>
-      </c>
+    <row r="274" spans="18:71" x14ac:dyDescent="0.25">
       <c r="AW274" s="2"/>
       <c r="BA274" s="2"/>
       <c r="BB274" s="2"/>
@@ -9071,13 +9250,7 @@
       <c r="BR274" s="2"/>
       <c r="BS274" s="2"/>
     </row>
-    <row r="275" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C275" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D275" s="1" t="s">
-        <v>13</v>
-      </c>
+    <row r="275" spans="18:71" x14ac:dyDescent="0.25">
       <c r="AW275" s="2"/>
       <c r="BA275" s="2"/>
       <c r="BB275" s="2"/>
@@ -9099,13 +9272,7 @@
       <c r="BR275" s="2"/>
       <c r="BS275" s="2"/>
     </row>
-    <row r="276" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C276" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D276" s="1" t="s">
-        <v>13</v>
-      </c>
+    <row r="276" spans="18:71" x14ac:dyDescent="0.25">
       <c r="AW276" s="2"/>
       <c r="BA276" s="2"/>
       <c r="BB276" s="2"/>
@@ -9127,25 +9294,7 @@
       <c r="BR276" s="2"/>
       <c r="BS276" s="2"/>
     </row>
-    <row r="277" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C277" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G277" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H277" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="W277" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="X277" s="1" t="s">
-        <v>13</v>
-      </c>
+    <row r="277" spans="18:71" x14ac:dyDescent="0.25">
       <c r="AW277" s="2"/>
       <c r="BA277" s="2"/>
       <c r="BB277" s="2"/>
@@ -9167,19 +9316,7 @@
       <c r="BR277" s="2"/>
       <c r="BS277" s="2"/>
     </row>
-    <row r="278" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C278" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G278" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H278" s="1" t="s">
-        <v>12</v>
-      </c>
+    <row r="278" spans="18:71" x14ac:dyDescent="0.25">
       <c r="AW278" s="2"/>
       <c r="AX278" s="2"/>
       <c r="AY278" s="2"/>
@@ -9204,13 +9341,7 @@
       <c r="BR278" s="2"/>
       <c r="BS278" s="2"/>
     </row>
-    <row r="279" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C279" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D279" s="1" t="s">
-        <v>13</v>
-      </c>
+    <row r="279" spans="18:71" x14ac:dyDescent="0.25">
       <c r="AW279" s="2"/>
       <c r="AX279" s="2"/>
       <c r="AY279" s="2"/>
@@ -9235,13 +9366,7 @@
       <c r="BR279" s="2"/>
       <c r="BS279" s="2"/>
     </row>
-    <row r="280" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C280" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>13</v>
-      </c>
+    <row r="280" spans="18:71" x14ac:dyDescent="0.25">
       <c r="AW280" s="2"/>
       <c r="AX280" s="2"/>
       <c r="AY280" s="2"/>
@@ -9266,7 +9391,7 @@
       <c r="BR280" s="2"/>
       <c r="BS280" s="2"/>
     </row>
-    <row r="281" spans="2:71" x14ac:dyDescent="0.25">
+    <row r="281" spans="18:71" x14ac:dyDescent="0.25">
       <c r="AW281" s="2"/>
       <c r="AX281" s="2"/>
       <c r="AY281" s="2"/>
@@ -9291,16 +9416,7 @@
       <c r="BR281" s="2"/>
       <c r="BS281" s="2"/>
     </row>
-    <row r="282" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="B282" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F282" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V282" s="1" t="s">
-        <v>40</v>
-      </c>
+    <row r="282" spans="18:71" x14ac:dyDescent="0.25">
       <c r="AW282" s="2"/>
       <c r="BA282" s="2"/>
       <c r="BB282" s="2"/>
@@ -9322,25 +9438,7 @@
       <c r="BR282" s="2"/>
       <c r="BS282" s="2"/>
     </row>
-    <row r="283" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C283" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G283" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H283" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="W283" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="X283" s="1" t="s">
-        <v>45</v>
-      </c>
+    <row r="283" spans="18:71" x14ac:dyDescent="0.25">
       <c r="AW283" s="2"/>
       <c r="BA283" s="2"/>
       <c r="BB283" s="2"/>
@@ -9362,25 +9460,7 @@
       <c r="BR283" s="2"/>
       <c r="BS283" s="2"/>
     </row>
-    <row r="284" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C284" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D284" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G284" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H284" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="W284" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X284" s="1" t="s">
-        <v>55</v>
-      </c>
+    <row r="284" spans="18:71" x14ac:dyDescent="0.25">
       <c r="AW284" s="2"/>
       <c r="BA284" s="2"/>
       <c r="BB284" s="2"/>
@@ -9402,13 +9482,7 @@
       <c r="BR284" s="2"/>
       <c r="BS284" s="2"/>
     </row>
-    <row r="285" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C285" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>45</v>
-      </c>
+    <row r="285" spans="18:71" x14ac:dyDescent="0.25">
       <c r="R285" s="10"/>
       <c r="S285" s="10"/>
       <c r="AW285" s="2"/>
@@ -9432,27 +9506,9 @@
       <c r="BR285" s="2"/>
       <c r="BS285" s="2"/>
     </row>
-    <row r="286" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C286" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D286" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G286" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H286" s="1" t="s">
-        <v>55</v>
-      </c>
+    <row r="286" spans="18:71" x14ac:dyDescent="0.25">
       <c r="R286" s="10"/>
       <c r="S286" s="10"/>
-      <c r="W286" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="X286" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="AW286" s="2"/>
       <c r="BA286" s="2"/>
       <c r="BB286" s="2"/>
@@ -9474,19 +9530,7 @@
       <c r="BR286" s="2"/>
       <c r="BS286" s="2"/>
     </row>
-    <row r="287" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C287" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D287" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G287" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H287" s="1" t="s">
-        <v>55</v>
-      </c>
+    <row r="287" spans="18:71" x14ac:dyDescent="0.25">
       <c r="R287" s="10"/>
       <c r="S287" s="10"/>
       <c r="AW287" s="2"/>
@@ -9510,25 +9554,7 @@
       <c r="BR287" s="2"/>
       <c r="BS287" s="2"/>
     </row>
-    <row r="288" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C288" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D288" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G288" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H288" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="W288" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="X288" s="1" t="s">
-        <v>45</v>
-      </c>
+    <row r="288" spans="18:71" x14ac:dyDescent="0.25">
       <c r="AW288" s="2"/>
       <c r="BA288" s="2"/>
       <c r="BB288" s="2"/>
@@ -9550,25 +9576,7 @@
       <c r="BR288" s="2"/>
       <c r="BS288" s="2"/>
     </row>
-    <row r="289" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C289" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G289" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H289" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="W289" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X289" s="1" t="s">
-        <v>55</v>
-      </c>
+    <row r="289" spans="14:71" x14ac:dyDescent="0.25">
       <c r="AW289" s="2"/>
       <c r="AY289" s="3"/>
       <c r="AZ289" s="3"/>
@@ -9592,13 +9600,7 @@
       <c r="BR289" s="2"/>
       <c r="BS289" s="2"/>
     </row>
-    <row r="290" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C290" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>45</v>
-      </c>
+    <row r="290" spans="14:71" x14ac:dyDescent="0.25">
       <c r="AW290" s="2"/>
       <c r="BA290" s="2"/>
       <c r="BB290" s="2"/>
@@ -9620,13 +9622,7 @@
       <c r="BR290" s="2"/>
       <c r="BS290" s="2"/>
     </row>
-    <row r="291" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C291" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D291" s="1" t="s">
-        <v>45</v>
-      </c>
+    <row r="291" spans="14:71" x14ac:dyDescent="0.25">
       <c r="AW291" s="2"/>
       <c r="BA291" s="2"/>
       <c r="BB291" s="2"/>
@@ -9648,27 +9644,9 @@
       <c r="BR291" s="2"/>
       <c r="BS291" s="2"/>
     </row>
-    <row r="292" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C292" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G292" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H292" s="1" t="s">
-        <v>45</v>
-      </c>
+    <row r="292" spans="14:71" x14ac:dyDescent="0.25">
       <c r="N292" s="3"/>
       <c r="O292" s="3"/>
-      <c r="W292" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="X292" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="AU292" s="3"/>
       <c r="AV292" s="3"/>
       <c r="AW292" s="2"/>
@@ -9692,19 +9670,7 @@
       <c r="BR292" s="2"/>
       <c r="BS292" s="2"/>
     </row>
-    <row r="293" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C293" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G293" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H293" s="1" t="s">
-        <v>55</v>
-      </c>
+    <row r="293" spans="14:71" x14ac:dyDescent="0.25">
       <c r="N293" s="3"/>
       <c r="O293" s="3"/>
       <c r="AW293" s="2"/>
@@ -9731,13 +9697,7 @@
       <c r="BR293" s="2"/>
       <c r="BS293" s="2"/>
     </row>
-    <row r="294" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C294" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>45</v>
-      </c>
+    <row r="294" spans="14:71" x14ac:dyDescent="0.25">
       <c r="N294" s="3"/>
       <c r="O294" s="3"/>
       <c r="AW294" s="2"/>
@@ -9764,13 +9724,7 @@
       <c r="BR294" s="2"/>
       <c r="BS294" s="2"/>
     </row>
-    <row r="295" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C295" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>45</v>
-      </c>
+    <row r="295" spans="14:71" x14ac:dyDescent="0.25">
       <c r="N295" s="3"/>
       <c r="O295" s="3"/>
       <c r="AW295" s="2"/>
@@ -9797,7 +9751,7 @@
       <c r="BR295" s="2"/>
       <c r="BS295" s="2"/>
     </row>
-    <row r="296" spans="2:71" x14ac:dyDescent="0.25">
+    <row r="296" spans="14:71" x14ac:dyDescent="0.25">
       <c r="N296" s="3"/>
       <c r="O296" s="3"/>
       <c r="AW296" s="2"/>
@@ -9824,18 +9778,9 @@
       <c r="BR296" s="2"/>
       <c r="BS296" s="2"/>
     </row>
-    <row r="297" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="B297" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F297" s="1" t="s">
-        <v>32</v>
-      </c>
+    <row r="297" spans="14:71" x14ac:dyDescent="0.25">
       <c r="N297" s="3"/>
       <c r="O297" s="3"/>
-      <c r="V297" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="AW297" s="2"/>
       <c r="AX297" s="2"/>
       <c r="AY297" s="2"/>
@@ -9860,27 +9805,9 @@
       <c r="BR297" s="2"/>
       <c r="BS297" s="2"/>
     </row>
-    <row r="298" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C298" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G298" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H298" s="1" t="s">
-        <v>10</v>
-      </c>
+    <row r="298" spans="14:71" x14ac:dyDescent="0.25">
       <c r="N298" s="3"/>
       <c r="O298" s="3"/>
-      <c r="W298" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X298" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="AU298" s="3"/>
       <c r="AV298" s="3"/>
       <c r="AW298" s="2"/>
@@ -9907,25 +9834,7 @@
       <c r="BR298" s="2"/>
       <c r="BS298" s="2"/>
     </row>
-    <row r="299" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C299" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G299" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H299" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="W299" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="X299" s="1" t="s">
-        <v>9</v>
-      </c>
+    <row r="299" spans="14:71" x14ac:dyDescent="0.25">
       <c r="AW299" s="2"/>
       <c r="AX299" s="2"/>
       <c r="AY299" s="2"/>
@@ -9950,25 +9859,7 @@
       <c r="BR299" s="2"/>
       <c r="BS299" s="2"/>
     </row>
-    <row r="300" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C300" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D300" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G300" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H300" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="W300" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X300" s="1" t="s">
-        <v>10</v>
-      </c>
+    <row r="300" spans="14:71" x14ac:dyDescent="0.25">
       <c r="AW300" s="2"/>
       <c r="AX300" s="2"/>
       <c r="AY300" s="2"/>
@@ -9993,13 +9884,7 @@
       <c r="BR300" s="2"/>
       <c r="BS300" s="2"/>
     </row>
-    <row r="301" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C301" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>9</v>
-      </c>
+    <row r="301" spans="14:71" x14ac:dyDescent="0.25">
       <c r="AW301" s="2"/>
       <c r="AX301" s="2"/>
       <c r="AY301" s="2"/>
@@ -10024,25 +9909,7 @@
       <c r="BR301" s="2"/>
       <c r="BS301" s="2"/>
     </row>
-    <row r="302" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C302" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G302" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H302" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="W302" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="X302" s="1" t="s">
-        <v>10</v>
-      </c>
+    <row r="302" spans="14:71" x14ac:dyDescent="0.25">
       <c r="AW302" s="2"/>
       <c r="AX302" s="2"/>
       <c r="AY302" s="2"/>
@@ -10067,19 +9934,7 @@
       <c r="BR302" s="2"/>
       <c r="BS302" s="2"/>
     </row>
-    <row r="303" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C303" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G303" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H303" s="1" t="s">
-        <v>10</v>
-      </c>
+    <row r="303" spans="14:71" x14ac:dyDescent="0.25">
       <c r="AW303" s="2"/>
       <c r="AX303" s="2"/>
       <c r="AY303" s="2"/>
@@ -10104,25 +9959,7 @@
       <c r="BR303" s="2"/>
       <c r="BS303" s="2"/>
     </row>
-    <row r="304" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C304" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G304" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H304" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="W304" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="X304" s="1" t="s">
-        <v>9</v>
-      </c>
+    <row r="304" spans="14:71" x14ac:dyDescent="0.25">
       <c r="AQ304" s="3"/>
       <c r="AR304" s="3"/>
       <c r="AW304" s="2"/>
@@ -10149,25 +9986,7 @@
       <c r="BR304" s="2"/>
       <c r="BS304" s="2"/>
     </row>
-    <row r="305" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C305" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D305" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G305" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H305" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="W305" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X305" s="1" t="s">
-        <v>10</v>
-      </c>
+    <row r="305" spans="22:71" x14ac:dyDescent="0.25">
       <c r="AH305" s="3"/>
       <c r="AI305" s="3"/>
       <c r="AW305" s="2"/>
@@ -10194,13 +10013,7 @@
       <c r="BR305" s="2"/>
       <c r="BS305" s="2"/>
     </row>
-    <row r="306" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C306" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>9</v>
-      </c>
+    <row r="306" spans="22:71" x14ac:dyDescent="0.25">
       <c r="AH306" s="3"/>
       <c r="AI306" s="3"/>
       <c r="AW306" s="2"/>
@@ -10227,13 +10040,7 @@
       <c r="BR306" s="2"/>
       <c r="BS306" s="2"/>
     </row>
-    <row r="307" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C307" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>9</v>
-      </c>
+    <row r="307" spans="22:71" x14ac:dyDescent="0.25">
       <c r="AH307" s="3"/>
       <c r="AI307" s="3"/>
       <c r="AW307" s="2"/>
@@ -10260,13 +10067,7 @@
       <c r="BR307" s="2"/>
       <c r="BS307" s="2"/>
     </row>
-    <row r="308" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C308" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D308" s="1" t="s">
-        <v>9</v>
-      </c>
+    <row r="308" spans="22:71" x14ac:dyDescent="0.25">
       <c r="AH308" s="3"/>
       <c r="AI308" s="3"/>
       <c r="AW308" s="2"/>
@@ -10293,19 +10094,7 @@
       <c r="BR308" s="2"/>
       <c r="BS308" s="2"/>
     </row>
-    <row r="309" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C309" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D309" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G309" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H309" s="1" t="s">
-        <v>10</v>
-      </c>
+    <row r="309" spans="22:71" x14ac:dyDescent="0.25">
       <c r="AH309" s="3"/>
       <c r="AI309" s="3"/>
       <c r="AW309" s="2"/>
@@ -10332,13 +10121,7 @@
       <c r="BR309" s="2"/>
       <c r="BS309" s="2"/>
     </row>
-    <row r="310" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C310" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D310" s="1" t="s">
-        <v>9</v>
-      </c>
+    <row r="310" spans="22:71" x14ac:dyDescent="0.25">
       <c r="V310" s="3"/>
       <c r="W310" s="3"/>
       <c r="AH310" s="3"/>
@@ -10367,7 +10150,7 @@
       <c r="BR310" s="2"/>
       <c r="BS310" s="2"/>
     </row>
-    <row r="311" spans="2:71" x14ac:dyDescent="0.25">
+    <row r="311" spans="22:71" x14ac:dyDescent="0.25">
       <c r="V311" s="3"/>
       <c r="W311" s="3"/>
       <c r="AH311" s="3"/>
@@ -10396,16 +10179,7 @@
       <c r="BR311" s="2"/>
       <c r="BS311" s="2"/>
     </row>
-    <row r="312" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="B312" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F312" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="V312" s="1" t="s">
-        <v>31</v>
-      </c>
+    <row r="312" spans="22:71" x14ac:dyDescent="0.25">
       <c r="AW312" s="2"/>
       <c r="AX312" s="2"/>
       <c r="AY312" s="2"/>
@@ -10430,25 +10204,7 @@
       <c r="BR312" s="2"/>
       <c r="BS312" s="2"/>
     </row>
-    <row r="313" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C313" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D313" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G313" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H313" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="W313" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X313" s="1" t="s">
-        <v>16</v>
-      </c>
+    <row r="313" spans="22:71" x14ac:dyDescent="0.25">
       <c r="AW313" s="2"/>
       <c r="AX313" s="2"/>
       <c r="AY313" s="2"/>
@@ -10473,25 +10229,7 @@
       <c r="BR313" s="2"/>
       <c r="BS313" s="2"/>
     </row>
-    <row r="314" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C314" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D314" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G314" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H314" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="W314" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="X314" s="1" t="s">
-        <v>46</v>
-      </c>
+    <row r="314" spans="22:71" x14ac:dyDescent="0.25">
       <c r="AM314" s="3"/>
       <c r="AN314" s="3"/>
       <c r="AW314" s="2"/>
@@ -10518,25 +10256,7 @@
       <c r="BR314" s="2"/>
       <c r="BS314" s="2"/>
     </row>
-    <row r="315" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C315" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D315" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G315" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H315" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="W315" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X315" s="1" t="s">
-        <v>16</v>
-      </c>
+    <row r="315" spans="22:71" x14ac:dyDescent="0.25">
       <c r="AH315" s="3"/>
       <c r="AI315" s="3"/>
       <c r="AL315" s="3"/>
@@ -10567,13 +10287,7 @@
       <c r="BR315" s="2"/>
       <c r="BS315" s="2"/>
     </row>
-    <row r="316" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C316" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>46</v>
-      </c>
+    <row r="316" spans="22:71" x14ac:dyDescent="0.25">
       <c r="AH316" s="3"/>
       <c r="AI316" s="3"/>
       <c r="AL316" s="3"/>
@@ -10604,25 +10318,7 @@
       <c r="BR316" s="2"/>
       <c r="BS316" s="2"/>
     </row>
-    <row r="317" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C317" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D317" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G317" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H317" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="W317" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="X317" s="1" t="s">
-        <v>16</v>
-      </c>
+    <row r="317" spans="22:71" x14ac:dyDescent="0.25">
       <c r="AH317" s="3"/>
       <c r="AI317" s="3"/>
       <c r="AL317" s="3"/>
@@ -10653,19 +10349,7 @@
       <c r="BR317" s="2"/>
       <c r="BS317" s="2"/>
     </row>
-    <row r="318" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C318" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D318" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G318" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H318" s="1" t="s">
-        <v>16</v>
-      </c>
+    <row r="318" spans="22:71" x14ac:dyDescent="0.25">
       <c r="AH318" s="3"/>
       <c r="AI318" s="3"/>
       <c r="AL318" s="3"/>
@@ -10696,25 +10380,7 @@
       <c r="BR318" s="2"/>
       <c r="BS318" s="2"/>
     </row>
-    <row r="319" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C319" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G319" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H319" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="W319" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X319" s="1" t="s">
-        <v>16</v>
-      </c>
+    <row r="319" spans="22:71" x14ac:dyDescent="0.25">
       <c r="AH319" s="3"/>
       <c r="AI319" s="3"/>
       <c r="AL319" s="3"/>
@@ -10745,13 +10411,7 @@
       <c r="BR319" s="2"/>
       <c r="BS319" s="2"/>
     </row>
-    <row r="320" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C320" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>46</v>
-      </c>
+    <row r="320" spans="22:71" x14ac:dyDescent="0.25">
       <c r="AH320" s="3"/>
       <c r="AI320" s="3"/>
       <c r="AL320" s="3"/>
@@ -10782,13 +10442,7 @@
       <c r="BR320" s="2"/>
       <c r="BS320" s="2"/>
     </row>
-    <row r="321" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C321" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D321" s="1" t="s">
-        <v>46</v>
-      </c>
+    <row r="321" spans="26:71" x14ac:dyDescent="0.25">
       <c r="AH321" s="3"/>
       <c r="AI321" s="3"/>
       <c r="AL321" s="3"/>
@@ -10819,13 +10473,7 @@
       <c r="BR321" s="2"/>
       <c r="BS321" s="2"/>
     </row>
-    <row r="322" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C322" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>46</v>
-      </c>
+    <row r="322" spans="26:71" x14ac:dyDescent="0.25">
       <c r="AH322" s="3"/>
       <c r="AI322" s="3"/>
       <c r="AL322" s="3"/>
@@ -10856,25 +10504,7 @@
       <c r="BR322" s="2"/>
       <c r="BS322" s="2"/>
     </row>
-    <row r="323" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C323" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D323" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G323" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H323" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="W323" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="X323" s="1" t="s">
-        <v>16</v>
-      </c>
+    <row r="323" spans="26:71" x14ac:dyDescent="0.25">
       <c r="AH323" s="3"/>
       <c r="AL323" s="3"/>
       <c r="AP323" s="3"/>
@@ -10904,19 +10534,7 @@
       <c r="BR323" s="2"/>
       <c r="BS323" s="2"/>
     </row>
-    <row r="324" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C324" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D324" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G324" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H324" s="1" t="s">
-        <v>16</v>
-      </c>
+    <row r="324" spans="26:71" x14ac:dyDescent="0.25">
       <c r="Z324" s="3"/>
       <c r="AA324" s="3"/>
       <c r="AL324" s="3"/>
@@ -10945,13 +10563,7 @@
       <c r="BR324" s="2"/>
       <c r="BS324" s="2"/>
     </row>
-    <row r="325" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C325" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D325" s="1" t="s">
-        <v>46</v>
-      </c>
+    <row r="325" spans="26:71" x14ac:dyDescent="0.25">
       <c r="Z325" s="3"/>
       <c r="AA325" s="3"/>
       <c r="AL325" s="3"/>
@@ -10980,7 +10592,7 @@
       <c r="BR325" s="2"/>
       <c r="BS325" s="2"/>
     </row>
-    <row r="326" spans="2:71" x14ac:dyDescent="0.25">
+    <row r="326" spans="26:71" x14ac:dyDescent="0.25">
       <c r="Z326" s="3"/>
       <c r="AA326" s="3"/>
       <c r="AL326" s="3"/>
@@ -11009,16 +10621,7 @@
       <c r="BR326" s="2"/>
       <c r="BS326" s="2"/>
     </row>
-    <row r="327" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="B327" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F327" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V327" s="1" t="s">
-        <v>23</v>
-      </c>
+    <row r="327" spans="26:71" x14ac:dyDescent="0.25">
       <c r="AW327" s="5"/>
       <c r="AX327" s="5"/>
       <c r="AY327" s="5"/>
@@ -11043,25 +10646,7 @@
       <c r="BR327" s="2"/>
       <c r="BS327" s="2"/>
     </row>
-    <row r="328" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C328" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G328" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H328" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W328" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X328" s="1" t="s">
-        <v>36</v>
-      </c>
+    <row r="328" spans="26:71" x14ac:dyDescent="0.25">
       <c r="AW328" s="5"/>
       <c r="AX328" s="5"/>
       <c r="AY328" s="5"/>
@@ -11086,25 +10671,7 @@
       <c r="BR328" s="2"/>
       <c r="BS328" s="2"/>
     </row>
-    <row r="329" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C329" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G329" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H329" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W329" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X329" s="1" t="s">
-        <v>36</v>
-      </c>
+    <row r="329" spans="26:71" x14ac:dyDescent="0.25">
       <c r="AW329" s="5"/>
       <c r="AX329" s="5"/>
       <c r="AY329" s="5"/>
@@ -11129,13 +10696,7 @@
       <c r="BR329" s="2"/>
       <c r="BS329" s="2"/>
     </row>
-    <row r="330" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C330" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>47</v>
-      </c>
+    <row r="330" spans="26:71" x14ac:dyDescent="0.25">
       <c r="AW330" s="5"/>
       <c r="AX330" s="5"/>
       <c r="AY330" s="5"/>
@@ -11160,25 +10721,7 @@
       <c r="BR330" s="3"/>
       <c r="BS330" s="3"/>
     </row>
-    <row r="331" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C331" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D331" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G331" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H331" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W331" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="X331" s="1" t="s">
-        <v>36</v>
-      </c>
+    <row r="331" spans="26:71" x14ac:dyDescent="0.25">
       <c r="AW331" s="5"/>
       <c r="AX331" s="5"/>
       <c r="AY331" s="5"/>
@@ -11203,19 +10746,7 @@
       <c r="BR331" s="2"/>
       <c r="BS331" s="2"/>
     </row>
-    <row r="332" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C332" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G332" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H332" s="1" t="s">
-        <v>36</v>
-      </c>
+    <row r="332" spans="26:71" x14ac:dyDescent="0.25">
       <c r="AW332" s="5"/>
       <c r="AX332" s="5"/>
       <c r="AY332" s="5"/>
@@ -11240,25 +10771,7 @@
       <c r="BR332" s="2"/>
       <c r="BS332" s="2"/>
     </row>
-    <row r="333" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C333" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G333" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H333" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W333" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="X333" s="1" t="s">
-        <v>36</v>
-      </c>
+    <row r="333" spans="26:71" x14ac:dyDescent="0.25">
       <c r="AM333" s="3"/>
       <c r="AN333" s="3"/>
       <c r="AW333" s="5"/>
@@ -11285,25 +10798,7 @@
       <c r="BR333" s="2"/>
       <c r="BS333" s="2"/>
     </row>
-    <row r="334" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C334" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D334" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G334" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H334" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W334" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X334" s="1" t="s">
-        <v>36</v>
-      </c>
+    <row r="334" spans="26:71" x14ac:dyDescent="0.25">
       <c r="AW334" s="5"/>
       <c r="AX334" s="5"/>
       <c r="AY334" s="5"/>
@@ -11328,13 +10823,7 @@
       <c r="BR334" s="2"/>
       <c r="BS334" s="2"/>
     </row>
-    <row r="335" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C335" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D335" s="1" t="s">
-        <v>47</v>
-      </c>
+    <row r="335" spans="26:71" x14ac:dyDescent="0.25">
       <c r="AW335" s="2"/>
       <c r="AX335" s="2"/>
       <c r="AY335" s="2"/>
@@ -11359,13 +10848,7 @@
       <c r="BR335" s="2"/>
       <c r="BS335" s="2"/>
     </row>
-    <row r="336" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C336" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D336" s="1" t="s">
-        <v>47</v>
-      </c>
+    <row r="336" spans="26:71" x14ac:dyDescent="0.25">
       <c r="AW336" s="2"/>
       <c r="AX336" s="2"/>
       <c r="AY336" s="2"/>
@@ -11390,13 +10873,7 @@
       <c r="BR336" s="2"/>
       <c r="BS336" s="2"/>
     </row>
-    <row r="337" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C337" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D337" s="1" t="s">
-        <v>48</v>
-      </c>
+    <row r="337" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW337" s="2"/>
       <c r="AX337" s="2"/>
       <c r="AY337" s="2"/>
@@ -11421,25 +10898,7 @@
       <c r="BR337" s="2"/>
       <c r="BS337" s="2"/>
     </row>
-    <row r="338" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C338" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G338" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H338" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W338" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="X338" s="1" t="s">
-        <v>36</v>
-      </c>
+    <row r="338" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW338" s="2"/>
       <c r="AX338" s="2"/>
       <c r="AY338" s="2"/>
@@ -11464,19 +10923,7 @@
       <c r="BR338" s="2"/>
       <c r="BS338" s="2"/>
     </row>
-    <row r="339" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C339" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D339" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G339" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H339" s="1" t="s">
-        <v>36</v>
-      </c>
+    <row r="339" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW339" s="2"/>
       <c r="AX339" s="2"/>
       <c r="AY339" s="2"/>
@@ -11501,13 +10948,7 @@
       <c r="BR339" s="2"/>
       <c r="BS339" s="2"/>
     </row>
-    <row r="340" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C340" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D340" s="1" t="s">
-        <v>49</v>
-      </c>
+    <row r="340" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW340" s="2"/>
       <c r="AX340" s="2"/>
       <c r="AY340" s="2"/>
@@ -11532,7 +10973,7 @@
       <c r="BR340" s="2"/>
       <c r="BS340" s="2"/>
     </row>
-    <row r="341" spans="2:71" x14ac:dyDescent="0.25">
+    <row r="341" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW341" s="2"/>
       <c r="AX341" s="2"/>
       <c r="AY341" s="2"/>
@@ -11557,10 +10998,7 @@
       <c r="BR341" s="2"/>
       <c r="BS341" s="2"/>
     </row>
-    <row r="342" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="B342" s="1" t="s">
-        <v>26</v>
-      </c>
+    <row r="342" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW342" s="2"/>
       <c r="AX342" s="2"/>
       <c r="AY342" s="2"/>
@@ -11585,13 +11023,7 @@
       <c r="BR342" s="2"/>
       <c r="BS342" s="2"/>
     </row>
-    <row r="343" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C343" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D343" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="343" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW343" s="2"/>
       <c r="AX343" s="2"/>
       <c r="AY343" s="2"/>
@@ -11616,13 +11048,7 @@
       <c r="BR343" s="2"/>
       <c r="BS343" s="2"/>
     </row>
-    <row r="344" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C344" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D344" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="344" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW344" s="2"/>
       <c r="AX344" s="2"/>
       <c r="AY344" s="2"/>
@@ -11647,13 +11073,7 @@
       <c r="BR344" s="2"/>
       <c r="BS344" s="2"/>
     </row>
-    <row r="345" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C345" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D345" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="345" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW345" s="2"/>
       <c r="AX345" s="2"/>
       <c r="AY345" s="2"/>
@@ -11678,13 +11098,7 @@
       <c r="BR345" s="2"/>
       <c r="BS345" s="2"/>
     </row>
-    <row r="346" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C346" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D346" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="346" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW346" s="2"/>
       <c r="AX346" s="2"/>
       <c r="AY346" s="2"/>
@@ -11709,13 +11123,7 @@
       <c r="BR346" s="2"/>
       <c r="BS346" s="2"/>
     </row>
-    <row r="347" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C347" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="347" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW347" s="2"/>
       <c r="AX347" s="2"/>
       <c r="AY347" s="2"/>
@@ -11740,13 +11148,7 @@
       <c r="BR347" s="2"/>
       <c r="BS347" s="2"/>
     </row>
-    <row r="348" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C348" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D348" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="348" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW348" s="2"/>
       <c r="AX348" s="2"/>
       <c r="AY348" s="2"/>
@@ -11771,13 +11173,7 @@
       <c r="BR348" s="2"/>
       <c r="BS348" s="2"/>
     </row>
-    <row r="349" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C349" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D349" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="349" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW349" s="2"/>
       <c r="AX349" s="2"/>
       <c r="AY349" s="2"/>
@@ -11802,13 +11198,7 @@
       <c r="BR349" s="2"/>
       <c r="BS349" s="2"/>
     </row>
-    <row r="350" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C350" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D350" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="350" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW350" s="2"/>
       <c r="AX350" s="2"/>
       <c r="AY350" s="2"/>
@@ -11833,13 +11223,7 @@
       <c r="BR350" s="2"/>
       <c r="BS350" s="2"/>
     </row>
-    <row r="351" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C351" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D351" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="351" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW351" s="2"/>
       <c r="AX351" s="2"/>
       <c r="AY351" s="2"/>
@@ -11864,13 +11248,7 @@
       <c r="BR351" s="2"/>
       <c r="BS351" s="2"/>
     </row>
-    <row r="352" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C352" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="352" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW352" s="2"/>
       <c r="AX352" s="2"/>
       <c r="AY352" s="2"/>
@@ -11895,13 +11273,7 @@
       <c r="BR352" s="2"/>
       <c r="BS352" s="2"/>
     </row>
-    <row r="353" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C353" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D353" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="353" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW353" s="2"/>
       <c r="AX353" s="2"/>
       <c r="AY353" s="2"/>
@@ -11926,13 +11298,7 @@
       <c r="BR353" s="2"/>
       <c r="BS353" s="2"/>
     </row>
-    <row r="354" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C354" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="354" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW354" s="2"/>
       <c r="AX354" s="2"/>
       <c r="AY354" s="2"/>
@@ -11957,13 +11323,7 @@
       <c r="BR354" s="2"/>
       <c r="BS354" s="2"/>
     </row>
-    <row r="355" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C355" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="355" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW355" s="2"/>
       <c r="AX355" s="2"/>
       <c r="AY355" s="2"/>
@@ -11988,7 +11348,7 @@
       <c r="BR355" s="2"/>
       <c r="BS355" s="2"/>
     </row>
-    <row r="356" spans="2:71" x14ac:dyDescent="0.25">
+    <row r="356" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW356" s="2"/>
       <c r="AX356" s="2"/>
       <c r="AY356" s="2"/>
@@ -12013,10 +11373,7 @@
       <c r="BR356" s="2"/>
       <c r="BS356" s="2"/>
     </row>
-    <row r="357" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="B357" s="1" t="s">
-        <v>30</v>
-      </c>
+    <row r="357" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW357" s="2"/>
       <c r="AX357" s="2"/>
       <c r="AY357" s="2"/>
@@ -12041,13 +11398,7 @@
       <c r="BR357" s="2"/>
       <c r="BS357" s="2"/>
     </row>
-    <row r="358" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C358" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D358" s="1" t="s">
-        <v>25</v>
-      </c>
+    <row r="358" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW358" s="2"/>
       <c r="AX358" s="2"/>
       <c r="AY358" s="2"/>
@@ -12072,13 +11423,7 @@
       <c r="BR358" s="2"/>
       <c r="BS358" s="2"/>
     </row>
-    <row r="359" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C359" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D359" s="1" t="s">
-        <v>25</v>
-      </c>
+    <row r="359" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW359" s="2"/>
       <c r="AX359" s="2"/>
       <c r="AY359" s="2"/>
@@ -12103,13 +11448,7 @@
       <c r="BR359" s="2"/>
       <c r="BS359" s="2"/>
     </row>
-    <row r="360" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C360" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D360" s="1" t="s">
-        <v>25</v>
-      </c>
+    <row r="360" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW360" s="2"/>
       <c r="AX360" s="2"/>
       <c r="AY360" s="2"/>
@@ -12134,13 +11473,7 @@
       <c r="BR360" s="2"/>
       <c r="BS360" s="2"/>
     </row>
-    <row r="361" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C361" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D361" s="1" t="s">
-        <v>25</v>
-      </c>
+    <row r="361" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW361" s="2"/>
       <c r="AX361" s="2"/>
       <c r="AY361" s="2"/>
@@ -12165,13 +11498,7 @@
       <c r="BR361" s="2"/>
       <c r="BS361" s="2"/>
     </row>
-    <row r="362" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C362" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D362" s="1" t="s">
-        <v>25</v>
-      </c>
+    <row r="362" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW362" s="2"/>
       <c r="AX362" s="2"/>
       <c r="AY362" s="2"/>
@@ -12196,13 +11523,7 @@
       <c r="BR362" s="2"/>
       <c r="BS362" s="2"/>
     </row>
-    <row r="363" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C363" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D363" s="1" t="s">
-        <v>25</v>
-      </c>
+    <row r="363" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW363" s="2"/>
       <c r="AX363" s="2"/>
       <c r="AY363" s="2"/>
@@ -12227,13 +11548,7 @@
       <c r="BR363" s="2"/>
       <c r="BS363" s="2"/>
     </row>
-    <row r="364" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C364" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D364" s="1" t="s">
-        <v>25</v>
-      </c>
+    <row r="364" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW364" s="2"/>
       <c r="AX364" s="2"/>
       <c r="AY364" s="2"/>
@@ -12258,13 +11573,7 @@
       <c r="BR364" s="2"/>
       <c r="BS364" s="2"/>
     </row>
-    <row r="365" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C365" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D365" s="1" t="s">
-        <v>25</v>
-      </c>
+    <row r="365" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW365" s="2"/>
       <c r="AX365" s="2"/>
       <c r="AY365" s="2"/>
@@ -12289,13 +11598,7 @@
       <c r="BR365" s="2"/>
       <c r="BS365" s="2"/>
     </row>
-    <row r="366" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C366" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D366" s="1" t="s">
-        <v>25</v>
-      </c>
+    <row r="366" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW366" s="2"/>
       <c r="AX366" s="2"/>
       <c r="AY366" s="2"/>
@@ -12320,13 +11623,7 @@
       <c r="BR366" s="2"/>
       <c r="BS366" s="2"/>
     </row>
-    <row r="367" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C367" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D367" s="1" t="s">
-        <v>25</v>
-      </c>
+    <row r="367" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW367" s="2"/>
       <c r="AX367" s="2"/>
       <c r="AY367" s="2"/>
@@ -12351,13 +11648,7 @@
       <c r="BR367" s="2"/>
       <c r="BS367" s="2"/>
     </row>
-    <row r="368" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C368" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D368" s="1" t="s">
-        <v>25</v>
-      </c>
+    <row r="368" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW368" s="2"/>
       <c r="AX368" s="2"/>
       <c r="AY368" s="2"/>
@@ -12382,13 +11673,7 @@
       <c r="BR368" s="2"/>
       <c r="BS368" s="2"/>
     </row>
-    <row r="369" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C369" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D369" s="1" t="s">
-        <v>25</v>
-      </c>
+    <row r="369" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW369" s="2"/>
       <c r="AX369" s="2"/>
       <c r="AY369" s="2"/>
@@ -12413,13 +11698,7 @@
       <c r="BR369" s="2"/>
       <c r="BS369" s="2"/>
     </row>
-    <row r="370" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C370" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D370" s="1" t="s">
-        <v>25</v>
-      </c>
+    <row r="370" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW370" s="2"/>
       <c r="AX370" s="2"/>
       <c r="AY370" s="2"/>
@@ -12444,7 +11723,7 @@
       <c r="BR370" s="2"/>
       <c r="BS370" s="2"/>
     </row>
-    <row r="371" spans="2:71" x14ac:dyDescent="0.25">
+    <row r="371" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW371" s="2"/>
       <c r="AX371" s="2"/>
       <c r="AY371" s="2"/>
@@ -12469,10 +11748,7 @@
       <c r="BR371" s="2"/>
       <c r="BS371" s="2"/>
     </row>
-    <row r="372" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="B372" s="1" t="s">
-        <v>41</v>
-      </c>
+    <row r="372" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW372" s="2"/>
       <c r="AX372" s="2"/>
       <c r="AY372" s="2"/>
@@ -12497,13 +11773,7 @@
       <c r="BR372" s="2"/>
       <c r="BS372" s="2"/>
     </row>
-    <row r="373" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C373" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D373" s="1" t="s">
-        <v>50</v>
-      </c>
+    <row r="373" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW373" s="2"/>
       <c r="AX373" s="2"/>
       <c r="AY373" s="2"/>
@@ -12528,13 +11798,7 @@
       <c r="BR373" s="2"/>
       <c r="BS373" s="2"/>
     </row>
-    <row r="374" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C374" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D374" s="1" t="s">
-        <v>50</v>
-      </c>
+    <row r="374" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW374" s="2"/>
       <c r="AX374" s="2"/>
       <c r="AY374" s="2"/>
@@ -12559,13 +11823,7 @@
       <c r="BR374" s="2"/>
       <c r="BS374" s="2"/>
     </row>
-    <row r="375" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C375" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D375" s="1" t="s">
-        <v>50</v>
-      </c>
+    <row r="375" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW375" s="2"/>
       <c r="AX375" s="2"/>
       <c r="AY375" s="2"/>
@@ -12590,13 +11848,7 @@
       <c r="BR375" s="2"/>
       <c r="BS375" s="2"/>
     </row>
-    <row r="376" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C376" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D376" s="1" t="s">
-        <v>50</v>
-      </c>
+    <row r="376" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW376" s="2"/>
       <c r="AX376" s="2"/>
       <c r="AY376" s="2"/>
@@ -12621,13 +11873,7 @@
       <c r="BR376" s="2"/>
       <c r="BS376" s="2"/>
     </row>
-    <row r="377" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C377" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D377" s="1" t="s">
-        <v>50</v>
-      </c>
+    <row r="377" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW377" s="2"/>
       <c r="AX377" s="2"/>
       <c r="AY377" s="2"/>
@@ -12652,13 +11898,7 @@
       <c r="BR377" s="2"/>
       <c r="BS377" s="2"/>
     </row>
-    <row r="378" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C378" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D378" s="1" t="s">
-        <v>50</v>
-      </c>
+    <row r="378" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW378" s="2"/>
       <c r="AX378" s="2"/>
       <c r="AY378" s="2"/>
@@ -12683,13 +11923,7 @@
       <c r="BR378" s="2"/>
       <c r="BS378" s="2"/>
     </row>
-    <row r="379" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C379" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D379" s="1" t="s">
-        <v>50</v>
-      </c>
+    <row r="379" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW379" s="2"/>
       <c r="AX379" s="2"/>
       <c r="AY379" s="2"/>
@@ -12714,13 +11948,7 @@
       <c r="BR379" s="2"/>
       <c r="BS379" s="2"/>
     </row>
-    <row r="380" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C380" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D380" s="1" t="s">
-        <v>50</v>
-      </c>
+    <row r="380" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW380" s="2"/>
       <c r="AX380" s="2"/>
       <c r="AY380" s="2"/>
@@ -12745,13 +11973,7 @@
       <c r="BR380" s="2"/>
       <c r="BS380" s="2"/>
     </row>
-    <row r="381" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C381" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D381" s="1" t="s">
-        <v>50</v>
-      </c>
+    <row r="381" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW381" s="2"/>
       <c r="AX381" s="2"/>
       <c r="AY381" s="2"/>
@@ -12776,13 +11998,7 @@
       <c r="BR381" s="2"/>
       <c r="BS381" s="2"/>
     </row>
-    <row r="382" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C382" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D382" s="1" t="s">
-        <v>50</v>
-      </c>
+    <row r="382" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW382" s="2"/>
       <c r="AX382" s="2"/>
       <c r="AY382" s="2"/>
@@ -12807,13 +12023,7 @@
       <c r="BR382" s="2"/>
       <c r="BS382" s="2"/>
     </row>
-    <row r="383" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C383" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D383" s="1" t="s">
-        <v>50</v>
-      </c>
+    <row r="383" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW383" s="2"/>
       <c r="AX383" s="2"/>
       <c r="AY383" s="2"/>
@@ -12838,13 +12048,7 @@
       <c r="BR383" s="2"/>
       <c r="BS383" s="2"/>
     </row>
-    <row r="384" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C384" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D384" s="1" t="s">
-        <v>50</v>
-      </c>
+    <row r="384" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW384" s="2"/>
       <c r="AX384" s="2"/>
       <c r="AY384" s="2"/>
@@ -12869,13 +12073,7 @@
       <c r="BR384" s="2"/>
       <c r="BS384" s="2"/>
     </row>
-    <row r="385" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C385" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D385" s="1" t="s">
-        <v>50</v>
-      </c>
+    <row r="385" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW385" s="2"/>
       <c r="AX385" s="2"/>
       <c r="AY385" s="2"/>
@@ -12900,7 +12098,7 @@
       <c r="BR385" s="2"/>
       <c r="BS385" s="2"/>
     </row>
-    <row r="386" spans="2:71" x14ac:dyDescent="0.25">
+    <row r="386" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW386" s="2"/>
       <c r="AX386" s="2"/>
       <c r="AY386" s="2"/>
@@ -12925,22 +12123,7 @@
       <c r="BR386" s="2"/>
       <c r="BS386" s="2"/>
     </row>
-    <row r="387" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="B387" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F387" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J387" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="N387" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="R387" s="1" t="s">
-        <v>35</v>
-      </c>
+    <row r="387" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW387" s="2"/>
       <c r="AX387" s="2"/>
       <c r="AY387" s="2"/>
@@ -12965,19 +12148,7 @@
       <c r="BR387" s="2"/>
       <c r="BS387" s="2"/>
     </row>
-    <row r="388" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C388" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D388" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G388" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H388" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="388" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW388" s="2"/>
       <c r="AX388" s="2"/>
       <c r="AY388" s="2"/>
@@ -13002,19 +12173,7 @@
       <c r="BR388" s="2"/>
       <c r="BS388" s="2"/>
     </row>
-    <row r="389" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C389" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D389" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G389" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H389" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="389" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW389" s="2"/>
       <c r="AX389" s="2"/>
       <c r="AY389" s="2"/>
@@ -13039,19 +12198,7 @@
       <c r="BR389" s="2"/>
       <c r="BS389" s="2"/>
     </row>
-    <row r="390" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C390" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D390" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G390" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H390" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="390" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW390" s="2"/>
       <c r="AX390" s="2"/>
       <c r="AY390" s="2"/>
@@ -13076,13 +12223,7 @@
       <c r="BR390" s="2"/>
       <c r="BS390" s="2"/>
     </row>
-    <row r="391" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C391" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D391" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="391" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW391" s="2"/>
       <c r="AX391" s="2"/>
       <c r="AY391" s="2"/>
@@ -13107,19 +12248,7 @@
       <c r="BR391" s="2"/>
       <c r="BS391" s="2"/>
     </row>
-    <row r="392" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C392" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D392" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G392" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H392" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="392" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW392" s="2"/>
       <c r="AX392" s="2"/>
       <c r="AY392" s="2"/>
@@ -13144,19 +12273,7 @@
       <c r="BR392" s="2"/>
       <c r="BS392" s="2"/>
     </row>
-    <row r="393" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C393" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D393" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G393" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H393" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="393" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW393" s="2"/>
       <c r="AX393" s="2"/>
       <c r="AY393" s="2"/>
@@ -13181,13 +12298,7 @@
       <c r="BR393" s="2"/>
       <c r="BS393" s="2"/>
     </row>
-    <row r="394" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C394" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D394" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="394" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW394" s="2"/>
       <c r="AX394" s="2"/>
       <c r="AY394" s="2"/>
@@ -13212,13 +12323,7 @@
       <c r="BR394" s="2"/>
       <c r="BS394" s="2"/>
     </row>
-    <row r="395" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C395" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D395" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="395" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW395" s="2"/>
       <c r="AX395" s="2"/>
       <c r="AY395" s="2"/>
@@ -13243,13 +12348,7 @@
       <c r="BR395" s="2"/>
       <c r="BS395" s="2"/>
     </row>
-    <row r="396" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C396" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D396" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="396" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW396" s="2"/>
       <c r="AX396" s="2"/>
       <c r="AY396" s="2"/>
@@ -13274,19 +12373,7 @@
       <c r="BR396" s="2"/>
       <c r="BS396" s="2"/>
     </row>
-    <row r="397" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C397" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D397" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G397" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H397" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="397" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW397" s="2"/>
       <c r="AX397" s="2"/>
       <c r="AY397" s="2"/>
@@ -13311,31 +12398,9 @@
       <c r="BR397" s="2"/>
       <c r="BS397" s="2"/>
     </row>
-    <row r="398" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C398" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D398" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G398" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H398" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K398" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L398" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="S398" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="T398" s="3" t="s">
-        <v>51</v>
-      </c>
+    <row r="398" spans="15:71" x14ac:dyDescent="0.25">
+      <c r="S398" s="3"/>
+      <c r="T398" s="3"/>
       <c r="AW398" s="2"/>
       <c r="AX398" s="2"/>
       <c r="AY398" s="2"/>
@@ -13360,13 +12425,7 @@
       <c r="BR398" s="2"/>
       <c r="BS398" s="2"/>
     </row>
-    <row r="399" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C399" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D399" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="399" spans="15:71" x14ac:dyDescent="0.25">
       <c r="AW399" s="2"/>
       <c r="AX399" s="2"/>
       <c r="AY399" s="2"/>
@@ -13391,31 +12450,9 @@
       <c r="BR399" s="2"/>
       <c r="BS399" s="2"/>
     </row>
-    <row r="400" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C400" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D400" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G400" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H400" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K400" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L400" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O400" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P400" s="3" t="s">
-        <v>21</v>
-      </c>
+    <row r="400" spans="15:71" x14ac:dyDescent="0.25">
+      <c r="O400" s="3"/>
+      <c r="P400" s="3"/>
       <c r="AW400" s="2"/>
       <c r="AX400" s="2"/>
       <c r="AY400" s="2"/>
@@ -13440,7 +12477,7 @@
       <c r="BR400" s="2"/>
       <c r="BS400" s="2"/>
     </row>
-    <row r="401" spans="2:71" x14ac:dyDescent="0.25">
+    <row r="401" spans="19:71" x14ac:dyDescent="0.25">
       <c r="AW401" s="2"/>
       <c r="AX401" s="2"/>
       <c r="AY401" s="2"/>
@@ -13465,19 +12502,7 @@
       <c r="BR401" s="2"/>
       <c r="BS401" s="2"/>
     </row>
-    <row r="402" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="B402" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F402" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J402" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="R402" s="1" t="s">
-        <v>43</v>
-      </c>
+    <row r="402" spans="19:71" x14ac:dyDescent="0.25">
       <c r="AW402" s="2"/>
       <c r="AX402" s="2"/>
       <c r="AY402" s="2"/>
@@ -13502,19 +12527,7 @@
       <c r="BR402" s="2"/>
       <c r="BS402" s="2"/>
     </row>
-    <row r="403" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C403" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D403" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G403" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H403" s="1" t="s">
-        <v>52</v>
-      </c>
+    <row r="403" spans="19:71" x14ac:dyDescent="0.25">
       <c r="AW403" s="2"/>
       <c r="AX403" s="2"/>
       <c r="AY403" s="2"/>
@@ -13539,19 +12552,7 @@
       <c r="BR403" s="2"/>
       <c r="BS403" s="2"/>
     </row>
-    <row r="404" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C404" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D404" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G404" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H404" s="1" t="s">
-        <v>52</v>
-      </c>
+    <row r="404" spans="19:71" x14ac:dyDescent="0.25">
       <c r="AW404" s="2"/>
       <c r="AX404" s="2"/>
       <c r="AY404" s="2"/>
@@ -13576,19 +12577,7 @@
       <c r="BR404" s="2"/>
       <c r="BS404" s="2"/>
     </row>
-    <row r="405" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C405" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D405" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G405" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H405" s="1" t="s">
-        <v>52</v>
-      </c>
+    <row r="405" spans="19:71" x14ac:dyDescent="0.25">
       <c r="AW405" s="2"/>
       <c r="AX405" s="2"/>
       <c r="AY405" s="2"/>
@@ -13613,13 +12602,7 @@
       <c r="BR405" s="2"/>
       <c r="BS405" s="2"/>
     </row>
-    <row r="406" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C406" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D406" s="1" t="s">
-        <v>52</v>
-      </c>
+    <row r="406" spans="19:71" x14ac:dyDescent="0.25">
       <c r="AW406" s="2"/>
       <c r="AX406" s="2"/>
       <c r="AY406" s="2"/>
@@ -13644,31 +12627,9 @@
       <c r="BR406" s="2"/>
       <c r="BS406" s="2"/>
     </row>
-    <row r="407" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C407" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D407" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G407" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H407" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K407" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L407" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="S407" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="T407" s="3" t="s">
-        <v>52</v>
-      </c>
+    <row r="407" spans="19:71" x14ac:dyDescent="0.25">
+      <c r="S407" s="3"/>
+      <c r="T407" s="3"/>
       <c r="AW407" s="2"/>
       <c r="AX407" s="2"/>
       <c r="AY407" s="2"/>
@@ -13693,19 +12654,7 @@
       <c r="BR407" s="2"/>
       <c r="BS407" s="2"/>
     </row>
-    <row r="408" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C408" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D408" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G408" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H408" s="1" t="s">
-        <v>52</v>
-      </c>
+    <row r="408" spans="19:71" x14ac:dyDescent="0.25">
       <c r="AW408" s="2"/>
       <c r="AX408" s="2"/>
       <c r="AY408" s="2"/>
@@ -13730,13 +12679,7 @@
       <c r="BR408" s="2"/>
       <c r="BS408" s="2"/>
     </row>
-    <row r="409" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C409" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D409" s="1" t="s">
-        <v>52</v>
-      </c>
+    <row r="409" spans="19:71" x14ac:dyDescent="0.25">
       <c r="AW409" s="2"/>
       <c r="AX409" s="2"/>
       <c r="AY409" s="2"/>
@@ -13761,13 +12704,7 @@
       <c r="BR409" s="2"/>
       <c r="BS409" s="2"/>
     </row>
-    <row r="410" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C410" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D410" s="1" t="s">
-        <v>52</v>
-      </c>
+    <row r="410" spans="19:71" x14ac:dyDescent="0.25">
       <c r="AW410" s="2"/>
       <c r="AX410" s="2"/>
       <c r="AY410" s="2"/>
@@ -13792,13 +12729,7 @@
       <c r="BR410" s="2"/>
       <c r="BS410" s="2"/>
     </row>
-    <row r="411" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C411" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D411" s="1" t="s">
-        <v>52</v>
-      </c>
+    <row r="411" spans="19:71" x14ac:dyDescent="0.25">
       <c r="AW411" s="2"/>
       <c r="AX411" s="2"/>
       <c r="AY411" s="2"/>
@@ -13823,19 +12754,7 @@
       <c r="BR411" s="2"/>
       <c r="BS411" s="2"/>
     </row>
-    <row r="412" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C412" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D412" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G412" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H412" s="1" t="s">
-        <v>52</v>
-      </c>
+    <row r="412" spans="19:71" x14ac:dyDescent="0.25">
       <c r="AW412" s="2"/>
       <c r="AX412" s="2"/>
       <c r="AY412" s="2"/>
@@ -13860,13 +12779,7 @@
       <c r="BR412" s="2"/>
       <c r="BS412" s="2"/>
     </row>
-    <row r="413" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C413" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D413" s="1" t="s">
-        <v>52</v>
-      </c>
+    <row r="413" spans="19:71" x14ac:dyDescent="0.25">
       <c r="AW413" s="2"/>
       <c r="AX413" s="2"/>
       <c r="AY413" s="2"/>
@@ -13891,25 +12804,7 @@
       <c r="BR413" s="2"/>
       <c r="BS413" s="2"/>
     </row>
-    <row r="414" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C414" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D414" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G414" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H414" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K414" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L414" s="1" t="s">
-        <v>52</v>
-      </c>
+    <row r="414" spans="19:71" x14ac:dyDescent="0.25">
       <c r="AW414" s="2"/>
       <c r="AX414" s="2"/>
       <c r="AY414" s="2"/>
@@ -13934,19 +12829,7 @@
       <c r="BR414" s="2"/>
       <c r="BS414" s="2"/>
     </row>
-    <row r="415" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C415" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D415" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G415" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H415" s="1" t="s">
-        <v>52</v>
-      </c>
+    <row r="415" spans="19:71" x14ac:dyDescent="0.25">
       <c r="AW415" s="2"/>
       <c r="AX415" s="2"/>
       <c r="AY415" s="2"/>
@@ -13971,7 +12854,7 @@
       <c r="BR415" s="2"/>
       <c r="BS415" s="2"/>
     </row>
-    <row r="416" spans="2:71" x14ac:dyDescent="0.25">
+    <row r="416" spans="19:71" x14ac:dyDescent="0.25">
       <c r="AW416" s="2"/>
       <c r="AX416" s="2"/>
       <c r="AY416" s="2"/>
@@ -13996,16 +12879,7 @@
       <c r="BR416" s="2"/>
       <c r="BS416" s="2"/>
     </row>
-    <row r="417" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="B417" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F417" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V417" s="1" t="s">
-        <v>36</v>
-      </c>
+    <row r="417" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW417" s="5"/>
       <c r="AX417" s="5"/>
       <c r="AY417" s="5"/>
@@ -14030,25 +12904,7 @@
       <c r="BR417" s="2"/>
       <c r="BS417" s="2"/>
     </row>
-    <row r="418" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C418" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D418" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G418" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H418" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W418" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X418" s="1" t="s">
-        <v>53</v>
-      </c>
+    <row r="418" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW418" s="5"/>
       <c r="AX418" s="5"/>
       <c r="AY418" s="5"/>
@@ -14073,25 +12929,7 @@
       <c r="BR418" s="2"/>
       <c r="BS418" s="2"/>
     </row>
-    <row r="419" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C419" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D419" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G419" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H419" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W419" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="X419" s="1" t="s">
-        <v>53</v>
-      </c>
+    <row r="419" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW419" s="5"/>
       <c r="AX419" s="5"/>
       <c r="AY419" s="5"/>
@@ -14116,13 +12954,7 @@
       <c r="BR419" s="2"/>
       <c r="BS419" s="2"/>
     </row>
-    <row r="420" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C420" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D420" s="1" t="s">
-        <v>53</v>
-      </c>
+    <row r="420" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW420" s="5"/>
       <c r="AX420" s="5"/>
       <c r="AY420" s="5"/>
@@ -14147,25 +12979,7 @@
       <c r="BR420" s="2"/>
       <c r="BS420" s="2"/>
     </row>
-    <row r="421" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C421" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D421" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G421" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H421" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W421" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="X421" s="1" t="s">
-        <v>53</v>
-      </c>
+    <row r="421" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW421" s="5"/>
       <c r="AX421" s="5"/>
       <c r="AY421" s="5"/>
@@ -14190,19 +13004,7 @@
       <c r="BR421" s="2"/>
       <c r="BS421" s="2"/>
     </row>
-    <row r="422" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C422" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D422" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G422" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H422" s="1" t="s">
-        <v>53</v>
-      </c>
+    <row r="422" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW422" s="5"/>
       <c r="AX422" s="5"/>
       <c r="AY422" s="5"/>
@@ -14227,25 +13029,7 @@
       <c r="BR422" s="2"/>
       <c r="BS422" s="2"/>
     </row>
-    <row r="423" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C423" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D423" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G423" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H423" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W423" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="X423" s="1" t="s">
-        <v>53</v>
-      </c>
+    <row r="423" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW423" s="5"/>
       <c r="AX423" s="5"/>
       <c r="AY423" s="5"/>
@@ -14270,25 +13054,7 @@
       <c r="BR423" s="2"/>
       <c r="BS423" s="2"/>
     </row>
-    <row r="424" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C424" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D424" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G424" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H424" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W424" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X424" s="1" t="s">
-        <v>53</v>
-      </c>
+    <row r="424" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW424" s="5"/>
       <c r="AX424" s="5"/>
       <c r="AY424" s="5"/>
@@ -14313,13 +13079,7 @@
       <c r="BR424" s="2"/>
       <c r="BS424" s="2"/>
     </row>
-    <row r="425" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C425" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D425" s="1" t="s">
-        <v>53</v>
-      </c>
+    <row r="425" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW425" s="2"/>
       <c r="AX425" s="2"/>
       <c r="AY425" s="2"/>
@@ -14344,13 +13104,7 @@
       <c r="BR425" s="2"/>
       <c r="BS425" s="2"/>
     </row>
-    <row r="426" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C426" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D426" s="1" t="s">
-        <v>53</v>
-      </c>
+    <row r="426" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW426" s="2"/>
       <c r="AX426" s="2"/>
       <c r="AY426" s="2"/>
@@ -14375,25 +13129,7 @@
       <c r="BR426" s="2"/>
       <c r="BS426" s="2"/>
     </row>
-    <row r="427" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C427" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D427" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G427" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H427" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W427" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="X427" s="1" t="s">
-        <v>53</v>
-      </c>
+    <row r="427" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW427" s="2"/>
       <c r="AX427" s="2"/>
       <c r="AY427" s="2"/>
@@ -14418,19 +13154,7 @@
       <c r="BR427" s="2"/>
       <c r="BS427" s="2"/>
     </row>
-    <row r="428" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C428" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D428" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G428" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H428" s="1" t="s">
-        <v>53</v>
-      </c>
+    <row r="428" spans="49:71" x14ac:dyDescent="0.25">
       <c r="AW428" s="2"/>
       <c r="AX428" s="2"/>
       <c r="AY428" s="2"/>
@@ -14455,22 +13179,6 @@
       <c r="BR428" s="2"/>
       <c r="BS428" s="2"/>
     </row>
-    <row r="429" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C429" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D429" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="430" spans="2:71" x14ac:dyDescent="0.25">
-      <c r="C430" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D430" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/temp/searchByMACTable.xlsx
+++ b/temp/searchByMACTable.xlsx
@@ -765,9 +765,10 @@
     <col min="39" max="39" width="5.42578125" style="1" customWidth="1"/>
     <col min="40" max="40" width="4.7109375" style="1" customWidth="1"/>
     <col min="41" max="42" width="5.5703125" style="1" customWidth="1"/>
-    <col min="43" max="44" width="5.28515625" style="1" customWidth="1"/>
+    <col min="43" max="43" width="5.28515625" style="1" customWidth="1"/>
+    <col min="44" max="44" width="7.140625" style="1" customWidth="1"/>
     <col min="45" max="45" width="4.7109375" style="1" customWidth="1"/>
-    <col min="46" max="46" width="4.5703125" style="1" customWidth="1"/>
+    <col min="46" max="46" width="5.5703125" style="1" customWidth="1"/>
     <col min="47" max="47" width="4.42578125" style="1" customWidth="1"/>
     <col min="48" max="48" width="4.28515625" style="1" customWidth="1"/>
     <col min="49" max="49" width="4.42578125" style="1" customWidth="1"/>
@@ -8289,10 +8290,10 @@
       <c r="BW238" s="3"/>
     </row>
     <row r="239" spans="9:75" x14ac:dyDescent="0.25">
-      <c r="J239" s="3" t="s">
+      <c r="J239" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K239" s="3" t="s">
+      <c r="K239" s="1" t="s">
         <v>28</v>
       </c>
       <c r="L239" s="1" t="s">
@@ -8340,10 +8341,10 @@
       <c r="BW239" s="3"/>
     </row>
     <row r="240" spans="9:75" x14ac:dyDescent="0.25">
-      <c r="J240" s="3" t="s">
+      <c r="J240" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K240" s="3" t="s">
+      <c r="K240" s="1" t="s">
         <v>67</v>
       </c>
       <c r="L240" s="1" t="s">
@@ -8391,10 +8392,10 @@
       <c r="BW240" s="3"/>
     </row>
     <row r="241" spans="10:75" x14ac:dyDescent="0.25">
-      <c r="J241" s="3" t="s">
+      <c r="J241" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="K241" s="3" t="s">
+      <c r="K241" s="1" t="s">
         <v>68</v>
       </c>
       <c r="L241" s="1" t="s">

--- a/temp/searchByMACTable.xlsx
+++ b/temp/searchByMACTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="102">
   <si>
     <t>2.1</t>
   </si>
@@ -7295,6 +7295,14 @@
       <c r="K211" s="5"/>
     </row>
     <row r="218" spans="3:71" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="3:71" x14ac:dyDescent="0.25">
+      <c r="AQ220" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AR220" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
     <row r="221" spans="3:71" x14ac:dyDescent="0.25">
       <c r="I221" s="1" t="s">
         <v>49</v>
@@ -7384,10 +7392,10 @@
         <v>50</v>
       </c>
       <c r="AQ221" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AR221" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="222" spans="3:71" x14ac:dyDescent="0.25">
@@ -7400,8 +7408,11 @@
       <c r="Z222" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="AQ222" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="AR222" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AX222" s="5"/>
       <c r="AY222" s="5"/>
@@ -7436,8 +7447,11 @@
       <c r="AA223" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AQ223" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="AR223" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AX223" s="5"/>
       <c r="AY223" s="5"/>
@@ -7487,8 +7501,11 @@
       <c r="AB224" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="AQ224" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="AR224" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AX224" s="5"/>
       <c r="AY224" s="5"/>
@@ -7541,6 +7558,9 @@
       <c r="AC225" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="AP225" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="AQ225" s="1" t="s">
         <v>26</v>
       </c>
@@ -7664,6 +7684,9 @@
       <c r="AE227" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AP227" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="AQ227" s="1" t="s">
         <v>27</v>
       </c>
@@ -7729,6 +7752,9 @@
       </c>
       <c r="AF228" s="1" t="s">
         <v>43</v>
+      </c>
+      <c r="AP228" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="AQ228" s="1" t="s">
         <v>28</v>
@@ -7795,6 +7821,9 @@
       <c r="AG229" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="AP229" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="AQ229" s="1" t="s">
         <v>30</v>
       </c>
@@ -7842,6 +7871,9 @@
       <c r="AH230" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="AP230" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="AQ230" s="1" t="s">
         <v>35</v>
       </c>
@@ -7998,6 +8030,9 @@
       <c r="AK233" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="AP233" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="AQ233" s="1" t="s">
         <v>34</v>
       </c>
@@ -8057,6 +8092,9 @@
       <c r="AL234" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AP234" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="AQ234" s="1" t="s">
         <v>31</v>
       </c>
@@ -8119,6 +8157,9 @@
       <c r="AM235" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="AP235" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="AQ235" s="1" t="s">
         <v>33</v>
       </c>
@@ -8165,6 +8206,9 @@
     <row r="236" spans="9:75" x14ac:dyDescent="0.25">
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
+      <c r="AP236" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="AQ236" s="1" t="s">
         <v>39</v>
       </c>
@@ -8214,6 +8258,9 @@
     <row r="237" spans="9:75" x14ac:dyDescent="0.25">
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
+      <c r="AP237" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="AQ237" s="1" t="s">
         <v>32</v>
       </c>

--- a/temp/searchByMACTable.xlsx
+++ b/temp/searchByMACTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="123">
   <si>
     <t>2.1</t>
   </si>
@@ -320,6 +320,69 @@
   </si>
   <si>
     <t>6.2.22</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>6.2_16</t>
+  </si>
+  <si>
+    <t>6.2_15</t>
+  </si>
+  <si>
+    <t>4_15</t>
+  </si>
+  <si>
+    <t>5_15</t>
+  </si>
+  <si>
+    <t>24_15</t>
+  </si>
+  <si>
+    <t>4_16</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>4_17</t>
+  </si>
+  <si>
+    <t>5_17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>4_18</t>
+  </si>
+  <si>
+    <t>24_18</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>6.2_19</t>
+  </si>
+  <si>
+    <t>6.2_20</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>6_19</t>
+  </si>
+  <si>
+    <t>2_20</t>
   </si>
 </sst>
 </file>
@@ -743,16 +806,16 @@
     <col min="15" max="15" width="5.85546875" style="1" customWidth="1"/>
     <col min="16" max="16" width="7.5703125" style="1" customWidth="1"/>
     <col min="17" max="17" width="7.85546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="1" customWidth="1"/>
     <col min="19" max="19" width="6.28515625" style="1" customWidth="1"/>
     <col min="20" max="20" width="6.42578125" style="1" customWidth="1"/>
     <col min="21" max="21" width="7" style="1" customWidth="1"/>
     <col min="22" max="22" width="6" style="1" customWidth="1"/>
     <col min="23" max="23" width="6.28515625" style="1" customWidth="1"/>
     <col min="24" max="24" width="4.85546875" style="1" customWidth="1"/>
-    <col min="25" max="25" width="4.28515625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="6.5703125" style="1" customWidth="1"/>
     <col min="26" max="26" width="4.42578125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="6.28515625" style="1" customWidth="1"/>
     <col min="28" max="29" width="5.140625" style="1" customWidth="1"/>
     <col min="30" max="30" width="5" style="1" customWidth="1"/>
     <col min="31" max="31" width="5.28515625" style="1" customWidth="1"/>
@@ -766,14 +829,16 @@
     <col min="40" max="40" width="4.7109375" style="1" customWidth="1"/>
     <col min="41" max="42" width="5.5703125" style="1" customWidth="1"/>
     <col min="43" max="43" width="5.28515625" style="1" customWidth="1"/>
-    <col min="44" max="44" width="7.140625" style="1" customWidth="1"/>
+    <col min="44" max="44" width="4" style="1" customWidth="1"/>
     <col min="45" max="45" width="4.7109375" style="1" customWidth="1"/>
     <col min="46" max="46" width="5.5703125" style="1" customWidth="1"/>
     <col min="47" max="47" width="4.42578125" style="1" customWidth="1"/>
     <col min="48" max="48" width="4.28515625" style="1" customWidth="1"/>
     <col min="49" max="49" width="4.42578125" style="1" customWidth="1"/>
     <col min="50" max="50" width="4" style="1" customWidth="1"/>
-    <col min="51" max="71" width="4.28515625" style="1" customWidth="1"/>
+    <col min="51" max="51" width="4.28515625" style="1" customWidth="1"/>
+    <col min="52" max="52" width="6.85546875" style="1" customWidth="1"/>
+    <col min="53" max="71" width="4.28515625" style="1" customWidth="1"/>
     <col min="72" max="72" width="4.5703125" style="1" customWidth="1"/>
     <col min="73" max="73" width="4.28515625" style="1" customWidth="1"/>
     <col min="74" max="74" width="4.5703125" style="1" customWidth="1"/>
@@ -7240,7 +7305,7 @@
       <c r="J208" s="5"/>
       <c r="K208" s="5"/>
     </row>
-    <row r="209" spans="3:71" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:71" x14ac:dyDescent="0.25">
       <c r="C209" s="5">
         <v>5</v>
       </c>
@@ -7258,7 +7323,7 @@
       <c r="J209" s="5"/>
       <c r="K209" s="5"/>
     </row>
-    <row r="210" spans="3:71" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:71" x14ac:dyDescent="0.25">
       <c r="C210" s="5">
         <v>13</v>
       </c>
@@ -7276,7 +7341,7 @@
       <c r="J210" s="5"/>
       <c r="K210" s="5"/>
     </row>
-    <row r="211" spans="3:71" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:71" x14ac:dyDescent="0.25">
       <c r="C211" s="5">
         <v>21</v>
       </c>
@@ -7294,134 +7359,183 @@
       <c r="J211" s="5"/>
       <c r="K211" s="5"/>
     </row>
-    <row r="218" spans="3:71" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="3:71" x14ac:dyDescent="0.25">
-      <c r="AQ220" s="1" t="s">
+    <row r="218" spans="2:71" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="AX220" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AY220" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AR220" s="1" t="s">
+      <c r="AZ220" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="221" spans="3:71" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="B221" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G221" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H221" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="I221" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J221" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K221" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L221" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M221" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N221" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O221" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P221" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q221" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="R221" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="S221" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T221" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="U221" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V221" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AB221" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC221" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD221" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE221" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF221" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG221" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH221" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI221" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ221" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK221" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL221" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM221" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN221" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO221" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AP221" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AQ221" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AR221" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS221" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AT221" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AU221" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AX221" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AY221" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J221" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K221" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L221" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M221" s="1" t="s">
+      <c r="AZ221" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="222" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="B222" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N221" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O221" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P221" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q221" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R221" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S221" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T221" s="1" t="s">
+      <c r="Q222" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R222" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="S222" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="T222" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA222" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB222" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX222" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="U221" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V221" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W221" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z221" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA221" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB221" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC221" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD221" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE221" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF221" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG221" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH221" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI221" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AJ221" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AK221" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AL221" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AM221" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AQ221" s="1" t="s">
+      <c r="AY222" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AR221" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="222" spans="3:71" x14ac:dyDescent="0.25">
-      <c r="I222" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y222" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z222" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ222" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AR222" s="1" t="s">
+      <c r="AZ222" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AX222" s="5"/>
-      <c r="AY222" s="5"/>
-      <c r="AZ222" s="5"/>
-      <c r="BA222" s="5"/>
-      <c r="BB222" s="5"/>
-      <c r="BC222" s="5"/>
-      <c r="BD222" s="5"/>
-      <c r="BE222" s="5"/>
       <c r="BF222" s="2"/>
       <c r="BG222" s="2"/>
       <c r="BH222" s="2"/>
@@ -7437,30 +7551,31 @@
       <c r="BR222" s="5"/>
       <c r="BS222" s="5"/>
     </row>
-    <row r="223" spans="3:71" x14ac:dyDescent="0.25">
-      <c r="I223" s="1" t="s">
+    <row r="223" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="B223" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Y223" s="1" t="s">
+      <c r="Q223" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="S223" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA223" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AA223" s="1" t="s">
+      <c r="AC223" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AQ223" s="1" t="s">
+      <c r="AX223" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AY223" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AR223" s="1" t="s">
+      <c r="AZ223" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AX223" s="5"/>
-      <c r="AY223" s="5"/>
-      <c r="AZ223" s="5"/>
-      <c r="BA223" s="5"/>
-      <c r="BB223" s="5"/>
-      <c r="BC223" s="5"/>
-      <c r="BD223" s="5"/>
-      <c r="BE223" s="5"/>
       <c r="BF223" s="2"/>
       <c r="BG223" s="2"/>
       <c r="BH223" s="2"/>
@@ -7476,45 +7591,40 @@
       <c r="BR223" s="5"/>
       <c r="BS223" s="5"/>
     </row>
-    <row r="224" spans="3:71" x14ac:dyDescent="0.25">
-      <c r="I224" s="1" t="s">
+    <row r="224" spans="2:71" x14ac:dyDescent="0.25">
+      <c r="B224" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J224" s="1" t="s">
+      <c r="C224" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K224" s="1" t="s">
+      <c r="D224" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L224" s="1" t="s">
+      <c r="E224" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="N224" s="1" t="s">
+      <c r="G224" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V224" s="1" t="s">
+      <c r="O224" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="Y224" s="1" t="s">
+      <c r="AA224" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AB224" s="1" t="s">
+      <c r="AD224" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AQ224" s="1" t="s">
+      <c r="AX224" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AY224" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AR224" s="1" t="s">
+      <c r="AZ224" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AX224" s="5"/>
-      <c r="AY224" s="5"/>
-      <c r="AZ224" s="5"/>
-      <c r="BA224" s="5"/>
-      <c r="BB224" s="5"/>
-      <c r="BC224" s="5"/>
-      <c r="BD224" s="5"/>
-      <c r="BE224" s="5"/>
       <c r="BF224" s="3"/>
       <c r="BG224" s="3"/>
       <c r="BH224" s="3"/>
@@ -7530,54 +7640,46 @@
       <c r="BR224" s="5"/>
       <c r="BS224" s="5"/>
     </row>
-    <row r="225" spans="9:75" x14ac:dyDescent="0.25">
-      <c r="I225" s="1" t="s">
+    <row r="225" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B225" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J225" s="1" t="s">
+      <c r="C225" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="G225" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H225" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="N225" s="1" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="O225" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="U225" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="V225" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="W225" s="1" t="s">
+      <c r="P225" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="Y225" s="1" t="s">
+      <c r="AA225" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AC225" s="1" t="s">
+      <c r="AE225" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AP225" s="1" t="s">
+      <c r="AX225" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AQ225" s="1" t="s">
+      <c r="AY225" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AR225" s="1" t="s">
+      <c r="AZ225" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AS225" s="1" t="s">
+      <c r="BA225" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AX225" s="5"/>
-      <c r="AY225" s="5"/>
-      <c r="AZ225" s="5"/>
-      <c r="BA225" s="5"/>
-      <c r="BB225" s="5"/>
-      <c r="BC225" s="5"/>
-      <c r="BD225" s="5"/>
-      <c r="BE225" s="5"/>
       <c r="BF225" s="2"/>
       <c r="BG225" s="2"/>
       <c r="BH225" s="2"/>
@@ -7593,51 +7695,46 @@
       <c r="BR225" s="9"/>
       <c r="BS225" s="9"/>
     </row>
-    <row r="226" spans="9:75" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B226" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G226" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H226" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="I226" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J226" s="1" t="s">
-        <v>58</v>
+        <v>80</v>
+      </c>
+      <c r="M226" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="N226" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O226" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="P226" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="T226" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="U226" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="Y226" s="1" t="s">
+      <c r="AA226" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AD226" s="1" t="s">
+      <c r="AF226" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AQ226" s="1" t="s">
+      <c r="AX226" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AY226" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AR226" s="1" t="s">
+      <c r="AZ226" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AS226" s="1" t="s">
+      <c r="BA226" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AX226" s="5"/>
-      <c r="AY226" s="5"/>
-      <c r="AZ226" s="5"/>
-      <c r="BA226" s="5"/>
-      <c r="BB226" s="5"/>
-      <c r="BC226" s="5"/>
-      <c r="BD226" s="5"/>
-      <c r="BE226" s="5"/>
       <c r="BF226" s="2"/>
       <c r="BG226" s="2"/>
       <c r="BH226" s="2"/>
@@ -7653,60 +7750,52 @@
       <c r="BR226" s="2"/>
       <c r="BS226" s="2"/>
     </row>
-    <row r="227" spans="9:75" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B227" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G227" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H227" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="I227" s="1" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N227" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O227" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="P227" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q227" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="S227" s="1" t="s">
+      <c r="L227" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="T227" s="1" t="s">
+      <c r="M227" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="Y227" s="1" t="s">
+      <c r="AA227" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="AE227" s="1" t="s">
+      <c r="AG227" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AP227" s="1" t="s">
+      <c r="AX227" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AQ227" s="1" t="s">
+      <c r="AY227" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AR227" s="1" t="s">
+      <c r="AZ227" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AS227" s="1" t="s">
+      <c r="BA227" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AT227" s="1" t="s">
+      <c r="BB227" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AX227" s="2"/>
-      <c r="AY227" s="2"/>
-      <c r="AZ227" s="2"/>
-      <c r="BA227" s="2"/>
-      <c r="BB227" s="2"/>
-      <c r="BC227" s="2"/>
-      <c r="BD227" s="2"/>
-      <c r="BE227" s="2"/>
       <c r="BF227" s="2"/>
       <c r="BG227" s="2"/>
       <c r="BH227" s="2"/>
@@ -7722,60 +7811,52 @@
       <c r="BR227" s="2"/>
       <c r="BS227" s="2"/>
     </row>
-    <row r="228" spans="9:75" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B228" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G228" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H228" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="I228" s="1" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="J228" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="N228" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O228" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="P228" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q228" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="R228" s="1" t="s">
+      <c r="K228" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="S228" s="1" t="s">
+      <c r="L228" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="Y228" s="1" t="s">
+      <c r="AA228" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="AF228" s="1" t="s">
+      <c r="AH228" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AP228" s="1" t="s">
+      <c r="AX228" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AQ228" s="1" t="s">
+      <c r="AY228" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AR228" s="1" t="s">
+      <c r="AZ228" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AS228" s="1" t="s">
+      <c r="BA228" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AT228" s="1" t="s">
+      <c r="BB228" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AX228" s="2"/>
-      <c r="AY228" s="2"/>
-      <c r="AZ228" s="2"/>
-      <c r="BA228" s="2"/>
-      <c r="BB228" s="2"/>
-      <c r="BC228" s="2"/>
-      <c r="BD228" s="2"/>
-      <c r="BE228" s="2"/>
       <c r="BF228" s="2"/>
       <c r="BG228" s="2"/>
       <c r="BH228" s="2"/>
@@ -7793,57 +7874,61 @@
       <c r="BV228" s="3"/>
       <c r="BW228" s="3"/>
     </row>
-    <row r="229" spans="9:75" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B229" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G229" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H229" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="I229" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="N229" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="O229" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="P229" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="K229" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="Q229" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="R229" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y229" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="U229" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="V229" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA229" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AG229" s="1" t="s">
+      <c r="AI229" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AP229" s="1" t="s">
+      <c r="AX229" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AQ229" s="1" t="s">
+      <c r="AY229" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AR229" s="1" t="s">
+      <c r="AZ229" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AS229" s="1" t="s">
+      <c r="BA229" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AT229" s="1" t="s">
+      <c r="BB229" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AX229" s="2"/>
-      <c r="AY229" s="2"/>
-      <c r="AZ229" s="2"/>
-      <c r="BA229" s="2"/>
-      <c r="BB229" s="2"/>
-      <c r="BC229" s="2"/>
-      <c r="BD229" s="2"/>
-      <c r="BE229" s="2"/>
       <c r="BF229" s="2"/>
       <c r="BG229" s="2"/>
       <c r="BH229" s="2"/>
@@ -7861,39 +7946,34 @@
       <c r="BV229" s="3"/>
       <c r="BW229" s="3"/>
     </row>
-    <row r="230" spans="9:75" x14ac:dyDescent="0.25">
-      <c r="I230" s="1" t="s">
+    <row r="230" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B230" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y230" s="1" t="s">
+      <c r="V230" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA230" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AH230" s="1" t="s">
+      <c r="AJ230" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AP230" s="1" t="s">
+      <c r="AX230" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AQ230" s="1" t="s">
+      <c r="AY230" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AR230" s="1" t="s">
+      <c r="AZ230" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AS230" s="1" t="s">
+      <c r="BA230" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AT230" s="1" t="s">
+      <c r="BB230" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AX230" s="2"/>
-      <c r="AY230" s="2"/>
-      <c r="AZ230" s="2"/>
-      <c r="BA230" s="2"/>
-      <c r="BB230" s="2"/>
-      <c r="BC230" s="2"/>
-      <c r="BD230" s="2"/>
-      <c r="BE230" s="2"/>
       <c r="BF230" s="2"/>
       <c r="BG230" s="2"/>
       <c r="BH230" s="2"/>
@@ -7911,36 +7991,34 @@
       <c r="BV230" s="3"/>
       <c r="BW230" s="3"/>
     </row>
-    <row r="231" spans="9:75" x14ac:dyDescent="0.25">
-      <c r="I231" s="1" t="s">
+    <row r="231" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B231" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Y231" s="1" t="s">
+      <c r="U231" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA231" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AI231" s="1" t="s">
+      <c r="AK231" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AQ231" s="1" t="s">
+      <c r="AX231" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY231" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AR231" s="1" t="s">
+      <c r="AZ231" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AS231" s="1" t="s">
+      <c r="BA231" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AT231" s="1" t="s">
+      <c r="BB231" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AX231" s="2"/>
-      <c r="AY231" s="2"/>
-      <c r="AZ231" s="2"/>
-      <c r="BA231" s="2"/>
-      <c r="BB231" s="2"/>
-      <c r="BC231" s="2"/>
-      <c r="BD231" s="2"/>
-      <c r="BE231" s="2"/>
       <c r="BF231" s="2"/>
       <c r="BG231" s="2"/>
       <c r="BH231" s="2"/>
@@ -7958,39 +8036,40 @@
       <c r="BV231" s="3"/>
       <c r="BW231" s="3"/>
     </row>
-    <row r="232" spans="9:75" x14ac:dyDescent="0.25">
-      <c r="I232" s="1" t="s">
+    <row r="232" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B232" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Y232" s="1" t="s">
+      <c r="Q232" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="T232" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA232" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AJ232" s="1" t="s">
+      <c r="AL232" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AQ232" s="1" t="s">
+      <c r="AX232" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AY232" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AR232" s="1" t="s">
+      <c r="AZ232" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AS232" s="1" t="s">
+      <c r="BA232" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AT232" s="1" t="s">
+      <c r="BB232" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AU232" s="1" t="s">
+      <c r="BC232" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AX232" s="2"/>
-      <c r="AY232" s="2"/>
-      <c r="AZ232" s="2"/>
-      <c r="BA232" s="2"/>
-      <c r="BB232" s="2"/>
-      <c r="BC232" s="2"/>
-      <c r="BD232" s="2"/>
-      <c r="BE232" s="2"/>
       <c r="BF232" s="2"/>
       <c r="BG232" s="2"/>
       <c r="BH232" s="2"/>
@@ -8008,54 +8087,46 @@
       <c r="BV232" s="3"/>
       <c r="BW232" s="3"/>
     </row>
-    <row r="233" spans="9:75" x14ac:dyDescent="0.25">
-      <c r="I233" s="1" t="s">
+    <row r="233" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B233" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J233" s="1" t="s">
+      <c r="C233" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K233" s="1" t="s">
+      <c r="D233" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L233" s="1" t="s">
+      <c r="E233" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="M233" s="1" t="s">
+      <c r="F233" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="Y233" s="1" t="s">
+      <c r="AA233" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="AK233" s="1" t="s">
+      <c r="AM233" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AP233" s="1" t="s">
+      <c r="AX233" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AQ233" s="1" t="s">
+      <c r="AY233" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AR233" s="1" t="s">
+      <c r="AZ233" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AS233" s="1" t="s">
+      <c r="BA233" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AT233" s="1" t="s">
+      <c r="BB233" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AU233" s="1" t="s">
+      <c r="BC233" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AX233" s="2"/>
-      <c r="AY233" s="2"/>
-      <c r="AZ233" s="2"/>
-      <c r="BA233" s="2"/>
-      <c r="BB233" s="2"/>
-      <c r="BC233" s="2"/>
-      <c r="BD233" s="2"/>
-      <c r="BE233" s="2"/>
       <c r="BF233" s="2"/>
       <c r="BG233" s="2"/>
       <c r="BH233" s="2"/>
@@ -8073,54 +8144,46 @@
       <c r="BV233" s="3"/>
       <c r="BW233" s="3"/>
     </row>
-    <row r="234" spans="9:75" x14ac:dyDescent="0.25">
-      <c r="I234" s="1" t="s">
+    <row r="234" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B234" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J234" s="1" t="s">
+      <c r="C234" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="K234" s="1" t="s">
+      <c r="D234" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="M234" s="1" t="s">
+      <c r="F234" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="Y234" s="1" t="s">
+      <c r="AA234" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="AL234" s="1" t="s">
+      <c r="AN234" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AP234" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ234" s="1" t="s">
+      <c r="AX234" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AY234" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AR234" s="1" t="s">
+      <c r="AZ234" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AS234" s="1" t="s">
+      <c r="BA234" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AT234" s="1" t="s">
+      <c r="BB234" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AU234" s="1" t="s">
+      <c r="BC234" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AV234" s="1" t="s">
+      <c r="BD234" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AX234" s="2"/>
-      <c r="AY234" s="2"/>
-      <c r="AZ234" s="2"/>
-      <c r="BA234" s="2"/>
-      <c r="BB234" s="2"/>
-      <c r="BC234" s="2"/>
-      <c r="BD234" s="2"/>
-      <c r="BE234" s="2"/>
       <c r="BF234" s="2"/>
       <c r="BG234" s="2"/>
       <c r="BH234" s="2"/>
@@ -8138,54 +8201,46 @@
       <c r="BV234" s="3"/>
       <c r="BW234" s="3"/>
     </row>
-    <row r="235" spans="9:75" x14ac:dyDescent="0.25">
-      <c r="I235" s="1" t="s">
+    <row r="235" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B235" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J235" s="1" t="s">
+      <c r="C235" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N235" s="1" t="s">
+      <c r="G235" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="W235" s="1" t="s">
+      <c r="P235" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="Y235" s="1" t="s">
+      <c r="AA235" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AM235" s="1" t="s">
+      <c r="AO235" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AP235" s="1" t="s">
+      <c r="AX235" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AQ235" s="1" t="s">
+      <c r="AY235" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR235" s="1" t="s">
+      <c r="AZ235" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AS235" s="1" t="s">
+      <c r="BA235" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AT235" s="1" t="s">
+      <c r="BB235" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AU235" s="1" t="s">
+      <c r="BC235" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AV235" s="1" t="s">
+      <c r="BD235" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AX235" s="2"/>
-      <c r="AY235" s="2"/>
-      <c r="AZ235" s="2"/>
-      <c r="BA235" s="2"/>
-      <c r="BB235" s="2"/>
-      <c r="BC235" s="2"/>
-      <c r="BD235" s="2"/>
-      <c r="BE235" s="2"/>
       <c r="BF235" s="2"/>
       <c r="BG235" s="2"/>
       <c r="BH235" s="2"/>
@@ -8203,41 +8258,39 @@
       <c r="BV235" s="3"/>
       <c r="BW235" s="3"/>
     </row>
-    <row r="236" spans="9:75" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:75" x14ac:dyDescent="0.25">
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
+      <c r="AA236" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="AP236" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AX236" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AQ236" s="1" t="s">
+      <c r="AY236" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AR236" s="1" t="s">
+      <c r="AZ236" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AS236" s="1" t="s">
+      <c r="BA236" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AT236" s="1" t="s">
+      <c r="BB236" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AU236" s="1" t="s">
+      <c r="BC236" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AV236" s="1" t="s">
+      <c r="BD236" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AW236" s="1" t="s">
+      <c r="BE236" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AX236" s="2"/>
-      <c r="AY236" s="2"/>
-      <c r="AZ236" s="2"/>
-      <c r="BA236" s="2"/>
-      <c r="BB236" s="2"/>
-      <c r="BC236" s="2"/>
-      <c r="BD236" s="2"/>
-      <c r="BE236" s="2"/>
       <c r="BF236" s="2"/>
       <c r="BG236" s="2"/>
       <c r="BH236" s="2"/>
@@ -8255,41 +8308,39 @@
       <c r="BV236" s="3"/>
       <c r="BW236" s="3"/>
     </row>
-    <row r="237" spans="9:75" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:75" x14ac:dyDescent="0.25">
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
-      <c r="AP237" s="1" t="s">
+      <c r="AA237" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AQ237" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AX237" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AQ237" s="1" t="s">
+      <c r="AY237" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AR237" s="1" t="s">
+      <c r="AZ237" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AS237" s="1" t="s">
+      <c r="BA237" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AT237" s="1" t="s">
+      <c r="BB237" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AU237" s="1" t="s">
+      <c r="BC237" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AV237" s="1" t="s">
+      <c r="BD237" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AW237" s="1" t="s">
+      <c r="BE237" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AX237" s="2"/>
-      <c r="AY237" s="2"/>
-      <c r="AZ237" s="2"/>
-      <c r="BA237" s="2"/>
-      <c r="BB237" s="2"/>
-      <c r="BC237" s="2"/>
-      <c r="BD237" s="2"/>
-      <c r="BE237" s="2"/>
       <c r="BF237" s="2"/>
       <c r="BG237" s="2"/>
       <c r="BH237" s="2"/>
@@ -8307,17 +8358,24 @@
       <c r="BV237" s="3"/>
       <c r="BW237" s="3"/>
     </row>
-    <row r="238" spans="9:75" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:75" x14ac:dyDescent="0.25">
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
-      <c r="AW238" s="2"/>
-      <c r="AX238" s="2"/>
-      <c r="AY238" s="2"/>
-      <c r="AZ238" s="2"/>
-      <c r="BA238" s="2"/>
-      <c r="BB238" s="2"/>
-      <c r="BC238" s="2"/>
-      <c r="BD238" s="2"/>
+      <c r="AA238" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AR238" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AX238" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AY238" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AZ238" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="BE238" s="2"/>
       <c r="BF238" s="2"/>
       <c r="BG238" s="2"/>
@@ -8336,7 +8394,7 @@
       <c r="BV238" s="3"/>
       <c r="BW238" s="3"/>
     </row>
-    <row r="239" spans="9:75" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:75" x14ac:dyDescent="0.25">
       <c r="J239" s="1" t="s">
         <v>27</v>
       </c>
@@ -8361,14 +8419,39 @@
       <c r="Q239" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AW239" s="2"/>
-      <c r="AX239" s="2"/>
-      <c r="AY239" s="2"/>
-      <c r="AZ239" s="2"/>
-      <c r="BA239" s="2"/>
-      <c r="BB239" s="2"/>
-      <c r="BC239" s="2"/>
-      <c r="BD239" s="2"/>
+      <c r="R239" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="S239" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T239" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="U239" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V239" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA239" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AS239" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AX239" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY239" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ239" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BA239" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="BE239" s="2"/>
       <c r="BF239" s="2"/>
       <c r="BG239" s="2"/>
@@ -8387,7 +8470,7 @@
       <c r="BV239" s="3"/>
       <c r="BW239" s="3"/>
     </row>
-    <row r="240" spans="9:75" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:75" x14ac:dyDescent="0.25">
       <c r="J240" s="1" t="s">
         <v>65</v>
       </c>
@@ -8412,14 +8495,39 @@
       <c r="Q240" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AW240" s="2"/>
-      <c r="AX240" s="2"/>
-      <c r="AY240" s="2"/>
-      <c r="AZ240" s="2"/>
-      <c r="BA240" s="2"/>
-      <c r="BB240" s="2"/>
-      <c r="BC240" s="2"/>
-      <c r="BD240" s="2"/>
+      <c r="R240" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="S240" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="T240" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="U240" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="V240" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA240" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AT240" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AX240" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY240" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ240" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BA240" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="BE240" s="2"/>
       <c r="BF240" s="2"/>
       <c r="BG240" s="2"/>
@@ -8463,14 +8571,39 @@
       <c r="Q241" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AW241" s="2"/>
-      <c r="AX241" s="2"/>
-      <c r="AY241" s="2"/>
-      <c r="AZ241" s="2"/>
-      <c r="BA241" s="2"/>
-      <c r="BB241" s="2"/>
-      <c r="BC241" s="2"/>
-      <c r="BD241" s="2"/>
+      <c r="R241" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="S241" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T241" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="U241" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="V241" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA241" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AU241" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX241" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY241" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AZ241" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BA241" s="1" t="s">
+        <v>111</v>
+      </c>
       <c r="BE241" s="2"/>
       <c r="BF241" s="2"/>
       <c r="BG241" s="2"/>
@@ -8491,9 +8624,15 @@
     </row>
     <row r="242" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW242" s="2"/>
-      <c r="AX242" s="2"/>
-      <c r="AY242" s="2"/>
-      <c r="AZ242" s="2"/>
+      <c r="AX242" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY242" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="AZ242" s="5" t="s">
+        <v>100</v>
+      </c>
       <c r="BA242" s="2"/>
       <c r="BB242" s="2"/>
       <c r="BC242" s="2"/>
@@ -8516,9 +8655,15 @@
     </row>
     <row r="243" spans="10:75" x14ac:dyDescent="0.25">
       <c r="AW243" s="2"/>
-      <c r="AX243" s="2"/>
-      <c r="AY243" s="2"/>
-      <c r="AZ243" s="2"/>
+      <c r="AX243" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY243" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="AZ243" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="BA243" s="2"/>
       <c r="BB243" s="2"/>
       <c r="BC243" s="2"/>

--- a/temp/searchByMACTable.xlsx
+++ b/temp/searchByMACTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="130">
   <si>
     <t>2.1</t>
   </si>
@@ -383,6 +383,27 @@
   </si>
   <si>
     <t>2_20</t>
+  </si>
+  <si>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>17.48</t>
+  </si>
+  <si>
+    <t>24.1</t>
+  </si>
+  <si>
+    <t>IDConcentrator</t>
+  </si>
+  <si>
+    <t>LinksRemainingNumber</t>
+  </si>
+  <si>
+    <t>43210</t>
+  </si>
+  <si>
+    <t>3210</t>
   </si>
 </sst>
 </file>
@@ -794,7 +815,7 @@
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="4" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7" style="1" customWidth="1"/>
     <col min="4" max="4" width="5" style="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="1" customWidth="1"/>
     <col min="6" max="8" width="5" style="1" customWidth="1"/>
@@ -7435,6 +7456,12 @@
       <c r="V221" s="1" t="s">
         <v>117</v>
       </c>
+      <c r="X221" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y221" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="AB221" s="1" t="s">
         <v>48</v>
       </c>
@@ -7520,6 +7547,12 @@
       </c>
       <c r="T222" s="1" t="s">
         <v>115</v>
+      </c>
+      <c r="X222" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y222" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="AA222" s="1" t="s">
         <v>60</v>
@@ -7561,6 +7594,12 @@
       <c r="S223" s="1" t="s">
         <v>113</v>
       </c>
+      <c r="X223" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y223" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="AA223" s="1" t="s">
         <v>62</v>
       </c>
@@ -7610,6 +7649,12 @@
       <c r="O224" s="1" t="s">
         <v>94</v>
       </c>
+      <c r="X224" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y224" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="AA224" s="1" t="s">
         <v>66</v>
       </c>
@@ -7662,6 +7707,12 @@
       <c r="P225" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="X225" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y225" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="AA225" s="1" t="s">
         <v>67</v>
       </c>
@@ -7717,6 +7768,12 @@
       <c r="N226" s="1" t="s">
         <v>93</v>
       </c>
+      <c r="X226" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y226" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="AA226" s="1" t="s">
         <v>69</v>
       </c>
@@ -7775,6 +7832,12 @@
       <c r="M227" s="1" t="s">
         <v>91</v>
       </c>
+      <c r="X227" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y227" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AA227" s="1" t="s">
         <v>76</v>
       </c>
@@ -7835,6 +7898,12 @@
       </c>
       <c r="L228" s="1" t="s">
         <v>89</v>
+      </c>
+      <c r="X228" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y228" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="AA228" s="1" t="s">
         <v>80</v>
@@ -7908,6 +7977,12 @@
       <c r="V229" s="1" t="s">
         <v>119</v>
       </c>
+      <c r="X229" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y229" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="AA229" s="1" t="s">
         <v>84</v>
       </c>
@@ -7953,6 +8028,12 @@
       <c r="V230" s="1" t="s">
         <v>122</v>
       </c>
+      <c r="X230" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y230" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="AA230" s="1" t="s">
         <v>86</v>
       </c>
@@ -7998,6 +8079,12 @@
       <c r="U231" s="1" t="s">
         <v>121</v>
       </c>
+      <c r="X231" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y231" s="2" t="s">
+        <v>125</v>
+      </c>
       <c r="AA231" s="1" t="s">
         <v>89</v>
       </c>
@@ -8046,6 +8133,12 @@
       <c r="T232" s="1" t="s">
         <v>116</v>
       </c>
+      <c r="X232" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y232" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="AA232" s="1" t="s">
         <v>91</v>
       </c>
@@ -8103,6 +8196,12 @@
       <c r="F233" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="X233" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y233" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="AA233" s="1" t="s">
         <v>93</v>
       </c>
@@ -8214,6 +8313,12 @@
       <c r="P235" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="X235" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y235" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="AA235" s="1" t="s">
         <v>96</v>
       </c>
@@ -8261,6 +8366,12 @@
     <row r="236" spans="2:75" x14ac:dyDescent="0.25">
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
+      <c r="X236" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y236" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="AA236" s="1" t="s">
         <v>106</v>
       </c>
@@ -8311,6 +8422,12 @@
     <row r="237" spans="2:75" x14ac:dyDescent="0.25">
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
+      <c r="X237" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y237" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="AA237" s="1" t="s">
         <v>110</v>
       </c>
@@ -8361,6 +8478,12 @@
     <row r="238" spans="2:75" x14ac:dyDescent="0.25">
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
+      <c r="X238" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y238" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AA238" s="1" t="s">
         <v>112</v>
       </c>
@@ -8434,6 +8557,12 @@
       <c r="V239" s="1" t="s">
         <v>117</v>
       </c>
+      <c r="X239" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y239" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="AA239" s="1" t="s">
         <v>115</v>
       </c>
@@ -8510,6 +8639,12 @@
       <c r="V240" s="1" t="s">
         <v>119</v>
       </c>
+      <c r="X240" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y240" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="AA240" s="1" t="s">
         <v>118</v>
       </c>
@@ -8546,7 +8681,7 @@
       <c r="BV240" s="3"/>
       <c r="BW240" s="3"/>
     </row>
-    <row r="241" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:75" x14ac:dyDescent="0.25">
       <c r="J241" s="1" t="s">
         <v>66</v>
       </c>
@@ -8585,6 +8720,12 @@
       </c>
       <c r="V241" s="1" t="s">
         <v>122</v>
+      </c>
+      <c r="X241" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y241" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="AA241" s="1" t="s">
         <v>119</v>
@@ -8622,7 +8763,13 @@
       <c r="BV241" s="3"/>
       <c r="BW241" s="3"/>
     </row>
-    <row r="242" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="X242" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y242" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="AW242" s="2"/>
       <c r="AX242" s="5" t="s">
         <v>48</v>
@@ -8653,7 +8800,19 @@
       <c r="BR242" s="2"/>
       <c r="BS242" s="2"/>
     </row>
-    <row r="243" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B243" t="s">
+        <v>126</v>
+      </c>
+      <c r="C243" t="s">
+        <v>127</v>
+      </c>
+      <c r="X243" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y243" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="AW243" s="2"/>
       <c r="AX243" s="5" t="s">
         <v>48</v>
@@ -8684,7 +8843,19 @@
       <c r="BR243" s="2"/>
       <c r="BS243" s="2"/>
     </row>
-    <row r="244" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B244" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="X244" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y244" s="1" t="s">
+        <v>123</v>
+      </c>
       <c r="AW244" s="2"/>
       <c r="AX244" s="2"/>
       <c r="AY244" s="2"/>
@@ -8709,7 +8880,19 @@
       <c r="BR244" s="2"/>
       <c r="BS244" s="2"/>
     </row>
-    <row r="245" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B245" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="X245" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y245" s="1" t="s">
+        <v>124</v>
+      </c>
       <c r="AW245" s="2"/>
       <c r="AX245" s="2"/>
       <c r="AY245" s="2"/>
@@ -8734,7 +8917,19 @@
       <c r="BR245" s="2"/>
       <c r="BS245" s="2"/>
     </row>
-    <row r="246" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="B246" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="X246" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y246" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="AW246" s="2"/>
       <c r="AX246" s="2"/>
       <c r="AY246" s="2"/>
@@ -8759,7 +8954,13 @@
       <c r="BR246" s="2"/>
       <c r="BS246" s="2"/>
     </row>
-    <row r="247" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="X247" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y247" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="AW247" s="2"/>
       <c r="AX247" s="2"/>
       <c r="AY247" s="2"/>
@@ -8784,7 +8985,7 @@
       <c r="BR247" s="2"/>
       <c r="BS247" s="2"/>
     </row>
-    <row r="248" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:75" x14ac:dyDescent="0.25">
       <c r="AW248" s="2"/>
       <c r="AX248" s="2"/>
       <c r="AY248" s="2"/>
@@ -8809,7 +9010,7 @@
       <c r="BR248" s="2"/>
       <c r="BS248" s="2"/>
     </row>
-    <row r="249" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:75" x14ac:dyDescent="0.25">
       <c r="AW249" s="2"/>
       <c r="AX249" s="2"/>
       <c r="AY249" s="2"/>
@@ -8834,7 +9035,7 @@
       <c r="BR249" s="2"/>
       <c r="BS249" s="2"/>
     </row>
-    <row r="250" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:75" x14ac:dyDescent="0.25">
       <c r="AW250" s="2"/>
       <c r="AX250" s="2"/>
       <c r="AY250" s="2"/>
@@ -8859,7 +9060,7 @@
       <c r="BR250" s="2"/>
       <c r="BS250" s="2"/>
     </row>
-    <row r="251" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:75" x14ac:dyDescent="0.25">
       <c r="AW251" s="2"/>
       <c r="AX251" s="2"/>
       <c r="AY251" s="2"/>
@@ -8884,7 +9085,7 @@
       <c r="BR251" s="2"/>
       <c r="BS251" s="2"/>
     </row>
-    <row r="252" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:75" x14ac:dyDescent="0.25">
       <c r="AW252" s="5"/>
       <c r="AX252" s="5"/>
       <c r="AY252" s="5"/>
@@ -8909,7 +9110,7 @@
       <c r="BR252" s="5"/>
       <c r="BS252" s="5"/>
     </row>
-    <row r="253" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:75" x14ac:dyDescent="0.25">
       <c r="AW253" s="5"/>
       <c r="AX253" s="5"/>
       <c r="AY253" s="5"/>
@@ -8934,7 +9135,7 @@
       <c r="BR253" s="5"/>
       <c r="BS253" s="5"/>
     </row>
-    <row r="254" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:75" x14ac:dyDescent="0.25">
       <c r="AW254" s="5"/>
       <c r="AX254" s="5"/>
       <c r="AY254" s="5"/>
@@ -8959,7 +9160,7 @@
       <c r="BR254" s="5"/>
       <c r="BS254" s="5"/>
     </row>
-    <row r="255" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:75" x14ac:dyDescent="0.25">
       <c r="AW255" s="5"/>
       <c r="AX255" s="5"/>
       <c r="AY255" s="5"/>
@@ -8984,7 +9185,7 @@
       <c r="BR255" s="5"/>
       <c r="BS255" s="5"/>
     </row>
-    <row r="256" spans="10:75" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:75" x14ac:dyDescent="0.25">
       <c r="AW256" s="5"/>
       <c r="AX256" s="5"/>
       <c r="AY256" s="5"/>

--- a/temp/searchByMACTable.xlsx
+++ b/temp/searchByMACTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="132">
   <si>
     <t>2.1</t>
   </si>
@@ -405,12 +405,18 @@
   <si>
     <t>3210</t>
   </si>
+  <si>
+    <t>вместо х_х просто 1</t>
+  </si>
+  <si>
+    <t>всегда можно взять контейнер и наполнять его сколь угодно долго классами (анонимными объектами), содержащими разные параметры и контейнеры с нужными значениями</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -460,6 +466,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -493,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -506,6 +519,7 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -7456,70 +7470,74 @@
       <c r="V221" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="X221" s="2" t="s">
+      <c r="W221" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="X221" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="Y221" s="2" t="s">
+      <c r="Y221" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="AB221" s="1" t="s">
+      <c r="AA221" s="2"/>
+      <c r="AB221" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AC221" s="1" t="s">
+      <c r="AC221" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AD221" s="1" t="s">
+      <c r="AD221" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AE221" s="1" t="s">
+      <c r="AE221" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AF221" s="1" t="s">
+      <c r="AF221" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AG221" s="1" t="s">
+      <c r="AG221" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AH221" s="1" t="s">
+      <c r="AH221" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AI221" s="1" t="s">
+      <c r="AI221" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AJ221" s="1" t="s">
+      <c r="AJ221" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AK221" s="1" t="s">
+      <c r="AK221" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AL221" s="1" t="s">
+      <c r="AL221" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AM221" s="1" t="s">
+      <c r="AM221" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AN221" s="1" t="s">
+      <c r="AN221" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AO221" s="1" t="s">
+      <c r="AO221" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AP221" s="1" t="s">
+      <c r="AP221" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AQ221" s="1" t="s">
+      <c r="AQ221" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AR221" s="1" t="s">
+      <c r="AR221" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AS221" s="1" t="s">
+      <c r="AS221" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AT221" s="1" t="s">
+      <c r="AT221" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AU221" s="1" t="s">
+      <c r="AU221" s="2" t="s">
         <v>117</v>
       </c>
       <c r="AX221" s="1" t="s">
@@ -7548,18 +7566,40 @@
       <c r="T222" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="X222" s="2" t="s">
+      <c r="W222" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="X222" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="Y222" s="2" t="s">
+      <c r="Y222" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="AA222" s="1" t="s">
+      <c r="AA222" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AB222" s="1" t="s">
+      <c r="AB222" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="AC222" s="2"/>
+      <c r="AD222" s="2"/>
+      <c r="AE222" s="2"/>
+      <c r="AF222" s="2"/>
+      <c r="AG222" s="2"/>
+      <c r="AH222" s="2"/>
+      <c r="AI222" s="2"/>
+      <c r="AJ222" s="2"/>
+      <c r="AK222" s="2"/>
+      <c r="AL222" s="2"/>
+      <c r="AM222" s="2"/>
+      <c r="AN222" s="2"/>
+      <c r="AO222" s="2"/>
+      <c r="AP222" s="2"/>
+      <c r="AQ222" s="2"/>
+      <c r="AR222" s="2"/>
+      <c r="AS222" s="2"/>
+      <c r="AT222" s="2"/>
+      <c r="AU222" s="2"/>
       <c r="AX222" s="1" t="s">
         <v>33</v>
       </c>
@@ -7594,18 +7634,40 @@
       <c r="S223" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="X223" s="2" t="s">
+      <c r="W223" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="X223" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="Y223" s="2" t="s">
+      <c r="Y223" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="AA223" s="1" t="s">
+      <c r="AA223" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC223" s="1" t="s">
+      <c r="AB223" s="2"/>
+      <c r="AC223" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="AD223" s="2"/>
+      <c r="AE223" s="2"/>
+      <c r="AF223" s="2"/>
+      <c r="AG223" s="2"/>
+      <c r="AH223" s="2"/>
+      <c r="AI223" s="2"/>
+      <c r="AJ223" s="2"/>
+      <c r="AK223" s="2"/>
+      <c r="AL223" s="2"/>
+      <c r="AM223" s="2"/>
+      <c r="AN223" s="2"/>
+      <c r="AO223" s="2"/>
+      <c r="AP223" s="2"/>
+      <c r="AQ223" s="2"/>
+      <c r="AR223" s="2"/>
+      <c r="AS223" s="2"/>
+      <c r="AT223" s="2"/>
+      <c r="AU223" s="2"/>
       <c r="AX223" s="1" t="s">
         <v>33</v>
       </c>
@@ -7649,18 +7711,40 @@
       <c r="O224" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="X224" s="2" t="s">
+      <c r="W224" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="X224" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="Y224" s="2" t="s">
+      <c r="Y224" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="AA224" s="1" t="s">
+      <c r="AA224" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AD224" s="1" t="s">
+      <c r="AB224" s="2"/>
+      <c r="AC224" s="2"/>
+      <c r="AD224" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="AE224" s="2"/>
+      <c r="AF224" s="2"/>
+      <c r="AG224" s="2"/>
+      <c r="AH224" s="2"/>
+      <c r="AI224" s="2"/>
+      <c r="AJ224" s="2"/>
+      <c r="AK224" s="2"/>
+      <c r="AL224" s="2"/>
+      <c r="AM224" s="2"/>
+      <c r="AN224" s="2"/>
+      <c r="AO224" s="2"/>
+      <c r="AP224" s="2"/>
+      <c r="AQ224" s="2"/>
+      <c r="AR224" s="2"/>
+      <c r="AS224" s="2"/>
+      <c r="AT224" s="2"/>
+      <c r="AU224" s="2"/>
       <c r="AX224" s="1" t="s">
         <v>33</v>
       </c>
@@ -7707,18 +7791,40 @@
       <c r="P225" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="X225" s="2" t="s">
+      <c r="W225" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="X225" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="Y225" s="2" t="s">
+      <c r="Y225" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="AA225" s="1" t="s">
+      <c r="AA225" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AE225" s="1" t="s">
+      <c r="AB225" s="2"/>
+      <c r="AC225" s="2"/>
+      <c r="AD225" s="2"/>
+      <c r="AE225" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="AF225" s="2"/>
+      <c r="AG225" s="2"/>
+      <c r="AH225" s="2"/>
+      <c r="AI225" s="2"/>
+      <c r="AJ225" s="2"/>
+      <c r="AK225" s="2"/>
+      <c r="AL225" s="2"/>
+      <c r="AM225" s="2"/>
+      <c r="AN225" s="2"/>
+      <c r="AO225" s="2"/>
+      <c r="AP225" s="2"/>
+      <c r="AQ225" s="2"/>
+      <c r="AR225" s="2"/>
+      <c r="AS225" s="2"/>
+      <c r="AT225" s="2"/>
+      <c r="AU225" s="2"/>
       <c r="AX225" s="1" t="s">
         <v>33</v>
       </c>
@@ -7768,18 +7874,40 @@
       <c r="N226" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="X226" s="2" t="s">
+      <c r="W226" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="X226" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="Y226" s="2" t="s">
+      <c r="Y226" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="AA226" s="1" t="s">
+      <c r="AA226" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AF226" s="1" t="s">
+      <c r="AB226" s="2"/>
+      <c r="AC226" s="2"/>
+      <c r="AD226" s="2"/>
+      <c r="AE226" s="2"/>
+      <c r="AF226" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="AG226" s="2"/>
+      <c r="AH226" s="2"/>
+      <c r="AI226" s="2"/>
+      <c r="AJ226" s="2"/>
+      <c r="AK226" s="2"/>
+      <c r="AL226" s="2"/>
+      <c r="AM226" s="2"/>
+      <c r="AN226" s="2"/>
+      <c r="AO226" s="2"/>
+      <c r="AP226" s="2"/>
+      <c r="AQ226" s="2"/>
+      <c r="AR226" s="2"/>
+      <c r="AS226" s="2"/>
+      <c r="AT226" s="2"/>
+      <c r="AU226" s="2"/>
       <c r="AX226" s="1" t="s">
         <v>33</v>
       </c>
@@ -7832,18 +7960,40 @@
       <c r="M227" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="X227" s="2" t="s">
+      <c r="W227" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="X227" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="Y227" s="2" t="s">
+      <c r="Y227" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="AA227" s="1" t="s">
+      <c r="AA227" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AG227" s="1" t="s">
+      <c r="AB227" s="2"/>
+      <c r="AC227" s="2"/>
+      <c r="AD227" s="2"/>
+      <c r="AE227" s="2"/>
+      <c r="AF227" s="2"/>
+      <c r="AG227" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AH227" s="2"/>
+      <c r="AI227" s="2"/>
+      <c r="AJ227" s="2"/>
+      <c r="AK227" s="2"/>
+      <c r="AL227" s="2"/>
+      <c r="AM227" s="2"/>
+      <c r="AN227" s="2"/>
+      <c r="AO227" s="2"/>
+      <c r="AP227" s="2"/>
+      <c r="AQ227" s="2"/>
+      <c r="AR227" s="2"/>
+      <c r="AS227" s="2"/>
+      <c r="AT227" s="2"/>
+      <c r="AU227" s="2"/>
       <c r="AX227" s="1" t="s">
         <v>48</v>
       </c>
@@ -7899,18 +8049,40 @@
       <c r="L228" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="X228" s="2" t="s">
+      <c r="W228" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="X228" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="Y228" s="2" t="s">
+      <c r="Y228" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="AA228" s="1" t="s">
+      <c r="AA228" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="AH228" s="1" t="s">
+      <c r="AB228" s="2"/>
+      <c r="AC228" s="2"/>
+      <c r="AD228" s="2"/>
+      <c r="AE228" s="2"/>
+      <c r="AF228" s="2"/>
+      <c r="AG228" s="2"/>
+      <c r="AH228" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="AI228" s="2"/>
+      <c r="AJ228" s="2"/>
+      <c r="AK228" s="2"/>
+      <c r="AL228" s="2"/>
+      <c r="AM228" s="2"/>
+      <c r="AN228" s="2"/>
+      <c r="AO228" s="2"/>
+      <c r="AP228" s="2"/>
+      <c r="AQ228" s="2"/>
+      <c r="AR228" s="2"/>
+      <c r="AS228" s="2"/>
+      <c r="AT228" s="2"/>
+      <c r="AU228" s="2"/>
       <c r="AX228" s="1" t="s">
         <v>48</v>
       </c>
@@ -7977,18 +8149,40 @@
       <c r="V229" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="X229" s="2" t="s">
+      <c r="W229" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="X229" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="Y229" s="2" t="s">
+      <c r="Y229" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="AA229" s="1" t="s">
+      <c r="AA229" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AI229" s="1" t="s">
+      <c r="AB229" s="2"/>
+      <c r="AC229" s="2"/>
+      <c r="AD229" s="2"/>
+      <c r="AE229" s="2"/>
+      <c r="AF229" s="2"/>
+      <c r="AG229" s="2"/>
+      <c r="AH229" s="2"/>
+      <c r="AI229" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="AJ229" s="2"/>
+      <c r="AK229" s="2"/>
+      <c r="AL229" s="2"/>
+      <c r="AM229" s="2"/>
+      <c r="AN229" s="2"/>
+      <c r="AO229" s="2"/>
+      <c r="AP229" s="2"/>
+      <c r="AQ229" s="2"/>
+      <c r="AR229" s="2"/>
+      <c r="AS229" s="2"/>
+      <c r="AT229" s="2"/>
+      <c r="AU229" s="2"/>
       <c r="AX229" s="1" t="s">
         <v>33</v>
       </c>
@@ -8028,18 +8222,40 @@
       <c r="V230" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="X230" s="2" t="s">
+      <c r="W230" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="X230" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="Y230" s="2" t="s">
+      <c r="Y230" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="AA230" s="1" t="s">
+      <c r="AA230" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AJ230" s="1" t="s">
+      <c r="AB230" s="2"/>
+      <c r="AC230" s="2"/>
+      <c r="AD230" s="2"/>
+      <c r="AE230" s="2"/>
+      <c r="AF230" s="2"/>
+      <c r="AG230" s="2"/>
+      <c r="AH230" s="2"/>
+      <c r="AI230" s="2"/>
+      <c r="AJ230" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="AK230" s="2"/>
+      <c r="AL230" s="2"/>
+      <c r="AM230" s="2"/>
+      <c r="AN230" s="2"/>
+      <c r="AO230" s="2"/>
+      <c r="AP230" s="2"/>
+      <c r="AQ230" s="2"/>
+      <c r="AR230" s="2"/>
+      <c r="AS230" s="2"/>
+      <c r="AT230" s="2"/>
+      <c r="AU230" s="2"/>
       <c r="AX230" s="1" t="s">
         <v>48</v>
       </c>
@@ -8079,18 +8295,40 @@
       <c r="U231" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="X231" s="2" t="s">
+      <c r="W231" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="X231" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="Y231" s="2" t="s">
+      <c r="Y231" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="AA231" s="1" t="s">
+      <c r="AA231" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AK231" s="1" t="s">
+      <c r="AB231" s="2"/>
+      <c r="AC231" s="2"/>
+      <c r="AD231" s="2"/>
+      <c r="AE231" s="2"/>
+      <c r="AF231" s="2"/>
+      <c r="AG231" s="2"/>
+      <c r="AH231" s="2"/>
+      <c r="AI231" s="2"/>
+      <c r="AJ231" s="2"/>
+      <c r="AK231" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="AL231" s="2"/>
+      <c r="AM231" s="2"/>
+      <c r="AN231" s="2"/>
+      <c r="AO231" s="2"/>
+      <c r="AP231" s="2"/>
+      <c r="AQ231" s="2"/>
+      <c r="AR231" s="2"/>
+      <c r="AS231" s="2"/>
+      <c r="AT231" s="2"/>
+      <c r="AU231" s="2"/>
       <c r="AX231" s="1" t="s">
         <v>48</v>
       </c>
@@ -8133,18 +8371,40 @@
       <c r="T232" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="X232" s="2" t="s">
+      <c r="W232" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="X232" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="Y232" s="2" t="s">
+      <c r="Y232" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="AA232" s="1" t="s">
+      <c r="AA232" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="AL232" s="1" t="s">
+      <c r="AB232" s="2"/>
+      <c r="AC232" s="2"/>
+      <c r="AD232" s="2"/>
+      <c r="AE232" s="2"/>
+      <c r="AF232" s="2"/>
+      <c r="AG232" s="2"/>
+      <c r="AH232" s="2"/>
+      <c r="AI232" s="2"/>
+      <c r="AJ232" s="2"/>
+      <c r="AK232" s="2"/>
+      <c r="AL232" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="AM232" s="2"/>
+      <c r="AN232" s="2"/>
+      <c r="AO232" s="2"/>
+      <c r="AP232" s="2"/>
+      <c r="AQ232" s="2"/>
+      <c r="AR232" s="2"/>
+      <c r="AS232" s="2"/>
+      <c r="AT232" s="2"/>
+      <c r="AU232" s="2"/>
       <c r="AX232" s="1" t="s">
         <v>33</v>
       </c>
@@ -8196,18 +8456,40 @@
       <c r="F233" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="X233" s="2" t="s">
+      <c r="W233" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="X233" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="Y233" s="2" t="s">
+      <c r="Y233" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="AA233" s="1" t="s">
+      <c r="AA233" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AM233" s="1" t="s">
+      <c r="AB233" s="2"/>
+      <c r="AC233" s="2"/>
+      <c r="AD233" s="2"/>
+      <c r="AE233" s="2"/>
+      <c r="AF233" s="2"/>
+      <c r="AG233" s="2"/>
+      <c r="AH233" s="2"/>
+      <c r="AI233" s="2"/>
+      <c r="AJ233" s="2"/>
+      <c r="AK233" s="2"/>
+      <c r="AL233" s="2"/>
+      <c r="AM233" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="AN233" s="2"/>
+      <c r="AO233" s="2"/>
+      <c r="AP233" s="2"/>
+      <c r="AQ233" s="2"/>
+      <c r="AR233" s="2"/>
+      <c r="AS233" s="2"/>
+      <c r="AT233" s="2"/>
+      <c r="AU233" s="2"/>
       <c r="AX233" s="1" t="s">
         <v>48</v>
       </c>
@@ -8256,12 +8538,31 @@
       <c r="F234" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AA234" s="1" t="s">
+      <c r="AA234" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="AN234" s="1" t="s">
+      <c r="AB234" s="2"/>
+      <c r="AC234" s="2"/>
+      <c r="AD234" s="2"/>
+      <c r="AE234" s="2"/>
+      <c r="AF234" s="2"/>
+      <c r="AG234" s="2"/>
+      <c r="AH234" s="2"/>
+      <c r="AI234" s="2"/>
+      <c r="AJ234" s="2"/>
+      <c r="AK234" s="2"/>
+      <c r="AL234" s="2"/>
+      <c r="AM234" s="2"/>
+      <c r="AN234" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="AO234" s="2"/>
+      <c r="AP234" s="2"/>
+      <c r="AQ234" s="2"/>
+      <c r="AR234" s="2"/>
+      <c r="AS234" s="2"/>
+      <c r="AT234" s="2"/>
+      <c r="AU234" s="2"/>
       <c r="AX234" s="1" t="s">
         <v>33</v>
       </c>
@@ -8319,12 +8620,31 @@
       <c r="Y235" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AA235" s="1" t="s">
+      <c r="AA235" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AO235" s="1" t="s">
+      <c r="AB235" s="2"/>
+      <c r="AC235" s="2"/>
+      <c r="AD235" s="2"/>
+      <c r="AE235" s="2"/>
+      <c r="AF235" s="2"/>
+      <c r="AG235" s="2"/>
+      <c r="AH235" s="2"/>
+      <c r="AI235" s="2"/>
+      <c r="AJ235" s="2"/>
+      <c r="AK235" s="2"/>
+      <c r="AL235" s="2"/>
+      <c r="AM235" s="2"/>
+      <c r="AN235" s="2"/>
+      <c r="AO235" s="2" t="s">
         <v>46</v>
       </c>
+      <c r="AP235" s="2"/>
+      <c r="AQ235" s="2"/>
+      <c r="AR235" s="2"/>
+      <c r="AS235" s="2"/>
+      <c r="AT235" s="2"/>
+      <c r="AU235" s="2"/>
       <c r="AX235" s="1" t="s">
         <v>48</v>
       </c>
@@ -8372,12 +8692,31 @@
       <c r="Y236" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AA236" s="1" t="s">
+      <c r="AA236" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AP236" s="1" t="s">
+      <c r="AB236" s="2"/>
+      <c r="AC236" s="2"/>
+      <c r="AD236" s="2"/>
+      <c r="AE236" s="2"/>
+      <c r="AF236" s="2"/>
+      <c r="AG236" s="2"/>
+      <c r="AH236" s="2"/>
+      <c r="AI236" s="2"/>
+      <c r="AJ236" s="2"/>
+      <c r="AK236" s="2"/>
+      <c r="AL236" s="2"/>
+      <c r="AM236" s="2"/>
+      <c r="AN236" s="2"/>
+      <c r="AO236" s="2"/>
+      <c r="AP236" s="2" t="s">
         <v>104</v>
       </c>
+      <c r="AQ236" s="2"/>
+      <c r="AR236" s="2"/>
+      <c r="AS236" s="2"/>
+      <c r="AT236" s="2"/>
+      <c r="AU236" s="2"/>
       <c r="AX236" s="1" t="s">
         <v>48</v>
       </c>
@@ -8420,6 +8759,9 @@
       <c r="BW236" s="3"/>
     </row>
     <row r="237" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="D237" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
       <c r="X237" s="1" t="s">
@@ -8428,12 +8770,31 @@
       <c r="Y237" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AA237" s="1" t="s">
+      <c r="AA237" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="AQ237" s="1" t="s">
+      <c r="AB237" s="2"/>
+      <c r="AC237" s="2"/>
+      <c r="AD237" s="2"/>
+      <c r="AE237" s="2"/>
+      <c r="AF237" s="2"/>
+      <c r="AG237" s="2"/>
+      <c r="AH237" s="2"/>
+      <c r="AI237" s="2"/>
+      <c r="AJ237" s="2"/>
+      <c r="AK237" s="2"/>
+      <c r="AL237" s="2"/>
+      <c r="AM237" s="2"/>
+      <c r="AN237" s="2"/>
+      <c r="AO237" s="2"/>
+      <c r="AP237" s="2"/>
+      <c r="AQ237" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="AR237" s="2"/>
+      <c r="AS237" s="2"/>
+      <c r="AT237" s="2"/>
+      <c r="AU237" s="2"/>
       <c r="AX237" s="1" t="s">
         <v>48</v>
       </c>
@@ -8484,12 +8845,31 @@
       <c r="Y238" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AA238" s="1" t="s">
+      <c r="AA238" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="AR238" s="1" t="s">
+      <c r="AB238" s="2"/>
+      <c r="AC238" s="2"/>
+      <c r="AD238" s="2"/>
+      <c r="AE238" s="2"/>
+      <c r="AF238" s="2"/>
+      <c r="AG238" s="2"/>
+      <c r="AH238" s="2"/>
+      <c r="AI238" s="2"/>
+      <c r="AJ238" s="2"/>
+      <c r="AK238" s="2"/>
+      <c r="AL238" s="2"/>
+      <c r="AM238" s="2"/>
+      <c r="AN238" s="2"/>
+      <c r="AO238" s="2"/>
+      <c r="AP238" s="2"/>
+      <c r="AQ238" s="2"/>
+      <c r="AR238" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="AS238" s="2"/>
+      <c r="AT238" s="2"/>
+      <c r="AU238" s="2"/>
       <c r="AX238" s="1" t="s">
         <v>33</v>
       </c>
@@ -8518,43 +8898,43 @@
       <c r="BW238" s="3"/>
     </row>
     <row r="239" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="J239" s="1" t="s">
+      <c r="J239" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K239" s="1" t="s">
+      <c r="K239" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="L239" s="1" t="s">
+      <c r="L239" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M239" s="1" t="s">
+      <c r="M239" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N239" s="1" t="s">
+      <c r="N239" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O239" s="1" t="s">
+      <c r="O239" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="P239" s="1" t="s">
+      <c r="P239" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q239" s="1" t="s">
+      <c r="Q239" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="R239" s="1" t="s">
+      <c r="R239" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="S239" s="1" t="s">
+      <c r="S239" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="T239" s="1" t="s">
+      <c r="T239" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="U239" s="1" t="s">
+      <c r="U239" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V239" s="1" t="s">
+      <c r="V239" s="2" t="s">
         <v>117</v>
       </c>
       <c r="X239" s="1" t="s">
@@ -8563,12 +8943,31 @@
       <c r="Y239" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AA239" s="1" t="s">
+      <c r="AA239" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AS239" s="1" t="s">
+      <c r="AB239" s="2"/>
+      <c r="AC239" s="2"/>
+      <c r="AD239" s="2"/>
+      <c r="AE239" s="2"/>
+      <c r="AF239" s="2"/>
+      <c r="AG239" s="2"/>
+      <c r="AH239" s="2"/>
+      <c r="AI239" s="2"/>
+      <c r="AJ239" s="2"/>
+      <c r="AK239" s="2"/>
+      <c r="AL239" s="2"/>
+      <c r="AM239" s="2"/>
+      <c r="AN239" s="2"/>
+      <c r="AO239" s="2"/>
+      <c r="AP239" s="2"/>
+      <c r="AQ239" s="2"/>
+      <c r="AR239" s="2"/>
+      <c r="AS239" s="2" t="s">
         <v>111</v>
       </c>
+      <c r="AT239" s="2"/>
+      <c r="AU239" s="2"/>
       <c r="AX239" s="1" t="s">
         <v>48</v>
       </c>
@@ -8600,43 +8999,43 @@
       <c r="BW239" s="3"/>
     </row>
     <row r="240" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="J240" s="1" t="s">
+      <c r="J240" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K240" s="1" t="s">
+      <c r="K240" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L240" s="1" t="s">
+      <c r="L240" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="M240" s="1" t="s">
+      <c r="M240" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="N240" s="1" t="s">
+      <c r="N240" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="O240" s="1" t="s">
+      <c r="O240" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="P240" s="1" t="s">
+      <c r="P240" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="Q240" s="1" t="s">
+      <c r="Q240" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="R240" s="1" t="s">
+      <c r="R240" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="S240" s="1" t="s">
+      <c r="S240" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="T240" s="1" t="s">
+      <c r="T240" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="U240" s="1" t="s">
+      <c r="U240" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="V240" s="1" t="s">
+      <c r="V240" s="2" t="s">
         <v>119</v>
       </c>
       <c r="X240" s="1" t="s">
@@ -8645,12 +9044,31 @@
       <c r="Y240" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA240" s="1" t="s">
+      <c r="AA240" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="AT240" s="1" t="s">
+      <c r="AB240" s="2"/>
+      <c r="AC240" s="2"/>
+      <c r="AD240" s="2"/>
+      <c r="AE240" s="2"/>
+      <c r="AF240" s="2"/>
+      <c r="AG240" s="2"/>
+      <c r="AH240" s="2"/>
+      <c r="AI240" s="2"/>
+      <c r="AJ240" s="2"/>
+      <c r="AK240" s="2"/>
+      <c r="AL240" s="2"/>
+      <c r="AM240" s="2"/>
+      <c r="AN240" s="2"/>
+      <c r="AO240" s="2"/>
+      <c r="AP240" s="2"/>
+      <c r="AQ240" s="2"/>
+      <c r="AR240" s="2"/>
+      <c r="AS240" s="2"/>
+      <c r="AT240" s="2" t="s">
         <v>120</v>
       </c>
+      <c r="AU240" s="2"/>
       <c r="AX240" s="1" t="s">
         <v>48</v>
       </c>
@@ -8682,43 +9100,43 @@
       <c r="BW240" s="3"/>
     </row>
     <row r="241" spans="2:75" x14ac:dyDescent="0.25">
-      <c r="J241" s="1" t="s">
+      <c r="J241" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K241" s="1" t="s">
+      <c r="K241" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L241" s="1" t="s">
+      <c r="L241" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="M241" s="1" t="s">
+      <c r="M241" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="N241" s="1" t="s">
+      <c r="N241" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="O241" s="1" t="s">
+      <c r="O241" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="P241" s="1" t="s">
+      <c r="P241" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="Q241" s="1" t="s">
+      <c r="Q241" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="R241" s="1" t="s">
+      <c r="R241" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="S241" s="1" t="s">
+      <c r="S241" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="T241" s="1" t="s">
+      <c r="T241" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="U241" s="1" t="s">
+      <c r="U241" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="V241" s="1" t="s">
+      <c r="V241" s="2" t="s">
         <v>122</v>
       </c>
       <c r="X241" s="1" t="s">
@@ -8727,10 +9145,29 @@
       <c r="Y241" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AA241" s="1" t="s">
+      <c r="AA241" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="AU241" s="1" t="s">
+      <c r="AB241" s="2"/>
+      <c r="AC241" s="2"/>
+      <c r="AD241" s="2"/>
+      <c r="AE241" s="2"/>
+      <c r="AF241" s="2"/>
+      <c r="AG241" s="2"/>
+      <c r="AH241" s="2"/>
+      <c r="AI241" s="2"/>
+      <c r="AJ241" s="2"/>
+      <c r="AK241" s="2"/>
+      <c r="AL241" s="2"/>
+      <c r="AM241" s="2"/>
+      <c r="AN241" s="2"/>
+      <c r="AO241" s="2"/>
+      <c r="AP241" s="2"/>
+      <c r="AQ241" s="2"/>
+      <c r="AR241" s="2"/>
+      <c r="AS241" s="2"/>
+      <c r="AT241" s="2"/>
+      <c r="AU241" s="2" t="s">
         <v>102</v>
       </c>
       <c r="AX241" s="1" t="s">
@@ -8986,6 +9423,9 @@
       <c r="BS247" s="2"/>
     </row>
     <row r="248" spans="2:75" x14ac:dyDescent="0.25">
+      <c r="E248" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="AW248" s="2"/>
       <c r="AX248" s="2"/>
       <c r="AY248" s="2"/>
